--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-09T00:27:26+00:00</t>
+          <t>2026-05-10T00:26:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-10T00:26:56+00:00</t>
+          <t>2026-05-11T00:27:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T00:27:19+00:00</t>
+          <t>2026-05-12T00:27:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-12T00:27:34+00:00</t>
+          <t>2026-05-13T00:29:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13T00:29:54+00:00</t>
+          <t>2026-05-14T00:30:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-14T00:30:53+00:00</t>
+          <t>2026-05-15T00:28:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-15T00:28:40+00:00</t>
+          <t>2026-05-16T00:27:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-16T00:27:11+00:00</t>
+          <t>2026-05-17T00:28:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-17T00:28:31+00:00</t>
+          <t>2026-05-18T00:29:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T00:29:05+00:00</t>
+          <t>2026-05-19T00:32:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19T00:32:11+00:00</t>
+          <t>2026-05-20T00:33:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:33:47+00:00</t>
+          <t>2026-05-21T00:34:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22T00:31:46+00:00</t>
+          <t>2026-05-23T00:32:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23T00:32:34+00:00</t>
+          <t>2026-05-24T00:30:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T00:30:12+00:00</t>
+          <t>2026-05-25T00:33:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25T00:33:33+00:00</t>
+          <t>2026-05-26T00:30:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:30:25+00:00</t>
+          <t>2026-05-27T00:33:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27T00:33:10+00:00</t>
+          <t>2026-05-28T00:29:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28T00:29:42+00:00</t>
+          <t>2026-05-29T00:35:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29T00:35:47+00:00</t>
+          <t>2026-05-30T00:32:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30T00:32:18+00:00</t>
+          <t>2026-05-31T00:33:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-31T00:33:30+00:00</t>
+          <t>2026-06-01T00:34:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01T00:34:35+00:00</t>
+          <t>2026-06-02T00:39:57+00:00</t>
         </is>
       </c>
     </row>
@@ -39269,7 +39269,7 @@
       </c>
       <c r="E965" s="5" t="inlineStr">
         <is>
-          <t>Jama'atu Ahlus-Sunnah Lidda'Awati Wal Jihad ; Jama'atu Ahlus-Sunna Lidda'Awati Wal Jihad ; جماعة أهل السنة للدعو�� والجهاد ; Boko Haram ; Western Education is a Sin</t>
+          <t>Jama'atu Ahlus-Sunnah Lidda'Awati Wal Jihad ; Jama'atu Ahlus-Sunna Lidda'Awati Wal Jihad ; جماعة أهل السنة للدعوة والجهاد ; Boko Haram ; Western Education is a Sin</t>
         </is>
       </c>
       <c r="F965" s="5" t="inlineStr"/>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02T00:39:57+00:00</t>
+          <t>2026-06-03T00:43:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03T00:43:21+00:00</t>
+          <t>2026-06-04T00:43:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04T00:43:04+00:00</t>
+          <t>2026-06-05T00:36:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05T00:36:16+00:00</t>
+          <t>2026-06-06T00:34:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06T00:34:19+00:00</t>
+          <t>2026-06-07T00:35:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07T00:35:15+00:00</t>
+          <t>2026-06-08T00:36:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08T00:36:52+00:00</t>
+          <t>2026-06-09T00:31:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09T00:31:56+00:00</t>
+          <t>2026-06-10T00:37:57+00:00</t>
         </is>
       </c>
     </row>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="G441" s="5" t="inlineStr">
         <is>
-          <t>Reportedly killed in an air strike in Syria on 25 May 2015. A veteran member of the ‘Chechen Network’ (not listed) and other terrorist groups. He was convicted of his role and membership in the ‘Chechen Network’ in France in 2006. Joined Jabhat al-Nusrah, listed as Al-Nusrah Front for the People of the Levant (QDe.137) in October 2013. Father’s name: Mohamed. Mother’s name: Saliha Boukhari. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly killed in an air strike in Syria on 25 May 2015. A veteran member of the ‘Chechen Network’ (not listed) and other terrorist groups. He was convicted of his role and membership in the ‘Chechen Network’ in France in 2006. Joined Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant in October 2013. Father’s name: Mohamed. Mother’s name: Saliha Boukhari. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H441" s="5" t="inlineStr">
@@ -18420,7 +18420,7 @@
       </c>
       <c r="G442" s="5" t="inlineStr">
         <is>
-          <t>A long time facilitator and financier for Al-Qaida (QDe.004), appointed as a regional leader of Jabhat al-Nusrah, listed as Al-Nusrah Front for the People of the Levant (QDe.137). Reportedly killed in a counterterrorism operation in Northwest Syria in October 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A long time facilitator and financier for Al-Qaida (QDe.004), appointed as a regional leader of Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant Reportedly killed in a counterterrorism operation in Northwest Syria in October 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H442" s="5" t="inlineStr">
@@ -18462,7 +18462,7 @@
       </c>
       <c r="G443" s="5" t="inlineStr">
         <is>
-          <t>Was the official spokesman of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), and emir of ISIL in Syria, closely associated with Abu Mohammed al-Jawlani (QDi.317) and Abu Bakr al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299). Reportedly killed in August 2016 in air strike near al-Bab, Syria. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Was the official spokesman of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), and emir of ISIL in Syria, closely associated with Abu Mohammed al-Jawlani (formerly listed) and Abu Bakr al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299). Reportedly killed in August 2016 in air strike near al-Bab, Syria. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H443" s="5" t="inlineStr">
@@ -18501,10 +18501,10 @@
       <c r="G444" s="5" t="inlineStr">
         <is>
           <t>A Kuwait-based financier, recruiter and facilitator for Islamic State in Iraq
-                and the Levant, listed as Al-Qaida in Iraq (QDe.115), and Jabhat al-Nusrah, listed
-                as Al-Nusrah Front for the People of the Levant (QDe.137). Associated with Ibrahim
+                and the Levant, listed as Al-Qaida in Iraq (QDe.115), and Jabhat al-Nusrah, formerly listed
+                as Al-Nusrah Front for the People of the Levant. Associated with Ibrahim
                 Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299) and Abu Mohammed al-Jawlani
-                (QDi.317). Review pursuant to Security Council resolution 2368 (2017) was concluded
+                (formerly listed). Review pursuant to Security Council resolution 2368 (2017) was concluded
                 on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
@@ -18547,8 +18547,8 @@
       </c>
       <c r="G445" s="5" t="inlineStr">
         <is>
-          <t>A member and regional commander of Jabhat al-Nusrah, listed as Al-Nusrah
-Front for the People of the Levant (QDe.137)and a facilitator of foreign recruits for
+          <t>A member and regional commander of Jabhat al-Nusrah, formerly listed as Al-Nusrah
+Front for the People of the Levant and a facilitator of foreign recruits for
 that group. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="G453" s="5" t="inlineStr">
         <is>
-          <t>Sharia amir of Al-Nusrah Front for the People of the Levant (QDe.137) as
+          <t>Sharia amir of Al-Nusrah Front for the People of the Levant (formerly listed) as
 of early 2014. Reportedly died in the Syrian Arab Republic on 2 April 2024, Mother’s name: Subhah Muhammad Sayf. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019 Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="G454" s="5" t="inlineStr">
         <is>
-          <t>Fundraiser for Al-Nusrah Front for the People of the Levant (QDe.137). In November 2023, he was released from prison in Kuwait as part of the Special Amiri Decree Pardon No. 225/2023. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.
+          <t>Fundraiser for Al-Nusrah Front for the People of the Levant (formerly listed). In November 2023, he was released from prison in Kuwait as part of the Special Amiri Decree Pardon No. 225/2023. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.
  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>French terrorist fighter associated with Al-Nusrah Front for the People of the Levant (QDe.137) and the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Facilitated foreign terrorist fighters travel from France to Syria. Activist in violent propaganda through the Internet. A warrant for his arrest was issued in 2014 by French authorities and executed in Jan. 2017 upon his expulsion from Turkey where he was arrested in Jun. 2016. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>French terrorist fighter associated with Al-Nusrah Front for the People of the Levant (formerly listed) and the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Facilitated foreign terrorist fighters travel from France to Syria. Activist in violent propaganda through the Internet. A warrant for his arrest was issued in 2014 by French authorities and executed in Jan. 2017 upon his expulsion from Turkey where he was arrested in Jun. 2016. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
@@ -19111,7 +19111,7 @@
       <c r="G458" s="5" t="inlineStr">
         <is>
           <t>A leader of an armed group linked to Al-Nusrah Front for the People of
-the Levant (QDe.137) and a key facilitator for a Syrian foreign terrorist fighter
+the Levant (formerly listed) and a key facilitator for a Syrian foreign terrorist fighter
 network. Active in terrorist propaganda through the Internet. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
@@ -19156,7 +19156,7 @@
         <is>
           <t>A member of Al-Qaida (QDe.004) as of 2012 and a fighter in the Syrian Arab
                 Republic since early 2014. Provided financial, material, and technological support
-                for Al-Qaida, Al-Nusrah Front for the People of the Levant (QDe.137) and Al-Qaida in
+                for Al-Qaida, Al-Nusrah Front for the People of the Levant (formerly listed) and Al-Qaida in
                 Iraq (AQI) (QDe.115).Review pursuant to Security Council resolution 2368 (2017) was
                 concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="G479" s="5" t="inlineStr">
         <is>
-          <t>As at Aug. 2015, leader of Jamaat Abu Hanifa, a terrorist group that is part of the Al-Nusrah Front for the People of the Levant (QDe.137). Physical description: eye colour: brown, hair colour: black, build: slim, height 175-180 cm. Distinguishing marks: long face, speech defect. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
+          <t>As at Aug. 2015, leader of Jamaat Abu Hanifa, a terrorist group that was part of the Al-Nusrah Front for the People of the Levant (formerly listed). Physical description: eye colour: brown, hair colour: black, build: slim, height 175-180 cm. Distinguishing marks: long face, speech defect. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
 Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
@@ -20228,7 +20228,7 @@
       </c>
       <c r="G484" s="5" t="inlineStr">
         <is>
-          <t>Believed to be fighting with Al-Nusrah Front for the People of the Levant (QDe.137) in Syrian Arab Republic and reported to be a leader in the group as of Apr. 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 February 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be fighting with Al-Nusrah Front for the People of the Levant (formerly listed) in Syrian Arab Republic and reported to be a leader in the group as of Apr. 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 February 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H484" s="5" t="inlineStr">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="G490" s="5" t="inlineStr">
         <is>
-          <t>Qatar-based facilitator who provides financial services to, or in support of, Al-Nusrah Front for the People of the Levant (QDe.137). Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Qatar-based facilitator who provides financial services to, or in support of, Al-Nusrah Front for the People of the Levant (formerly listed). Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H490" s="5" t="inlineStr">
@@ -20989,7 +20989,7 @@
       <c r="G502" s="5" t="inlineStr">
         <is>
           <t>May use a fake passport of a Syrian or Iraqi citizen. Member of the Al-Nusrah
-                Front for the People of the Levant (ANF) (QDe.137), “Bulgar Group”, leads a group of
+                Front for the People of the Levant (ANF) (formerly listed), “Bulgar Group”, leads a group of
                 100 fighters. Photo available for inclusion in the INTERPOL-UN Security Council
                 Special Notice. Review pursuant to Security Council resolution 2368 (2017) was
                 concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="G504" s="5" t="inlineStr">
         <is>
-          <t>Leader of Al-Nusrah Front for the People of the Levant (QDe.137) for southern Syrian Arab Republic since July 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) for southern Syrian Arab Republic since July 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H504" s="5" t="inlineStr">
@@ -21118,7 +21118,7 @@
       </c>
       <c r="G505" s="5" t="inlineStr">
         <is>
-          <t>Leader of Al-Nusrah Front for the People of the Levant (QDe.137) for coastal area of Syrian Arab Republic since March 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) for coastal area of Syrian Arab Republic since March 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H505" s="5" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="G510" s="5" t="inlineStr">
         <is>
-          <t>Associated with Jabhat al-Nusrah, listed as Al-Nusrah Front for the People of the Levant (QDe.137).Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H510" s="5" t="inlineStr">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G532" s="5" t="inlineStr">
         <is>
-          <t>Leader of AL-NUSRAH FRONT FOR THE PEOPLE OF THE LEVANT (QDe.137) in West Kalamoun, Syrian Arab Republic. Mother’s name is Amina Tohmeh.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) in West Kalamoun, Syrian Arab Republic. Mother’s name is Amina Tohmeh.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H532" s="5" t="inlineStr">
@@ -39518,7 +39518,7 @@
       <c r="G971" s="5" t="inlineStr">
         <is>
           <t>An armed group that has carried out joint attacks with Al-Nusrah Front
-for the People of the Levant (QDe.137).  Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+for the People of the Levant (formerly listed).  Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H971" s="5" t="inlineStr">
@@ -39686,7 +39686,7 @@
           <t>Established by foreign terrorist fighters in 2013. Location: Syrian Arab
                 Republic. Affiliated with Islamic State in Iraq and the Levant, listed as Al-Qaida
                 in Iraq (QDe.115) and AI-Nusrah Front for the People of the Levant
-                (QDe.137). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+                (formerly listed). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H975" s="5" t="inlineStr">
@@ -39724,7 +39724,7 @@
       <c r="F976" s="5" t="inlineStr"/>
       <c r="G976" s="5" t="inlineStr">
         <is>
-          <t>Moroccan-led terrorist organization formed in Aug. 2013 and operating in Syrian Arab Republic. Principally composed of foreign terrorist fighters and associated with AI-Nusrah Front for the People of the Levant (QDe.137).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Moroccan-led terrorist organization formed in Aug. 2013 and operating in Syrian Arab Republic. Principally composed of foreign terrorist fighters and associated with AI-Nusrah Front for the People of the Levant (formerly listed).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H976" s="5" t="inlineStr">
@@ -39993,7 +39993,7 @@
       <c r="F983" s="5" t="inlineStr"/>
       <c r="G983" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Al Nusrah Front for the People of the Levant (QDe.137). Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Al Nusrah Front for the People of the Levant (formerly listed). Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H983" s="5" t="inlineStr">
@@ -40071,7 +40071,7 @@
       <c r="F985" s="5" t="inlineStr"/>
       <c r="G985" s="5" t="inlineStr">
         <is>
-          <t>Associated with Al-Nusrah Front for the People of the Levant (QDe.137). Committed terrorist attacks in the Syrian Arab Republic. Since 2016 redeployed to Northern Afghanistan to project attacks against Central Asia countries. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with Al-Nusrah Front for the People of the Levant (formerly listed). Committed terrorist attacks in the Syrian Arab Republic. Since 2016 redeployed to Northern Afghanistan to project attacks against Central Asia countries. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H985" s="5" t="inlineStr">
@@ -40455,7 +40455,7 @@
       <c r="F995" s="5" t="inlineStr"/>
       <c r="G995" s="5" t="inlineStr">
         <is>
-          <t>Khatiba al-Tawhid wal-Jihad (formerly known as Jannat Oshiklari) is a terrorist organization operating under the umbrella of the international terrorist organization Al-Nusrah Front for the People of the Levant (QDe.137). The group mainly operates in the provinces of Hama, Idlib and Ladhiqiyah, in the Syrian Arab Republic, and also conduct operations in Turkey, Kyrgyzstan, Uzbekistan, Russian Federation, Tajikistan, Kazakhstan, Egypt, Afghanistan, Ukraine.  The number of fighters of KTJ is about 500. KTJ also cooperates with such terrorist organizations as Khatiba Imam al-Bukhari (QDe.158) and the Islamic Jihad Group (QDe.119).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Khatiba al-Tawhid wal-Jihad (formerly known as Jannat Oshiklari) is a terrorist organization operating under the umbrella of the international terrorist organization Al-Nusrah Front for the People of the Levant (formerly listed). The group mainly operates in the provinces of Hama, Idlib and Ladhiqiyah, in the Syrian Arab Republic, and also conduct operations in Turkey, Kyrgyzstan, Uzbekistan, Russian Federation, Tajikistan, Kazakhstan, Egypt, Afghanistan, Ukraine.  The number of fighters of KTJ is about 500. KTJ also cooperates with such terrorist organizations as Khatiba Imam al-Bukhari (QDe.158) and the Islamic Jihad Group (QDe.119).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H995" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10T00:37:57+00:00</t>
+          <t>2026-06-11T00:38:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11T00:38:25+00:00</t>
+          <t>2026-06-12T00:39:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12T00:39:38+00:00</t>
+          <t>2026-06-13T00:38:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13T00:38:58+00:00</t>
+          <t>2026-06-14T00:37:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T00:37:36+00:00</t>
+          <t>2026-06-15T00:38:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15T00:38:44+00:00</t>
+          <t>2026-06-16T00:44:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16T00:44:04+00:00</t>
+          <t>2026-06-17T00:39:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17T00:39:22+00:00</t>
+          <t>2026-06-18T00:43:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18T00:43:37+00:00</t>
+          <t>2026-06-19T00:43:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19T00:43:22+00:00</t>
+          <t>2026-06-20T00:34:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20T00:34:18+00:00</t>
+          <t>2026-06-21T00:38:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-21T00:38:47+00:00</t>
+          <t>2026-06-22T00:37:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22T00:37:48+00:00</t>
+          <t>2026-06-23T00:35:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23T00:35:33+00:00</t>
+          <t>2026-06-24T00:29:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24T00:29:51+00:00</t>
+          <t>2026-06-25T00:34:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25T00:34:53+00:00</t>
+          <t>2026-06-26T00:41:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26T00:41:25+00:00</t>
+          <t>2026-06-27T00:32:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27T00:32:46+00:00</t>
+          <t>2026-06-28T00:32:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28T00:32:34+00:00</t>
+          <t>2026-06-29T00:34:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29T00:34:54+00:00</t>
+          <t>2026-06-30T00:33:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30T00:33:10+00:00</t>
+          <t>2026-07-01T00:38:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01T00:38:10+00:00</t>
+          <t>2026-07-02T00:33:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02T00:33:15+00:00</t>
+          <t>2026-07-03T02:05:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03T02:05:10+00:00</t>
+          <t>2026-07-04T02:02:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04T02:02:48+00:00</t>
+          <t>2026-07-05T02:10:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05T02:10:50+00:00</t>
+          <t>2026-07-06T02:15:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06T02:15:36+00:00</t>
+          <t>2026-07-07T02:11:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07T02:11:07+00:00</t>
+          <t>2026-07-08T01:52:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08T01:52:30+00:00</t>
+          <t>2026-07-09T02:05:32+00:00</t>
         </is>
       </c>
     </row>
@@ -22641,7 +22641,7 @@
       </c>
       <c r="B542" s="5" t="inlineStr">
         <is>
-          <t>6909556</t>
+          <t>6909621</t>
         </is>
       </c>
       <c r="C542" s="5" t="inlineStr">
@@ -22651,7 +22651,7 @@
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>HAMIDAH NABAGALA</t>
+          <t>HAMIDA NABAGGALA</t>
         </is>
       </c>
       <c r="E542" s="5" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="G542" s="5" t="inlineStr">
         <is>
-          <t>Works as a mediator in financing channels for ISIL in Central Africa, has been charged with financing a bombing that occurred in the Ugandan capital, Kampala, in 2021, attempted to coerce her three children in Uganda to send them to ISIL camps in the Democratic Republic of the Congo. Gender: Female.  INTERPOL-UN Security Council Special Notice web link:</t>
+          <t>Works as a mediator in financing channels for ISIL in Central Africa, has been charged with financing a bombing that occurred in the Ugandan capital, Kampala, in 2021, attempted to coerce her three children in Uganda to send them to ISIL camps in the Democratic Republic of the Congo. Gender: Female.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2026-23487</t>
         </is>
       </c>
       <c r="H542" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09T02:05:32+00:00</t>
+          <t>2026-07-10T02:04:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10T02:04:03+00:00</t>
+          <t>2026-07-11T01:50:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11T01:50:53+00:00</t>
+          <t>2026-07-12T01:53:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:53:26+00:00</t>
+          <t>2026-07-13T01:56:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13T01:56:05+00:00</t>
+          <t>2026-07-14T01:43:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14T01:43:10+00:00</t>
+          <t>2026-07-15T01:29:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15T01:29:00+00:00</t>
+          <t>2026-07-16T01:49:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17T01:52:52+00:00</t>
+          <t>2026-07-18T01:43:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18T01:43:36+00:00</t>
+          <t>2026-07-19T01:51:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-19T01:51:40+00:00</t>
+          <t>2026-07-20T03:25:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20T03:25:18+00:00</t>
+          <t>2026-07-21T01:55:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21T01:55:01+00:00</t>
+          <t>2026-07-22T01:50:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22T01:50:18+00:00</t>
+          <t>2026-07-23T01:59:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$H$1011</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$H$1012</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23T01:59:01+00:00</t>
+          <t>2026-07-24T01:54:28+00:00</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1011"/>
+  <dimension ref="A1:H1012"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37392,62 +37392,97 @@
       </c>
       <c r="B917" s="5" t="inlineStr">
         <is>
-          <t>113445</t>
+          <t>6909568</t>
         </is>
       </c>
       <c r="C917" s="5" t="inlineStr">
         <is>
-          <t>2001-10-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D917" s="5" t="inlineStr">
         <is>
-          <t>ABU SAYYAF GROUP</t>
-        </is>
-      </c>
-      <c r="E917" s="5" t="inlineStr">
-        <is>
-          <t>Al Harakat Al Islamiyya</t>
-        </is>
-      </c>
+          <t>AVAX</t>
+        </is>
+      </c>
+      <c r="E917" s="5" t="inlineStr"/>
       <c r="F917" s="5" t="inlineStr"/>
       <c r="G917" s="5" t="inlineStr">
+        <is>
+          <t>IMO: 9058713 
+Listed pursuant to paragraphs 10(a), 10 (b), 10(c) and 10(d) of resolution 2146 (2014), as amended by paragraph 2 of resolutions 2441 (2018) and 2509 (2020) and extended in resolution 2819 (2026) (prohibition to load, transport or discharge; prohibition to enter ports; prohibition to provide bunkering and vessel services; prohibition to engage in financial transactions with regard to petroleum). Pursuant to paragraph 11 of resolution 2146, as modified by paragraph 2 of resolution 2509 (2020), this designation is valid from 22 July 2026 to 22 July 2027, unless terminated earlier by the Committee pursuant to paragraph 12 of resolution 2146 (2014). Flag State: Cameroon. As of 4 April 2026, the vessel was located near the anchorage area of the Benghazi Old Harbour, Libya.</t>
+        </is>
+      </c>
+      <c r="H917" s="5" t="inlineStr">
+        <is>
+          <t>LYe.006</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B918" s="5" t="inlineStr">
+        <is>
+          <t>113445</t>
+        </is>
+      </c>
+      <c r="C918" s="5" t="inlineStr">
+        <is>
+          <t>2001-10-06</t>
+        </is>
+      </c>
+      <c r="D918" s="5" t="inlineStr">
+        <is>
+          <t>ABU SAYYAF GROUP</t>
+        </is>
+      </c>
+      <c r="E918" s="5" t="inlineStr">
+        <is>
+          <t>Al Harakat Al Islamiyya</t>
+        </is>
+      </c>
+      <c r="F918" s="5" t="inlineStr"/>
+      <c r="G918" s="5" t="inlineStr">
         <is>
           <t>Associated with Jemaah Islamiyah (JI) (QDe.092). Current leader is
 Radulan Sahiron (QDi.208). Review pursuant to Security Council resolution 1822 (2008)
 was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H917" s="5" t="inlineStr">
+      <c r="H918" s="5" t="inlineStr">
         <is>
           <t>QDe.001</t>
         </is>
       </c>
     </row>
-    <row r="918">
-      <c r="A918" s="5" t="inlineStr">
+    <row r="919">
+      <c r="A919" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B918" s="5" t="inlineStr">
+      <c r="B919" s="5" t="inlineStr">
         <is>
           <t>113457</t>
         </is>
       </c>
-      <c r="C918" s="5" t="inlineStr">
+      <c r="C919" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D918" s="5" t="inlineStr">
+      <c r="D919" s="5" t="inlineStr">
         <is>
           <t>AL-ITIHAAD AL-ISLAMIYA / AIAI</t>
         </is>
       </c>
-      <c r="E918" s="5" t="inlineStr"/>
-      <c r="F918" s="5" t="inlineStr"/>
-      <c r="G918" s="5" t="inlineStr">
+      <c r="E919" s="5" t="inlineStr"/>
+      <c r="F919" s="5" t="inlineStr"/>
+      <c r="G919" s="5" t="inlineStr">
         <is>
           <t>Reported to have operated in Somalia and Ethiopia and to have merged with
 Harakat Al-Shabaab Al-Mujaahidiin (Al-Shabaab), which was accepted as an affiliate of
@@ -37460,126 +37495,88 @@
 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H918" s="5" t="inlineStr">
+      <c r="H919" s="5" t="inlineStr">
         <is>
           <t>QDe.002</t>
         </is>
       </c>
     </row>
-    <row r="919">
-      <c r="A919" s="5" t="inlineStr">
+    <row r="920">
+      <c r="A920" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B919" s="5" t="inlineStr">
+      <c r="B920" s="5" t="inlineStr">
         <is>
           <t>113236</t>
         </is>
       </c>
-      <c r="C919" s="5" t="inlineStr">
+      <c r="C920" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D919" s="5" t="inlineStr">
+      <c r="D920" s="5" t="inlineStr">
         <is>
           <t>EGYPTIAN ISLAMIC JIHAD</t>
         </is>
       </c>
-      <c r="E919" s="5" t="inlineStr">
+      <c r="E920" s="5" t="inlineStr">
         <is>
           <t>Egyptian Al-Jihad ; Jihad Group ; New Jihad ; Al-Jihad ; Egyptian Islamic Movement</t>
         </is>
       </c>
-      <c r="F919" s="5" t="inlineStr"/>
-      <c r="G919" s="5" t="inlineStr">
+      <c r="F920" s="5" t="inlineStr"/>
+      <c r="G920" s="5" t="inlineStr">
         <is>
           <t>Co-founded by Aiman Muhammed Rabi al-Zawahiri (QDi.006), who was also its
 military leader. Review pursuant to Security Council resolution 1822 (2008) was
 concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H919" s="5" t="inlineStr">
+      <c r="H920" s="5" t="inlineStr">
         <is>
           <t>QDe.003</t>
         </is>
       </c>
     </row>
-    <row r="920">
-      <c r="A920" s="5" t="inlineStr">
+    <row r="921">
+      <c r="A921" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B920" s="5" t="inlineStr">
+      <c r="B921" s="5" t="inlineStr">
         <is>
           <t>113458</t>
         </is>
       </c>
-      <c r="C920" s="5" t="inlineStr">
+      <c r="C921" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D920" s="5" t="inlineStr">
+      <c r="D921" s="5" t="inlineStr">
         <is>
           <t>AL-QAIDA</t>
         </is>
       </c>
-      <c r="E920" s="5" t="inlineStr">
+      <c r="E921" s="5" t="inlineStr">
         <is>
           <t>"The Base" ; Al Qaeda ; Islamic Salvation Foundation ; The Group for the Preservation of the Holy Sites ; The Islamic Army for the Liberation of Holy Places ; The World Islamic Front for Jihad Against Jews and Crusaders ; Usama Bin Laden Network ; Usama Bin Laden Organization ; Al Qa'ida ; Al Qa’ida/Islamic Army</t>
         </is>
       </c>
-      <c r="F920" s="5" t="inlineStr"/>
-      <c r="G920" s="5" t="inlineStr">
+      <c r="F921" s="5" t="inlineStr"/>
+      <c r="G921" s="5" t="inlineStr">
         <is>
           <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
 on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H920" s="5" t="inlineStr">
+      <c r="H921" s="5" t="inlineStr">
         <is>
           <t>QDe.004</t>
-        </is>
-      </c>
-    </row>
-    <row r="921">
-      <c r="A921" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B921" s="5" t="inlineStr">
-        <is>
-          <t>113459</t>
-        </is>
-      </c>
-      <c r="C921" s="5" t="inlineStr">
-        <is>
-          <t>2001-10-06</t>
-        </is>
-      </c>
-      <c r="D921" s="5" t="inlineStr">
-        <is>
-          <t>AL RASHID TRUST</t>
-        </is>
-      </c>
-      <c r="E921" s="5" t="inlineStr">
-        <is>
-          <t>Al-Rasheed Trust ; Al Rasheed Trust ; Al-Rashid Trust ; Aid Organization of the Ulema, Pakistan ; Al Amin Welfare Trust ; Al Amin Trust ; Al Ameen Trust ; Al-Ameen Trust ; Al Madina Trust ; Al-Madina Trust</t>
-        </is>
-      </c>
-      <c r="F921" s="5" t="inlineStr"/>
-      <c r="G921" s="5" t="inlineStr">
-        <is>
-          <t>Reportedly defunct. Headquarters were in Pakistan. Operations in Afghanistan: Herat Jalalabad, Kabul, Kandahar, Mazar Sherif. Also operations in Kosovo, Chechnya. Involved in the financing of Al-Qaida and the Taliban. Until 21 Oct. 2008, this entity appeared also as "Aid Organization of the Ulema, Pakistan" (QDe.073), listed on 24 Apr. 2002 and amended on 25 Jul. 2006. The two entries Al Rashid Trust (QDe.005) and Aid Organization of the Ulema, Pakistan (QDe.073) were consolidated into this entity on 21 Oct. 2008. Founded by Mufti Rashid Ahmad Ledahyanoy (deceased). Associated with Jaish-i-Mohammed (QDe.019). Banned in Pakistan since Oct. 2001. No indication of any activity under the name of Al-Rashid Trust has emerged as of November 2023. Review pursuant to Security Council resolution 1822 (2008) was concluded on 6 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H921" s="5" t="inlineStr">
-        <is>
-          <t>QDe.005</t>
         </is>
       </c>
     </row>
@@ -37591,7 +37588,7 @@
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>113237</t>
+          <t>113459</t>
         </is>
       </c>
       <c r="C922" s="5" t="inlineStr">
@@ -37601,91 +37598,129 @@
       </c>
       <c r="D922" s="5" t="inlineStr">
         <is>
-          <t>ARMED ISLAMIC GROUP</t>
+          <t>AL RASHID TRUST</t>
         </is>
       </c>
       <c r="E922" s="5" t="inlineStr">
         <is>
-          <t>Al Jamm’ah Al-Islamiah Al- Musallah ; GIA ; Groupe Islamique Armé</t>
+          <t>Al-Rasheed Trust ; Al Rasheed Trust ; Al-Rashid Trust ; Aid Organization of the Ulema, Pakistan ; Al Amin Welfare Trust ; Al Amin Trust ; Al Ameen Trust ; Al-Ameen Trust ; Al Madina Trust ; Al-Madina Trust</t>
         </is>
       </c>
       <c r="F922" s="5" t="inlineStr"/>
       <c r="G922" s="5" t="inlineStr">
         <is>
+          <t>Reportedly defunct. Headquarters were in Pakistan. Operations in Afghanistan: Herat Jalalabad, Kabul, Kandahar, Mazar Sherif. Also operations in Kosovo, Chechnya. Involved in the financing of Al-Qaida and the Taliban. Until 21 Oct. 2008, this entity appeared also as "Aid Organization of the Ulema, Pakistan" (QDe.073), listed on 24 Apr. 2002 and amended on 25 Jul. 2006. The two entries Al Rashid Trust (QDe.005) and Aid Organization of the Ulema, Pakistan (QDe.073) were consolidated into this entity on 21 Oct. 2008. Founded by Mufti Rashid Ahmad Ledahyanoy (deceased). Associated with Jaish-i-Mohammed (QDe.019). Banned in Pakistan since Oct. 2001. No indication of any activity under the name of Al-Rashid Trust has emerged as of November 2023. Review pursuant to Security Council resolution 1822 (2008) was concluded on 6 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H922" s="5" t="inlineStr">
+        <is>
+          <t>QDe.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B923" s="5" t="inlineStr">
+        <is>
+          <t>113237</t>
+        </is>
+      </c>
+      <c r="C923" s="5" t="inlineStr">
+        <is>
+          <t>2001-10-06</t>
+        </is>
+      </c>
+      <c r="D923" s="5" t="inlineStr">
+        <is>
+          <t>ARMED ISLAMIC GROUP</t>
+        </is>
+      </c>
+      <c r="E923" s="5" t="inlineStr">
+        <is>
+          <t>Al Jamm’ah Al-Islamiah Al- Musallah ; GIA ; Groupe Islamique Armé</t>
+        </is>
+      </c>
+      <c r="F923" s="5" t="inlineStr"/>
+      <c r="G923" s="5" t="inlineStr">
+        <is>
           <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
 on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H922" s="5" t="inlineStr">
+      <c r="H923" s="5" t="inlineStr">
         <is>
           <t>QDe.006</t>
         </is>
       </c>
     </row>
-    <row r="923">
-      <c r="A923" s="5" t="inlineStr">
+    <row r="924">
+      <c r="A924" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B923" s="5" t="inlineStr">
+      <c r="B924" s="5" t="inlineStr">
         <is>
           <t>113461</t>
         </is>
       </c>
-      <c r="C923" s="5" t="inlineStr">
+      <c r="C924" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D923" s="5" t="inlineStr">
+      <c r="D924" s="5" t="inlineStr">
         <is>
           <t>ASBAT AL-ANSAR</t>
         </is>
       </c>
-      <c r="E923" s="5" t="inlineStr"/>
-      <c r="F923" s="5" t="inlineStr"/>
-      <c r="G923" s="5" t="inlineStr">
+      <c r="E924" s="5" t="inlineStr"/>
+      <c r="F924" s="5" t="inlineStr"/>
+      <c r="G924" s="5" t="inlineStr">
         <is>
           <t>Active in northern Iraq. Associated with Al-Qaida in Iraq (QDe.115).
 Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun.
 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H923" s="5" t="inlineStr">
+      <c r="H924" s="5" t="inlineStr">
         <is>
           <t>QDe.007</t>
         </is>
       </c>
     </row>
-    <row r="924">
-      <c r="A924" s="5" t="inlineStr">
+    <row r="925">
+      <c r="A925" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B924" s="5" t="inlineStr">
+      <c r="B925" s="5" t="inlineStr">
         <is>
           <t>113263</t>
         </is>
       </c>
-      <c r="C924" s="5" t="inlineStr">
+      <c r="C925" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D924" s="5" t="inlineStr">
+      <c r="D925" s="5" t="inlineStr">
         <is>
           <t>HARAKAT UL-MUJAHIDIN / HUM</t>
         </is>
       </c>
-      <c r="E924" s="5" t="inlineStr">
+      <c r="E925" s="5" t="inlineStr">
         <is>
           <t>Al-Faran ; Al-Hadid ; Al-Hadith ; Harakat Ul-Ansar ; HUA ; Harakat Ul- Mujahideen</t>
         </is>
       </c>
-      <c r="F924" s="5" t="inlineStr"/>
-      <c r="G924" s="5" t="inlineStr">
+      <c r="F925" s="5" t="inlineStr"/>
+      <c r="G925" s="5" t="inlineStr">
         <is>
           <t>Associated with Jaish-i-Mohammed (QDe.019), Lashkar i Jhangvi (LJ)
 (QDe.096) and Lashkar-e-Tayyiba (QDe.118). Active in Pakistan and Afghanistan. Banned in
@@ -37693,75 +37728,75 @@
 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H924" s="5" t="inlineStr">
+      <c r="H925" s="5" t="inlineStr">
         <is>
           <t>QDe.008</t>
         </is>
       </c>
     </row>
-    <row r="925">
-      <c r="A925" s="5" t="inlineStr">
+    <row r="926">
+      <c r="A926" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B925" s="5" t="inlineStr">
+      <c r="B926" s="5" t="inlineStr">
         <is>
           <t>114074</t>
         </is>
       </c>
-      <c r="C925" s="5" t="inlineStr">
+      <c r="C926" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D925" s="5" t="inlineStr">
+      <c r="D926" s="5" t="inlineStr">
         <is>
           <t>ISLAMIC ARMY OF ADEN</t>
         </is>
       </c>
-      <c r="E925" s="5" t="inlineStr"/>
-      <c r="F925" s="5" t="inlineStr"/>
-      <c r="G925" s="5" t="inlineStr">
+      <c r="E926" s="5" t="inlineStr"/>
+      <c r="F926" s="5" t="inlineStr"/>
+      <c r="G926" s="5" t="inlineStr">
         <is>
           <t>Review pursuant to Security Council resolution 1822 (2008) was concluded on 9
 Jul. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H925" s="5" t="inlineStr">
+      <c r="H926" s="5" t="inlineStr">
         <is>
           <t>QDe.009</t>
         </is>
       </c>
     </row>
-    <row r="926">
-      <c r="A926" s="5" t="inlineStr">
+    <row r="927">
+      <c r="A927" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B926" s="5" t="inlineStr">
+      <c r="B927" s="5" t="inlineStr">
         <is>
           <t>113964</t>
         </is>
       </c>
-      <c r="C926" s="5" t="inlineStr">
+      <c r="C927" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D926" s="5" t="inlineStr">
+      <c r="D927" s="5" t="inlineStr">
         <is>
           <t>ISLAMIC MOVEMENT OF UZBEKISTAN</t>
         </is>
       </c>
-      <c r="E926" s="5" t="inlineStr">
+      <c r="E927" s="5" t="inlineStr">
         <is>
           <t>IMU</t>
         </is>
       </c>
-      <c r="F926" s="5" t="inlineStr"/>
-      <c r="G926" s="5" t="inlineStr">
+      <c r="F927" s="5" t="inlineStr"/>
+      <c r="G927" s="5" t="inlineStr">
         <is>
           <t>Associated with the Eastern Turkistan Islamic Movement (QDe.088), Islamic
 Jihad Group (QDe.119) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan
@@ -37769,199 +37804,199 @@
 resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H926" s="5" t="inlineStr">
+      <c r="H927" s="5" t="inlineStr">
         <is>
           <t>QDe.010</t>
         </is>
       </c>
     </row>
-    <row r="927">
-      <c r="A927" s="5" t="inlineStr">
+    <row r="928">
+      <c r="A928" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B927" s="5" t="inlineStr">
+      <c r="B928" s="5" t="inlineStr">
         <is>
           <t>114090</t>
         </is>
       </c>
-      <c r="C927" s="5" t="inlineStr">
+      <c r="C928" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D927" s="5" t="inlineStr">
+      <c r="D928" s="5" t="inlineStr">
         <is>
           <t>LIBYAN ISLAMIC FIGHTING GROUP</t>
         </is>
       </c>
-      <c r="E927" s="5" t="inlineStr">
+      <c r="E928" s="5" t="inlineStr">
         <is>
           <t>LIFG</t>
         </is>
       </c>
-      <c r="F927" s="5" t="inlineStr"/>
-      <c r="G927" s="5" t="inlineStr">
+      <c r="F928" s="5" t="inlineStr"/>
+      <c r="G928" s="5" t="inlineStr">
         <is>
           <t>Members in Afghanistan merged with Al-Qaida (QDe.004) in Nov. 2007.
 Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun.
 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H927" s="5" t="inlineStr">
+      <c r="H928" s="5" t="inlineStr">
         <is>
           <t>QDe.011</t>
         </is>
       </c>
     </row>
-    <row r="928">
-      <c r="A928" s="5" t="inlineStr">
+    <row r="929">
+      <c r="A929" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B928" s="5" t="inlineStr">
+      <c r="B929" s="5" t="inlineStr">
         <is>
           <t>113858</t>
         </is>
       </c>
-      <c r="C928" s="5" t="inlineStr">
+      <c r="C929" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D928" s="5" t="inlineStr">
+      <c r="D929" s="5" t="inlineStr">
         <is>
           <t>MAKHTAB AL-KHIDAMAT</t>
         </is>
       </c>
-      <c r="E928" s="5" t="inlineStr">
+      <c r="E929" s="5" t="inlineStr">
         <is>
           <t>MAK ; Al Kifah ; AFGHAN SERVICE BUREAU</t>
         </is>
       </c>
-      <c r="F928" s="5" t="inlineStr"/>
-      <c r="G928" s="5" t="inlineStr">
+      <c r="F929" s="5" t="inlineStr"/>
+      <c r="G929" s="5" t="inlineStr">
         <is>
           <t>Absorbed into Al-Qaida (QDe.004). Review pursuant to Security Council
 resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H928" s="5" t="inlineStr">
+      <c r="H929" s="5" t="inlineStr">
         <is>
           <t>QDe.012</t>
         </is>
       </c>
     </row>
-    <row r="929">
-      <c r="A929" s="5" t="inlineStr">
+    <row r="930">
+      <c r="A930" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B929" s="5" t="inlineStr">
+      <c r="B930" s="5" t="inlineStr">
         <is>
           <t>113995</t>
         </is>
       </c>
-      <c r="C929" s="5" t="inlineStr">
+      <c r="C930" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D929" s="5" t="inlineStr">
+      <c r="D930" s="5" t="inlineStr">
         <is>
           <t>THE ORGANIZATION OF AL-QAIDA IN THE ISLAMIC MAGHREB</t>
         </is>
       </c>
-      <c r="E929" s="5" t="inlineStr">
+      <c r="E930" s="5" t="inlineStr">
         <is>
           <t>AQIM ; Al Qaïda au Maghreb islamique (AQMI) ; Le Groupe Salafiste pour La Prédication et le Combat (GSPC) ; Salafist Group For Call and Combat</t>
         </is>
       </c>
-      <c r="F929" s="5" t="inlineStr"/>
-      <c r="G929" s="5" t="inlineStr">
+      <c r="F930" s="5" t="inlineStr"/>
+      <c r="G930" s="5" t="inlineStr">
         <is>
           <t>Headed by Abdelmalek Droukdel (QDi.232). Zone of operation includes
 Algeria and parts of Mali, Mauritania, Niger, Tunisia and Morocco. Review pursuant to
 Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H929" s="5" t="inlineStr">
+      <c r="H930" s="5" t="inlineStr">
         <is>
           <t>QDe.014</t>
         </is>
       </c>
     </row>
-    <row r="930">
-      <c r="A930" s="5" t="inlineStr">
+    <row r="931">
+      <c r="A931" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B930" s="5" t="inlineStr">
+      <c r="B931" s="5" t="inlineStr">
         <is>
           <t>114113</t>
         </is>
       </c>
-      <c r="C930" s="5" t="inlineStr">
+      <c r="C931" s="5" t="inlineStr">
         <is>
           <t>2001-10-06</t>
         </is>
       </c>
-      <c r="D930" s="5" t="inlineStr">
+      <c r="D931" s="5" t="inlineStr">
         <is>
           <t>WAFA HUMANITARIAN ORGANIZATION</t>
         </is>
       </c>
-      <c r="E930" s="5" t="inlineStr">
+      <c r="E931" s="5" t="inlineStr">
         <is>
           <t>Al Wafa ; Al Wafa Organization ; Wafa Al-Igatha Al-Islamia</t>
         </is>
       </c>
-      <c r="F930" s="5" t="inlineStr"/>
-      <c r="G930" s="5" t="inlineStr">
+      <c r="F931" s="5" t="inlineStr"/>
+      <c r="G931" s="5" t="inlineStr">
         <is>
           <t>Headquarters was in Kandahar, Afghanistan as at 2001. Wafa was a
 component of Al-Qaida (QDe.004) in 2001. Review pursuant to Security Council resolution
 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H930" s="5" t="inlineStr">
+      <c r="H931" s="5" t="inlineStr">
         <is>
           <t>QDe.015</t>
         </is>
       </c>
     </row>
-    <row r="931">
-      <c r="A931" s="5" t="inlineStr">
+    <row r="932">
+      <c r="A932" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B931" s="5" t="inlineStr">
+      <c r="B932" s="5" t="inlineStr">
         <is>
           <t>113965</t>
         </is>
       </c>
-      <c r="C931" s="5" t="inlineStr">
+      <c r="C932" s="5" t="inlineStr">
         <is>
           <t>2001-10-17</t>
         </is>
       </c>
-      <c r="D931" s="5" t="inlineStr">
+      <c r="D932" s="5" t="inlineStr">
         <is>
           <t>JAISH-I-MOHAMMED</t>
         </is>
       </c>
-      <c r="E931" s="5" t="inlineStr">
+      <c r="E932" s="5" t="inlineStr">
         <is>
           <t>Army of Mohammed</t>
         </is>
       </c>
-      <c r="F931" s="5" t="inlineStr"/>
-      <c r="G931" s="5" t="inlineStr">
+      <c r="F932" s="5" t="inlineStr"/>
+      <c r="G932" s="5" t="inlineStr">
         <is>
           <t>Based in Peshawar and Muzaffarabad, Pakistan Associated with Harakat
 ul-Mujahidin / HUM (QDe.008), Lashkar-e-Tayyiba (QDe.118), Al-Akhtar Trust International
@@ -37969,84 +38004,49 @@
 Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H931" s="5" t="inlineStr">
+      <c r="H932" s="5" t="inlineStr">
         <is>
           <t>QDe.019</t>
         </is>
       </c>
     </row>
-    <row r="932">
-      <c r="A932" s="5" t="inlineStr">
+    <row r="933">
+      <c r="A933" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B932" s="5" t="inlineStr">
+      <c r="B933" s="5" t="inlineStr">
         <is>
           <t>113854</t>
         </is>
       </c>
-      <c r="C932" s="5" t="inlineStr">
+      <c r="C933" s="5" t="inlineStr">
         <is>
           <t>2001-10-17</t>
         </is>
       </c>
-      <c r="D932" s="5" t="inlineStr">
+      <c r="D933" s="5" t="inlineStr">
         <is>
           <t>JAM'YAH TA'AWUN AL-ISLAMIA</t>
         </is>
       </c>
-      <c r="E932" s="5" t="inlineStr">
+      <c r="E933" s="5" t="inlineStr">
         <is>
           <t>Society of Islamic Cooperation ; Jam'iyat Al Ta'awun Al Islamiyya ; Jit</t>
         </is>
       </c>
-      <c r="F932" s="5" t="inlineStr"/>
-      <c r="G932" s="5" t="inlineStr">
+      <c r="F933" s="5" t="inlineStr"/>
+      <c r="G933" s="5" t="inlineStr">
         <is>
           <t>Founded by Usama Mohammad Awad bin Laden (deceased) in 2001. Review
 pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun.
 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H932" s="5" t="inlineStr">
+      <c r="H933" s="5" t="inlineStr">
         <is>
           <t>QDe.020</t>
-        </is>
-      </c>
-    </row>
-    <row r="933">
-      <c r="A933" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B933" s="5" t="inlineStr">
-        <is>
-          <t>113993</t>
-        </is>
-      </c>
-      <c r="C933" s="5" t="inlineStr">
-        <is>
-          <t>2001-10-17</t>
-        </is>
-      </c>
-      <c r="D933" s="5" t="inlineStr">
-        <is>
-          <t>RABITA TRUST</t>
-        </is>
-      </c>
-      <c r="E933" s="5" t="inlineStr"/>
-      <c r="F933" s="5" t="inlineStr"/>
-      <c r="G933" s="5" t="inlineStr">
-        <is>
-          <t>Banned in Pakistan. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H933" s="5" t="inlineStr">
-        <is>
-          <t>QDe.021</t>
         </is>
       </c>
     </row>
@@ -38058,29 +38058,30 @@
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>113883</t>
+          <t>113993</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
         <is>
-          <t>2001-12-24</t>
+          <t>2001-10-17</t>
         </is>
       </c>
       <c r="D934" s="5" t="inlineStr">
         <is>
-          <t>UMMAH TAMEER E-NAU (UTN)</t>
+          <t>RABITA TRUST</t>
         </is>
       </c>
       <c r="E934" s="5" t="inlineStr"/>
       <c r="F934" s="5" t="inlineStr"/>
       <c r="G934" s="5" t="inlineStr">
         <is>
-          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055), Majeed Abdul Chaudhry (QDi.054) and Mohammed Tufail (QDi.056). Banned in Pakistan. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Banned in Pakistan. Review pursuant to Security Council resolution 1822
+(2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H934" s="5" t="inlineStr">
         <is>
-          <t>QDe.068</t>
+          <t>QDe.021</t>
         </is>
       </c>
     </row>
@@ -38092,33 +38093,29 @@
       </c>
       <c r="B935" s="5" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>113883</t>
         </is>
       </c>
       <c r="C935" s="5" t="inlineStr">
         <is>
-          <t>2002-01-11</t>
+          <t>2001-12-24</t>
         </is>
       </c>
       <c r="D935" s="5" t="inlineStr">
         <is>
-          <t>AFGHAN SUPPORT COMMITTEE (ASC)</t>
-        </is>
-      </c>
-      <c r="E935" s="5" t="inlineStr">
-        <is>
-          <t>Lajnat ul Masa Eidatul Afghania ; Jamiat Ayat-ur-Rhas al Islamiac ; Jamiat Ihya ul Turath al Islamia ; Ahya ul Turas</t>
-        </is>
-      </c>
+          <t>UMMAH TAMEER E-NAU (UTN)</t>
+        </is>
+      </c>
+      <c r="E935" s="5" t="inlineStr"/>
       <c r="F935" s="5" t="inlineStr"/>
       <c r="G935" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Revival of Islamic Heritage Society (QDe.070). Abu Bakr al-Jaziri (QDi.058) served as finance chief of ASC. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055), Majeed Abdul Chaudhry (QDi.054) and Mohammed Tufail (QDi.056). Banned in Pakistan. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H935" s="5" t="inlineStr">
         <is>
-          <t>QDe.069</t>
+          <t>QDe.068</t>
         </is>
       </c>
     </row>
@@ -38130,7 +38127,7 @@
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>113994</t>
+          <t>113226</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -38140,16 +38137,54 @@
       </c>
       <c r="D936" s="5" t="inlineStr">
         <is>
-          <t>REVIVAL OF ISLAMIC HERITAGE SOCIETY</t>
+          <t>AFGHAN SUPPORT COMMITTEE (ASC)</t>
         </is>
       </c>
       <c r="E936" s="5" t="inlineStr">
         <is>
-          <t>Revival of Islamic Society Heritage on the African Continent ; Jamia Ihya ul Turath ; RIHS ; Jamiat Ihia Al-Turath Al-Islamiya ; Al-Furqan Foundation Welfare Trust ; Al-Furqan Welfare Foundation</t>
+          <t>Lajnat ul Masa Eidatul Afghania ; Jamiat Ayat-ur-Rhas al Islamiac ; Jamiat Ihya ul Turath al Islamia ; Ahya ul Turas</t>
         </is>
       </c>
       <c r="F936" s="5" t="inlineStr"/>
       <c r="G936" s="5" t="inlineStr">
+        <is>
+          <t>Associated with the Revival of Islamic Heritage Society (QDe.070). Abu Bakr al-Jaziri (QDi.058) served as finance chief of ASC. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H936" s="5" t="inlineStr">
+        <is>
+          <t>QDe.069</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B937" s="5" t="inlineStr">
+        <is>
+          <t>113994</t>
+        </is>
+      </c>
+      <c r="C937" s="5" t="inlineStr">
+        <is>
+          <t>2002-01-11</t>
+        </is>
+      </c>
+      <c r="D937" s="5" t="inlineStr">
+        <is>
+          <t>REVIVAL OF ISLAMIC HERITAGE SOCIETY</t>
+        </is>
+      </c>
+      <c r="E937" s="5" t="inlineStr">
+        <is>
+          <t>Revival of Islamic Society Heritage on the African Continent ; Jamia Ihya ul Turath ; RIHS ; Jamiat Ihia Al-Turath Al-Islamiya ; Al-Furqan Foundation Welfare Trust ; Al-Furqan Welfare Foundation</t>
+        </is>
+      </c>
+      <c r="F937" s="5" t="inlineStr"/>
+      <c r="G937" s="5" t="inlineStr">
         <is>
           <t>NOTE: Only the Pakistan and Afghanistan offices of this entity are
 designated. Associated with Abu Bakr al-Jaziri (QDi.058) and Afghan Support Committee
@@ -38157,119 +38192,119 @@
 concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H936" s="5" t="inlineStr">
+      <c r="H937" s="5" t="inlineStr">
         <is>
           <t>QDe.070</t>
         </is>
       </c>
     </row>
-    <row r="937">
-      <c r="A937" s="5" t="inlineStr">
+    <row r="938">
+      <c r="A938" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B937" s="5" t="inlineStr">
+      <c r="B938" s="5" t="inlineStr">
         <is>
           <t>113356</t>
         </is>
       </c>
-      <c r="C937" s="5" t="inlineStr">
+      <c r="C938" s="5" t="inlineStr">
         <is>
           <t>2002-09-11</t>
         </is>
       </c>
-      <c r="D937" s="5" t="inlineStr">
+      <c r="D938" s="5" t="inlineStr">
         <is>
           <t>EASTERN TURKISTAN ISLAMIC MOVEMENT (ETIM)</t>
         </is>
       </c>
-      <c r="E937" s="5" t="inlineStr">
+      <c r="E938" s="5" t="inlineStr">
         <is>
           <t>The Eastern Turkistan Islamic Party ; The Eastern Turkistan Islamic Party of Allah ; Islamic Party of Turkestan ; Djamaat Turkistan</t>
         </is>
       </c>
-      <c r="F937" s="5" t="inlineStr"/>
-      <c r="G937" s="5" t="inlineStr">
+      <c r="F938" s="5" t="inlineStr"/>
+      <c r="G938" s="5" t="inlineStr">
         <is>
           <t>Active in China, South Asia and Central Asia. Review pursuant to Security
 Council resolution 1822 (2008) was concluded on 20 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H937" s="5" t="inlineStr">
+      <c r="H938" s="5" t="inlineStr">
         <is>
           <t>QDe.088</t>
         </is>
       </c>
     </row>
-    <row r="938">
-      <c r="A938" s="5" t="inlineStr">
+    <row r="939">
+      <c r="A939" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B938" s="5" t="inlineStr">
+      <c r="B939" s="5" t="inlineStr">
         <is>
           <t>113977</t>
         </is>
       </c>
-      <c r="C938" s="5" t="inlineStr">
+      <c r="C939" s="5" t="inlineStr">
         <is>
           <t>2002-10-10</t>
         </is>
       </c>
-      <c r="D938" s="5" t="inlineStr">
+      <c r="D939" s="5" t="inlineStr">
         <is>
           <t>MOROCCAN ISLAMIC COMBATANT GROUP</t>
         </is>
       </c>
-      <c r="E938" s="5" t="inlineStr">
+      <c r="E939" s="5" t="inlineStr">
         <is>
           <t>Groupe Islamique Combattant Marocain ; GICM</t>
         </is>
       </c>
-      <c r="F938" s="5" t="inlineStr"/>
-      <c r="G938" s="5" t="inlineStr">
+      <c r="F939" s="5" t="inlineStr"/>
+      <c r="G939" s="5" t="inlineStr">
         <is>
           <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb
 (QDe.014). Review pursuant to Security Council resolution 1822 (2008) was concluded on
 20 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H938" s="5" t="inlineStr">
+      <c r="H939" s="5" t="inlineStr">
         <is>
           <t>QDe.089</t>
         </is>
       </c>
     </row>
-    <row r="939">
-      <c r="A939" s="5" t="inlineStr">
+    <row r="940">
+      <c r="A940" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B939" s="5" t="inlineStr">
+      <c r="B940" s="5" t="inlineStr">
         <is>
           <t>113997</t>
         </is>
       </c>
-      <c r="C939" s="5" t="inlineStr">
+      <c r="C940" s="5" t="inlineStr">
         <is>
           <t>2002-10-10</t>
         </is>
       </c>
-      <c r="D939" s="5" t="inlineStr">
+      <c r="D940" s="5" t="inlineStr">
         <is>
           <t>TUNISIAN COMBATANT GROUP</t>
         </is>
       </c>
-      <c r="E939" s="5" t="inlineStr">
+      <c r="E940" s="5" t="inlineStr">
         <is>
           <t>Groupe Combattant Tunisien ; Groupe Islamiste Combattant Tunisien ; GICT</t>
         </is>
       </c>
-      <c r="F939" s="5" t="inlineStr"/>
-      <c r="G939" s="5" t="inlineStr">
+      <c r="F940" s="5" t="inlineStr"/>
+      <c r="G940" s="5" t="inlineStr">
         <is>
           <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014).
                 Review pursuant to Security Council resolution 1822 (2008) was concluded on 6 May
@@ -38277,36 +38312,36 @@
                 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H939" s="5" t="inlineStr">
+      <c r="H940" s="5" t="inlineStr">
         <is>
           <t>QDe.090</t>
         </is>
       </c>
     </row>
-    <row r="940">
-      <c r="A940" s="5" t="inlineStr">
+    <row r="941">
+      <c r="A941" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B940" s="5" t="inlineStr">
+      <c r="B941" s="5" t="inlineStr">
         <is>
           <t>113476</t>
         </is>
       </c>
-      <c r="C940" s="5" t="inlineStr">
+      <c r="C941" s="5" t="inlineStr">
         <is>
           <t>2002-10-22</t>
         </is>
       </c>
-      <c r="D940" s="5" t="inlineStr">
+      <c r="D941" s="5" t="inlineStr">
         <is>
           <t>GLOBAL RELIEF FOUNDATION (GRF)</t>
         </is>
       </c>
-      <c r="E940" s="5" t="inlineStr"/>
-      <c r="F940" s="5" t="inlineStr"/>
-      <c r="G940" s="5" t="inlineStr">
+      <c r="E941" s="5" t="inlineStr"/>
+      <c r="F941" s="5" t="inlineStr"/>
+      <c r="G941" s="5" t="inlineStr">
         <is>
           <t>Other Foreign Locations: Afghanistan, Bangladesh, Eritrea, Ethiopia,
 India, Iraq, West Bank and Gaza, Somalia and Syria. Federal Employer Identification
@@ -38314,87 +38349,49 @@
 resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H940" s="5" t="inlineStr">
+      <c r="H941" s="5" t="inlineStr">
         <is>
           <t>QDe.091</t>
         </is>
       </c>
     </row>
-    <row r="941">
-      <c r="A941" s="5" t="inlineStr">
+    <row r="942">
+      <c r="A942" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B941" s="5" t="inlineStr">
+      <c r="B942" s="5" t="inlineStr">
         <is>
           <t>113967</t>
         </is>
       </c>
-      <c r="C941" s="5" t="inlineStr">
+      <c r="C942" s="5" t="inlineStr">
         <is>
           <t>2002-10-25</t>
         </is>
       </c>
-      <c r="D941" s="5" t="inlineStr">
+      <c r="D942" s="5" t="inlineStr">
         <is>
           <t>JEMAAH ISLAMIYAH</t>
         </is>
       </c>
-      <c r="E941" s="5" t="inlineStr">
+      <c r="E942" s="5" t="inlineStr">
         <is>
           <t>Jema’ah Islamiyah ; Jemaah Islamiya ; Jemaah Islamiah ; Jamaah Islamiyah ; Jama’ah Islamiyah</t>
         </is>
       </c>
-      <c r="F941" s="5" t="inlineStr"/>
-      <c r="G941" s="5" t="inlineStr">
+      <c r="F942" s="5" t="inlineStr"/>
+      <c r="G942" s="5" t="inlineStr">
         <is>
           <t>Operates in Southeast Asia, including Indonesia, Malaysia and the
 Philippines. Associated with the Abu Sayyaf Group (QDe.001). Review pursuant to Security
 Council resolution 1822 (2008) was concluded on 25 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H941" s="5" t="inlineStr">
+      <c r="H942" s="5" t="inlineStr">
         <is>
           <t>QDe.092</t>
-        </is>
-      </c>
-    </row>
-    <row r="942">
-      <c r="A942" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B942" s="5" t="inlineStr">
-        <is>
-          <t>113474</t>
-        </is>
-      </c>
-      <c r="C942" s="5" t="inlineStr">
-        <is>
-          <t>2002-11-21</t>
-        </is>
-      </c>
-      <c r="D942" s="5" t="inlineStr">
-        <is>
-          <t>BENEVOLENCE INTERNATIONAL FOUNDATION</t>
-        </is>
-      </c>
-      <c r="E942" s="5" t="inlineStr">
-        <is>
-          <t>Al Bir Al Dawalia ; BIF ; BIF-USA ; Mezhdunarodnyj Blagotvoritel'nyl Fond</t>
-        </is>
-      </c>
-      <c r="F942" s="5" t="inlineStr"/>
-      <c r="G942" s="5" t="inlineStr">
-        <is>
-          <t>Reportedly defunct. No longer operates in Bosnia and Herzegovina. Employer Identification Number (United States of America): 36-3823186.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H942" s="5" t="inlineStr">
-        <is>
-          <t>QDe.093</t>
         </is>
       </c>
     </row>
@@ -38406,29 +38403,33 @@
       </c>
       <c r="B943" s="5" t="inlineStr">
         <is>
-          <t>114089</t>
+          <t>113474</t>
         </is>
       </c>
       <c r="C943" s="5" t="inlineStr">
         <is>
-          <t>2003-02-03</t>
+          <t>2002-11-21</t>
         </is>
       </c>
       <c r="D943" s="5" t="inlineStr">
         <is>
-          <t>LASHKAR I JHANGVI (LJ)</t>
-        </is>
-      </c>
-      <c r="E943" s="5" t="inlineStr"/>
+          <t>BENEVOLENCE INTERNATIONAL FOUNDATION</t>
+        </is>
+      </c>
+      <c r="E943" s="5" t="inlineStr">
+        <is>
+          <t>Al Bir Al Dawalia ; BIF ; BIF-USA ; Mezhdunarodnyj Blagotvoritel'nyl Fond</t>
+        </is>
+      </c>
       <c r="F943" s="5" t="inlineStr"/>
       <c r="G943" s="5" t="inlineStr">
         <is>
-          <t>Based primarily in Pakistan’s Punjab region and in the city of Karachi. Active in Pakistan although banned as at 2010. Review pursuant to Security Council resolution 2161 (2014) was concluded on 23 Dec. 2016. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reportedly defunct. No longer operates in Bosnia and Herzegovina. Employer Identification Number (United States of America): 36-3823186.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H943" s="5" t="inlineStr">
         <is>
-          <t>QDe.096</t>
+          <t>QDe.093</t>
         </is>
       </c>
     </row>
@@ -38440,26 +38441,60 @@
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>113460</t>
+          <t>114089</t>
         </is>
       </c>
       <c r="C944" s="5" t="inlineStr">
         <is>
-          <t>2003-02-24</t>
+          <t>2003-02-03</t>
         </is>
       </c>
       <c r="D944" s="5" t="inlineStr">
         <is>
-          <t>ANSAR AL-ISLAM</t>
-        </is>
-      </c>
-      <c r="E944" s="5" t="inlineStr">
-        <is>
-          <t>Devotees of Islam ; Jund al-Islam ; Soldiers of Islam ; Kurdistan Supporters of Islam ; Supporters of Islam in Kurdistan ; Followers of Islam in Kurdistan ; Kurdish Taliban ; Soldiers of God ; Ansar al-Sunna Army ; Jaish Ansar al-Sunna ; Ansar al-Sunna</t>
-        </is>
-      </c>
+          <t>LASHKAR I JHANGVI (LJ)</t>
+        </is>
+      </c>
+      <c r="E944" s="5" t="inlineStr"/>
       <c r="F944" s="5" t="inlineStr"/>
       <c r="G944" s="5" t="inlineStr">
+        <is>
+          <t>Based primarily in Pakistan’s Punjab region and in the city of Karachi. Active in Pakistan although banned as at 2010. Review pursuant to Security Council resolution 2161 (2014) was concluded on 23 Dec. 2016. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H944" s="5" t="inlineStr">
+        <is>
+          <t>QDe.096</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B945" s="5" t="inlineStr">
+        <is>
+          <t>113460</t>
+        </is>
+      </c>
+      <c r="C945" s="5" t="inlineStr">
+        <is>
+          <t>2003-02-24</t>
+        </is>
+      </c>
+      <c r="D945" s="5" t="inlineStr">
+        <is>
+          <t>ANSAR AL-ISLAM</t>
+        </is>
+      </c>
+      <c r="E945" s="5" t="inlineStr">
+        <is>
+          <t>Devotees of Islam ; Jund al-Islam ; Soldiers of Islam ; Kurdistan Supporters of Islam ; Supporters of Islam in Kurdistan ; Followers of Islam in Kurdistan ; Kurdish Taliban ; Soldiers of God ; Ansar al-Sunna Army ; Jaish Ansar al-Sunna ; Ansar al-Sunna</t>
+        </is>
+      </c>
+      <c r="F945" s="5" t="inlineStr"/>
+      <c r="G945" s="5" t="inlineStr">
         <is>
           <t>The founder is Najmuddin Faraj Ahmad (QDi.226). Associated with Al-Qaida in
                 Iraq (QDe.115). Located and primarily active in northern Iraq but maintains a
@@ -38468,40 +38503,40 @@
                 resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H944" s="5" t="inlineStr">
+      <c r="H945" s="5" t="inlineStr">
         <is>
           <t>QDe.098</t>
         </is>
       </c>
     </row>
-    <row r="945">
-      <c r="A945" s="5" t="inlineStr">
+    <row r="946">
+      <c r="A946" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B945" s="5" t="inlineStr">
+      <c r="B946" s="5" t="inlineStr">
         <is>
           <t>113963</t>
         </is>
       </c>
-      <c r="C945" s="5" t="inlineStr">
+      <c r="C946" s="5" t="inlineStr">
         <is>
           <t>2003-03-04</t>
         </is>
       </c>
-      <c r="D945" s="5" t="inlineStr">
+      <c r="D946" s="5" t="inlineStr">
         <is>
           <t>ISLAMIC INTERNATIONAL BRIGADE (IIB)</t>
         </is>
       </c>
-      <c r="E945" s="5" t="inlineStr">
+      <c r="E946" s="5" t="inlineStr">
         <is>
           <t>The Islamic Peacekeeping Brigade ; The Islamic Peacekeeping Army ; The International Brigade ; Islamic Peacekeeping Battalion ; International Battalion ; Islamic Peacekeeping International Brigade</t>
         </is>
       </c>
-      <c r="F945" s="5" t="inlineStr"/>
-      <c r="G945" s="5" t="inlineStr">
+      <c r="F946" s="5" t="inlineStr"/>
+      <c r="G946" s="5" t="inlineStr">
         <is>
           <t>Linked to the Riyadus-Salikhin Reconnaissance and Sabotage Battalion of Chechen
                 Martyrs (RSRSBCM) (QDe.100) and the Special Purpose Islamic Regiment (SPIR)
@@ -38510,40 +38545,40 @@
                 concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H945" s="5" t="inlineStr">
+      <c r="H946" s="5" t="inlineStr">
         <is>
           <t>QDe.099</t>
         </is>
       </c>
     </row>
-    <row r="946">
-      <c r="A946" s="5" t="inlineStr">
+    <row r="947">
+      <c r="A947" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B946" s="5" t="inlineStr">
+      <c r="B947" s="5" t="inlineStr">
         <is>
           <t>113868</t>
         </is>
       </c>
-      <c r="C946" s="5" t="inlineStr">
+      <c r="C947" s="5" t="inlineStr">
         <is>
           <t>2003-03-04</t>
         </is>
       </c>
-      <c r="D946" s="5" t="inlineStr">
+      <c r="D947" s="5" t="inlineStr">
         <is>
           <t>RIYADUS-SALIKHIN RECONNAISSANCE AND SABOTAGE BATTALION OF CHECHEN MARTYRS (RSRSBCM)</t>
         </is>
       </c>
-      <c r="E946" s="5" t="inlineStr">
+      <c r="E947" s="5" t="inlineStr">
         <is>
           <t>Riyadus-Salikhin Reconnaissance and Sabotage Battalion ; Riyadh-as-Saliheen ; The Sabotage and Military Surveillance Group of the Riyadh al-Salihin Martyrs ; Firqat al-Takhrib wa al-Istitla al-Askariyah li Shuhada Riyadh al-Salihin ; Riyadus-Salikhin Reconnaissance and Sabotage battalion of Shahids (martyrs)</t>
         </is>
       </c>
-      <c r="F946" s="5" t="inlineStr"/>
-      <c r="G946" s="5" t="inlineStr">
+      <c r="F947" s="5" t="inlineStr"/>
+      <c r="G947" s="5" t="inlineStr">
         <is>
           <t>Associated with the Islamic International Brigade (IIB) (QDe.099), the
 Special Purpose Islamic Regiment (SPIR) (QDe.101) and Emarat Kavkaz (QDe.131). Review
@@ -38551,40 +38586,40 @@
 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H946" s="5" t="inlineStr">
+      <c r="H947" s="5" t="inlineStr">
         <is>
           <t>QDe.100</t>
         </is>
       </c>
     </row>
-    <row r="947">
-      <c r="A947" s="5" t="inlineStr">
+    <row r="948">
+      <c r="A948" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B947" s="5" t="inlineStr">
+      <c r="B948" s="5" t="inlineStr">
         <is>
           <t>114111</t>
         </is>
       </c>
-      <c r="C947" s="5" t="inlineStr">
+      <c r="C948" s="5" t="inlineStr">
         <is>
           <t>2003-03-04</t>
         </is>
       </c>
-      <c r="D947" s="5" t="inlineStr">
+      <c r="D948" s="5" t="inlineStr">
         <is>
           <t>SPECIAL PURPOSE ISLAMIC REGIMENT (SPIR)</t>
         </is>
       </c>
-      <c r="E947" s="5" t="inlineStr">
+      <c r="E948" s="5" t="inlineStr">
         <is>
           <t>The Islamic Special Purpose Regiment ; The al-Jihad-Fisi-Sabililah Special Islamic Regiment ; Islamic Regiment of Special Meaning</t>
         </is>
       </c>
-      <c r="F947" s="5" t="inlineStr"/>
-      <c r="G947" s="5" t="inlineStr">
+      <c r="F948" s="5" t="inlineStr"/>
+      <c r="G948" s="5" t="inlineStr">
         <is>
           <t>Linked to the Islamic International Brigade (IIB) (QDe.099) and the
 Riyadus-Salikhin Reconnaissance and Sabotage Battalion of Chechen Martyrs (RSRSBCM)
@@ -38592,44 +38627,9 @@
 17 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H947" s="5" t="inlineStr">
+      <c r="H948" s="5" t="inlineStr">
         <is>
           <t>QDe.101</t>
-        </is>
-      </c>
-    </row>
-    <row r="948">
-      <c r="A948" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B948" s="5" t="inlineStr">
-        <is>
-          <t>113455</t>
-        </is>
-      </c>
-      <c r="C948" s="5" t="inlineStr">
-        <is>
-          <t>2004-01-26</t>
-        </is>
-      </c>
-      <c r="D948" s="5" t="inlineStr">
-        <is>
-          <t>AL-HARAMAIN FOUNDATION (PAKISTAN)</t>
-        </is>
-      </c>
-      <c r="E948" s="5" t="inlineStr"/>
-      <c r="F948" s="5" t="inlineStr"/>
-      <c r="G948" s="5" t="inlineStr">
-        <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 19 Oct. 2009. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H948" s="5" t="inlineStr">
-        <is>
-          <t>QDe.104</t>
         </is>
       </c>
     </row>
@@ -38641,7 +38641,7 @@
       </c>
       <c r="B949" s="5" t="inlineStr">
         <is>
-          <t>113338</t>
+          <t>113455</t>
         </is>
       </c>
       <c r="C949" s="5" t="inlineStr">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="D949" s="5" t="inlineStr">
         <is>
-          <t>AL-HARAMAYN FOUNDATION (KENYA)</t>
+          <t>AL-HARAMAIN FOUNDATION (PAKISTAN)</t>
         </is>
       </c>
       <c r="E949" s="5" t="inlineStr"/>
@@ -38659,12 +38659,12 @@
       <c r="G949" s="5" t="inlineStr">
         <is>
           <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+on 19 Oct. 2009. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H949" s="5" t="inlineStr">
         <is>
-          <t>QDe.105</t>
+          <t>QDe.104</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="B950" s="5" t="inlineStr">
         <is>
-          <t>113339</t>
+          <t>113338</t>
         </is>
       </c>
       <c r="C950" s="5" t="inlineStr">
@@ -38686,7 +38686,7 @@
       </c>
       <c r="D950" s="5" t="inlineStr">
         <is>
-          <t>AL-HARAMAYN FOUNDATION (TANZANIA)</t>
+          <t>AL-HARAMAYN FOUNDATION (KENYA)</t>
         </is>
       </c>
       <c r="E950" s="5" t="inlineStr"/>
@@ -38694,12 +38694,12 @@
       <c r="G950" s="5" t="inlineStr">
         <is>
           <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+on 22 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H950" s="5" t="inlineStr">
         <is>
-          <t>QDe.106</t>
+          <t>QDe.105</t>
         </is>
       </c>
     </row>
@@ -38711,33 +38711,30 @@
       </c>
       <c r="B951" s="5" t="inlineStr">
         <is>
-          <t>113231</t>
+          <t>113339</t>
         </is>
       </c>
       <c r="C951" s="5" t="inlineStr">
         <is>
-          <t>2004-05-11</t>
+          <t>2004-01-26</t>
         </is>
       </c>
       <c r="D951" s="5" t="inlineStr">
         <is>
-          <t>AL FURQAN</t>
-        </is>
-      </c>
-      <c r="E951" s="5" t="inlineStr">
-        <is>
-          <t>Dzemilijati Furkan ; Dzem'ijjetul Furqan ; Association for Citizens Rights and Resistance to Lies ; Dzemijetul Furkan ; Association of Citizens for the Support of Truth and Supression of Lies ; Sirat ; Association for Education, Culture and Building Society-Sirat ; Association for Education, Cultural, and to Create Society -Sirat ; Istikamet ; In Siratel ; Citizens’ Association for Support and Prevention of lies – Furqan</t>
-        </is>
-      </c>
+          <t>AL-HARAMAYN FOUNDATION (TANZANIA)</t>
+        </is>
+      </c>
+      <c r="E951" s="5" t="inlineStr"/>
       <c r="F951" s="5" t="inlineStr"/>
       <c r="G951" s="5" t="inlineStr">
         <is>
-          <t>Reportedly defunct. Registered in Bosnia and Herzegovina as a citizens’ association under the name of “Citizens’ Association for Support and Prevention of lies – Furqan” on 26 Sep. 1997. Al Furqan ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision number 03-054-286/97 dated 8 Nov. 2002). Al Furqan was no longer in existence as of Dec. 2008. Review pursuant to Security Council resolution 1822 (2008) was concluded on 15 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
+on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H951" s="5" t="inlineStr">
         <is>
-          <t>QDe.107</t>
+          <t>QDe.106</t>
         </is>
       </c>
     </row>
@@ -38749,7 +38746,7 @@
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>114112</t>
+          <t>113231</t>
         </is>
       </c>
       <c r="C952" s="5" t="inlineStr">
@@ -38759,16 +38756,54 @@
       </c>
       <c r="D952" s="5" t="inlineStr">
         <is>
-          <t>TAIBAH INTERNATIONAL-BOSNIA OFFICES</t>
+          <t>AL FURQAN</t>
         </is>
       </c>
       <c r="E952" s="5" t="inlineStr">
         <is>
-          <t>Taibah International Aid Agency ; Taibah International Aid Association ; Al Taibah, Intl. ; Taibah International Aide Association</t>
+          <t>Dzemilijati Furkan ; Dzem'ijjetul Furqan ; Association for Citizens Rights and Resistance to Lies ; Dzemijetul Furkan ; Association of Citizens for the Support of Truth and Supression of Lies ; Sirat ; Association for Education, Culture and Building Society-Sirat ; Association for Education, Cultural, and to Create Society -Sirat ; Istikamet ; In Siratel ; Citizens’ Association for Support and Prevention of lies – Furqan</t>
         </is>
       </c>
       <c r="F952" s="5" t="inlineStr"/>
       <c r="G952" s="5" t="inlineStr">
+        <is>
+          <t>Reportedly defunct. Registered in Bosnia and Herzegovina as a citizens’ association under the name of “Citizens’ Association for Support and Prevention of lies – Furqan” on 26 Sep. 1997. Al Furqan ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision number 03-054-286/97 dated 8 Nov. 2002). Al Furqan was no longer in existence as of Dec. 2008. Review pursuant to Security Council resolution 1822 (2008) was concluded on 15 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H952" s="5" t="inlineStr">
+        <is>
+          <t>QDe.107</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B953" s="5" t="inlineStr">
+        <is>
+          <t>114112</t>
+        </is>
+      </c>
+      <c r="C953" s="5" t="inlineStr">
+        <is>
+          <t>2004-05-11</t>
+        </is>
+      </c>
+      <c r="D953" s="5" t="inlineStr">
+        <is>
+          <t>TAIBAH INTERNATIONAL-BOSNIA OFFICES</t>
+        </is>
+      </c>
+      <c r="E953" s="5" t="inlineStr">
+        <is>
+          <t>Taibah International Aid Agency ; Taibah International Aid Association ; Al Taibah, Intl. ; Taibah International Aide Association</t>
+        </is>
+      </c>
+      <c r="F953" s="5" t="inlineStr"/>
+      <c r="G953" s="5" t="inlineStr">
         <is>
           <t>Reportedly defunct. In 2002-2004, Taibah International – Bosnia offices used premises of the
 Culture Home in Hadzici, Sarajevo, Bosnia and Herzegovina. The organization was
@@ -38779,47 +38814,9 @@
 Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H952" s="5" t="inlineStr">
+      <c r="H953" s="5" t="inlineStr">
         <is>
           <t>QDe.108</t>
-        </is>
-      </c>
-    </row>
-    <row r="953">
-      <c r="A953" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B953" s="5" t="inlineStr">
-        <is>
-          <t>113232</t>
-        </is>
-      </c>
-      <c r="C953" s="5" t="inlineStr">
-        <is>
-          <t>2004-06-28</t>
-        </is>
-      </c>
-      <c r="D953" s="5" t="inlineStr">
-        <is>
-          <t>AL-HARAMAIN &amp; AL MASJED AL-AQSA CHARITY FOUNDATION</t>
-        </is>
-      </c>
-      <c r="E953" s="5" t="inlineStr">
-        <is>
-          <t>Al Haramain Al Masjed Al Aqsa ; Al Haramayn Al Masjid Al Aqsa ; Al-Haramayn and Al Masjid Al Aqsa Charitable Foundation ; Al Harammein Al Masjed Al-Aqsa Charity Foundation</t>
-        </is>
-      </c>
-      <c r="F953" s="5" t="inlineStr"/>
-      <c r="G953" s="5" t="inlineStr">
-        <is>
-          <t>Reportedly defunct. Used to be officially registered in Bosnia and Herzegovina under registry number 24. Al-Haramain &amp; Al Masjed Al-Aqsa Charity Foundation ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision on cessation of operation number 03-05-2-203/04). It was no longer in existence as of Dec. 2008. Its premises and humanitarian activities were transferred under Government supervision to a new entity called Sretna Buducnost. Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H953" s="5" t="inlineStr">
-        <is>
-          <t>QDe.109</t>
         </is>
       </c>
     </row>
@@ -38831,30 +38828,33 @@
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>113453</t>
+          <t>113232</t>
         </is>
       </c>
       <c r="C954" s="5" t="inlineStr">
         <is>
-          <t>2004-07-06</t>
+          <t>2004-06-28</t>
         </is>
       </c>
       <c r="D954" s="5" t="inlineStr">
         <is>
-          <t>AL-HARAMAIN: AFGHANISTAN BRANCH</t>
-        </is>
-      </c>
-      <c r="E954" s="5" t="inlineStr"/>
+          <t>AL-HARAMAIN &amp; AL MASJED AL-AQSA CHARITY FOUNDATION</t>
+        </is>
+      </c>
+      <c r="E954" s="5" t="inlineStr">
+        <is>
+          <t>Al Haramain Al Masjed Al Aqsa ; Al Haramayn Al Masjid Al Aqsa ; Al-Haramayn and Al Masjid Al Aqsa Charitable Foundation ; Al Harammein Al Masjed Al-Aqsa Charity Foundation</t>
+        </is>
+      </c>
       <c r="F954" s="5" t="inlineStr"/>
       <c r="G954" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reportedly defunct. Used to be officially registered in Bosnia and Herzegovina under registry number 24. Al-Haramain &amp; Al Masjed Al-Aqsa Charity Foundation ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision on cessation of operation number 03-05-2-203/04). It was no longer in existence as of Dec. 2008. Its premises and humanitarian activities were transferred under Government supervision to a new entity called Sretna Buducnost. Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H954" s="5" t="inlineStr">
         <is>
-          <t>QDe.110</t>
+          <t>QDe.109</t>
         </is>
       </c>
     </row>
@@ -38866,7 +38866,7 @@
       </c>
       <c r="B955" s="5" t="inlineStr">
         <is>
-          <t>113335</t>
+          <t>113453</t>
         </is>
       </c>
       <c r="C955" s="5" t="inlineStr">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="D955" s="5" t="inlineStr">
         <is>
-          <t>AL-HARAMAIN: ALBANIA BRANCH</t>
+          <t>AL-HARAMAIN: AFGHANISTAN BRANCH</t>
         </is>
       </c>
       <c r="E955" s="5" t="inlineStr"/>
@@ -38889,7 +38889,7 @@
       </c>
       <c r="H955" s="5" t="inlineStr">
         <is>
-          <t>QDe.111</t>
+          <t>QDe.110</t>
         </is>
       </c>
     </row>
@@ -38901,7 +38901,7 @@
       </c>
       <c r="B956" s="5" t="inlineStr">
         <is>
-          <t>113454</t>
+          <t>113335</t>
         </is>
       </c>
       <c r="C956" s="5" t="inlineStr">
@@ -38911,7 +38911,7 @@
       </c>
       <c r="D956" s="5" t="inlineStr">
         <is>
-          <t>AL-HARAMAIN: BANGLADESH BRANCH</t>
+          <t>AL-HARAMAIN: ALBANIA BRANCH</t>
         </is>
       </c>
       <c r="E956" s="5" t="inlineStr"/>
@@ -38924,7 +38924,7 @@
       </c>
       <c r="H956" s="5" t="inlineStr">
         <is>
-          <t>QDe.112</t>
+          <t>QDe.111</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="B957" s="5" t="inlineStr">
         <is>
-          <t>113233</t>
+          <t>113454</t>
         </is>
       </c>
       <c r="C957" s="5" t="inlineStr">
@@ -38946,7 +38946,7 @@
       </c>
       <c r="D957" s="5" t="inlineStr">
         <is>
-          <t>AL-HARAMAIN: ETHIOPIA BRANCH</t>
+          <t>AL-HARAMAIN: BANGLADESH BRANCH</t>
         </is>
       </c>
       <c r="E957" s="5" t="inlineStr"/>
@@ -38959,7 +38959,7 @@
       </c>
       <c r="H957" s="5" t="inlineStr">
         <is>
-          <t>QDe.113</t>
+          <t>QDe.112</t>
         </is>
       </c>
     </row>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="B958" s="5" t="inlineStr">
         <is>
-          <t>113235</t>
+          <t>113233</t>
         </is>
       </c>
       <c r="C958" s="5" t="inlineStr">
@@ -38981,55 +38981,90 @@
       </c>
       <c r="D958" s="5" t="inlineStr">
         <is>
-          <t>AL-HARAMAIN: THE NETHERLANDS BRANCH</t>
-        </is>
-      </c>
-      <c r="E958" s="5" t="inlineStr">
-        <is>
-          <t>Stichting Al Haramain Humanitarian Aid</t>
-        </is>
-      </c>
+          <t>AL-HARAMAIN: ETHIOPIA BRANCH</t>
+        </is>
+      </c>
+      <c r="E958" s="5" t="inlineStr"/>
       <c r="F958" s="5" t="inlineStr"/>
       <c r="G958" s="5" t="inlineStr">
         <is>
+          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
+on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H958" s="5" t="inlineStr">
+        <is>
+          <t>QDe.113</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B959" s="5" t="inlineStr">
+        <is>
+          <t>113235</t>
+        </is>
+      </c>
+      <c r="C959" s="5" t="inlineStr">
+        <is>
+          <t>2004-07-06</t>
+        </is>
+      </c>
+      <c r="D959" s="5" t="inlineStr">
+        <is>
+          <t>AL-HARAMAIN: THE NETHERLANDS BRANCH</t>
+        </is>
+      </c>
+      <c r="E959" s="5" t="inlineStr">
+        <is>
+          <t>Stichting Al Haramain Humanitarian Aid</t>
+        </is>
+      </c>
+      <c r="F959" s="5" t="inlineStr"/>
+      <c r="G959" s="5" t="inlineStr">
+        <is>
           <t>Reportedly defunct.Review pursuant to Security Council resolution 1822 (2008) was concluded
 on 28 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H958" s="5" t="inlineStr">
+      <c r="H959" s="5" t="inlineStr">
         <is>
           <t>QDe.114</t>
         </is>
       </c>
     </row>
-    <row r="959">
-      <c r="A959" s="5" t="inlineStr">
+    <row r="960">
+      <c r="A960" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B959" s="5" t="inlineStr">
+      <c r="B960" s="5" t="inlineStr">
         <is>
           <t>113966</t>
         </is>
       </c>
-      <c r="C959" s="5" t="inlineStr">
+      <c r="C960" s="5" t="inlineStr">
         <is>
           <t>2004-10-18</t>
         </is>
       </c>
-      <c r="D959" s="5" t="inlineStr">
+      <c r="D960" s="5" t="inlineStr">
         <is>
           <t>AL-QAIDA IN IRAQ</t>
         </is>
       </c>
-      <c r="E959" s="5" t="inlineStr">
+      <c r="E960" s="5" t="inlineStr">
         <is>
           <t>AQI ; al-Tawhid ; the Monotheism and Jihad Group ; Qaida of the Jihad in the Land of the Two Rivers ; Al-Qaida of Jihad in the Land of the Two Rivers ; The Organization of Jihad’s Base in the Country of the Two Rivers ; The Organization Base of Jihad/Country of the Two Rivers ; The Organization Base of Jihad/Mesopotamia ; Tanzim Qa’idat Al-Jihad fi Bilad al-Rafidayn ; Tanzeem Qa’idat al Jihad/Bilad al Raafidaini ; Jama'at Al-Tawhid Wa'al-Jihad ; JTJ ; Islamic State of Iraq ; ISI ; al-Zarqawi network ; Islamic State in Iraq and the Levant</t>
         </is>
       </c>
-      <c r="F959" s="5" t="inlineStr"/>
-      <c r="G959" s="5" t="inlineStr">
+      <c r="F960" s="5" t="inlineStr"/>
+      <c r="G960" s="5" t="inlineStr">
         <is>
           <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
 on 25 May 2010. 
@@ -39037,115 +39072,115 @@
  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H959" s="5" t="inlineStr">
+      <c r="H960" s="5" t="inlineStr">
         <is>
           <t>QDe.115</t>
         </is>
       </c>
     </row>
-    <row r="960">
-      <c r="A960" s="5" t="inlineStr">
+    <row r="961">
+      <c r="A961" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B960" s="5" t="inlineStr">
+      <c r="B961" s="5" t="inlineStr">
         <is>
           <t>113234</t>
         </is>
       </c>
-      <c r="C960" s="5" t="inlineStr">
+      <c r="C961" s="5" t="inlineStr">
         <is>
           <t>2004-09-28</t>
         </is>
       </c>
-      <c r="D960" s="5" t="inlineStr">
+      <c r="D961" s="5" t="inlineStr">
         <is>
           <t>AL-HARAMAIN FOUNDATION (UNION OF THE COMOROS)</t>
         </is>
       </c>
-      <c r="E960" s="5" t="inlineStr"/>
-      <c r="F960" s="5" t="inlineStr"/>
-      <c r="G960" s="5" t="inlineStr">
+      <c r="E961" s="5" t="inlineStr"/>
+      <c r="F961" s="5" t="inlineStr"/>
+      <c r="G961" s="5" t="inlineStr">
         <is>
           <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
 on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H960" s="5" t="inlineStr">
+      <c r="H961" s="5" t="inlineStr">
         <is>
           <t>QDe.116</t>
         </is>
       </c>
     </row>
-    <row r="961">
-      <c r="A961" s="5" t="inlineStr">
+    <row r="962">
+      <c r="A962" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B961" s="5" t="inlineStr">
+      <c r="B962" s="5" t="inlineStr">
         <is>
           <t>114076</t>
         </is>
       </c>
-      <c r="C961" s="5" t="inlineStr">
+      <c r="C962" s="5" t="inlineStr">
         <is>
           <t>2005-05-02</t>
         </is>
       </c>
-      <c r="D961" s="5" t="inlineStr">
+      <c r="D962" s="5" t="inlineStr">
         <is>
           <t>LASHKAR-E-TAYYIBA</t>
         </is>
       </c>
-      <c r="E961" s="5" t="inlineStr">
+      <c r="E962" s="5" t="inlineStr">
         <is>
           <t>Lashkar-e-Toiba ; Lashkar-i-Taiba ; al Mansoorian ; al Mansooreen ; Army of the Pure ; Army of the Righteous ; Army of the Pure and Righteous ; Paasban-e-Kashmir ; Paasban-i-Ahle-Hadith ; Pasban-e-Kashmir ; Pasban-e-Ahle-Hadith ; Paasban-e-Ahle-Hadis ; Pashan-e-ahle Hadis ; Lashkar e Tayyaba ; LET ; Jamaat-ud-Dawa ; JUD ; Jama'at al-Dawa ; Jamaat ud-Daawa ; Jamaat ul-Dawah ; Jamaat-ul-Dawa ; Jama'at-i-Dawat ; Jamaiat-ud-Dawa ; Jama'at-ud-Da'awah ; Jama'at-ud-Da'awa ; Jamaati-ud-Dawa ; Falah-i-Insaniat Foundation (FIF)</t>
         </is>
       </c>
-      <c r="F961" s="5" t="inlineStr"/>
-      <c r="G961" s="5" t="inlineStr">
+      <c r="F962" s="5" t="inlineStr"/>
+      <c r="G962" s="5" t="inlineStr">
         <is>
           <t>Associated with Hafiz Muhammad Saeed (QDi.263) who is the leader of
 Lashkar-e-Tayyiba. Review pursuant to Security Council resolution 1822 (2008) was
 concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H961" s="5" t="inlineStr">
+      <c r="H962" s="5" t="inlineStr">
         <is>
           <t>QDe.118</t>
         </is>
       </c>
     </row>
-    <row r="962">
-      <c r="A962" s="5" t="inlineStr">
+    <row r="963">
+      <c r="A963" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B962" s="5" t="inlineStr">
+      <c r="B963" s="5" t="inlineStr">
         <is>
           <t>113853</t>
         </is>
       </c>
-      <c r="C962" s="5" t="inlineStr">
+      <c r="C963" s="5" t="inlineStr">
         <is>
           <t>2005-06-01</t>
         </is>
       </c>
-      <c r="D962" s="5" t="inlineStr">
+      <c r="D963" s="5" t="inlineStr">
         <is>
           <t>ISLAMIC JIHAD GROUP</t>
         </is>
       </c>
-      <c r="E962" s="5" t="inlineStr">
+      <c r="E963" s="5" t="inlineStr">
         <is>
           <t>Jama’at al-Jihad ; Libyan Society ; Kazakh Jama’at ; Jamaat Mojahedin ; Jamiyat ; Jamiat al-Jihad al-Islami ; Dzhamaat Modzhakhedov ; Islamic Jihad Group of Uzbekistan ; al-Djihad al-Islami ; Zamaat Modzhakhedov Tsentralnoy Asii ; Islamic Jihad Union</t>
         </is>
       </c>
-      <c r="F962" s="5" t="inlineStr"/>
-      <c r="G962" s="5" t="inlineStr">
+      <c r="F963" s="5" t="inlineStr"/>
+      <c r="G963" s="5" t="inlineStr">
         <is>
           <t>Founded and led by Najmiddin Kamolitdinovich Jalolov (deceased) and Suhayl
                 Fatilloevich Buranov (deceased). Associated with the Islamic Movement of Uzbekistan
@@ -39154,40 +39189,40 @@
                 Security Council resolution 1822 (2008) was concluded on 20 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H962" s="5" t="inlineStr">
+      <c r="H963" s="5" t="inlineStr">
         <is>
           <t>QDe.119</t>
         </is>
       </c>
     </row>
-    <row r="963">
-      <c r="A963" s="5" t="inlineStr">
+    <row r="964">
+      <c r="A964" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B963" s="5" t="inlineStr">
+      <c r="B964" s="5" t="inlineStr">
         <is>
           <t>113227</t>
         </is>
       </c>
-      <c r="C963" s="5" t="inlineStr">
+      <c r="C964" s="5" t="inlineStr">
         <is>
           <t>2005-08-17</t>
         </is>
       </c>
-      <c r="D963" s="5" t="inlineStr">
+      <c r="D964" s="5" t="inlineStr">
         <is>
           <t>AL-AKHTAR TRUST INTERNATIONAL</t>
         </is>
       </c>
-      <c r="E963" s="5" t="inlineStr">
+      <c r="E964" s="5" t="inlineStr">
         <is>
           <t>Al Akhtar Trust ; Al-Akhtar Medical Centre ; Akhtarabad Medical Camp ; Pakistan Relief Foundation ; Pakistani Relief Foundation ; Azmat-e-Pakistan Trust ; Azmat Pakistan Trust</t>
         </is>
       </c>
-      <c r="F963" s="5" t="inlineStr"/>
-      <c r="G963" s="5" t="inlineStr">
+      <c r="F964" s="5" t="inlineStr"/>
+      <c r="G964" s="5" t="inlineStr">
         <is>
           <t>Regional offices in Pakistan: Bahawalpur, Bawalnagar, Gilgit, Islamabad,
 Mirpur Khas, Tando-Jan-Muhammad. Akhtarabad Medical Camp is in Spin Boldak, Afghanistan.
@@ -39197,40 +39232,40 @@
 (2008) was concluded on 14 Sep. 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H963" s="5" t="inlineStr">
+      <c r="H964" s="5" t="inlineStr">
         <is>
           <t>QDe.121</t>
         </is>
       </c>
     </row>
-    <row r="964">
-      <c r="A964" s="5" t="inlineStr">
+    <row r="965">
+      <c r="A965" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B964" s="5" t="inlineStr">
+      <c r="B965" s="5" t="inlineStr">
         <is>
           <t>2812924</t>
         </is>
       </c>
-      <c r="C964" s="5" t="inlineStr">
+      <c r="C965" s="5" t="inlineStr">
         <is>
           <t>2008-06-04</t>
         </is>
       </c>
-      <c r="D964" s="5" t="inlineStr">
+      <c r="D965" s="5" t="inlineStr">
         <is>
           <t>RAJAH SOLAIMAN MOVEMENT</t>
         </is>
       </c>
-      <c r="E964" s="5" t="inlineStr">
+      <c r="E965" s="5" t="inlineStr">
         <is>
           <t>Rajah Solaiman Islamic Movement ; Rajah Solaiman Revolutionary Movement</t>
         </is>
       </c>
-      <c r="F964" s="5" t="inlineStr"/>
-      <c r="G964" s="5" t="inlineStr">
+      <c r="F965" s="5" t="inlineStr"/>
+      <c r="G965" s="5" t="inlineStr">
         <is>
           <t>Founded and headed by Hilarion Del Rosario Santos III (QDi.244).
 Associated with the Abu Sayyaf Group (QDe.001), Jemaah Islamiyah (QDe.092) and Khadafi
@@ -39240,40 +39275,40 @@
  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H964" s="5" t="inlineStr">
+      <c r="H965" s="5" t="inlineStr">
         <is>
           <t>QDe.128</t>
         </is>
       </c>
     </row>
-    <row r="965">
-      <c r="A965" s="5" t="inlineStr">
+    <row r="966">
+      <c r="A966" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B965" s="5" t="inlineStr">
+      <c r="B966" s="5" t="inlineStr">
         <is>
           <t>2881836</t>
         </is>
       </c>
-      <c r="C965" s="5" t="inlineStr">
+      <c r="C966" s="5" t="inlineStr">
         <is>
           <t>2010-01-19</t>
         </is>
       </c>
-      <c r="D965" s="5" t="inlineStr">
+      <c r="D966" s="5" t="inlineStr">
         <is>
           <t>AL-QAIDA IN THE ARABIAN PENINSULA (AQAP)</t>
         </is>
       </c>
-      <c r="E965" s="5" t="inlineStr">
+      <c r="E966" s="5" t="inlineStr">
         <is>
           <t>Al-Qaida of Jihad Organization in the Arabian Peninsula ; Tanzim Qa’idat al-Jihad fi Jazirat al-Arab ; Al-Qaida Organization in the Arabian Peninsula (AQAP) ; Al-Qaida in the South Arabian Peninsula ; Ansar al-Shari'a (AAS) ; Al-Qaida in Yemen (AQY)</t>
         </is>
       </c>
-      <c r="F965" s="5" t="inlineStr"/>
-      <c r="G965" s="5" t="inlineStr">
+      <c r="F966" s="5" t="inlineStr"/>
+      <c r="G966" s="5" t="inlineStr">
         <is>
           <t>AQAP is a regional affiliate of Al-Qaida (QDe.004) and an armed group operating
                 primarily in Arabian Peninsula. Location: Yemen. Alternative location: Saudi Arabia
@@ -39284,40 +39319,40 @@
                 targets. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H965" s="5" t="inlineStr">
+      <c r="H966" s="5" t="inlineStr">
         <is>
           <t>QDe.129</t>
         </is>
       </c>
     </row>
-    <row r="966">
-      <c r="A966" s="5" t="inlineStr">
+    <row r="967">
+      <c r="A967" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B966" s="5" t="inlineStr">
+      <c r="B967" s="5" t="inlineStr">
         <is>
           <t>2921366</t>
         </is>
       </c>
-      <c r="C966" s="5" t="inlineStr">
+      <c r="C967" s="5" t="inlineStr">
         <is>
           <t>2010-08-06</t>
         </is>
       </c>
-      <c r="D966" s="5" t="inlineStr">
+      <c r="D967" s="5" t="inlineStr">
         <is>
           <t>HARAKAT-UL JIHAD ISLAMI</t>
         </is>
       </c>
-      <c r="E966" s="5" t="inlineStr">
+      <c r="E967" s="5" t="inlineStr">
         <is>
           <t>HUJI ; Movement of Islamic Holy War ; Harkat-ul-Jihad-al Islami ; Harkat-al-Jihad-ul Islami ; Harkat-ul-Jehad-al-Islami ; Harakat ul Jihad-e-Islami ; Harakat-ul-Ansar ; HUA</t>
         </is>
       </c>
-      <c r="F966" s="5" t="inlineStr"/>
-      <c r="G966" s="5" t="inlineStr">
+      <c r="F967" s="5" t="inlineStr"/>
+      <c r="G967" s="5" t="inlineStr">
         <is>
           <t>Was established in Afghanistan in 1980. In 1993, Harakat-ul Jihad Islami merged
                 with Harakat ul-Mujahidin (QDe.008) to form Harakat ul-Ansar. In 1997, Harakat-ul
@@ -39325,114 +39360,114 @@
                 Operations are in India, Pakistan and Afghanistan. Banned in Pakistan. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H966" s="5" t="inlineStr">
+      <c r="H967" s="5" t="inlineStr">
         <is>
           <t>QDe.130</t>
         </is>
       </c>
     </row>
-    <row r="967">
-      <c r="A967" s="5" t="inlineStr">
+    <row r="968">
+      <c r="A968" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B967" s="5" t="inlineStr">
+      <c r="B968" s="5" t="inlineStr">
         <is>
           <t>2971893</t>
         </is>
       </c>
-      <c r="C967" s="5" t="inlineStr">
+      <c r="C968" s="5" t="inlineStr">
         <is>
           <t>2011-07-29</t>
         </is>
       </c>
-      <c r="D967" s="5" t="inlineStr">
+      <c r="D968" s="5" t="inlineStr">
         <is>
           <t>EMARAT KAVKAZ</t>
         </is>
       </c>
-      <c r="E967" s="5" t="inlineStr"/>
-      <c r="F967" s="5" t="inlineStr"/>
-      <c r="G967" s="5" t="inlineStr">
+      <c r="E968" s="5" t="inlineStr"/>
+      <c r="F968" s="5" t="inlineStr"/>
+      <c r="G968" s="5" t="inlineStr">
         <is>
           <t>Mainly active in the Russian Federation, Afghanistan and Pakistan. Led by Doku
 Khamatovich Umarov (QDi.290). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H967" s="5" t="inlineStr">
+      <c r="H968" s="5" t="inlineStr">
         <is>
           <t>QDe.131</t>
         </is>
       </c>
     </row>
-    <row r="968">
-      <c r="A968" s="5" t="inlineStr">
+    <row r="969">
+      <c r="A969" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B968" s="5" t="inlineStr">
+      <c r="B969" s="5" t="inlineStr">
         <is>
           <t>2971894</t>
         </is>
       </c>
-      <c r="C968" s="5" t="inlineStr">
+      <c r="C969" s="5" t="inlineStr">
         <is>
           <t>2011-07-29</t>
         </is>
       </c>
-      <c r="D968" s="5" t="inlineStr">
+      <c r="D969" s="5" t="inlineStr">
         <is>
           <t>TEHRIK-E TALIBAN PAKISTAN (TTP)</t>
         </is>
       </c>
-      <c r="E968" s="5" t="inlineStr">
+      <c r="E969" s="5" t="inlineStr">
         <is>
           <t>Tehrik-I-Taliban Pakistan ; Tehrik-e-Taliban ; Pakistani Taliban ; Tehreek-e-Taliban</t>
         </is>
       </c>
-      <c r="F968" s="5" t="inlineStr"/>
-      <c r="G968" s="5" t="inlineStr">
+      <c r="F969" s="5" t="inlineStr"/>
+      <c r="G969" s="5" t="inlineStr">
         <is>
           <t>Tehrik-e Taliban is based in the tribal areas along the Afghanistan/Pakistan
 border. Formed in 2007, its leader is Maulana Fazlullah (QDi.352). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H968" s="5" t="inlineStr">
+      <c r="H969" s="5" t="inlineStr">
         <is>
           <t>QDe.132</t>
         </is>
       </c>
     </row>
-    <row r="969">
-      <c r="A969" s="5" t="inlineStr">
+    <row r="970">
+      <c r="A970" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B969" s="5" t="inlineStr">
+      <c r="B970" s="5" t="inlineStr">
         <is>
           <t>2983820</t>
         </is>
       </c>
-      <c r="C969" s="5" t="inlineStr">
+      <c r="C970" s="5" t="inlineStr">
         <is>
           <t>2012-03-12</t>
         </is>
       </c>
-      <c r="D969" s="5" t="inlineStr">
+      <c r="D970" s="5" t="inlineStr">
         <is>
           <t>JEMMAH ANSHORUT TAUHID (JAT)</t>
         </is>
       </c>
-      <c r="E969" s="5" t="inlineStr">
+      <c r="E970" s="5" t="inlineStr">
         <is>
           <t>Jemaah Anshorut Tauhid ; Jemmah Ansharut Tauhid ; Jem’mah Ansharut Tauhid ; Jamaah Ansharut Tauhid ; Jama’ah Ansharut Tauhid ; Laskar 99</t>
         </is>
       </c>
-      <c r="F969" s="5" t="inlineStr"/>
-      <c r="G969" s="5" t="inlineStr">
+      <c r="F970" s="5" t="inlineStr"/>
+      <c r="G970" s="5" t="inlineStr">
         <is>
           <t>A group affiliated with the Islamic State in Iraq and the Levant (ISIL), listed
                 as Al-Qaida in Iraq (QDe.115), that has perpetrated attacks in Indonesia. Founded
@@ -39443,43 +39478,9 @@
                 Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H969" s="5" t="inlineStr">
+      <c r="H970" s="5" t="inlineStr">
         <is>
           <t>QDe.133</t>
-        </is>
-      </c>
-    </row>
-    <row r="970">
-      <c r="A970" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B970" s="5" t="inlineStr">
-        <is>
-          <t>3001252</t>
-        </is>
-      </c>
-      <c r="C970" s="5" t="inlineStr">
-        <is>
-          <t>2012-12-05</t>
-        </is>
-      </c>
-      <c r="D970" s="5" t="inlineStr">
-        <is>
-          <t>MOUVEMENT POUR L’UNIFICATION ET LE JIHAD EN AFRIQUE DE L’OUEST (MUJAO)</t>
-        </is>
-      </c>
-      <c r="E970" s="5" t="inlineStr"/>
-      <c r="F970" s="5" t="inlineStr"/>
-      <c r="G970" s="5" t="inlineStr">
-        <is>
-          <t>Associated with The Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H970" s="5" t="inlineStr">
-        <is>
-          <t>QDe.134</t>
         </is>
       </c>
     </row>
@@ -39491,26 +39492,60 @@
       </c>
       <c r="B971" s="5" t="inlineStr">
         <is>
-          <t>3014161</t>
+          <t>3001252</t>
         </is>
       </c>
       <c r="C971" s="5" t="inlineStr">
         <is>
-          <t>2013-03-20</t>
+          <t>2012-12-05</t>
         </is>
       </c>
       <c r="D971" s="5" t="inlineStr">
         <is>
-          <t>ANSAR EDDINE</t>
-        </is>
-      </c>
-      <c r="E971" s="5" t="inlineStr">
-        <is>
-          <t>Ansar Dine</t>
-        </is>
-      </c>
+          <t>MOUVEMENT POUR L’UNIFICATION ET LE JIHAD EN AFRIQUE DE L’OUEST (MUJAO)</t>
+        </is>
+      </c>
+      <c r="E971" s="5" t="inlineStr"/>
       <c r="F971" s="5" t="inlineStr"/>
       <c r="G971" s="5" t="inlineStr">
+        <is>
+          <t>Associated with The Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H971" s="5" t="inlineStr">
+        <is>
+          <t>QDe.134</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B972" s="5" t="inlineStr">
+        <is>
+          <t>3014161</t>
+        </is>
+      </c>
+      <c r="C972" s="5" t="inlineStr">
+        <is>
+          <t>2013-03-20</t>
+        </is>
+      </c>
+      <c r="D972" s="5" t="inlineStr">
+        <is>
+          <t>ANSAR EDDINE</t>
+        </is>
+      </c>
+      <c r="E972" s="5" t="inlineStr">
+        <is>
+          <t>Ansar Dine</t>
+        </is>
+      </c>
+      <c r="F972" s="5" t="inlineStr"/>
+      <c r="G972" s="5" t="inlineStr">
         <is>
           <t>Was founded in December 2011 by Iyad ag Ghali (QDi.316). Linked to the
 Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mouvement pour
@@ -39518,47 +39553,9 @@
 Abdelmalek Droukdel (QDi.232). Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H971" s="5" t="inlineStr">
+      <c r="H972" s="5" t="inlineStr">
         <is>
           <t>QDe.135</t>
-        </is>
-      </c>
-    </row>
-    <row r="972">
-      <c r="A972" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B972" s="5" t="inlineStr">
-        <is>
-          <t>3026605</t>
-        </is>
-      </c>
-      <c r="C972" s="5" t="inlineStr">
-        <is>
-          <t>2013-10-21</t>
-        </is>
-      </c>
-      <c r="D972" s="5" t="inlineStr">
-        <is>
-          <t>MUHAMMAD JAMAL NETWORK (MJN)</t>
-        </is>
-      </c>
-      <c r="E972" s="5" t="inlineStr">
-        <is>
-          <t>Muhammad Jamal Group ; Jamal Network ; Abu Ahmed Group ; Al-Qaida in Egypt (AQE)</t>
-        </is>
-      </c>
-      <c r="F972" s="5" t="inlineStr"/>
-      <c r="G972" s="5" t="inlineStr">
-        <is>
-          <t>Terrorist and paramilitary group established by Muhammad Jamal al Kashif (QDi.318) in 2011 and linked to Al-Qaida (QDe.004), Aiman al-Zawahiri (QDi.006), and the leadership of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129) and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Funded and supported by AQAP. Multiple terrorist training camps in Egypt and Libya. Reportedly acquiring weapons, conducting training and establishing terrorist groups in the Sinai, Egypt. Training suicide bombers, foreign fighters and planning terrorist attacks in Egypt, Libya and elsewhere as of Sep. 2013. MJN members were reported to be involved in the attack on the United States Mission in Benghazi, Libya, on 11 Sep. 2012. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H972" s="5" t="inlineStr">
-        <is>
-          <t>QDe.136</t>
         </is>
       </c>
     </row>
@@ -39570,33 +39567,33 @@
       </c>
       <c r="B973" s="5" t="inlineStr">
         <is>
-          <t>6908431</t>
+          <t>3026605</t>
         </is>
       </c>
       <c r="C973" s="5" t="inlineStr">
         <is>
-          <t>2014-05-22</t>
+          <t>2013-10-21</t>
         </is>
       </c>
       <c r="D973" s="5" t="inlineStr">
         <is>
-          <t>JAMA'ATU AHLIS SUNNA LIDDA'AWATI WAL-JIHAD</t>
+          <t>MUHAMMAD JAMAL NETWORK (MJN)</t>
         </is>
       </c>
       <c r="E973" s="5" t="inlineStr">
         <is>
-          <t>Jama'atu Ahlus-Sunnah Lidda'Awati Wal Jihad ; Jama'atu Ahlus-Sunna Lidda'Awati Wal Jihad ; جماعة أهل السنة للدعوة والجهاد ; Boko Haram ; Western Education is a Sin</t>
+          <t>Muhammad Jamal Group ; Jamal Network ; Abu Ahmed Group ; Al-Qaida in Egypt (AQE)</t>
         </is>
       </c>
       <c r="F973" s="5" t="inlineStr"/>
       <c r="G973" s="5" t="inlineStr">
         <is>
-          <t>Affiliate of Al-Qaida (QDe.004), and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Associated with Jama'atu Ansarul Muslimina Fi Biladis-Sudan (Ansaru). The leader is Abubakar Shekau. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Terrorist and paramilitary group established by Muhammad Jamal al Kashif (QDi.318) in 2011 and linked to Al-Qaida (QDe.004), Aiman al-Zawahiri (QDi.006), and the leadership of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129) and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Funded and supported by AQAP. Multiple terrorist training camps in Egypt and Libya. Reportedly acquiring weapons, conducting training and establishing terrorist groups in the Sinai, Egypt. Training suicide bombers, foreign fighters and planning terrorist attacks in Egypt, Libya and elsewhere as of Sep. 2013. MJN members were reported to be involved in the attack on the United States Mission in Benghazi, Libya, on 11 Sep. 2012. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H973" s="5" t="inlineStr">
         <is>
-          <t>QDe.138</t>
+          <t>QDe.136</t>
         </is>
       </c>
     </row>
@@ -39608,66 +39605,104 @@
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>6908426</t>
+          <t>6908431</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
         <is>
-          <t>2014-06-02</t>
+          <t>2014-05-22</t>
         </is>
       </c>
       <c r="D974" s="5" t="inlineStr">
         <is>
-          <t>AL MOUAKAOUNE BIDDAM</t>
+          <t>JAMA'ATU AHLIS SUNNA LIDDA'AWATI WAL-JIHAD</t>
         </is>
       </c>
       <c r="E974" s="5" t="inlineStr">
         <is>
-          <t>Les Signataires par le Sang ; Ceux Qui Signent avec le Sang ; Those Who Sign in Blood</t>
+          <t>Jama'atu Ahlus-Sunnah Lidda'Awati Wal Jihad ; Jama'atu Ahlus-Sunna Lidda'Awati Wal Jihad ; جماعة أهل السنة للدعوة والجهاد ; Boko Haram ; Western Education is a Sin</t>
         </is>
       </c>
       <c r="F974" s="5" t="inlineStr"/>
       <c r="G974" s="5" t="inlineStr">
+        <is>
+          <t>Affiliate of Al-Qaida (QDe.004), and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Associated with Jama'atu Ansarul Muslimina Fi Biladis-Sudan (Ansaru). The leader is Abubakar Shekau. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H974" s="5" t="inlineStr">
+        <is>
+          <t>QDe.138</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B975" s="5" t="inlineStr">
+        <is>
+          <t>6908426</t>
+        </is>
+      </c>
+      <c r="C975" s="5" t="inlineStr">
+        <is>
+          <t>2014-06-02</t>
+        </is>
+      </c>
+      <c r="D975" s="5" t="inlineStr">
+        <is>
+          <t>AL MOUAKAOUNE BIDDAM</t>
+        </is>
+      </c>
+      <c r="E975" s="5" t="inlineStr">
+        <is>
+          <t>Les Signataires par le Sang ; Ceux Qui Signent avec le Sang ; Those Who Sign in Blood</t>
+        </is>
+      </c>
+      <c r="F975" s="5" t="inlineStr"/>
+      <c r="G975" s="5" t="inlineStr">
         <is>
           <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb
 (QDe.014) and led by Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara
 region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H974" s="5" t="inlineStr">
+      <c r="H975" s="5" t="inlineStr">
         <is>
           <t>QDe.139</t>
         </is>
       </c>
     </row>
-    <row r="975">
-      <c r="A975" s="5" t="inlineStr">
+    <row r="976">
+      <c r="A976" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B975" s="5" t="inlineStr">
+      <c r="B976" s="5" t="inlineStr">
         <is>
           <t>6908427</t>
         </is>
       </c>
-      <c r="C975" s="5" t="inlineStr">
+      <c r="C976" s="5" t="inlineStr">
         <is>
           <t>2014-06-02</t>
         </is>
       </c>
-      <c r="D975" s="5" t="inlineStr">
+      <c r="D976" s="5" t="inlineStr">
         <is>
           <t>AL MOULATHAMOUN</t>
         </is>
       </c>
-      <c r="E975" s="5" t="inlineStr">
+      <c r="E976" s="5" t="inlineStr">
         <is>
           <t>Les Enturbannés ; The Veiled</t>
         </is>
       </c>
-      <c r="F975" s="5" t="inlineStr"/>
-      <c r="G975" s="5" t="inlineStr">
+      <c r="F976" s="5" t="inlineStr"/>
+      <c r="G976" s="5" t="inlineStr">
         <is>
           <t>Founded in 2012 as a splinter group of the Organization of Al-Qaida in
 the Islamic Maghreb (QDe.014). On 20 Aug. 2013, Al Moulathamoun merged with the
@@ -39677,40 +39712,40 @@
 Sahel/Sahara region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H975" s="5" t="inlineStr">
+      <c r="H976" s="5" t="inlineStr">
         <is>
           <t>QDe.140</t>
         </is>
       </c>
     </row>
-    <row r="976">
-      <c r="A976" s="5" t="inlineStr">
+    <row r="977">
+      <c r="A977" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B976" s="5" t="inlineStr">
+      <c r="B977" s="5" t="inlineStr">
         <is>
           <t>6908428</t>
         </is>
       </c>
-      <c r="C976" s="5" t="inlineStr">
+      <c r="C977" s="5" t="inlineStr">
         <is>
           <t>2014-06-02</t>
         </is>
       </c>
-      <c r="D976" s="5" t="inlineStr">
+      <c r="D977" s="5" t="inlineStr">
         <is>
           <t>AL MOURABITOUN</t>
         </is>
       </c>
-      <c r="E976" s="5" t="inlineStr">
+      <c r="E977" s="5" t="inlineStr">
         <is>
           <t>Les Sentinelles ; The Sentinels</t>
         </is>
       </c>
-      <c r="F976" s="5" t="inlineStr"/>
-      <c r="G976" s="5" t="inlineStr">
+      <c r="F977" s="5" t="inlineStr"/>
+      <c r="G977" s="5" t="inlineStr">
         <is>
           <t>Founded on 20 Aug. 2013 as result of a merger between Al Moulathamoun
 (QDe.140) and the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO)
@@ -39718,40 +39753,40 @@
 and led by Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H976" s="5" t="inlineStr">
+      <c r="H977" s="5" t="inlineStr">
         <is>
           <t>QDe.141</t>
         </is>
       </c>
     </row>
-    <row r="977">
-      <c r="A977" s="5" t="inlineStr">
+    <row r="978">
+      <c r="A978" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B977" s="5" t="inlineStr">
+      <c r="B978" s="5" t="inlineStr">
         <is>
           <t>6908430</t>
         </is>
       </c>
-      <c r="C977" s="5" t="inlineStr">
+      <c r="C978" s="5" t="inlineStr">
         <is>
           <t>2014-06-26</t>
         </is>
       </c>
-      <c r="D977" s="5" t="inlineStr">
+      <c r="D978" s="5" t="inlineStr">
         <is>
           <t>ANSARUL MUSLIMINA FI BILADIS SUDAN</t>
         </is>
       </c>
-      <c r="E977" s="5" t="inlineStr">
+      <c r="E978" s="5" t="inlineStr">
         <is>
           <t>Ansaru ; Jama'atu Ansaril Muslimina fi Biladis Sudan (JAMBS) ; Jama’atu Ansarul Muslimina fi Biladis-Sudan (JAMBS) ; Jamma’atu Ansarul Muslimina fi Biladis-Sudan (JAMBS) ; Vanguards for the Protection of Muslims in Black Africa ; Vanguard for the Protection of Muslims in Black Africa</t>
         </is>
       </c>
-      <c r="F977" s="5" t="inlineStr"/>
-      <c r="G977" s="5" t="inlineStr">
+      <c r="F978" s="5" t="inlineStr"/>
+      <c r="G978" s="5" t="inlineStr">
         <is>
           <t>Terrorist and paramilitary group established in 2012 and operating in
 Nigeria. Associated with the Organization of Al-Qaida in the Islamic Maghreb (AQIM)
@@ -39759,118 +39794,118 @@
 Abubakar Mohammed Shekau (QDi322). Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H977" s="5" t="inlineStr">
+      <c r="H978" s="5" t="inlineStr">
         <is>
           <t>QDe.142</t>
         </is>
       </c>
     </row>
-    <row r="978">
-      <c r="A978" s="5" t="inlineStr">
+    <row r="979">
+      <c r="A979" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B978" s="5" t="inlineStr">
+      <c r="B979" s="5" t="inlineStr">
         <is>
           <t>6908410</t>
         </is>
       </c>
-      <c r="C978" s="5" t="inlineStr">
+      <c r="C979" s="5" t="inlineStr">
         <is>
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="D978" s="5" t="inlineStr">
+      <c r="D979" s="5" t="inlineStr">
         <is>
           <t>ANSAR AL-SHARI’A IN TUNISIA (AAS-T)</t>
         </is>
       </c>
-      <c r="E978" s="5" t="inlineStr">
+      <c r="E979" s="5" t="inlineStr">
         <is>
           <t>Ansar al-Sharia in Tunisia ; Ansar al-Shari’ah in Tunisia ; Ansar al-Shari’ah ; Ansar al-Sharia ; Supporters of Islamic Law ; Al-Qayrawan Media Foundation</t>
         </is>
       </c>
-      <c r="F978" s="5" t="inlineStr"/>
-      <c r="G978" s="5" t="inlineStr">
+      <c r="F979" s="5" t="inlineStr"/>
+      <c r="G979" s="5" t="inlineStr">
         <is>
           <t>A Tunisian armed group with links to the Organization of Al-Qaida in the
 Islamic Maghreb (QDe.014). The leader is Seifallah ben Hassine (QDi.333). Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H978" s="5" t="inlineStr">
+      <c r="H979" s="5" t="inlineStr">
         <is>
           <t>QDe.143</t>
         </is>
       </c>
     </row>
-    <row r="979">
-      <c r="A979" s="5" t="inlineStr">
+    <row r="980">
+      <c r="A980" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B979" s="5" t="inlineStr">
+      <c r="B980" s="5" t="inlineStr">
         <is>
           <t>6908409</t>
         </is>
       </c>
-      <c r="C979" s="5" t="inlineStr">
+      <c r="C980" s="5" t="inlineStr">
         <is>
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="D979" s="5" t="inlineStr">
+      <c r="D980" s="5" t="inlineStr">
         <is>
           <t>ABDALLAH AZZAM BRIGADES (AAB)</t>
         </is>
       </c>
-      <c r="E979" s="5" t="inlineStr">
+      <c r="E980" s="5" t="inlineStr">
         <is>
           <t>Abdullah Azzam Brigades ; Ziyad al-Jarrah Battalions of the Abdallah Azzam Brigades ; Yusuf al-'Uyayri Battalions of the Abdallah Azzam Brigades</t>
         </is>
       </c>
-      <c r="F979" s="5" t="inlineStr"/>
-      <c r="G979" s="5" t="inlineStr">
+      <c r="F980" s="5" t="inlineStr"/>
+      <c r="G980" s="5" t="inlineStr">
         <is>
           <t>An armed group that has carried out joint attacks with Al-Nusrah Front
 for the People of the Levant (formerly listed).  Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H979" s="5" t="inlineStr">
+      <c r="H980" s="5" t="inlineStr">
         <is>
           <t>QDe.144</t>
         </is>
       </c>
     </row>
-    <row r="980">
-      <c r="A980" s="5" t="inlineStr">
+    <row r="981">
+      <c r="A981" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B980" s="5" t="inlineStr">
+      <c r="B981" s="5" t="inlineStr">
         <is>
           <t>6908437</t>
         </is>
       </c>
-      <c r="C980" s="5" t="inlineStr">
+      <c r="C981" s="5" t="inlineStr">
         <is>
           <t>2014-11-19</t>
         </is>
       </c>
-      <c r="D980" s="5" t="inlineStr">
+      <c r="D981" s="5" t="inlineStr">
         <is>
           <t>ANSAR AL CHARIA DERNA</t>
         </is>
       </c>
-      <c r="E980" s="5" t="inlineStr">
+      <c r="E981" s="5" t="inlineStr">
         <is>
           <t>Ansar al-Charia Derna ; Ansar al-Sharia Derna ; أنصار الشريعة (Ansar al Charia) ; Ansar al-Sharia ; Ansar al Sharia</t>
         </is>
       </c>
-      <c r="F980" s="5" t="inlineStr"/>
-      <c r="G980" s="5" t="inlineStr">
+      <c r="F981" s="5" t="inlineStr"/>
+      <c r="G981" s="5" t="inlineStr">
         <is>
           <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb
 (QDe.014), Ansar al-Shari’a in Tunisia (AAS-T) (QDe.143) and Ansar al Charia Benghazi
@@ -39878,40 +39913,40 @@
 Iraq. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H980" s="5" t="inlineStr">
+      <c r="H981" s="5" t="inlineStr">
         <is>
           <t>QDe.145</t>
         </is>
       </c>
     </row>
-    <row r="981">
-      <c r="A981" s="5" t="inlineStr">
+    <row r="982">
+      <c r="A982" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B981" s="5" t="inlineStr">
+      <c r="B982" s="5" t="inlineStr">
         <is>
           <t>6908438</t>
         </is>
       </c>
-      <c r="C981" s="5" t="inlineStr">
+      <c r="C982" s="5" t="inlineStr">
         <is>
           <t>2014-11-19</t>
         </is>
       </c>
-      <c r="D981" s="5" t="inlineStr">
+      <c r="D982" s="5" t="inlineStr">
         <is>
           <t>ANSAR AL CHARIA BENGHAZI</t>
         </is>
       </c>
-      <c r="E981" s="5" t="inlineStr">
+      <c r="E982" s="5" t="inlineStr">
         <is>
           <t>نصار الشريعة (Ansar al Charia) ; Ansar al-Charia ; Ansar al-Sharia ; Ansar al-Charia Benghazi ; Ansar al-Sharia Benghazi ; أنصار الشريعة بليبيا (Ansar al Charia in Libya (ASL)) ; كتيبة أنصار الشريعة (Katibat Ansar al Charia) ; Ansar al Sharia</t>
         </is>
       </c>
-      <c r="F981" s="5" t="inlineStr"/>
-      <c r="G981" s="5" t="inlineStr">
+      <c r="F982" s="5" t="inlineStr"/>
+      <c r="G982" s="5" t="inlineStr">
         <is>
           <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb
 (QDe.014), Al Mourabitoun (QDe.141), Ansar al-Shari’a in Tunisia (AAS-T) (QDe.143), and
@@ -39922,40 +39957,40 @@
  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H981" s="5" t="inlineStr">
+      <c r="H982" s="5" t="inlineStr">
         <is>
           <t>QDe.146</t>
         </is>
       </c>
     </row>
-    <row r="982">
-      <c r="A982" s="5" t="inlineStr">
+    <row r="983">
+      <c r="A983" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B982" s="5" t="inlineStr">
+      <c r="B983" s="5" t="inlineStr">
         <is>
           <t>6908448</t>
         </is>
       </c>
-      <c r="C982" s="5" t="inlineStr">
+      <c r="C983" s="5" t="inlineStr">
         <is>
           <t>2015-03-13</t>
         </is>
       </c>
-      <c r="D982" s="5" t="inlineStr">
+      <c r="D983" s="5" t="inlineStr">
         <is>
           <t>HILAL AHMAR SOCIETY INDONESIA (HASI)</t>
         </is>
       </c>
-      <c r="E982" s="5" t="inlineStr">
+      <c r="E983" s="5" t="inlineStr">
         <is>
           <t>Yayasan Hilal Ahmar ; Indonesia Hilal Ahmar Society for Syria</t>
         </is>
       </c>
-      <c r="F982" s="5" t="inlineStr"/>
-      <c r="G982" s="5" t="inlineStr">
+      <c r="F983" s="5" t="inlineStr"/>
+      <c r="G983" s="5" t="inlineStr">
         <is>
           <t>Ostensibly humanitarian wing of Jemaah Islamiyah (QDe.092). Operates in
                 Lampung, Jakarta, Semarang, Yogyakarta, Solo, Surabaya and Makassar, Indonesia. Has
@@ -39964,40 +39999,40 @@
                 Red Cross and Red Crescent Societies (IFRC). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H982" s="5" t="inlineStr">
+      <c r="H983" s="5" t="inlineStr">
         <is>
           <t>QDe.147</t>
         </is>
       </c>
     </row>
-    <row r="983">
-      <c r="A983" s="5" t="inlineStr">
+    <row r="984">
+      <c r="A984" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B983" s="5" t="inlineStr">
+      <c r="B984" s="5" t="inlineStr">
         <is>
           <t>6908463</t>
         </is>
       </c>
-      <c r="C983" s="5" t="inlineStr">
+      <c r="C984" s="5" t="inlineStr">
         <is>
           <t>2015-08-06</t>
         </is>
       </c>
-      <c r="D983" s="5" t="inlineStr">
+      <c r="D984" s="5" t="inlineStr">
         <is>
           <t>THE ARMY OF EMIGRANTS AND SUPPORTERS</t>
         </is>
       </c>
-      <c r="E983" s="5" t="inlineStr">
+      <c r="E984" s="5" t="inlineStr">
         <is>
           <t>Battalion of Emigrants and Supporters ; Army of Emigrants and Supporters organization ; Battalion of Emigrants and Ansar ; Jaysh al-Muhajirin wal-Ansar (JAMWA)</t>
         </is>
       </c>
-      <c r="F983" s="5" t="inlineStr"/>
-      <c r="G983" s="5" t="inlineStr">
+      <c r="F984" s="5" t="inlineStr"/>
+      <c r="G984" s="5" t="inlineStr">
         <is>
           <t>Established by foreign terrorist fighters in 2013. Location: Syrian Arab
                 Republic. Affiliated with Islamic State in Iraq and the Levant, listed as Al-Qaida
@@ -40005,47 +40040,9 @@
                 (formerly listed). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H983" s="5" t="inlineStr">
+      <c r="H984" s="5" t="inlineStr">
         <is>
           <t>QDe.148</t>
-        </is>
-      </c>
-    </row>
-    <row r="984">
-      <c r="A984" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B984" s="5" t="inlineStr">
-        <is>
-          <t>6908521</t>
-        </is>
-      </c>
-      <c r="C984" s="5" t="inlineStr">
-        <is>
-          <t>2016-02-29</t>
-        </is>
-      </c>
-      <c r="D984" s="5" t="inlineStr">
-        <is>
-          <t>HARAKAT SHAM AL-ISLAM</t>
-        </is>
-      </c>
-      <c r="E984" s="5" t="inlineStr">
-        <is>
-          <t>Haraket Sham al-Islam ; Sham al-Islam ; Sham al-Islam Movement</t>
-        </is>
-      </c>
-      <c r="F984" s="5" t="inlineStr"/>
-      <c r="G984" s="5" t="inlineStr">
-        <is>
-          <t>Moroccan-led terrorist organization formed in Aug. 2013 and operating in Syrian Arab Republic. Principally composed of foreign terrorist fighters and associated with AI-Nusrah Front for the People of the Levant (formerly listed).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H984" s="5" t="inlineStr">
-        <is>
-          <t>QDe.149</t>
         </is>
       </c>
     </row>
@@ -40057,112 +40054,112 @@
       </c>
       <c r="B985" s="5" t="inlineStr">
         <is>
-          <t>6908485</t>
+          <t>6908521</t>
         </is>
       </c>
       <c r="C985" s="5" t="inlineStr">
         <is>
-          <t>2015-09-29</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="D985" s="5" t="inlineStr">
         <is>
-          <t>MUJAHIDIN INDONESIAN TIMUR (MIT)</t>
+          <t>HARAKAT SHAM AL-ISLAM</t>
         </is>
       </c>
       <c r="E985" s="5" t="inlineStr">
         <is>
-          <t>Mujahidin of Eastern Indonesia ; East Indonesia Mujahideen ; Mujahidin Indonesia Timor ; Mujahidin Indonesia Barat (MIB) ; Mujahidin of Western Indonesia</t>
+          <t>Haraket Sham al-Islam ; Sham al-Islam ; Sham al-Islam Movement</t>
         </is>
       </c>
       <c r="F985" s="5" t="inlineStr"/>
       <c r="G985" s="5" t="inlineStr">
         <is>
+          <t>Moroccan-led terrorist organization formed in Aug. 2013 and operating in Syrian Arab Republic. Principally composed of foreign terrorist fighters and associated with AI-Nusrah Front for the People of the Levant (formerly listed).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H985" s="5" t="inlineStr">
+        <is>
+          <t>QDe.149</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B986" s="5" t="inlineStr">
+        <is>
+          <t>6908485</t>
+        </is>
+      </c>
+      <c r="C986" s="5" t="inlineStr">
+        <is>
+          <t>2015-09-29</t>
+        </is>
+      </c>
+      <c r="D986" s="5" t="inlineStr">
+        <is>
+          <t>MUJAHIDIN INDONESIAN TIMUR (MIT)</t>
+        </is>
+      </c>
+      <c r="E986" s="5" t="inlineStr">
+        <is>
+          <t>Mujahidin of Eastern Indonesia ; East Indonesia Mujahideen ; Mujahidin Indonesia Timor ; Mujahidin Indonesia Barat (MIB) ; Mujahidin of Western Indonesia</t>
+        </is>
+      </c>
+      <c r="F986" s="5" t="inlineStr"/>
+      <c r="G986" s="5" t="inlineStr">
+        <is>
           <t>Terrorist group linked to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), Jemaah Islamiyah (JI) (QDe.092), and Jemmah Anshorut Tauhid (JAT) (QDe.133). Operates in Java and Sulawesi, Indonesia and also active in Indonesia’s eastern provinces. Its former leader was Abu Wardah, a.k.a. Santoso (deceased). 
 Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H985" s="5" t="inlineStr">
+      <c r="H986" s="5" t="inlineStr">
         <is>
           <t>QDe.150</t>
         </is>
       </c>
     </row>
-    <row r="986">
-      <c r="A986" s="5" t="inlineStr">
+    <row r="987">
+      <c r="A987" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B986" s="5" t="inlineStr">
+      <c r="B987" s="5" t="inlineStr">
         <is>
           <t>6908486</t>
         </is>
       </c>
-      <c r="C986" s="5" t="inlineStr">
+      <c r="C987" s="5" t="inlineStr">
         <is>
           <t>2015-09-29</t>
         </is>
       </c>
-      <c r="D986" s="5" t="inlineStr">
+      <c r="D987" s="5" t="inlineStr">
         <is>
           <t>JUND AL-KHILAFAH IN ALGERIA (JAK-A)</t>
         </is>
       </c>
-      <c r="E986" s="5" t="inlineStr">
+      <c r="E987" s="5" t="inlineStr">
         <is>
           <t>Jund al Khalifa ; Jund al-Khilafah fi Ard al-Jaza’ir ; Jund al-Khalifa fi Ard al-Jazayer ; Soldiers of the Caliphate in Algeria ; Soldiers of the Caliphate of Algeria ; Soldiers of the Caliphate in the Land of Algeria</t>
         </is>
       </c>
-      <c r="F986" s="5" t="inlineStr"/>
-      <c r="G986" s="5" t="inlineStr">
+      <c r="F987" s="5" t="inlineStr"/>
+      <c r="G987" s="5" t="inlineStr">
         <is>
           <t>Emerged on 13 Sep. 2014. Most known for its abduction and subsequent beheading
                 of French national Herve Gourdel. Claimed responsibility for attacking police and
                 gendarmes in Algeria and continued planning future attacks. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H986" s="5" t="inlineStr">
+      <c r="H987" s="5" t="inlineStr">
         <is>
           <t>QDe.151</t>
-        </is>
-      </c>
-    </row>
-    <row r="987">
-      <c r="A987" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B987" s="5" t="inlineStr">
-        <is>
-          <t>6908599</t>
-        </is>
-      </c>
-      <c r="C987" s="5" t="inlineStr">
-        <is>
-          <t>2017-07-06</t>
-        </is>
-      </c>
-      <c r="D987" s="5" t="inlineStr">
-        <is>
-          <t>JAMAAT-UL-AHRAR (JuA)</t>
-        </is>
-      </c>
-      <c r="E987" s="5" t="inlineStr">
-        <is>
-          <t>Jamaat-e-Ahrar ; Tehrik-e Taliban Pakistan Jamaat ul Ahrar ; Ahrar-ul-Hind</t>
-        </is>
-      </c>
-      <c r="F987" s="5" t="inlineStr"/>
-      <c r="G987" s="5" t="inlineStr">
-        <is>
-          <t>Splinter group of the Tehrik-e Taliban Pakistan (QDe.132). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Formed in Aug. 2014 in Mohmand Agency, Pakistan. Operates from Nangarhar Province, Afghanistan and Pakistan-Afghanistan border region. Banned in Pakistan on 21 Nov. 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H987" s="5" t="inlineStr">
-        <is>
-          <t>QDe.152</t>
         </is>
       </c>
     </row>
@@ -40174,33 +40171,33 @@
       </c>
       <c r="B988" s="5" t="inlineStr">
         <is>
-          <t>6908604</t>
+          <t>6908599</t>
         </is>
       </c>
       <c r="C988" s="5" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="D988" s="5" t="inlineStr">
         <is>
-          <t>HANIFA MONEY EXCHANGE OFFICE (BRANCH LOCATED IN ALBU KAMAL, SYRIAN ARAB REPUBLIC)</t>
+          <t>JAMAAT-UL-AHRAR (JuA)</t>
         </is>
       </c>
       <c r="E988" s="5" t="inlineStr">
         <is>
-          <t>Hanifah Currency Exchange ; Hanifeh Exchange ; Hanifa Exchange ; Hunaifa Office ; Hanifah Exchange Company ; Hanifa Money Exchange Office</t>
+          <t>Jamaat-e-Ahrar ; Tehrik-e Taliban Pakistan Jamaat ul Ahrar ; Ahrar-ul-Hind</t>
         </is>
       </c>
       <c r="F988" s="5" t="inlineStr"/>
       <c r="G988" s="5" t="inlineStr">
         <is>
-          <t>Money exchange business in Albu Kamal (Al-Bukamal), Syrian Arab Republic, facilitating the movement of funds on behalf of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Used exclusively for ISIL-related transactions. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Splinter group of the Tehrik-e Taliban Pakistan (QDe.132). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Formed in Aug. 2014 in Mohmand Agency, Pakistan. Operates from Nangarhar Province, Afghanistan and Pakistan-Afghanistan border region. Banned in Pakistan on 21 Nov. 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H988" s="5" t="inlineStr">
         <is>
-          <t>QDe.153</t>
+          <t>QDe.152</t>
         </is>
       </c>
     </row>
@@ -40212,7 +40209,7 @@
       </c>
       <c r="B989" s="5" t="inlineStr">
         <is>
-          <t>6908605</t>
+          <t>6908604</t>
         </is>
       </c>
       <c r="C989" s="5" t="inlineStr">
@@ -40222,23 +40219,23 @@
       </c>
       <c r="D989" s="5" t="inlineStr">
         <is>
-          <t>SELSELAT AL-THAHAB</t>
+          <t>HANIFA MONEY EXCHANGE OFFICE (BRANCH LOCATED IN ALBU KAMAL, SYRIAN ARAB REPUBLIC)</t>
         </is>
       </c>
       <c r="E989" s="5" t="inlineStr">
         <is>
-          <t>Silsilet al Thahab ; Selselat al Thahab For Money Exchange ; Silsilat Money Exchange Company ; Silsilah Money Exchange Company ; Al Silsilah al Dhahaba ; Silsalat al Dhab</t>
+          <t>Hanifah Currency Exchange ; Hanifeh Exchange ; Hanifa Exchange ; Hunaifa Office ; Hanifah Exchange Company ; Hanifa Money Exchange Office</t>
         </is>
       </c>
       <c r="F989" s="5" t="inlineStr"/>
       <c r="G989" s="5" t="inlineStr">
         <is>
-          <t>Money exchange business facilitating the movement of funds on behalf of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), as of Apr. 2016. Conducted over one hundred financial transfers into ISIL-controlled territory. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Money exchange business in Albu Kamal (Al-Bukamal), Syrian Arab Republic, facilitating the movement of funds on behalf of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Used exclusively for ISIL-related transactions. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H989" s="5" t="inlineStr">
         <is>
-          <t>QDe.154</t>
+          <t>QDe.153</t>
         </is>
       </c>
     </row>
@@ -40250,7 +40247,7 @@
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>6908606</t>
+          <t>6908605</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
@@ -40260,23 +40257,23 @@
       </c>
       <c r="D990" s="5" t="inlineStr">
         <is>
-          <t>Jaysh Khalid Ibn al Waleed</t>
+          <t>SELSELAT AL-THAHAB</t>
         </is>
       </c>
       <c r="E990" s="5" t="inlineStr">
         <is>
-          <t>Khalid ibn al-Walid Army ; Liwa Shuhada al-Yarmouk ; Harakat al-Muthanna al-Islamia</t>
+          <t>Silsilet al Thahab ; Selselat al Thahab For Money Exchange ; Silsilat Money Exchange Company ; Silsilah Money Exchange Company ; Al Silsilah al Dhahaba ; Silsalat al Dhab</t>
         </is>
       </c>
       <c r="F990" s="5" t="inlineStr"/>
       <c r="G990" s="5" t="inlineStr">
         <is>
-          <t>Joined the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in May 2015. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Money exchange business facilitating the movement of funds on behalf of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), as of Apr. 2016. Conducted over one hundred financial transfers into ISIL-controlled territory. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H990" s="5" t="inlineStr">
         <is>
-          <t>QDe.155</t>
+          <t>QDe.154</t>
         </is>
       </c>
     </row>
@@ -40288,7 +40285,7 @@
       </c>
       <c r="B991" s="5" t="inlineStr">
         <is>
-          <t>6908607</t>
+          <t>6908606</t>
         </is>
       </c>
       <c r="C991" s="5" t="inlineStr">
@@ -40298,23 +40295,23 @@
       </c>
       <c r="D991" s="5" t="inlineStr">
         <is>
-          <t>JUND AL AQSA</t>
+          <t>Jaysh Khalid Ibn al Waleed</t>
         </is>
       </c>
       <c r="E991" s="5" t="inlineStr">
         <is>
-          <t>The Soldiers of Aqsa ; Soldiers of Aqsa ; Sarayat Al Quds</t>
+          <t>Khalid ibn al-Walid Army ; Liwa Shuhada al-Yarmouk ; Harakat al-Muthanna al-Islamia</t>
         </is>
       </c>
       <c r="F991" s="5" t="inlineStr"/>
       <c r="G991" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Al Nusrah Front for the People of the Levant (formerly listed). Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Joined the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in May 2015. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H991" s="5" t="inlineStr">
         <is>
-          <t>QDe.156</t>
+          <t>QDe.155</t>
         </is>
       </c>
     </row>
@@ -40326,73 +40323,73 @@
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>6908660</t>
+          <t>6908607</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
         <is>
-          <t>2018-03-06</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="D992" s="5" t="inlineStr">
         <is>
-          <t>AL-KAWTHAR MONEY EXCHANGE</t>
+          <t>JUND AL AQSA</t>
         </is>
       </c>
       <c r="E992" s="5" t="inlineStr">
         <is>
-          <t>Al Kawthar Co. ; Al Kawthar Company ; Al-Kawthar Hawala</t>
+          <t>The Soldiers of Aqsa ; Soldiers of Aqsa ; Sarayat Al Quds</t>
         </is>
       </c>
       <c r="F992" s="5" t="inlineStr"/>
       <c r="G992" s="5" t="inlineStr">
+        <is>
+          <t>Associated with the Al Nusrah Front for the People of the Levant (formerly listed). Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H992" s="5" t="inlineStr">
+        <is>
+          <t>QDe.156</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B993" s="5" t="inlineStr">
+        <is>
+          <t>6908660</t>
+        </is>
+      </c>
+      <c r="C993" s="5" t="inlineStr">
+        <is>
+          <t>2018-03-06</t>
+        </is>
+      </c>
+      <c r="D993" s="5" t="inlineStr">
+        <is>
+          <t>AL-KAWTHAR MONEY EXCHANGE</t>
+        </is>
+      </c>
+      <c r="E993" s="5" t="inlineStr">
+        <is>
+          <t>Al Kawthar Co. ; Al Kawthar Company ; Al-Kawthar Hawala</t>
+        </is>
+      </c>
+      <c r="F993" s="5" t="inlineStr"/>
+      <c r="G993" s="5" t="inlineStr">
         <is>
           <t>Money exchange business and owned by Umar Mahmud Irhayyim al-Kubaysi (QDi.412) as of mid-2016. Facilitated financial transactions on behalf of companies associated with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Established in 2000 under License number 202, issued on 17 May 2000, and since withdrawn. 
 Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. 
  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H992" s="5" t="inlineStr">
+      <c r="H993" s="5" t="inlineStr">
         <is>
           <t>QDe.157</t>
-        </is>
-      </c>
-    </row>
-    <row r="993">
-      <c r="A993" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B993" s="5" t="inlineStr">
-        <is>
-          <t>6908669</t>
-        </is>
-      </c>
-      <c r="C993" s="5" t="inlineStr">
-        <is>
-          <t>2018-03-29</t>
-        </is>
-      </c>
-      <c r="D993" s="5" t="inlineStr">
-        <is>
-          <t>KHATIBA IMAM AL-BUKHARI (KIB)</t>
-        </is>
-      </c>
-      <c r="E993" s="5" t="inlineStr">
-        <is>
-          <t>Khataib al-Imam al-Bukhari</t>
-        </is>
-      </c>
-      <c r="F993" s="5" t="inlineStr"/>
-      <c r="G993" s="5" t="inlineStr">
-        <is>
-          <t>Associated with Al-Nusrah Front for the People of the Levant (formerly listed). Committed terrorist attacks in the Syrian Arab Republic. Since 2016 redeployed to Northern Afghanistan to project attacks against Central Asia countries. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H993" s="5" t="inlineStr">
-        <is>
-          <t>QDe.158</t>
         </is>
       </c>
     </row>
@@ -40404,69 +40401,69 @@
       </c>
       <c r="B994" s="5" t="inlineStr">
         <is>
-          <t>6908726</t>
+          <t>6908669</t>
         </is>
       </c>
       <c r="C994" s="5" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2018-03-29</t>
         </is>
       </c>
       <c r="D994" s="5" t="inlineStr">
         <is>
-          <t>JAMA'A NUSRAT UL-ISLAM WA AL-MUSLIMIN (JNIM)</t>
-        </is>
-      </c>
-      <c r="E994" s="5" t="inlineStr"/>
+          <t>KHATIBA IMAM AL-BUKHARI (KIB)</t>
+        </is>
+      </c>
+      <c r="E994" s="5" t="inlineStr">
+        <is>
+          <t>Khataib al-Imam al-Bukhari</t>
+        </is>
+      </c>
       <c r="F994" s="5" t="inlineStr"/>
       <c r="G994" s="5" t="inlineStr">
+        <is>
+          <t>Associated with Al-Nusrah Front for the People of the Levant (formerly listed). Committed terrorist attacks in the Syrian Arab Republic. Since 2016 redeployed to Northern Afghanistan to project attacks against Central Asia countries. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H994" s="5" t="inlineStr">
+        <is>
+          <t>QDe.158</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B995" s="5" t="inlineStr">
+        <is>
+          <t>6908726</t>
+        </is>
+      </c>
+      <c r="C995" s="5" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="D995" s="5" t="inlineStr">
+        <is>
+          <t>JAMA'A NUSRAT UL-ISLAM WA AL-MUSLIMIN (JNIM)</t>
+        </is>
+      </c>
+      <c r="E995" s="5" t="inlineStr"/>
+      <c r="F995" s="5" t="inlineStr"/>
+      <c r="G995" s="5" t="inlineStr">
         <is>
           <t>Associated with Al-Qaida (QDe.004), the Organization of Al-Qaida in the Islamic Maghreb (QDe.014), Ansar Eddine (QDe.135) and Al-Mourabitoun (QDe.141). Operations in Mali and Burkina Faso. 
 Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. 
  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H994" s="5" t="inlineStr">
+      <c r="H995" s="5" t="inlineStr">
         <is>
           <t>QDe.159</t>
-        </is>
-      </c>
-    </row>
-    <row r="995">
-      <c r="A995" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B995" s="5" t="inlineStr">
-        <is>
-          <t>6908768</t>
-        </is>
-      </c>
-      <c r="C995" s="5" t="inlineStr">
-        <is>
-          <t>2019-03-22</t>
-        </is>
-      </c>
-      <c r="D995" s="5" t="inlineStr">
-        <is>
-          <t>TARIQ GIDAR GROUP (TGG)</t>
-        </is>
-      </c>
-      <c r="E995" s="5" t="inlineStr">
-        <is>
-          <t>TEHRIK-E-TALIBAN-TARIQ GIDAR GROUP ; TTP-TARIQ GIDAR GROUP ; TEHREEK-I-TALIBAN PAKISTAN GEEDAR GROUP ; TTP GEEDAR GROUP ; TARIQ GEEDAR GROUP ; COMMANDER TARIQ AFRIDI GROUP ; TARIQ AFRIDI GROUP ; TARIQ GIDAR AFRIDI GROUP ; THE ASIAN TIGERS</t>
-        </is>
-      </c>
-      <c r="F995" s="5" t="inlineStr"/>
-      <c r="G995" s="5" t="inlineStr">
-        <is>
-          <t>Splinter group of Tehrik-e Taliban Pakistan (TTP) (QDe.132). The group was formed in Darra Adam Khel, Federally Administered Tribal Area (FATA), Pakistan, in 2007.       INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H995" s="5" t="inlineStr">
-        <is>
-          <t>QDe.160</t>
         </is>
       </c>
     </row>
@@ -40478,26 +40475,64 @@
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>6908777</t>
+          <t>6908768</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
         <is>
-          <t>2019-05-14</t>
+          <t>2019-03-22</t>
         </is>
       </c>
       <c r="D996" s="5" t="inlineStr">
         <is>
-          <t>ISLAMIC STATE IN IRAQ AND THE LEVANT - KHORASAN (ISIL-K)</t>
+          <t>TARIQ GIDAR GROUP (TGG)</t>
         </is>
       </c>
       <c r="E996" s="5" t="inlineStr">
         <is>
-          <t>ISIL KHORASAN ; ISLAMIC STATE’S KHORASAN PROVINCE ; ISIS WILAYAT KHORASAN ; ISIL’S SOUTH ASIA BRANCH ; SOUTH ASIAN CHAPTER OF ISIL ; The Islamic State of Iraq and ash-Sham—Khorasan Province ; The Islamic State of Iraq and Syria—Khorasan ; Islamic State of Iraq and Levant in Khorasan Province ; Islamic State Khurasan ; ISIS-K ; ISISK ; IS-Khorasan</t>
+          <t>TEHRIK-E-TALIBAN-TARIQ GIDAR GROUP ; TTP-TARIQ GIDAR GROUP ; TEHREEK-I-TALIBAN PAKISTAN GEEDAR GROUP ; TTP GEEDAR GROUP ; TARIQ GEEDAR GROUP ; COMMANDER TARIQ AFRIDI GROUP ; TARIQ AFRIDI GROUP ; TARIQ GIDAR AFRIDI GROUP ; THE ASIAN TIGERS</t>
         </is>
       </c>
       <c r="F996" s="5" t="inlineStr"/>
       <c r="G996" s="5" t="inlineStr">
+        <is>
+          <t>Splinter group of Tehrik-e Taliban Pakistan (TTP) (QDe.132). The group was formed in Darra Adam Khel, Federally Administered Tribal Area (FATA), Pakistan, in 2007.       INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H996" s="5" t="inlineStr">
+        <is>
+          <t>QDe.160</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B997" s="5" t="inlineStr">
+        <is>
+          <t>6908777</t>
+        </is>
+      </c>
+      <c r="C997" s="5" t="inlineStr">
+        <is>
+          <t>2019-05-14</t>
+        </is>
+      </c>
+      <c r="D997" s="5" t="inlineStr">
+        <is>
+          <t>ISLAMIC STATE IN IRAQ AND THE LEVANT - KHORASAN (ISIL-K)</t>
+        </is>
+      </c>
+      <c r="E997" s="5" t="inlineStr">
+        <is>
+          <t>ISIL KHORASAN ; ISLAMIC STATE’S KHORASAN PROVINCE ; ISIS WILAYAT KHORASAN ; ISIL’S SOUTH ASIA BRANCH ; SOUTH ASIAN CHAPTER OF ISIL ; The Islamic State of Iraq and ash-Sham—Khorasan Province ; The Islamic State of Iraq and Syria—Khorasan ; Islamic State of Iraq and Levant in Khorasan Province ; Islamic State Khurasan ; ISIS-K ; ISISK ; IS-Khorasan</t>
+        </is>
+      </c>
+      <c r="F997" s="5" t="inlineStr"/>
+      <c r="G997" s="5" t="inlineStr">
         <is>
           <t>Islamic State of Iraq and the Levant - Khorasan (ISIL - K) was formed on
                 January 10, 2015 by a former Tehrik-e Taliban Pakistan (TTP) (QDe.132) commander and
@@ -40507,47 +40542,9 @@
                 Pakistan.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H996" s="5" t="inlineStr">
+      <c r="H997" s="5" t="inlineStr">
         <is>
           <t>QDe.161</t>
-        </is>
-      </c>
-    </row>
-    <row r="997">
-      <c r="A997" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B997" s="5" t="inlineStr">
-        <is>
-          <t>6908802</t>
-        </is>
-      </c>
-      <c r="C997" s="5" t="inlineStr">
-        <is>
-          <t>2020-02-23</t>
-        </is>
-      </c>
-      <c r="D997" s="5" t="inlineStr">
-        <is>
-          <t>ISLAMIC STATE WEST AFRICA PROVINCE (ISWAP)</t>
-        </is>
-      </c>
-      <c r="E997" s="5" t="inlineStr">
-        <is>
-          <t>Islamic State in Iraq and the Levant – West Africa (ISIL-WA) ; Islamic State of Iraq and Syria – West Africa (ISIS-WA) ; Islamic State of Iraq and Syria West Africa Province (ISISWAP) ; Islamic State of Iraq and the Levant – West Africa</t>
-        </is>
-      </c>
-      <c r="F997" s="5" t="inlineStr"/>
-      <c r="G997" s="5" t="inlineStr">
-        <is>
-          <t>Associated with the Islamic State in Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). Formed in March 2015 by Abubakar Shekau (QDi.322). Splinter group of Jama'atu Ahlis Sunna Lidda'Awati Wal-Jihad (Boko Haram) (QDe.138). Committed terrorist attacks in Nigeria.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H997" s="5" t="inlineStr">
-        <is>
-          <t>QDe.162</t>
         </is>
       </c>
     </row>
@@ -40559,7 +40556,7 @@
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>6908803</t>
+          <t>6908802</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
@@ -40569,23 +40566,23 @@
       </c>
       <c r="D998" s="5" t="inlineStr">
         <is>
-          <t>ISLAMIC STATE IN THE GREATER SAHARA (ISGS)</t>
+          <t>ISLAMIC STATE WEST AFRICA PROVINCE (ISWAP)</t>
         </is>
       </c>
       <c r="E998" s="5" t="inlineStr">
         <is>
-          <t>Islamic State in Iraq and Syria – Greater Sahara (ISIS-GS) ; Islamic State of Iraq and Syria – Greater Sahara (ISIS-GS) ; Islamic State of Iraq and the Levant - Greater Sahara (ISIL-GS) ; Islamic State of the Greater Sahel ; ISIS in the Greater Sahel ; ISIS in the Greater Sahara ; ISIS in the Islamic Sahel</t>
+          <t>Islamic State in Iraq and the Levant – West Africa (ISIL-WA) ; Islamic State of Iraq and Syria – West Africa (ISIS-WA) ; Islamic State of Iraq and Syria West Africa Province (ISISWAP) ; Islamic State of Iraq and the Levant – West Africa</t>
         </is>
       </c>
       <c r="F998" s="5" t="inlineStr"/>
       <c r="G998" s="5" t="inlineStr">
         <is>
-          <t>Formed in May 2015 by Adnan Abu Walid al-Sahraoui (QDi.415). Associated with the Islamic State in Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). Splinter group of Al-Mourabitoun (QDe.141). Committed terrorist attacks in Mali, Niger and Burkina Faso.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Islamic State in Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). Formed in March 2015 by Abubakar Shekau (QDi.322). Splinter group of Jama'atu Ahlis Sunna Lidda'Awati Wal-Jihad (Boko Haram) (QDe.138). Committed terrorist attacks in Nigeria.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H998" s="5" t="inlineStr">
         <is>
-          <t>QDe.163</t>
+          <t>QDe.162</t>
         </is>
       </c>
     </row>
@@ -40597,33 +40594,33 @@
       </c>
       <c r="B999" s="5" t="inlineStr">
         <is>
-          <t>6908835</t>
+          <t>6908803</t>
         </is>
       </c>
       <c r="C999" s="5" t="inlineStr">
         <is>
-          <t>2020-03-04</t>
+          <t>2020-02-23</t>
         </is>
       </c>
       <c r="D999" s="5" t="inlineStr">
         <is>
-          <t>JAMAAH ANSHARUT DAULAH</t>
+          <t>ISLAMIC STATE IN THE GREATER SAHARA (ISGS)</t>
         </is>
       </c>
       <c r="E999" s="5" t="inlineStr">
         <is>
-          <t>Jemaah Anshorut Daulah ; Jamaah Ansharut Daulat</t>
+          <t>Islamic State in Iraq and Syria – Greater Sahara (ISIS-GS) ; Islamic State of Iraq and Syria – Greater Sahara (ISIS-GS) ; Islamic State of Iraq and the Levant - Greater Sahara (ISIL-GS) ; Islamic State of the Greater Sahel ; ISIS in the Greater Sahel ; ISIS in the Greater Sahara ; ISIS in the Islamic Sahel</t>
         </is>
       </c>
       <c r="F999" s="5" t="inlineStr"/>
       <c r="G999" s="5" t="inlineStr">
         <is>
-          <t>Established in 2015 as an umbrella group of Indonesian extremist groups that pledged allegiance to then-ISIL leader Abu Bakr al-Baghdadi.  Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Formed in May 2015 by Adnan Abu Walid al-Sahraoui (QDi.415). Associated with the Islamic State in Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). Splinter group of Al-Mourabitoun (QDe.141). Committed terrorist attacks in Mali, Niger and Burkina Faso.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H999" s="5" t="inlineStr">
         <is>
-          <t>QDe.164</t>
+          <t>QDe.163</t>
         </is>
       </c>
     </row>
@@ -40635,7 +40632,7 @@
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>6908836</t>
+          <t>6908835</t>
         </is>
       </c>
       <c r="C1000" s="5" t="inlineStr">
@@ -40645,23 +40642,23 @@
       </c>
       <c r="D1000" s="5" t="inlineStr">
         <is>
-          <t>ISLAMIC STATE IN IRAQ AND THE LEVANT - LIBYA</t>
+          <t>JAMAAH ANSHARUT DAULAH</t>
         </is>
       </c>
       <c r="E1000" s="5" t="inlineStr">
         <is>
-          <t>Islamic state of Iraq and the Levant in Libya ; Wilayat Barqa ; Wilayat Fezzan ; Wilayat Tripolitania ; Wilayat Tarablus ; Wilayat Al-Tarablus</t>
+          <t>Jemaah Anshorut Daulah ; Jamaah Ansharut Daulat</t>
         </is>
       </c>
       <c r="F1000" s="5" t="inlineStr"/>
       <c r="G1000" s="5" t="inlineStr">
         <is>
-          <t>Formed in November 2014 upon announcement by Abu Bakr Al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali Al-Badri Al-Samarrai (QDi.299). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Established in 2015 as an umbrella group of Indonesian extremist groups that pledged allegiance to then-ISIL leader Abu Bakr al-Baghdadi.  Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1000" s="5" t="inlineStr">
         <is>
-          <t>QDe.165</t>
+          <t>QDe.164</t>
         </is>
       </c>
     </row>
@@ -40673,7 +40670,7 @@
       </c>
       <c r="B1001" s="5" t="inlineStr">
         <is>
-          <t>6908837</t>
+          <t>6908836</t>
         </is>
       </c>
       <c r="C1001" s="5" t="inlineStr">
@@ -40683,23 +40680,23 @@
       </c>
       <c r="D1001" s="5" t="inlineStr">
         <is>
-          <t>ISLAMIC STATE IN IRAQ AND THE LEVANT - YEMEN</t>
+          <t>ISLAMIC STATE IN IRAQ AND THE LEVANT - LIBYA</t>
         </is>
       </c>
       <c r="E1001" s="5" t="inlineStr">
         <is>
-          <t>Islamic State of Iraq and the Levant of Yemen ; Islamic State in Yemen ; ISIL in Yemen ; ISIS in Yemen ; Wilayat al-Yemen, Province of Yemen</t>
+          <t>Islamic state of Iraq and the Levant in Libya ; Wilayat Barqa ; Wilayat Fezzan ; Wilayat Tripolitania ; Wilayat Tarablus ; Wilayat Al-Tarablus</t>
         </is>
       </c>
       <c r="F1001" s="5" t="inlineStr"/>
       <c r="G1001" s="5" t="inlineStr">
         <is>
-          <t>Formed in November 2014 upon acceptance of oaths of allegiance by Abu Bakr Al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali Al-Badri Al-Samarrai (QDi.299). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Formed in November 2014 upon announcement by Abu Bakr Al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali Al-Badri Al-Samarrai (QDi.299). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1001" s="5" t="inlineStr">
         <is>
-          <t>QDe.166</t>
+          <t>QDe.165</t>
         </is>
       </c>
     </row>
@@ -40711,72 +40708,72 @@
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>6908862</t>
+          <t>6908837</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
         <is>
-          <t>2021-12-29</t>
+          <t>2020-03-04</t>
         </is>
       </c>
       <c r="D1002" s="5" t="inlineStr">
         <is>
-          <t>JUND AL-KHILAFAH IN TUNISIA (JAK-T)</t>
+          <t>ISLAMIC STATE IN IRAQ AND THE LEVANT - YEMEN</t>
         </is>
       </c>
       <c r="E1002" s="5" t="inlineStr">
         <is>
-          <t>ISIL-Tunisia ; ISIL-Tunisia Province ; Soldiers of the Caliphate ; Jund al-Khilafa ; Jund al Khilafah ; Jund al-Khilafah fi Tunis ; Soldiers of the Caliphate in Tunisia ; Tala I Jund al-Khilafah ; Vanguards of the Soldiers of the Caliphate ; Daesh Tunisia ; Ajnad</t>
+          <t>Islamic State of Iraq and the Levant of Yemen ; Islamic State in Yemen ; ISIL in Yemen ; ISIS in Yemen ; Wilayat al-Yemen, Province of Yemen</t>
         </is>
       </c>
       <c r="F1002" s="5" t="inlineStr"/>
       <c r="G1002" s="5" t="inlineStr">
         <is>
+          <t>Formed in November 2014 upon acceptance of oaths of allegiance by Abu Bakr Al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali Al-Badri Al-Samarrai (QDi.299). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H1002" s="5" t="inlineStr">
+        <is>
+          <t>QDe.166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B1003" s="5" t="inlineStr">
+        <is>
+          <t>6908862</t>
+        </is>
+      </c>
+      <c r="C1003" s="5" t="inlineStr">
+        <is>
+          <t>2021-12-29</t>
+        </is>
+      </c>
+      <c r="D1003" s="5" t="inlineStr">
+        <is>
+          <t>JUND AL-KHILAFAH IN TUNISIA (JAK-T)</t>
+        </is>
+      </c>
+      <c r="E1003" s="5" t="inlineStr">
+        <is>
+          <t>ISIL-Tunisia ; ISIL-Tunisia Province ; Soldiers of the Caliphate ; Jund al-Khilafa ; Jund al Khilafah ; Jund al-Khilafah fi Tunis ; Soldiers of the Caliphate in Tunisia ; Tala I Jund al-Khilafah ; Vanguards of the Soldiers of the Caliphate ; Daesh Tunisia ; Ajnad</t>
+        </is>
+      </c>
+      <c r="F1003" s="5" t="inlineStr"/>
+      <c r="G1003" s="5" t="inlineStr">
+        <is>
           <t>Formed in November 2014.Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115).    
  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H1002" s="5" t="inlineStr">
+      <c r="H1003" s="5" t="inlineStr">
         <is>
           <t>QDe.167</t>
-        </is>
-      </c>
-    </row>
-    <row r="1003">
-      <c r="A1003" s="5" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B1003" s="5" t="inlineStr">
-        <is>
-          <t>6908877</t>
-        </is>
-      </c>
-      <c r="C1003" s="5" t="inlineStr">
-        <is>
-          <t>2022-03-07</t>
-        </is>
-      </c>
-      <c r="D1003" s="5" t="inlineStr">
-        <is>
-          <t>KHATIBA AL-TAWHID WAL-JIHAD (KTJ)</t>
-        </is>
-      </c>
-      <c r="E1003" s="5" t="inlineStr">
-        <is>
-          <t>JANNAT OSHIKLARI ; Jama`at al-Tawhid wal-Jihad ; JANNAT OSHIKLARI</t>
-        </is>
-      </c>
-      <c r="F1003" s="5" t="inlineStr"/>
-      <c r="G1003" s="5" t="inlineStr">
-        <is>
-          <t>Khatiba al-Tawhid wal-Jihad (formerly known as Jannat Oshiklari) is a terrorist organization operating under the umbrella of the international terrorist organization Al-Nusrah Front for the People of the Levant (formerly listed). The group mainly operates in the provinces of Hama, Idlib and Ladhiqiyah, in the Syrian Arab Republic, and also conduct operations in Turkey, Kyrgyzstan, Uzbekistan, Russian Federation, Tajikistan, Kazakhstan, Egypt, Afghanistan, Ukraine.  The number of fighters of KTJ is about 500. KTJ also cooperates with such terrorist organizations as Khatiba Imam al-Bukhari (QDe.158) and the Islamic Jihad Group (QDe.119).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
-        </is>
-      </c>
-      <c r="H1003" s="5" t="inlineStr">
-        <is>
-          <t>QDe.168</t>
         </is>
       </c>
     </row>
@@ -40788,33 +40785,33 @@
       </c>
       <c r="B1004" s="5" t="inlineStr">
         <is>
-          <t>6908886</t>
+          <t>6908877</t>
         </is>
       </c>
       <c r="C1004" s="5" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2022-03-07</t>
         </is>
       </c>
       <c r="D1004" s="5" t="inlineStr">
         <is>
-          <t>Islamic State In Iraq And the Levant In South-East Asia (ISIL-SEA, ISIL-South East Asia)</t>
+          <t>KHATIBA AL-TAWHID WAL-JIHAD (KTJ)</t>
         </is>
       </c>
       <c r="E1004" s="5" t="inlineStr">
         <is>
-          <t>Islamic State East Asia Division ; Dawlatul Islamiyah Waliyatul Mashriq</t>
+          <t>JANNAT OSHIKLARI ; Jama`at al-Tawhid wal-Jihad ; JANNAT OSHIKLARI</t>
         </is>
       </c>
       <c r="F1004" s="5" t="inlineStr"/>
       <c r="G1004" s="5" t="inlineStr">
         <is>
-          <t>Formed in June 2016 upon announcement by now-deceased Isnilon Hapilon (QDi.204). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Khatiba al-Tawhid wal-Jihad (formerly known as Jannat Oshiklari) is a terrorist organization operating under the umbrella of the international terrorist organization Al-Nusrah Front for the People of the Levant (formerly listed). The group mainly operates in the provinces of Hama, Idlib and Ladhiqiyah, in the Syrian Arab Republic, and also conduct operations in Turkey, Kyrgyzstan, Uzbekistan, Russian Federation, Tajikistan, Kazakhstan, Egypt, Afghanistan, Ukraine.  The number of fighters of KTJ is about 500. KTJ also cooperates with such terrorist organizations as Khatiba Imam al-Bukhari (QDe.158) and the Islamic Jihad Group (QDe.119).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1004" s="5" t="inlineStr">
         <is>
-          <t>QDe.169</t>
+          <t>QDe.168</t>
         </is>
       </c>
     </row>
@@ -40826,33 +40823,33 @@
       </c>
       <c r="B1005" s="5" t="inlineStr">
         <is>
-          <t>6908033</t>
+          <t>6908886</t>
         </is>
       </c>
       <c r="C1005" s="5" t="inlineStr">
         <is>
-          <t>2010-04-12</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D1005" s="5" t="inlineStr">
         <is>
-          <t>AL-SHABAAB</t>
+          <t>Islamic State In Iraq And the Levant In South-East Asia (ISIL-SEA, ISIL-South East Asia)</t>
         </is>
       </c>
       <c r="E1005" s="5" t="inlineStr">
         <is>
-          <t>AL-SHABAB ; SHABAAB ; THE YOUTH ; MUJAHIDIN AL-SHABAAB MOVEMENT ; MUJAHIDEEN YOUTH MOVEMENT ; MUJAHIDIN YOUTH MOVEMENT ; MYM ; HARAKAT SHABAB AL-MUJAHIDIN ; HIZBUL SHABAAB ; HISB’UL SHABAAB ; AL-SHABAAB AL-ISLAMIYA ; YOUTH WING ; AL-SHABAAB AL-ISLAAM ; AL-SHABAAB AL-JIHAAD ; THE UNITY OF ISLAMIC YOUTH ; HARAKAT AL - SHABAAB AL - MUJAAHIDIIN ; HARAKATUL SHABAAB AL MUJAAHIDIIN ; MUJAAHIDIIN YOUTH MOVEMENT</t>
+          <t>Islamic State East Asia Division ; Dawlatul Islamiyah Waliyatul Mashriq</t>
         </is>
       </c>
       <c r="F1005" s="5" t="inlineStr"/>
       <c r="G1005" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Formed in June 2016 upon announcement by now-deceased Isnilon Hapilon (QDi.204). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1005" s="5" t="inlineStr">
         <is>
-          <t>SOe.001</t>
+          <t>QDe.169</t>
         </is>
       </c>
     </row>
@@ -40864,33 +40861,33 @@
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>2989469</t>
+          <t>6908033</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
         <is>
-          <t>2012-06-29</t>
+          <t>2010-04-12</t>
         </is>
       </c>
       <c r="D1006" s="5" t="inlineStr">
         <is>
-          <t>HAJI KHAIRULLAH HAJI SATTAR MONEY EXCHANGE</t>
+          <t>AL-SHABAAB</t>
         </is>
       </c>
       <c r="E1006" s="5" t="inlineStr">
         <is>
-          <t>Haji Khairullah-Haji Sattar Sarafi ; Haji Khairullah and Abdul Sattar and Company ; Haji Khairullah Money Exchange ; Haji Khair Ullah Money Service ; Haji Salam Hawala ; Haji Hakim Hawala ; Haji Alim Hawala ; Sarafi-yi Haji Khairullah Haji Satar Haji Esmatullah</t>
+          <t>AL-SHABAB ; SHABAAB ; THE YOUTH ; MUJAHIDIN AL-SHABAAB MOVEMENT ; MUJAHIDEEN YOUTH MOVEMENT ; MUJAHIDIN YOUTH MOVEMENT ; MYM ; HARAKAT SHABAB AL-MUJAHIDIN ; HIZBUL SHABAAB ; HISB’UL SHABAAB ; AL-SHABAAB AL-ISLAMIYA ; YOUTH WING ; AL-SHABAAB AL-ISLAAM ; AL-SHABAAB AL-JIHAAD ; THE UNITY OF ISLAMIC YOUTH ; HARAKAT AL - SHABAAB AL - MUJAAHIDIIN ; HARAKATUL SHABAAB AL MUJAAHIDIIN ; MUJAAHIDIIN YOUTH MOVEMENT</t>
         </is>
       </c>
       <c r="F1006" s="5" t="inlineStr"/>
       <c r="G1006" s="5" t="inlineStr">
         <is>
-          <t>Afghan Money Service Provider License Number: 044. Haji Khairullah Haji Sattar Money Exchange was used by Taliban leadership to transfer money to Taliban commanders to fund fighters and operations in Afghanistan as of 2011. Active in Kunar Province. Associated with Abdul Sattar Abdul Manan (TAi.162) and Khairullah Barakzai Khudai Nazar (TAi.163). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1006" s="5" t="inlineStr">
         <is>
-          <t>TAe.010</t>
+          <t>SOe.001</t>
         </is>
       </c>
     </row>
@@ -40902,7 +40899,7 @@
       </c>
       <c r="B1007" s="5" t="inlineStr">
         <is>
-          <t>2989573</t>
+          <t>2989469</t>
         </is>
       </c>
       <c r="C1007" s="5" t="inlineStr">
@@ -40912,52 +40909,90 @@
       </c>
       <c r="D1007" s="5" t="inlineStr">
         <is>
-          <t>ROSHAN MONEY EXCHANGE</t>
+          <t>HAJI KHAIRULLAH HAJI SATTAR MONEY EXCHANGE</t>
         </is>
       </c>
       <c r="E1007" s="5" t="inlineStr">
         <is>
-          <t>Roshan Sarafi ; Roshan Trading Company ; Rushaan Trading Company ; Roshan Shirkat ; Maulawi Ahmed Shah Hawala ; Mullah Ahmed Shah Hawala ; Haji Ahmad Shah Hawala ; Ahmad Shah Hawala</t>
+          <t>Haji Khairullah-Haji Sattar Sarafi ; Haji Khairullah and Abdul Sattar and Company ; Haji Khairullah Money Exchange ; Haji Khair Ullah Money Service ; Haji Salam Hawala ; Haji Hakim Hawala ; Haji Alim Hawala ; Sarafi-yi Haji Khairullah Haji Satar Haji Esmatullah</t>
         </is>
       </c>
       <c r="F1007" s="5" t="inlineStr"/>
       <c r="G1007" s="5" t="inlineStr">
+        <is>
+          <t>Afghan Money Service Provider License Number: 044. Haji Khairullah Haji Sattar Money Exchange was used by Taliban leadership to transfer money to Taliban commanders to fund fighters and operations in Afghanistan as of 2011. Active in Kunar Province. Associated with Abdul Sattar Abdul Manan (TAi.162) and Khairullah Barakzai Khudai Nazar (TAi.163). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+        </is>
+      </c>
+      <c r="H1007" s="5" t="inlineStr">
+        <is>
+          <t>TAe.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="5" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B1008" s="5" t="inlineStr">
+        <is>
+          <t>2989573</t>
+        </is>
+      </c>
+      <c r="C1008" s="5" t="inlineStr">
+        <is>
+          <t>2012-06-29</t>
+        </is>
+      </c>
+      <c r="D1008" s="5" t="inlineStr">
+        <is>
+          <t>ROSHAN MONEY EXCHANGE</t>
+        </is>
+      </c>
+      <c r="E1008" s="5" t="inlineStr">
+        <is>
+          <t>Roshan Sarafi ; Roshan Trading Company ; Rushaan Trading Company ; Roshan Shirkat ; Maulawi Ahmed Shah Hawala ; Mullah Ahmed Shah Hawala ; Haji Ahmad Shah Hawala ; Ahmad Shah Hawala</t>
+        </is>
+      </c>
+      <c r="F1008" s="5" t="inlineStr"/>
+      <c r="G1008" s="5" t="inlineStr">
         <is>
           <t>Roshan Money Exchange stores and transfers funds to support Taliban
 military operations and narcotics trade in Afghanistan. Owned by Ahmed Shah Noorzai
 Obaidullah (TAi.166). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H1007" s="5" t="inlineStr">
+      <c r="H1008" s="5" t="inlineStr">
         <is>
           <t>TAe.011</t>
         </is>
       </c>
     </row>
-    <row r="1008">
-      <c r="A1008" s="5" t="inlineStr">
+    <row r="1009">
+      <c r="A1009" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B1008" s="5" t="inlineStr">
+      <c r="B1009" s="5" t="inlineStr">
         <is>
           <t>3000441</t>
         </is>
       </c>
-      <c r="C1008" s="5" t="inlineStr">
+      <c r="C1009" s="5" t="inlineStr">
         <is>
           <t>2012-11-05</t>
         </is>
       </c>
-      <c r="D1008" s="5" t="inlineStr">
+      <c r="D1009" s="5" t="inlineStr">
         <is>
           <t>HAQQANI NETWORK (HQN)</t>
         </is>
       </c>
-      <c r="E1008" s="5" t="inlineStr"/>
-      <c r="F1008" s="5" t="inlineStr"/>
-      <c r="G1008" s="5" t="inlineStr">
+      <c r="E1009" s="5" t="inlineStr"/>
+      <c r="F1009" s="5" t="inlineStr"/>
+      <c r="G1009" s="5" t="inlineStr">
         <is>
           <t>Network of Taliban fighters centered around the border between Khost
 Province, Afghanistan and North Waziristan, Pakistan. Founded by Jalaluddin Haqqani
@@ -40971,40 +41006,40 @@
 (QDe.019). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H1008" s="5" t="inlineStr">
+      <c r="H1009" s="5" t="inlineStr">
         <is>
           <t>TAe.012</t>
         </is>
       </c>
     </row>
-    <row r="1009">
-      <c r="A1009" s="5" t="inlineStr">
+    <row r="1010">
+      <c r="A1010" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B1009" s="5" t="inlineStr">
+      <c r="B1010" s="5" t="inlineStr">
         <is>
           <t>3000510</t>
         </is>
       </c>
-      <c r="C1009" s="5" t="inlineStr">
+      <c r="C1010" s="5" t="inlineStr">
         <is>
           <t>2012-11-21</t>
         </is>
       </c>
-      <c r="D1009" s="5" t="inlineStr">
+      <c r="D1010" s="5" t="inlineStr">
         <is>
           <t>RAHAT LTD.</t>
         </is>
       </c>
-      <c r="E1009" s="5" t="inlineStr">
+      <c r="E1010" s="5" t="inlineStr">
         <is>
           <t>Rahat Trading Company ; Haji Muhammad Qasim Sarafi ; New Chagai Trading ; Musa Kalim Hawala</t>
         </is>
       </c>
-      <c r="F1009" s="5" t="inlineStr"/>
-      <c r="G1009" s="5" t="inlineStr">
+      <c r="F1010" s="5" t="inlineStr"/>
+      <c r="G1010" s="5" t="inlineStr">
         <is>
           <t>Rahat Ltd. was used by Taliban leadership to transfer funds originating
 from external donors and narcotics trafficking to finance Taliban activity as of 2011
@@ -41012,91 +41047,91 @@
 Mohammad Naim Barich Khudaidad (TAi.013). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H1009" s="5" t="inlineStr">
+      <c r="H1010" s="5" t="inlineStr">
         <is>
           <t>TAe.013</t>
         </is>
       </c>
     </row>
-    <row r="1010">
-      <c r="A1010" s="5" t="inlineStr">
+    <row r="1011">
+      <c r="A1011" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B1010" s="5" t="inlineStr">
+      <c r="B1011" s="5" t="inlineStr">
         <is>
           <t>6908451</t>
         </is>
       </c>
-      <c r="C1010" s="5" t="inlineStr">
+      <c r="C1011" s="5" t="inlineStr">
         <is>
           <t>2015-03-27-04:00</t>
         </is>
       </c>
-      <c r="D1010" s="5" t="inlineStr">
+      <c r="D1011" s="5" t="inlineStr">
         <is>
           <t>HAJI BASIR AND ZARJMIL COMPANY HAWALA</t>
         </is>
       </c>
-      <c r="E1010" s="5" t="inlineStr">
+      <c r="E1011" s="5" t="inlineStr">
         <is>
           <t>Haji Bashir and Zarjmil Hawala Company ; Haji Abdul Basir and Zar Jameel Hawala ; Haji Basir Hawala ; Haji Baseer Hawala ; Haji Abdul Basir Exchange Shop ; Haji Basir and Zarjamil Currency Exchange ; Haji Zar Jamil, Haji Abdul Baseer Money Changer</t>
         </is>
       </c>
-      <c r="F1010" s="5" t="inlineStr"/>
-      <c r="G1010" s="5" t="inlineStr">
+      <c r="F1011" s="5" t="inlineStr"/>
+      <c r="G1011" s="5" t="inlineStr">
         <is>
           <t>Money service provider used by senior Taliban leaders to transfer funds
 to Taliban commanders in the region. Owned by Abdul Basir Noorzai (TAi.173). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H1010" s="5" t="inlineStr">
+      <c r="H1011" s="5" t="inlineStr">
         <is>
           <t>TAe.014</t>
         </is>
       </c>
     </row>
-    <row r="1011">
-      <c r="A1011" s="5" t="inlineStr">
+    <row r="1012">
+      <c r="A1012" s="5" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="B1011" s="5" t="inlineStr">
+      <c r="B1012" s="5" t="inlineStr">
         <is>
           <t>6908876</t>
         </is>
       </c>
-      <c r="C1011" s="5" t="inlineStr">
+      <c r="C1012" s="5" t="inlineStr">
         <is>
           <t>2022-02-28</t>
         </is>
       </c>
-      <c r="D1011" s="5" t="inlineStr">
+      <c r="D1012" s="5" t="inlineStr">
         <is>
           <t>THE HOUTHIS</t>
         </is>
       </c>
-      <c r="E1011" s="5" t="inlineStr">
+      <c r="E1012" s="5" t="inlineStr">
         <is>
           <t>ANSARALLAH ; ANSAR ALLAH ; PARTISANS OF GOD ; SUPPORTERS OF GOD</t>
         </is>
       </c>
-      <c r="F1011" s="5" t="inlineStr"/>
-      <c r="G1011" s="5" t="inlineStr">
+      <c r="F1012" s="5" t="inlineStr"/>
+      <c r="G1012" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 5 of resolution 2624 (2022) as subject to the measures imposed by paragraph 14 of resolution 2216 (2015) (targeted arms embargo). The Houthis have engaged in acts that threaten the peace, security, and stability of Yemen. The Houthis have engaged in attacks striking civilians and civilian infrastructure in Yemen, implemented a policy of sexual violence and repression against politically active and professional women, engaged in the recruitment and use of children, incited violence against groups including on the basis of religion and nationality, and indiscriminately used landmines and improvised explosive devices on the West Coast of Yemen. The Houthis have also obstructed the delivery of humanitarian assistance to Yemen, or access to, or distribution of, humanitarian assistance in Yemen. The Houthis have conducted attacks on commercial shipping in the Red Sea using waterborne improvised explosive devices and sea mines. The Houthis have also perpetrated repeated cross-border terrorist attacks striking civilians and civilian infrastructure in the Kingdom of Saudi Arabia and the United Arab Emirates and threatened to intentionally target civilian sites.    INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
-      <c r="H1011" s="5" t="inlineStr">
+      <c r="H1012" s="5" t="inlineStr">
         <is>
           <t>YEe.001</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1011"/>
+  <autoFilter ref="A1:H1012"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24T01:54:28+00:00</t>
+          <t>2026-07-25T01:53:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25T01:53:07+00:00</t>
+          <t>2026-07-26T01:56:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26T01:56:36+00:00</t>
+          <t>2026-07-27T02:07:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27T02:07:06+00:00</t>
+          <t>2026-07-28T01:46:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28T01:46:42+00:00</t>
+          <t>2026-07-29T01:48:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29T01:48:26+00:00</t>
+          <t>2026-07-30T01:31:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30T01:31:25+00:00</t>
+          <t>2026-07-31T01:58:24+00:00</t>
         </is>
       </c>
     </row>
@@ -28274,7 +28274,7 @@
       </c>
       <c r="G675" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council and Head of Taliban Religious Committee. Belongs to Ahmadzai tribe. Height 175 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-26129</t>
+          <t>Member of Taliban Supreme Council and Head of Taliban Religious Committee. Belongs to Ahmadzai tribe. Height 175 cm or 180 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-26129</t>
         </is>
       </c>
       <c r="H675" s="5" t="inlineStr">
@@ -29269,7 +29269,7 @@
       </c>
       <c r="G699" s="5" t="inlineStr">
         <is>
-          <t>Heading the Haqqani Network (TAe.012) as of late 2012. Son of Jalaluddin Haqqani (TAi.040). Belongs to Sultan Khel section, Zadran tribe of Garda Saray of Paktia province, Afghanistan. Height 187 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-44300</t>
+          <t>Heading the Haqqani Network (TAe.012) as of late 2012. Son of Jalaluddin Haqqani (TAi.040). Belongs to Sultan Khel section, Zadran tribe of Garda Saray of Paktia province, Afghanistan. Height 187 cm or 180cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-44300</t>
         </is>
       </c>
       <c r="H699" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31T01:58:24+00:00</t>
+          <t>2026-08-01T01:58:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01T01:58:57+00:00</t>
+          <t>2026-08-02T01:55:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02T01:55:00+00:00</t>
+          <t>2026-08-03T01:57:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03T01:57:40+00:00</t>
+          <t>2026-08-04T01:44:32+00:00</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>He fled to Rwanda in March 2013 and is still living there as of early 2016. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>He fled to Rwanda in March 2013 and is still living there as of early 2016. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -664,7 +664,7 @@
 government’s Programme de Stabilisation et Reconstruction des Zones Sortant des Conflits
 Armés (STAREC), including participation in a STAREC mission to Goma and Beni in March
 2011. DRC authorities arrested him in December 2013 in Beni, North Kivu Province, for
-allegedly blocking the DDR process. He left the DRC and lived in Kenya for some time, before being called back by the DRC Government to assist them with the situation in the Territory of Beni.  He was arrested in October 2015 in the area of Mambasa for allegedly supporting a Mai Mai group, but no charges were brought and as of June 2016, he lived in Kinshasa. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+allegedly blocking the DDR process. He left the DRC and lived in Kenya for some time, before being called back by the DRC Government to assist them with the situation in the Territory of Beni.  He was arrested in October 2015 in the area of Mambasa for allegedly supporting a Mai Mai group, but no charges were brought and as of June 2016, he lived in Kinshasa. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -744,7 +744,7 @@
       <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>: Became M23 deputy commander after the flight of Bosco Taganda’s faction to Rwanda in March 2013. Fled to Uganda in November 2013. In Uganda as of early 2016.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>: Became M23 deputy commander after the flight of Bosco Taganda’s faction to Rwanda in March 2013. Fled to Uganda in November 2013. In Uganda as of early 2016.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -789,7 +789,7 @@
           <t>Given the rank of General in the FARDC in December 2004. As of June 2011,
 detained in Makala Prison in Kinshasa. As of 25 March 2011, the High Military Court in
 Kinshasa opened a trial against Kakwavu for war crimes. In November 2014, convicted by a
-DRC military court to ten years in prison for rape, murder, and torture. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+DRC military court to ten years in prison for rape, murder, and torture. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -868,7 +868,7 @@
         <is>
           <t>Arrested in Kinshasa in March 2005 for UPC/L involvement in human rights
 abuses violations. Transferred to the ICC on 17 March 2006. Convicted by the ICC in
-March 2012 and sentenced to 14 years in prison.  On 1 December 2014, ICC appeals judges upheld Lubanga’s conviction and sentence. Transferred to a prison facility in the DRC on 19 December 2015 to serve out his sentence of imprisonment. He was released on 15 March 2020 after having served his ICC sentence. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+March 2012 and sentenced to 14 years in prison.  On 1 December 2014, ICC appeals judges upheld Lubanga’s conviction and sentence. Transferred to a prison facility in the DRC on 19 December 2015 to serve out his sentence of imprisonment. He was released on 15 March 2020 after having served his ICC sentence. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -911,7 +911,7 @@
       <c r="G9" s="5" t="inlineStr">
         <is>
           <t>A military leader of the Mouvement du 23 Mars (M23) group operating in
-the Democratic Republic of the Congo. In Uganda as of late 2014. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+the Democratic Republic of the Congo. In Uganda as of late 2014. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -957,7 +957,7 @@
 process. Arrested by Congolese authorities in October 2005, acquitted by the Court of
 Appeal in Kisangani, subsequently transferred to the judicial authorities in Kinshasa on
 new charges of crimes against humanity, war crimes, murder, aggravated assault and
-battery. In August 2014, a DRC military court in Kisangani convicted him of war crimes and crimes against humanity, sentenced him to nine years in prison, and ordered him to pay approximately $85,000 to his victims. He served his sentence and resides in Uganda as of May 2016. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+battery. In August 2014, a DRC military court in Kisangani convicted him of war crimes and crimes against humanity, sentenced him to nine years in prison, and ordered him to pay approximately $85,000 to his victims. He served his sentence and resides in Uganda as of May 2016. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1038,7 +1038,7 @@
       <c r="G12" s="5" t="inlineStr">
         <is>
           <t>No known occupation since two of the planes managed by Great Lakes
-Business Company (GLBC) crashed. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Business Company (GLBC) crashed. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>FDLR-FOCA Chief of Staff, in charge of administration. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>FDLR-FOCA Chief of Staff, in charge of administration. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Became acting FDLR-FOCA Deputy Commander in 2014. Captured in Goma, DRC by Congolese security services in early May 2016 and transferred to Kinshasa.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Became acting FDLR-FOCA Deputy Commander in 2014. Captured in Goma, DRC by Congolese security services in early May 2016 and transferred to Kinshasa.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Arrested in April 2015 in Tanzania and extradited to Uganda in July 2015. As of September 2016, Mukulu is reportedly being held in a police detention cell awaiting his trial for war crimes and grave breaches of the Geneva Convection under Ugandan Law.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Arrested in April 2015 in Tanzania and extradited to Uganda in July 2015. As of September 2016, Mukulu is reportedly being held in a police detention cell awaiting his trial for war crimes and grave breaches of the Geneva Convection under Ugandan Law.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Reported to have died in prison in Germany on 16 April 2019. Arrested by German authorities on 17 November 2009 and found guilty by a German court on 28 September 2015 of leadership of a foreign terrorist group and aiding in war crimes. Received a 13-year sentence and is in prison in Germany as of June 2016. Re-elected FDLR President on 29 November 2014 for a five-year term.   INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reported to have died in prison in Germany on 16 April 2019. Arrested by German authorities on 17 November 2009 and found guilty by a German court on 28 September 2015 of leadership of a foreign terrorist group and aiding in war crimes. Received a 13-year sentence and is in prison in Germany as of June 2016. Re-elected FDLR President on 29 November 2014 for a five-year term.   INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Arrested by German authorities on 17 November 2009, found guilty in a German court on 28 September 2015 of leadership of a foreign terrorist group, and received an 8-year sentence. Musoni was released from prison immediately after the trial, having served over 5 years of his sentence. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Arrested by German authorities on 17 November 2009, found guilty in a German court on 28 September 2015 of leadership of a foreign terrorist group, and received an 8-year sentence. Musoni was released from prison immediately after the trial, having served over 5 years of his sentence. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Former FARDC Deputy Military Regional Commander of 10th Military Region in April 2004, dismissed for indiscipline. In December 2007, he was arrested by Rwandan authorities when he tried to cross the border into the DRC. Reported to have died in Kigali on 9 May 2014.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Former FARDC Deputy Military Regional Commander of 10th Military Region in April 2004, dismissed for indiscipline. In December 2007, he was arrested by Rwandan authorities when he tried to cross the border into the DRC. Reported to have died in Kigali on 9 May 2014.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1375,7 +1375,7 @@
       <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Entered the Republic of Rwanda on 16 March 2013. As of late 2014, living
-in Ngoma camp, Rwanda. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+in Ngoma camp, Rwanda. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Arrested by MONUC in Bunia in October 2003. Surrendered by the Government of the DRC to the International Criminal Court on 7 February 2008. Acquitted of all charges by the ICC in December 2012, and the verdict was upheld by the Appeals Chamber on 27 February 2015. Ngudjolo filed a claim for asylum in the Netherlands, but was denied. He was deported to the DRC on 11 May 2015. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Arrested by MONUC in Bunia in October 2003. Surrendered by the Government of the DRC to the International Criminal Court on 7 February 2008. Acquitted of all charges by the ICC in December 2012, and the verdict was upheld by the Appeals Chamber on 27 February 2015. Ngudjolo filed a claim for asylum in the Netherlands, but was denied. He was deported to the DRC on 11 May 2015. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1463,7 +1463,7 @@
 human rights abuses. Transferred to The Hague on 27 March 2011 to testify in the ICC
 Germain Katanga and Mathieu Ngudjolo trials. Applied for asylum in the Netherlands in
 May 2011. In October 2012, a Dutch court denied his asylum claim. In July 2014, he was
-deported from the Netherlands to DRC, where he was placed under arrest. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+deported from the Netherlands to DRC, where he was placed under arrest. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1513,7 +1513,7 @@
 extradite Nkunda for crimes committed in eastern DRC has been refused by Rwanda. In
 2010, Nkunda’s appeal for illegal detention was rejected by Rwandan court in Gisenyi,
 ruling that the matter should be examined by a military court. Nkunda’s lawyers appealed
-with the Rwandan Military Court. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+with the Rwandan Military Court. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Received military training in Egypt.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Received military training in Egypt.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1678,7 +1678,7 @@
       <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Disappeared while in Tanzania in early 2013. Whereabouts unknown as of
-June 2016. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+June 2016. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1722,7 +1722,7 @@
         <is>
           <t>While president of the Fédération des entreprises congolaises (FEC) in
 Aru territory, Dieudonné Ozia Mazio is believed to have died in Ariwara on 23 September
-2008. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+2008. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -1760,7 +1760,7 @@
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Entered the Republic of Rwanda on 16 March 2013. As of 2016, residing in Rwanda. Participated in the creation of a new Congolese political party in June 2016, the Alliance pour le Salut du Peuple (ASP). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Entered the Republic of Rwanda on 16 March 2013. As of 2016, residing in Rwanda. Participated in the creation of a new Congolese political party in June 2016, the Alliance pour le Salut du Peuple (ASP). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>He surrendered to MONUSCO on 26 July 2017 and has been since detained by the Congolese authorities. His trial for war crimes, crimes against humanity and participation in an insurrectional movement, before the Military Court in Goma, started in November 2018. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>He surrendered to MONUSCO on 26 July 2017 and has been since detained by the Congolese authorities. His trial for war crimes, crimes against humanity and participation in an insurrectional movement, before the Military Court in Goma, started in November 2018. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Born in Rwanda, he moved to Nyamitaba, Masisi territory, North Kivu, when he was a child. Nominated FARDC Brigadier-General by Presidential Decree on 11 December 2004, following Ituri peace agreements. Formerly Chief of Staff in CNDP and became CNDP military commander since the arrest of Laurent Nkunda in January 2009. Since January 2009, de facto Deputy Commander of consecutive anti-FDLR operations ‘Umoja Wetu’, ‘Kimia II’, and ‘Amani Leo’ in North and South Kivu. Entered Rwanda in March 2013, and voluntarily surrender to ICC officials in Kigali on March 22. Transferred to the ICC in The Hague, Netherlands. On 9 June 2014, ICC confirmed 13 charges of war crimes and five charges of crimes against humanity against him; the trial started in September 2015. On 8 July 2019, the ICC found him guilty of 18 counts of war crimes and crimes against humanity, committed in Ituri in 2002-2003. On 7 November 2019, he was sentenced to a total of 30 years imprisonment.  He has appealed both his conviction and sentence. On 30 March 2021, the ICC Appeals Chamber confirmed his conviction and sentence. On 14 December 2022, he was transferred to the territory of Belgium for enforcement of sentence. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Born in Rwanda, he moved to Nyamitaba, Masisi territory, North Kivu, when he was a child. Nominated FARDC Brigadier-General by Presidential Decree on 11 December 2004, following Ituri peace agreements. Formerly Chief of Staff in CNDP and became CNDP military commander since the arrest of Laurent Nkunda in January 2009. Since January 2009, de facto Deputy Commander of consecutive anti-FDLR operations ‘Umoja Wetu’, ‘Kimia II’, and ‘Amani Leo’ in North and South Kivu. Entered Rwanda in March 2013, and voluntarily surrender to ICC officials in Kigali on March 22. Transferred to the ICC in The Hague, Netherlands. On 9 June 2014, ICC confirmed 13 charges of war crimes and five charges of crimes against humanity against him; the trial started in September 2015. On 8 July 2019, the ICC found him guilty of 18 counts of war crimes and crimes against humanity, committed in Ituri in 2002-2003. On 7 November 2019, he was sentenced to a total of 30 years imprisonment.  He has appealed both his conviction and sentence. On 30 March 2021, the ICC Appeals Chamber confirmed his conviction and sentence. On 14 December 2022, he was transferred to the territory of Belgium for enforcement of sentence. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -1891,7 +1891,7 @@
 wears the newly issued FARDC rank and uniform. In December 2010, recruitment activities
 carried out by elements under the command of Zimurinda were denounced in open source
 reports. Entered the Republic of Rwanda on 16 March 2013. As of late 2014, residing in
-Ngoma camp, Rwanda. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Ngoma camp, Rwanda. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Muhindo Akili Mundos is an FARDC General, Commander of the 31st Brigade. He was appointed commander of the FARDC’s Operational Sector in the areas of Beni and Lubero, including Operation Sukola I against the Allied Democratic Forces (ADF) in September 2014. He remained in that position until June 2015. He is also a threat to the peace, stability and security of the DRC under UNSCR 2293 paragraph 7(e).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Muhindo Akili Mundos is an FARDC General, Commander of the 31st Brigade. He was appointed commander of the FARDC’s Operational Sector in the areas of Beni and Lubero, including Operation Sukola I against the Allied Democratic Forces (ADF) in September 2014. He remained in that position until June 2015. He is also a threat to the peace, stability and security of the DRC under UNSCR 2293 paragraph 7(e).  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -1967,7 +1967,7 @@
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Graduated secondary school humanités sociales in Mpofi; joined the armed group commanded by She Kasikila at the age of 16; integrated the FARDC with Kasikila, becoming his battalion S3; injured in 2007, thereafter joining Mai Mai Simba under then-commander “Mando;” participated in the creation of the NDC in 2008, becoming the deputy commander in charge of the Aigle Lemabé Brigade. He is also a threat to the peace, stability and security of the DRC under UNSCR 2293 paragraph 7(g). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Graduated secondary school humanités sociales in Mpofi; joined the armed group commanded by She Kasikila at the age of 16; integrated the FARDC with Kasikila, becoming his battalion S3; injured in 2007, thereafter joining Mai Mai Simba under then-commander “Mando;” participated in the creation of the NDC in 2008, becoming the deputy commander in charge of the Aigle Lemabé Brigade. He is also a threat to the peace, stability and security of the DRC under UNSCR 2293 paragraph 7(g). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>He is a threat to the peace, stability and security of the DRC under UNSCR 2293 paragraph 7(j). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>He is a threat to the peace, stability and security of the DRC under UNSCR 2293 paragraph 7(j). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2043,7 +2043,7 @@
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Gédéon Kyungu belongs to the Balubakat ethnic group. After completing primary education in Likasi and secondary school in Manono, he obtained a degree in pedagogy. In 1999 he joined the Maï Maï movement, commanding from 2003 one of the most active groups in the province of Katanga. In 2006, he visited UN peacekeeping forces to integrate through the disarmament, demobilization and reintegration (DDR) process. He escaped from prison in 2011 and surrendered in October 2016. He is a threat to the peace, stability and security of the DRC under UNSCR 2293 paragraph 7(e). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gédéon Kyungu belongs to the Balubakat ethnic group. After completing primary education in Likasi and secondary school in Manono, he obtained a degree in pedagogy. In 1999 he joined the Maï Maï movement, commanding from 2003 one of the most active groups in the province of Katanga. In 2006, he visited UN peacekeeping forces to integrate through the disarmament, demobilization and reintegration (DDR) process. He escaped from prison in 2011 and surrendered in October 2016. He is a threat to the peace, stability and security of the DRC under UNSCR 2293 paragraph 7(e). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. Corneille Nangaa Yobeluo is the leader of the Alliance Fleuve Congo (AFC) (CDe.010), a politico-military movement allied with the United Nations-sanctioned March 23 Movement/Congolese Revolutionary Army (M23/ARC) (CDe.006).   INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male. Corneille Nangaa Yobeluo is the leader of the Alliance Fleuve Congo (AFC) (CDe.010), a politico-military movement allied with the United Nations-sanctioned March 23 Movement/Congolese Revolutionary Army (M23/ARC) (CDe.006).   INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. Sebastien Uwimbabazi has and continues to engage in or provide support for acts that undermine the peace, stability and security of the DRC.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male. Sebastien Uwimbabazi has and continues to engage in or provide support for acts that undermine the peace, stability and security of the DRC.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. As one of the commanders of the Allied Democratic Forces (ADF) (CDe.001), MUHAMMED LUMISA is involved in planning, promulgating, and supporting the militia’s activities. He also oversees the group’s external logistics. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male. As one of the commanders of the Allied Democratic Forces (ADF) (CDe.001), MUHAMMED LUMISA is involved in planning, promulgating, and supporting the militia’s activities. He also oversees the group’s external logistics. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. As a leader of M23 (CDe.006), JOHN IMANI NZENZE is involved in planning, promulgating and supporting the armed group’s activities. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male. As a leader of M23 (CDe.006), JOHN IMANI NZENZE is involved in planning, promulgating and supporting the armed group’s activities. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. As one of the main Democratic Forces for the Liberation of Rwanda Forces Combattantes Abacunguzi (FDLR-FOCA) (CDe.005) commanders and the new commander of the Commando de Recherche et d'Action en Profondeur (CRAP), GUSTAVE KUBWAYO alias SIRKOOF is involved in planning, promulgating and supporting the armed group’s activities, such as targeting civilians, kidnapping for ransom and illegally exploiting natural resources.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male. As one of the main Democratic Forces for the Liberation of Rwanda Forces Combattantes Abacunguzi (FDLR-FOCA) (CDe.005) commanders and the new commander of the Commando de Recherche et d'Action en Profondeur (CRAP), GUSTAVE KUBWAYO alias SIRKOOF is involved in planning, promulgating and supporting the armed group’s activities, such as targeting civilians, kidnapping for ransom and illegally exploiting natural resources.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Mother’s name is Martine Kofio. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother’s name is Martine Kofio. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -2792,7 +2792,7 @@
 Saragba, an anti-Balaka commander in Batalimo, Lobaye province, and a former FACA
 soldier. Physical description: eye colour: black; hair colour: bold; complexion: black;
 height: 170cm; weight: 100kg. Photo available for inclusion in the INTERPOL-UN Security
-Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Appointed as anti-balaka zone commander (COMZONE) of Boda on 11 April 2014 and on 28 June 2014, for the entire Lobaye Province. Under his command, targeted killings, clashes and attacks against humanitarian organizations and aid workers have continued to take place. Physical description: eye colour: brown; hair colour: black; height: 160cm; weight: 60kg. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Appointed as anti-balaka zone commander (COMZONE) of Boda on 11 April 2014 and on 28 June 2014, for the entire Lobaye Province. Under his command, targeted killings, clashes and attacks against humanitarian organizations and aid workers have continued to take place. Physical description: eye colour: brown; hair colour: black; height: 160cm; weight: 60kg. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -2879,7 +2879,7 @@
           <t>Is a diamond smuggler and a three-star general of the Séléka and close
 confident of former CAR interim president Michel Djotodia. Physical description: hair
 colour: black; height: 180cm; belongs to the Fulani ethnic group. Photo available for
-inclusion in the INTERPOL-UN Security Council Special Notice. Reportedly deceased as at 11 October 2015 INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+inclusion in the INTERPOL-UN Security Council Special Notice. Reportedly deceased as at 11 October 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -2917,7 +2917,7 @@
       <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Gaye is a leader of the Front Populaire pour la Renaissance de Centrafrique (FPRC) (not listed) a marginalized ex-Seleka armed group in Bangui. He is also a leader of the so-called “Defense Committee” of Bangui’s PK5 (known as PK5 Resistance’ or ‘Texas’) (not listed), which extorts money from residents and threatens and employs physical violence. Gaye was appointed on 2 November 2014 by Nourredine Adam (CFi.002) as rapporteur of the political coordination of the FPRC. On 9 May 2014, the Security Council Committee established by resolution 2127 (2013) on CAR included Adam on its sanctions list. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gaye is a leader of the Front Populaire pour la Renaissance de Centrafrique (FPRC) (not listed) a marginalized ex-Seleka armed group in Bangui. He is also a leader of the so-called “Defense Committee” of Bangui’s PK5 (known as PK5 Resistance’ or ‘Texas’) (not listed), which extorts money from residents and threatens and employs physical violence. Gaye was appointed on 2 November 2014 by Nourredine Adam (CFi.002) as rapporteur of the political coordination of the FPRC. On 9 May 2014, the Security Council Committee established by resolution 2127 (2013) on CAR included Adam on its sanctions list. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -2955,7 +2955,7 @@
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Captain Eugène Barret Ngaïkosset is a former member of former President François Bozizé’s (CFi.001) presidential guard and associated with the anti-Balaka movement. He escaped from jail on 17 May 2015 following his extradition from Brazzaville and created his own anti-balaka faction including former FACA fighters. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Captain Eugène Barret Ngaïkosset is a former member of former President François Bozizé’s (CFi.001) presidential guard and associated with the anti-Balaka movement. He escaped from jail on 17 May 2015 following his extradition from Brazzaville and created his own anti-balaka faction including former FACA fighters. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Kony is the founder and leader of the Lord’s Resistance Army (LRA) (CFe.002). Under his leadership, the LRA has engaged in the abduction, killing, and mutilation of thousands of civilians across Central Africa. The LRA has been responsible for kidnapping, displacing, committing sexual violence against, and killing hundreds of individuals across CAR, and has looted and destroyed civilian property. Father’s name is Luizi Obol. Mother’s name is Nora Obol. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Kony is the founder and leader of the Lord’s Resistance Army (LRA) (CFe.002). Under his leadership, the LRA has engaged in the abduction, killing, and mutilation of thousands of civilians across Central Africa. The LRA has been responsible for kidnapping, displacing, committing sexual violence against, and killing hundreds of individuals across CAR, and has looted and destroyed civilian property. Father’s name is Luizi Obol. Mother’s name is Nora Obol. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Ali Kony is a deputy in the Lord’s Resistance Army (LRA) (CFe.002), a designated entity and the son of LRA leader Joseph Kony (CFi.009), a designated individual.  Ali was incorporated into the LRA’s leadership hierarchy in 2010.  He is part of a group of senior LRA officers who are based with Joseph Kony.   INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Ali Kony is a deputy in the Lord’s Resistance Army (LRA) (CFe.002), a designated entity and the son of LRA leader Joseph Kony (CFi.009), a designated individual.  Ali was incorporated into the LRA’s leadership hierarchy in 2010.  He is part of a group of senior LRA officers who are based with Joseph Kony.   INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -3073,7 +3073,7 @@
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Salim Kony is a deputy in the Lord’s Resistance Army (LRA) (CFe.002), a designated entity and the son of LRA leader Joseph Kony (CFi.009), a designated individual. Salim was incorporated into the LRA’s leadership hierarchy in 2010.  He is part of a group of senior LRA officers who are based with Joseph Kony.   INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Salim Kony is a deputy in the Lord’s Resistance Army (LRA) (CFe.002), a designated entity and the son of LRA leader Joseph Kony (CFi.009), a designated individual. Salim was incorporated into the LRA’s leadership hierarchy in 2010.  He is part of a group of senior LRA officers who are based with Joseph Kony.   INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Hissène was formerly the Minister of Youth and Sports as part of the Cabinet for the Central African Republic’s former President Michel Djotodia. Prior to that, he was the head of the Convention of Patriots for Justice and Peace, a political party. He also established himself as a leader of armed militias in Bangui, in particular in the “PK5” (3rd district) neighborhood. In October 2016, Abdoulaye Hissène was appointed President of the Conseil National de Défense et de Sécurité, a body which was created at the time to gather military leaders and commanding fighters from all ex-Séléka factions. He has remained in this position since then, but has actual control over FPRC fighters only. Father’s name is Abdoulaye. Mother’s name is Absita Moussa. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Hissène was formerly the Minister of Youth and Sports as part of the Cabinet for the Central African Republic’s former President Michel Djotodia. Prior to that, he was the head of the Convention of Patriots for Justice and Peace, a political party. He also established himself as a leader of armed militias in Bangui, in particular in the “PK5” (3rd district) neighborhood. In October 2016, Abdoulaye Hissène was appointed President of the Conseil National de Défense et de Sécurité, a body which was created at the time to gather military leaders and commanding fighters from all ex-Séléka factions. He has remained in this position since then, but has actual control over FPRC fighters only. Father’s name is Abdoulaye. Mother’s name is Absita Moussa. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Bi Sidi Souleman leads the Central African Republic (CAR)-based militia group Return, Reclamation, Rehabilitation (3R) which has killed, tortured, raped, and displaced civilians and engaged in arms trafficking, illegal taxation activities, and warfare with other militias since its creation in 2015. Bi Sidi Souleman himself has also participated in torture. On 6 February 2019, 3R signed the Political Agreement for Peace and Reconciliation in the CAR but has engaged in acts violating the Agreement and remains a threat to the peace, stability and security of the CAR. For instance, on 21 May 2019, 3R killed 34 unarmed civilians in three villages, summarily executing adult males. Bi Sidi Souleman openly confirmed to a UN Entity that he had ordered 3R elements to the villages on the date of the attacks, but did not admit to giving the orders for 3R to kill.  In December 2020, after having joined a coalition of armed groups established to disrupt the electoral process, Bi Sidi Souleman was reportedly killed during fighting.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Bi Sidi Souleman leads the Central African Republic (CAR)-based militia group Return, Reclamation, Rehabilitation (3R) which has killed, tortured, raped, and displaced civilians and engaged in arms trafficking, illegal taxation activities, and warfare with other militias since its creation in 2015. Bi Sidi Souleman himself has also participated in torture. On 6 February 2019, 3R signed the Political Agreement for Peace and Reconciliation in the CAR but has engaged in acts violating the Agreement and remains a threat to the peace, stability and security of the CAR. For instance, on 21 May 2019, 3R killed 34 unarmed civilians in three villages, summarily executing adult males. Bi Sidi Souleman openly confirmed to a UN Entity that he had ordered 3R elements to the villages on the date of the attacks, but did not admit to giving the orders for 3R to kill.  In December 2020, after having joined a coalition of armed groups established to disrupt the electoral process, Bi Sidi Souleman was reportedly killed during fighting.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Ali Darassa founded and still leads the Central African Republic (CAR)-based militia group Unité pour la Paix en Centrafrique (UPC), which has killed, tortured, raped, and displaced civilians, committed a large number of abuses of human rights and violations of international humanitarian law, and engaged in arms trafficking, illegal taxation activities, and warfare against CAR defence and security forces, as well as other militias, since its creation in 2014. In December 2020, he played a leading role in the creation of the Coalition des patriotes pour le changement (CPC) that took up arms to oppose the elections and attempted to enter the capital Bangui, in violation of the commitments made by the UPC under the Accord politique pour la paix et la reconciliation (APPR) signed on 6 February 2019.   INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Ali Darassa founded and still leads the Central African Republic (CAR)-based militia group Unité pour la Paix en Centrafrique (UPC), which has killed, tortured, raped, and displaced civilians, committed a large number of abuses of human rights and violations of international humanitarian law, and engaged in arms trafficking, illegal taxation activities, and warfare against CAR defence and security forces, as well as other militias, since its creation in 2014. In December 2020, he played a leading role in the creation of the Coalition des patriotes pour le changement (CPC) that took up arms to oppose the elections and attempted to enter the capital Bangui, in violation of the commitments made by the UPC under the Accord politique pour la paix et la reconciliation (APPR) signed on 6 February 2019.   INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -3293,7 +3293,7 @@
           <t>Camará was listed on 18 May 2012 pursuant to paragraph 4 of resolution
 2048 (2012) as “Member of the “Military Command”, which has assumed responsibility for
 the coup d’état of 12 April 2012.” Father’s name is Suareba Camará; Mother’s name is
-Sale Queita. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Sale Queita. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -3334,7 +3334,7 @@
           <t>Danfa was listed on 18 Jul. 2012 pursuant to paragraph 4 of resolution
 2048 (2012) as “Member of the “Military Command” which has assumed responsibility for
 the coup d'état of 12 April 2012. Close Advisor to Armed Forces Chief of Staff António
-Injai.” INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Injai.” INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -3381,7 +3381,7 @@
 responsibility for the coup d'état of 12 April 2012 and one of its most active members.
 He was one of the first officers to publicly assume his affiliation to the “Military
 Command”, having signed one of its first communiqués (nº5, dated 13 April 2012). Major
-Djaló also belongs to the Military Intelligence.” INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Djaló also belongs to the Military Intelligence.” INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
 the coup d’état of 12 April 2012. In the aftermath of the coup, the first communiqué by
 the “Military Command” was issued by the Armed Forces General Staff, which is led by
 General Injai.” Father’s name is Wasna Injai; Mother’s name is Quiritche
-Cofte. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Cofte. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -3473,7 +3473,7 @@
         <is>
           <t>Na Bidon was listed on 18 Jul. 2012 pursuant to paragraph 4 of resolution
 2048 (2012) as “Member of the “Military Command” which has assumed responsibility for
-the coup d'état of 12 April 2012.” Parentage: “Nabidom”. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+the coup d'état of 12 April 2012.” Parentage: “Nabidom”. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
 2048 (2012) as “Member of the “Military Command” which has assumed responsibility for
 the coup d'état of 12 April 2012. Also a member of the Military High Command (highest
 hierarchy of the Bissau-Guinean Armed Forces).” Father’s name is Biute Naman; Mother’s
-name is Ndjade Na Noa. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+name is Ndjade Na Noa. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -3559,7 +3559,7 @@
         <is>
           <t>Na Mena was listed on 18 May 2012 pursuant to paragraph 4 of resolution
 2048 (2012) as “Member of the “Military Command” which has assumed responsibility for
-the coup d’état of 12 April 2012.” INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+the coup d’état of 12 April 2012.” INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -3604,7 +3604,7 @@
           <t>Naualna was listed on 18 May 2012 pursuant to paragraph 4 of resolution
 2048 (2012) as “Spokesperson of the “Military Command” which has assumed responsibility
 for the coup d’état of 12 April 2012.” Father’s name is Samba Naualna; Mother’s name is
-In-Uasne Nanfafe. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+In-Uasne Nanfafe. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -3646,7 +3646,7 @@
 2048 (2012) as “Member of the "Military Command" which has assumed responsibility for
 the coup d'état of 12 April 2012. A loyal ally of António Injai, Lt.Col. Júlio Nhate has
 the material responsibility for the 12 April 2012 coup, having conducted the military
-operation.”  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+operation.”  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -3690,7 +3690,7 @@
         <is>
           <t>Ture was listed on 18 May 2012 pursuant to paragraph 4 of resolution 2048
 (2012) as “Member of the “Military Command” which has assumed responsibility for the
-coup d’état of 12 April 2012.” INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+coup d’état of 12 April 2012.” INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Jimmy Cherizier (AKA “Barbeque”) has engaged in acts that threaten the peace, security, and stability of Haiti and has planned, directed, or committed acts that constitute serious human rights abuses. Jimmy Cherizier is one of Haiti’s most influential gang leaders and leads an alliance of Haitian gangs known as the "G9 Family and Allies." INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Jimmy Cherizier (AKA “Barbeque”) has engaged in acts that threaten the peace, security, and stability of Haiti and has planned, directed, or committed acts that constitute serious human rights abuses. Jimmy Cherizier is one of Haiti’s most influential gang leaders and leads an alliance of Haitian gangs known as the "G9 Family and Allies." INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -11200,7 +11200,7 @@
       <c r="G273" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel Ban). Believed
-status/location: deceased. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+status/location: deceased. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
@@ -11235,7 +11235,7 @@
       <c r="G274" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel
-Ban). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Ban). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
@@ -11274,7 +11274,7 @@
       <c r="G275" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel
-Ban). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Ban). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -11387,7 +11387,7 @@
       <c r="G278" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel Ban). Listed
-on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
@@ -11423,7 +11423,7 @@
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel Ban). Listed
 on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). Believed
-status/location: deceased. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+status/location: deceased. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
@@ -11459,7 +11459,7 @@
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel Ban). Listed
 on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). Believed
-status/location: unknown, believed captured. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+status/location: unknown, believed captured. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
@@ -11498,7 +11498,7 @@
       <c r="G281" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 17 of resolution 1970 (
-Asset Freeze). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Asset Freeze). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
@@ -11533,7 +11533,7 @@
       <c r="G282" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban,
-Asset Freeze). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Asset Freeze). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
@@ -11568,7 +11568,7 @@
       <c r="G283" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban,
-Asset Freeze). Believed status/location: deceased. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Asset Freeze). Believed status/location: deceased. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
@@ -11607,7 +11607,7 @@
       <c r="G284" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban,
-Asset Freeze). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Asset Freeze). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
@@ -11642,7 +11642,7 @@
       <c r="G285" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban,
-Asset Freeze). Believed status/location: deceased. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Asset Freeze). Believed status/location: deceased. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
@@ -11680,7 +11680,7 @@
       <c r="F286" s="5" t="inlineStr"/>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban,Asset Freeze). Believed status/location: deceased. Reportedly deceased in Sirte, Libya, on 20 October 2011. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban,Asset Freeze). Believed status/location: deceased. Reportedly deceased in Sirte, Libya, on 20 October 2011. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
@@ -11715,7 +11715,7 @@
       <c r="G287" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel Ban). Listed
-on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
@@ -11751,7 +11751,7 @@
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel Ban). Listed
 on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). Believed
-status/location: deceased. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+status/location: deceased. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
@@ -11786,7 +11786,7 @@
       <c r="G289" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban,
-Asset Freeze). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+Asset Freeze). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
@@ -11825,7 +11825,7 @@
       <c r="G290" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 15 of resolution 1970 (Travel Ban). Listed
-on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+on 17 March 2011 pursuant to paragraph 17 of resolution 1970 (Asset Freeze). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
@@ -11863,7 +11863,7 @@
       <c r="F291" s="5" t="inlineStr"/>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraph 19 of resolution 1973 (Asset Freeze).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Listed pursuant to paragraph 19 of resolution 1973 (Asset Freeze).  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>As de facto manager of the Al Nasr detention center the person concerned has directly, and/or through subordinates engaged in or provided support to acts that violate applicable international human rights law, or acts that constitute human rights abuses in Libya. The Person concerned has acted for or on behalf of or at the direction of two listed individuals intrinsically linked to the human trafficking activities of the Zawiyah network, namely Mohamed Kashlaf (LYi.025) and Abdulrahman al Milad (LYi.026).  Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze)  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As de facto manager of the Al Nasr detention center the person concerned has directly, and/or through subordinates engaged in or provided support to acts that violate applicable international human rights law, or acts that constitute human rights abuses in Libya. The Person concerned has acted for or on behalf of or at the direction of two listed individuals intrinsically linked to the human trafficking activities of the Zawiyah network, namely Mohamed Kashlaf (LYi.025) and Abdulrahman al Milad (LYi.026).  Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze)  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Responsible for Usama bin Laden’s (deceased) security. Hair: Dark. Eyes: Dark. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice . Review pursuant to Security Council resolution 1822 (2008) was concluded on 15 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 February 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Responsible for Usama bin Laden’s (deceased) security. Hair: Dark. Eyes: Dark. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -12317,9 +12317,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>Security coordinator for Usama bin Laden (deceased). Repatriated to
-Afghanistan in February 2006. He was in Afghanistan as of August 2021. Review pursuant to Security Council resolution 1822 (2008)
-was concluded on 15 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Security coordinator for Usama bin Laden (deceased). Repatriated to Afghanistan in February 2006. He was in Afghanistan as of August 2021 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -12357,10 +12355,7 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>Driver and private bodyguard to Usama bin Laden (deceased) from 1996
-until 2001. Transferred from United States custody to Yemen in Nov. 2008. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jul.
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.</t>
+          <t>Driver and private bodyguard to Usama bin Laden (deceased) from 1996 until 2001. Transferred from United States custody to Yemen in Nov. 2008</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
@@ -12402,7 +12397,7 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>Leader of Al-Qaida (QDe.004). Former operational and military leader of Egyptian Islamic Jihad (QDe.003), was a close associate of Usama Bin Laden (deceased). Believed to have been in the Afghanistan/Pakistan border area before going to Afghanistan in 2014. Reportedly killed in drone strike in Kabul, Afghanistan on 31 July 2022. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Al-Qaida (QDe.004). Former operational and military leader of Egyptian Islamic Jihad (QDe.003), was a close associate of Usama Bin Laden (deceased). Believed to have been in the Afghanistan/Pakistan border area before going to Afghanistan in 2014. Reportedly killed in drone strike in Kabul, Afghanistan on 31 July 2022. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
@@ -12436,8 +12431,7 @@
       <c r="F305" s="5" t="inlineStr"/>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>Senior lieutenant of UBL. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior lieutenant of UBL INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
@@ -12479,14 +12473,7 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>Joined Al-Qaida in 1996 and was at that time an important liaison to the
-                Taliban in Afghanistan. Received money from Ansar al-Islam (QDe.098) in order to
-                conduct attacks in Kirkuk and Ninveh in Iraq during spring and summer of 2005.
-                Al-Qaida senior official. In custody of the United States of America, as of Aug.
-                2014. Father’s name: Abd al-Razzaq Abd al-Baqi. Mother’s name: Nadira Ayoub Asaad.
-                Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-                Review pursuant to Security Council resolution 1822 (2008) was concluded on 15 Jun.
-                2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Joined Al-Qaida in 1996 and was at that time an important liaison to the Taliban in Afghanistan. Received money from Ansar al-Islam (QDe.098) in order to conduct attacks in Kirkuk and Ninveh in Iraq during spring and summer of 2005. Al-Qaida senior official. In custody of the United States of America, as of Aug. 2014. Father’s name: Abd al-Razzaq Abd al-Baqi. Mother’s name: Nadira Ayoub Asaad. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
@@ -12528,10 +12515,7 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased in October 2001. Review pursuant to Security Council
-                resolution 1822 (2008) was concluded on 29 Jul. 2010. Review pursuant to Security
-                Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to
-                Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased in October 2001 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
@@ -12573,8 +12557,7 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 15 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
@@ -12616,8 +12599,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 15 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -12655,8 +12637,7 @@
       <c r="F310" s="5" t="inlineStr"/>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Pakistan. Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 15 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -12698,8 +12679,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Afghanistan. Review pursuant to Security Council resolution 1822 (2008)
-was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Afghanistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -12741,12 +12721,7 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>Responsible for the finances of Al-Qa’ida (QDe.004) in Yemen. Accused of
-involvement in the attack on the USS Cole in 2000. Arrested in Yemen in Nov. 2003.
-Sentenced to three years and one month of imprisonment by the specialized criminal court
-of first instance in Yemen. Released on 25 Dec. 2006 after the completion of his
-sentence. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8
-Jul. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Responsible for the finances of Al-Qa’ida (QDe.004) in Yemen. Accused of involvement in the attack on the USS Cole in 2000. Arrested in Yemen in Nov. 2003. Sentenced to three years and one month of imprisonment by the specialized criminal court of first instance in Yemen. Released on 25 Dec. 2006 after the completion of his sentence INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
@@ -12788,9 +12763,7 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>Apprehended in July 2004 and in custody for trial in the United States of
-America, as at October 2010. Review pursuant to Security Council resolution 1822 (2008)
-was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Apprehended in July 2004 and in custody for trial in the United States of America, as at October 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
@@ -12832,7 +12805,7 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>In custody in Jordan since 26 Feb. 2015 for recruitment and support to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Father’s name is Mohammad Hijazi. Mother’s name is Sakina. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>In custody in Jordan since 26 Feb. 2015 for recruitment and support to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Father’s name is Mohammad Hijazi. Mother’s name is Sakina INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
@@ -12874,12 +12847,7 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>Associated with Al-Qaida-related groups in the United Kingdom and other
-countries. Convicted in absentia in Jordan for involvement in terrorist acts in 1998.
-Arrested in Feb. 2001 in the United Kingdom, was further detained between Oct. 2002 and
-Mar. 2005 and between Aug. 2005 and Jun. 2008. In custody since Dec. 2008. Deported to
-Jordan from the United Kingdom on 7 July 2013 to face terrorism charges. Review pursuant
-to Security Council resolution 1822 (2008) was concluded on 19 Oct. 2009. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Al-Qaida-related groups in the United Kingdom and other countries. Convicted in absentia in Jordan for involvement in terrorist acts in 1998. Arrested in Feb. 2001 in the United Kingdom, was further detained between Oct. 2002 and Mar. 2005 and between Aug. 2005 and Jun. 2008. In custody since Dec. 2008. Deported to Jordan from the United Kingdom on 7 July 2013 to face terrorism charges INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
@@ -12921,8 +12889,7 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>Abdul Rahman Yasin is in Iraq. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Abdul Rahman Yasin is in Iraq INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
@@ -12964,12 +12931,7 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>Family background: from the Hawiye's Habergidir, Ayr clan. Senior leader
-of Al-Itihaad Al-Islamiya (AIAI) (QDe.002) and Hizbul Islam in Somalia. Since 12 April
-2010, also subject to the sanctions measures set out in Security Council resolution 1844
-(2008) concerning Somalia and Eritrea (seehttps://www.un.org/sc/suborg/en/sanctions/751).
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Jun.
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Family background: from the Hawiye's Habergidir, Ayr clan. Senior leader of Al-Itihaad Al-Islamiya (AIAI) (QDe.002) and Hizbul Islam in Somalia. Since 12 April 2010, also subject to the sanctions measures set out in Security Council resolution 1844 (2008) concerning Somalia and Eritrea (seehttps://www.un.org/sc/suborg/en/sanctions/751) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
@@ -13011,8 +12973,7 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 1 Jun. 2010.  Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
@@ -13054,7 +13015,7 @@
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>Associated with Afghan Support Committee (ASC) (QDe.069), Revival of Islamic Heritage Society (RIHS)(QDe.070) and the Libyan Islamic Fighting Group (LIFG) (QDe.011). Photograph and fingerprints available for inclusion in the INTERPOL-UNSC Special Notice. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Afghan Support Committee (ASC) (QDe.069), Revival of Islamic Heritage Society (RIHS)(QDe.070) and the Libyan Islamic Fighting Group (LIFG) (QDe.011). Photograph and fingerprints available for inclusion in the INTERPOL-UNSC Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
@@ -13096,7 +13057,7 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>Finance chief of the Afghan Support Committee (ASC) (QDe.069). Al-Qaida (QDe.004) facilitator and communication expert. Believed to be in Algeria as of Apr. 2010 and May 2022. Son of Mohamed and Fatma Aribi. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Finance chief of the Afghan Support Committee (ASC) (QDe.069). Al-Qaida (QDe.004) facilitator and communication expert. Believed to be in Algeria as of Apr. 2010 and May 2022. Son of Mohamed and Fatma Aribi INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
@@ -13138,7 +13099,7 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>Extradited from the United Kingdom to the United States of America on 5 Oct. 2012. Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Apr. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Extradited from the United Kingdom to the United States of America on 5 Oct. 2012 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -13180,7 +13141,7 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>Head of security wing of Ansar al-Shari'a in Tunisia (AAS-T) (QDe.143). Mother's name is Ourida Bint Mohamed. Deported from Italy to Tunisia on 1 Dec. 2004. Arrested in Tunisia in Aug. 2013. Imprisoned in the civilian prison of Burj al-‘Amiri on 13 Sep. 2013. Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Apr. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Head of security wing of Ansar al-Shari'a in Tunisia (AAS-T) (QDe.143). Mother's name is Ourida Bint Mohamed. Deported from Italy to Tunisia on 1 Dec. 2004. Arrested in Tunisia in Aug. 2013. Imprisoned in the civilian prison of Burj al-‘Amiri on 13 Sep. 2013 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
@@ -13222,9 +13183,7 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>Professor of Chemistry. Deported from Italy to Tunisia on 27 Aug. 2006.
-Legally changed family name from Aouani to Lakhal in 2014. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 22 Apr. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Professor of Chemistry. Deported from Italy to Tunisia on 27 Aug. 2006. Legally changed family name from Aouani to Lakhal in 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
@@ -13266,9 +13225,7 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>Mother’s name is Beya Al-Saidani. Deported from Italy to Tunisia on 2
-Jun. 2008. Imprisoned in Tunisia in Aug. 2014. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 22 Apr. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother’s name is Beya Al-Saidani. Deported from Italy to Tunisia on 2 Jun. 2008. Imprisoned in Tunisia in Aug. 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
@@ -13310,7 +13267,7 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>Italian Fiscal Code: SSYBLK62T26Z336L. Sentenced to 8 years imprisonment in Italy on 2 February 2004. Considered a fugitive from justice by the Italian authorities. Reportedly killed in 2012. Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Apr. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Italian Fiscal Code: SSYBLK62T26Z336L. Sentenced to 8 years imprisonment in Italy on 2 February 2004. Considered a fugitive from justice by the Italian authorities. Reportedly killed in 2012 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
@@ -13352,10 +13309,7 @@
       </c>
       <c r="G326" s="5" t="inlineStr">
         <is>
-          <t>Extradited from the United Kingdom to the United States of America on 5
-Oct. 2012. Convicted on terrorism charges by a court in the United States of America in
-May 2014. Review pursuant to Security Council resolution 1822 (2008) was concluded on 22
-Apr. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Extradited from the United Kingdom to the United States of America on 5 Oct. 2012. Convicted on terrorism charges by a court in the United States of America in May 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H326" s="5" t="inlineStr">
@@ -13397,11 +13351,7 @@
       </c>
       <c r="G327" s="5" t="inlineStr">
         <is>
-          <t>Deported from Italy to Tunisia on 28 February 2004. Serving a 12-year
-prison sentence in Tunisia for membership in a terrorist organization abroad as at Jan.
-2010. Arrested in Tunisia in 2013. Legally changed family name from Ben Soltane to Hamdi
-in 2014. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21
-Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Deported from Italy to Tunisia on 28 February 2004. Serving a 12-year prison sentence in Tunisia for membership in a terrorist organization abroad as at Jan. 2010. Arrested in Tunisia in 2013. Legally changed family name from Ben Soltane to Hamdi in 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H327" s="5" t="inlineStr">
@@ -13443,10 +13393,7 @@
       </c>
       <c r="G328" s="5" t="inlineStr">
         <is>
-          <t>Italian Fiscal Code: KMMMHD68D03Z352N. Deported from Italy to Tunisia on
-22 July 2005. Serving an eight-year prison term in Tunisia for membership of a terrorist
-organization abroad as at Jan. 2010. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023 INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Italian Fiscal Code: KMMMHD68D03Z352N. Deported from Italy to Tunisia on 22 July 2005. Serving an eight-year prison term in Tunisia for membership of a terrorist organization abroad as at Jan. 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H328" s="5" t="inlineStr">
@@ -13488,9 +13435,7 @@
       </c>
       <c r="G329" s="5" t="inlineStr">
         <is>
-          <t>Belgian nationality withdrawn on 26 Jan. 2009. In detention in Nivelles,
-Belgium, as of Oct. 2010. Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belgian nationality withdrawn on 26 Jan. 2009. In detention in Nivelles, Belgium, as of Oct. 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H329" s="5" t="inlineStr">
@@ -13532,8 +13477,7 @@
       </c>
       <c r="G330" s="5" t="inlineStr">
         <is>
-          <t>Deported from Italy to Algeria on 12 Aug. 2006. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 8 Dec. 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Deported from Italy to Algeria on 12 Aug. 2006 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H330" s="5" t="inlineStr">
@@ -13575,8 +13519,7 @@
       </c>
       <c r="G331" s="5" t="inlineStr">
         <is>
-          <t>Was deported from Germany to Jordan in Feb. 2005. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Was deported from Germany to Jordan in Feb. 2005 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H331" s="5" t="inlineStr">
@@ -13618,7 +13561,7 @@
       </c>
       <c r="G332" s="5" t="inlineStr">
         <is>
-          <t>Deputy head of the media committee of Al-Qaida (QDe.004) as at Apr. 2010. German authorities issued an arrest warrant for him on 21 Sep. 2001. Review pursuant to Security Council resolution 1822 (2008) was concluded on 20 May 2010. Reportedly deceased in September 2013 in the Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Deputy head of the media committee of Al-Qaida (QDe.004) as at Apr. 2010. German authorities issued an arrest warrant for him on 21 Sep. 2001. Reportedly deceased in September 2013 in the Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H332" s="5" t="inlineStr">
@@ -13660,9 +13603,7 @@
       </c>
       <c r="G333" s="5" t="inlineStr">
         <is>
-          <t>Arrested in Karachi, Pakistan, 30 Sep. 2002. In custody of the United
-States of America, as of May 2010. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 25 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019 INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Arrested in Karachi, Pakistan, 30 Sep. 2002. In custody of the United States of America, as of May 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H333" s="5" t="inlineStr">
@@ -13704,11 +13645,7 @@
       </c>
       <c r="G334" s="5" t="inlineStr">
         <is>
-          <t>Arrested on 28 Nov. 2001 and found guilty in Germany of being an
-accessory to murder and of membership in a terrorist organization and sentenced to 15
-years of imprisonment on 8 Jan. 2007. Father's name is Brahim Brik. Mother's name is
-Habiba Abbes. Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 20 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019 INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Arrested on 28 Nov. 2001 and found guilty in Germany of being an accessory to murder and of membership in a terrorist organization and sentenced to 15 years of imprisonment on 8 Jan. 2007. Father's name is Brahim Brik. Mother's name is Habiba Abbes INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H334" s="5" t="inlineStr">
@@ -13750,9 +13687,7 @@
       </c>
       <c r="G335" s="5" t="inlineStr">
         <is>
-          <t>Father's name is Mohamed ben Ahmed. Mother's name is Sfia bent Toubali.
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 20 May
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father's name is Mohamed ben Ahmed. Mother's name is Sfia bent Toubali INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H335" s="5" t="inlineStr">
@@ -13794,7 +13729,7 @@
       </c>
       <c r="G336" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H336" s="5" t="inlineStr">
@@ -13836,10 +13771,7 @@
       </c>
       <c r="G337" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of Jemaah Islamiyah (QDe.092). Brother of Gun Gun Rusman
-Gunawan (QDi.218). In custody of the United States of America, as of July 2007. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 13 Apr.
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior leader of Jemaah Islamiyah (QDe.092). Brother of Gun Gun Rusman Gunawan (QDi.218). In custody of the United States of America, as of July 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H337" s="5" t="inlineStr">
@@ -13881,9 +13813,7 @@
       </c>
       <c r="G338" s="5" t="inlineStr">
         <is>
-          <t>Father’s name is Mahmoud ben Sasi. Mother’s name is Maryam bint
-al-Tijani. Inadmissible to the Schengen area. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 22 Apr. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father’s name is Mahmoud ben Sasi. Mother’s name is Maryam bint al-Tijani. Inadmissible to the Schengen area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H338" s="5" t="inlineStr">
@@ -13925,11 +13855,7 @@
       </c>
       <c r="G339" s="5" t="inlineStr">
         <is>
-          <t>Considered by Italian authorities as a wanted fugitive (in Oct 2019). Left Sudan for Tunisia in 2011.
-The review pursuant to Security Council resolution 1822 (2008) was completed on 15 June 2010 
-The review pursuant to resolution 2368 (2017) concluded on 4 Dec 2019
-The review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Considered by Italian authorities as a wanted fugitive (in Oct 2019). Left Sudan for Tunisia in 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H339" s="5" t="inlineStr">
@@ -13967,11 +13893,7 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>Arrested 13 Mar. 2002, sentenced 12 July 2002 in the Philippines.
-Released from custody in the Philippines on 1 Jan. 2014 and subsequently deported to
-Indonesia. Physical description: height 165 cm. Photo available for inclusion in the
-INTERPOL-UN Security Council Special Notice. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 25 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Arrested 13 Mar. 2002, sentenced 12 July 2002 in the Philippines. Released from custody in the Philippines on 1 Jan. 2014 and subsequently deported to Indonesia. Physical description: height 165 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
@@ -14013,8 +13935,7 @@
       </c>
       <c r="G341" s="5" t="inlineStr">
         <is>
-          <t>In detention in the Philippines as at May 2011. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 25 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>In detention in the Philippines as at May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H341" s="5" t="inlineStr">
@@ -14052,8 +13973,7 @@
       </c>
       <c r="G342" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 25 May 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H342" s="5" t="inlineStr">
@@ -14095,9 +14015,7 @@
       </c>
       <c r="G343" s="5" t="inlineStr">
         <is>
-          <t>Mother's name is Aminah Ahmad Sher al-Baloushi. In custody of the United
-States. Review pursuant to Security Council resolution 1822 (2008) was concluded on 25
-May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother's name is Aminah Ahmad Sher al-Baloushi. In custody of the United States INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H343" s="5" t="inlineStr">
@@ -14139,8 +14057,7 @@
       </c>
       <c r="G344" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 25 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H344" s="5" t="inlineStr">
@@ -14182,8 +14099,7 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>At large as at Dec. 2003. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 25 May 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 February 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>At large as at Dec. 2003 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
@@ -14225,7 +14141,7 @@
       </c>
       <c r="G346" s="5" t="inlineStr">
         <is>
-          <t>Founding member of Jemaah Islamiyah (JI) (QDe.092) who worked on Al-Qaida’s (QDe.004) biological weapons program, provided support to those involved in Al-Qaida’s 11 Sep. 2001 attacks in the United States of America, and was involved in JI bombing operations. Detained in Malaysia from 2001 to 2008. Arrested in Malaysia in 2013 and sentenced to 7 years in Jan. 2016 for failing to report information relating to terrorist acts. Completed detention on 20 November 2019. Served a two-year restricted residence order in Selangor Malaysia until 21 November 2021. Review pursuant to Security Council resolution 1989 (2011) was concluded on 6 Mar. 2014. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. Photos included in  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Founding member of Jemaah Islamiyah (JI) (QDe.092) who worked on Al-Qaida’s (QDe.004) biological weapons program, provided support to those involved in Al-Qaida’s 11 Sep. 2001 attacks in the United States of America, and was involved in JI bombing operations. Detained in Malaysia from 2001 to 2008. Arrested in Malaysia in 2013 and sentenced to 7 years in Jan. 2016 for failing to report information relating to terrorist acts. Completed detention on 20 November 2019. Served a two-year restricted residence order in Selangor Malaysia until 21 November 2021.. Photos included in INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H346" s="5" t="inlineStr">
@@ -14267,10 +14183,7 @@
       </c>
       <c r="G347" s="5" t="inlineStr">
         <is>
-          <t>Sentenced to life without parole in the Philippines on 23 Jan. 2009 for his
-                involvement in the bombings of 30 Dec. 2000 in Manila, the Philippines. Review
-                pursuant to Security Council resolution 1822 (2008) was concluded on 25 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.
-                Photos included in INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Sentenced to life without parole in the Philippines on 23 Jan. 2009 for his involvement in the bombings of 30 Dec. 2000 in Manila, the Philippines.. Photos included in INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H347" s="5" t="inlineStr">
@@ -14312,10 +14225,7 @@
       </c>
       <c r="G348" s="5" t="inlineStr">
         <is>
-          <t>Father's name is Djelalli Moustfa. Mother's name is Kadeja Mansore.
-Deported from Germany to Algeria in Sep. 2007.
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 19 Oct.
-2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father's name is Djelalli Moustfa. Mother's name is Kadeja Mansore. Deported from Germany to Algeria in Sep. 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H348" s="5" t="inlineStr">
@@ -14357,10 +14267,7 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>Father’s name is Sheikh Ibrahim Ali Kaskar, mother’s name is Amina Bi, wife’s
-name is Mehjabeen Shaikh. International arrest warrant issued by the Government of India. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 20 May
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father’s name is Sheikh Ibrahim Ali Kaskar, mother’s name is Amina Bi, wife’s name is Mehjabeen Shaikh. International arrest warrant issued by the Government of India INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
@@ -14402,11 +14309,7 @@
       </c>
       <c r="G350" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased in November 2016. Father's name is Mohamed. Mother's name is Zohra Chemkha. Member of the
-Council of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) (AQIM). Head of
-Al Mouakaoune Biddam (QDe.139), Al Moulathamoun (QDe.140) and Al Mourabitoun (QDe.141).
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 30 Jul.
-2009.  Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased in November 2016. Father's name is Mohamed. Mother's name is Zohra Chemkha. Member of the Council of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) (AQIM). Head of Al Mouakaoune Biddam (QDe.139), Al Moulathamoun (QDe.140) and Al Mourabitoun (QDe.141) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H350" s="5" t="inlineStr">
@@ -14448,7 +14351,7 @@
       </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
-          <t>Mother’s name is Zina al-Zarkaoui. Sentenced to seven years and one month of imprisonment by the Court of Appeals of Milan in Italy. Released on 31 Mar. 2014 on early release. Review pursuant to Security Council resolution 1822 (2008) was concluded on 6 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother’s name is Zina al-Zarkaoui. Sentenced to seven years and one month of imprisonment by the Court of Appeals of Milan in Italy. Released on 31 Mar. 2014 on early release INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H351" s="5" t="inlineStr">
@@ -14490,7 +14393,7 @@
       </c>
       <c r="G352" s="5" t="inlineStr">
         <is>
-          <t>Mother’s name is Khamisah al-Kathiri. Subject to a decree of expulsion, suspended on 17 Apr. 2007 by the European Court of Human Rights. Re-arrested in Italy on 20 May 2008. Deported from Italy to Tunisia on 6 May 2015. Inadmissible to the Schengen area. Review pursuant to Security Council resolution 1822 (2008) was concluded on 6 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother’s name is Khamisah al-Kathiri. Subject to a decree of expulsion, suspended on 17 Apr. 2007 by the European Court of Human Rights. Re-arrested in Italy on 20 May 2008. Deported from Italy to Tunisia on 6 May 2015. Inadmissible to the Schengen area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H352" s="5" t="inlineStr">
@@ -14532,10 +14435,7 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>Present in Somalia as of Apr. 2009 following transfer from United Kingdom.
-                Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun.
-                2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24
-                November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Present in Somalia as of Apr. 2009 following transfer from United Kingdom INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
@@ -14577,10 +14477,7 @@
       </c>
       <c r="G354" s="5" t="inlineStr">
         <is>
-          <t>Sentenced to ten years of imprisonment by the Court of first instance of
-Milan on 21 Sep. 2006. In custody in Italy. Due for release on 6 Jan. 2012. Subject to
-expulsion from Italy after serving the sentence. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Sentenced to ten years of imprisonment by the Court of first instance of Milan on 21 Sep. 2006. In custody in Italy. Due for release on 6 Jan. 2012. Subject to expulsion from Italy after serving the sentence INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H354" s="5" t="inlineStr">
@@ -14622,7 +14519,7 @@
       </c>
       <c r="G355" s="5" t="inlineStr">
         <is>
-          <t>In prison in Italy until 6 February 2026. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>In prison in Italy until 6 February 2026 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H355" s="5" t="inlineStr">
@@ -14664,7 +14561,7 @@
       </c>
       <c r="G356" s="5" t="inlineStr">
         <is>
-          <t>Mother's name: Attia Mohiuddin Taha. A deportation order was issued by the Italian authorities on 18 Oct. 2004. Considered a fugitive from justice by the Italian authorities as of Sep. 2007. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 February 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother's name: Attia Mohiuddin Taha. A deportation order was issued by the Italian authorities on 18 Oct. 2004. Considered a fugitive from justice by the Italian authorities as of Sep. 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H356" s="5" t="inlineStr">
@@ -14702,10 +14599,7 @@
       </c>
       <c r="G357" s="5" t="inlineStr">
         <is>
-          <t>Under administrative control measure in Italy which expired on 15
-Jan. 2012. Review pursuant to Security Council resolution 1822 (2008) was concluded on
-21 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019.  Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Under administrative control measure in Italy which expired on 15 Jan. 2012 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H357" s="5" t="inlineStr">
@@ -14747,7 +14641,7 @@
       </c>
       <c r="G358" s="5" t="inlineStr">
         <is>
-          <t>Sentenced to six years of imprisonment for international terrorism in 2008. Deported from Italy to Tunisia on 10 Feb. 2013. Inadmissible to the Schengen area. Mother’s name is Khadijah al-Drissi. Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Apr. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Sentenced to six years of imprisonment for international terrorism in 2008. Deported from Italy to Tunisia on 10 Feb. 2013. Inadmissible to the Schengen area. Mother’s name is Khadijah al-Drissi INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H358" s="5" t="inlineStr">
@@ -14789,14 +14683,7 @@
       </c>
       <c r="G359" s="5" t="inlineStr">
         <is>
-          <t>Sentenced to six years and ten months of imprisonment for membership of a
-                terrorist association by the Appeal Court of Milan, Italy, on 7 Feb. 2008.
-                Imprisoned in Sfax Prison on 5 June 2007 pursuant to an order issued by the Appeals
-                Tribunal in Tunisia for joining an organization linked to terrorist crimes (case
-                No.9301/207). Sentenced to two years and 15 days’ imprisonment and released on 18
-                June 2008. Considered a fugitive from justice by the Italian authorities as at Jul.
-                2008. On 20 January 2009, Italian authorities issued a detention order (No. 70/2009 S.I.E.P), following a 3 years 4 months and 29 days sentence for terrorism-related crimes. Under administrative control measure in Tunisia as at 2010. Review pursuant to
-                Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Sentenced to six years and ten months of imprisonment for membership of a terrorist association by the Appeal Court of Milan, Italy, on 7 Feb. 2008. Imprisoned in Sfax Prison on 5 June 2007 pursuant to an order issued by the Appeals Tribunal in Tunisia for joining an organization linked to terrorist crimes (case No.9301/207). Sentenced to two years and 15 days’ imprisonment and released on 18 June 2008. Considered a fugitive from justice by the Italian authorities as at Jul. 2008. On 20 January 2009, Italian authorities issued a detention order (No. 70/2009 S.I.E.P), following a 3 years 4 months and 29 days sentence for terrorism-related crimes. Under administrative control measure in Tunisia as at 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H359" s="5" t="inlineStr">
@@ -14838,7 +14725,7 @@
       </c>
       <c r="G360" s="5" t="inlineStr">
         <is>
-          <t>In detention in Algeria since Oct. 2004. Incarcerated in Algeria since 7 March 2011. Former member of the GSPC listed as The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Father’s name: Abdellah. Mother’s name: Draham Belanchi. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>In detention in Algeria since Oct. 2004. Incarcerated in Algeria since 7 March 2011. Former member of the GSPC listed as The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Father’s name: Abdellah. Mother’s name: Draham Belanchi. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H360" s="5" t="inlineStr">
@@ -14880,8 +14767,7 @@
       </c>
       <c r="G361" s="5" t="inlineStr">
         <is>
-          <t>Left Kuwait for Pakistan in June 2001. His Kuwaiti citizenship has been revoked since 2001, and he is currently incarcerated in the United States of America. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Left Kuwait for Pakistan in June 2001. His Kuwaiti citizenship has been revoked since 2001, and he is currently incarcerated in the United States of America INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H361" s="5" t="inlineStr">
@@ -14923,7 +14809,7 @@
       </c>
       <c r="G362" s="5" t="inlineStr">
         <is>
-          <t>Father's name is Abdelkader. Mother's name is Djohra Birouch. Returned from France to Algeria where he resides since Sep. 2008. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father's name is Abdelkader. Mother's name is Djohra Birouch. Returned from France to Algeria where he resides since Sep. 2008 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H362" s="5" t="inlineStr">
@@ -14965,8 +14851,7 @@
       </c>
       <c r="G363" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 2 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H363" s="5" t="inlineStr">
@@ -15008,7 +14893,7 @@
       </c>
       <c r="G364" s="5" t="inlineStr">
         <is>
-          <t>In detention in Algeria as  of November 2023. Sentenced to 18 years imprisonment for conducting terrorist activities by the Algiers Criminal Court on 25 January 2023. Arrest warrant issued by the German authorities on 9 Oct. 2003 and 18 July 2018 respectively for involvement in kidnapping, robbery and extortion. Former member of the Katibat Tarek Ibn Ziad of The Organization of Al Qaida in the Islamic Maghreb (QDe.014). Father’s name: Sliman. Mother’s name Oum Hani Djermane.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>In detention in Algeria as of November 2023. Sentenced to 18 years imprisonment for conducting terrorist activities by the Algiers Criminal Court on 25 January 2023. Arrest warrant issued by the German authorities on 9 Oct. 2003 and 18 July 2018 respectively for involvement in kidnapping, robbery and extortion. Former member of the Katibat Tarek Ibn Ziad of The Organization of Al Qaida in the Islamic Maghreb (QDe.014). Father’s name: Sliman. Mother’s name Oum Hani Djermane INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H364" s="5" t="inlineStr">
@@ -15050,7 +14935,7 @@
       </c>
       <c r="G365" s="5" t="inlineStr">
         <is>
-          <t>Italian Fiscal Code: LBR HBB 61S17 Z352F. In detention in Tunisia as of Dec. 2009.  Reportedly fled to Afghanistan in June 2014. Mother’s name is Fatima al-Galasi. Review pursuant to Security Council resolution 1822 (2008) was concluded on 9 Apr. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019 Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023 INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Italian Fiscal Code: LBR HBB 61S17 Z352F. In detention in Tunisia as of Dec. 2009. Reportedly fled to Afghanistan in June 2014. Mother’s name is Fatima al-Galasi INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H365" s="5" t="inlineStr">
@@ -15092,7 +14977,7 @@
       </c>
       <c r="G366" s="5" t="inlineStr">
         <is>
-          <t>Wanted by the Kuwaiti Security Authorities. Wanted by the Saudi security forces. Fugitive as of Jul. 2008. Reportedly killed in a counterterrorism operation in 2015 in Syria. Review pursuant to Security Council resolution 1822 (2008) was concluded on 1 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Wanted by the Kuwaiti Security Authorities. Wanted by the Saudi security forces. Fugitive as of Jul. 2008. Reportedly killed in a counterterrorism operation in 2015 in Syria.. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H366" s="5" t="inlineStr">
@@ -15130,7 +15015,7 @@
       <c r="F367" s="5" t="inlineStr"/>
       <c r="G367" s="5" t="inlineStr">
         <is>
-          <t>Arrested in Indonesia in 2021. Was the acting Jemaah Islamiyah (JI, QDe.092) emir before his arrest, and remains a senior figure of JI.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Arrested in Indonesia in 2021. Was the acting Jemaah Islamiyah (JI, QDe.092) emir before his arrest, and remains a senior figure of JI INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H367" s="5" t="inlineStr">
@@ -15172,10 +15057,7 @@
       </c>
       <c r="G368" s="5" t="inlineStr">
         <is>
-          <t>He was sentenced to 15 years in prison in Indonesia in January 2022. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8
-                Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded
-                on 7 June 2018. Review pursuant to Security Council resolution 2368 (2017) was
-                concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>He was sentenced to 15 years in prison in Indonesia in January 2022 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H368" s="5" t="inlineStr">
@@ -15217,10 +15099,7 @@
       </c>
       <c r="G369" s="5" t="inlineStr">
         <is>
-          <t>Italian Fiscal code: BGHFCL66R28Z352G. Sentenced to 7 years imprisonment
-in Italy on 29 Jun. 2007 by the Brescia Second Appeals Court. In detention in Italy as
-at Jun. 2009. Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 20 Jul. 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Italian Fiscal code: BGHFCL66R28Z352G. Sentenced to 7 years imprisonment in Italy on 29 Jun. 2007 by the Brescia Second Appeals Court. In detention in Italy as at Jun. 2009 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
@@ -15262,9 +15141,7 @@
       </c>
       <c r="G370" s="5" t="inlineStr">
         <is>
-          <t>Italian Fiscal code: LGBBLK66D23Z330U. Father’s name is Mamoune Mohamed.
-Mother’s name is Fatna Ahmed. Review pursuant to Security Council resolution 1822 (2008)
-was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Italian Fiscal code: LGBBLK66D23Z330U. Father’s name is Mamoune Mohamed. Mother’s name is Fatna Ahmed INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H370" s="5" t="inlineStr">
@@ -15306,7 +15183,7 @@
       </c>
       <c r="G371" s="5" t="inlineStr">
         <is>
-          <t>Member of Egyptian Islamic Jihad (QDe.003). Reportedly killed in Syria in February 2017. Review pursuant to Security Council resolution 1822 (2008) was concluded on 1 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Egyptian Islamic Jihad (QDe.003). Reportedly killed in Syria in February 2017 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H371" s="5" t="inlineStr">
@@ -15348,7 +15225,7 @@
       </c>
       <c r="G372" s="5" t="inlineStr">
         <is>
-          <t>Father’s name is Ahmed Ezat Zaki. Member of Egyptian Islamic Jihad (QDe.003). Review pursuant to Security Council resolution 1822 (2008) was concluded on 1 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father’s name is Ahmed Ezat Zaki. Member of Egyptian Islamic Jihad (QDe.003) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H372" s="5" t="inlineStr">
@@ -15390,9 +15267,7 @@
       </c>
       <c r="G373" s="5" t="inlineStr">
         <is>
-          <t>Member of the Shura Council of Al-Qaida (QDe.004) and Egyptian Islamic
-Jihad (QDe.003). Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 1 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Shura Council of Al-Qaida (QDe.004) and Egyptian Islamic Jihad (QDe.003) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H373" s="5" t="inlineStr">
@@ -15434,8 +15309,7 @@
       </c>
       <c r="G374" s="5" t="inlineStr">
         <is>
-          <t>Father's name is Mohamed Elsayed Elsebai. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 29 Jul. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019.Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father's name is Mohamed Elsayed Elsebai INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H374" s="5" t="inlineStr">
@@ -15477,7 +15351,7 @@
       </c>
       <c r="G375" s="5" t="inlineStr">
         <is>
-          <t>Mother’s name: Farida Hussein Khadir. Released from custody in Germany on 10 Dec. 2010 and relocated to Iraq on 6 Dec. 2011. Review pursuant to Security Council resolution 1822 (2008) was concluded on 5 Oct. 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother’s name: Farida Hussein Khadir. Released from custody in Germany on 10 Dec. 2010 and relocated to Iraq on 6 Dec. 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H375" s="5" t="inlineStr">
@@ -15519,7 +15393,7 @@
       </c>
       <c r="G376" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of Abu Sayyaf Group (ASG) (QDe.001). Leader of local affiliates of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115), in the southern Philippines as of May 2017. Reportedly deceased in 2017.  Physical description: eye colour: brown; hair colour: brown; height: 5 feet 6 inches – 168 cm; weight: 120 pounds – 54 kg; build: slim; complexion: light-skinned; has facial birthmarks. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Wanted by the Philippines authorities for terrorist offences and by authorities of the United States of America for involvement in terrorist acts. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Photos included in. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior leader of Abu Sayyaf Group (ASG) (QDe.001). Leader of local affiliates of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115), in the southern Philippines as of May 2017. Reportedly deceased in 2017. Physical description: eye colour: brown; hair colour: brown; height: 5 feet 6 inches – 168 cm; weight: 120 pounds – 54 kg; build: slim; complexion: light-skinned; has facial birthmarks. Wanted by the Philippines authorities for terrorist offences and by authorities of the United States of America for involvement in terrorist acts. Photos included in INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H376" s="5" t="inlineStr">
@@ -15561,7 +15435,7 @@
       </c>
       <c r="G377" s="5" t="inlineStr">
         <is>
-          <t>Physical description: eye colour: black; hair colour: gray; height: 5 feet 6 inches – 168 cm; weight: 140 pounds – 64 kg; build: slight; right arm is amputated above his elbow.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Wanted by the Philippines authorities for terrorist offences  and by authorities of the United States of America for involvement in the kidnapping of its national.   Photos included in. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Physical description: eye colour: black; hair colour: gray; height: 5 feet 6 inches – 168 cm; weight: 140 pounds – 64 kg; build: slight; right arm is amputated above his elbow. Wanted by the Philippines authorities for terrorist offences and by authorities of the United States of America for involvement in the kidnapping of its national. Photos included in INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H377" s="5" t="inlineStr">
@@ -15603,8 +15477,7 @@
       </c>
       <c r="G378" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of Jemaah Islamiyah (QDe.092). Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior leader of Jemaah Islamiyah (QDe.092) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H378" s="5" t="inlineStr">
@@ -15646,7 +15519,7 @@
       </c>
       <c r="G379" s="5" t="inlineStr">
         <is>
-          <t>Formed Jemmah Anshorut Tauhid (JAT) (QDe.133) in 2008. In 2010, arrested for incitement to commit terrorism and fundraising with respect to a training camp in Aceh, Indonesia and sentenced to 15 years in 2011. Ba'asyir was released from prison on 8 January 2021 after serving his sentence in accordance with Indonesian laws and regulations. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Formed Jemmah Anshorut Tauhid (JAT) (QDe.133) in 2008. In 2010, arrested for incitement to commit terrorism and fundraising with respect to a training camp in Aceh, Indonesia and sentenced to 15 years in 2011. Ba'asyir was released from prison on 8 January 2021 after serving his sentence in accordance with Indonesian laws and regulations INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
@@ -15688,8 +15561,7 @@
       </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
-          <t>Brother of Nurjaman Riduan Isamuddin (QDi.087). Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Brother of Nurjaman Riduan Isamuddin (QDi.087) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
@@ -15731,9 +15603,7 @@
       </c>
       <c r="G381" s="5" t="inlineStr">
         <is>
-          <t>In detention in the Philippines as at May 2011. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>In detention in the Philippines as at May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H381" s="5" t="inlineStr">
@@ -15775,11 +15645,7 @@
       </c>
       <c r="G382" s="5" t="inlineStr">
         <is>
-          <t>Considered a fugitive from justice by the Italian authorities and
-sentenced in absentia to 6 years detention on 20 Nov. 2008. Sentenced in Tunisia to 4
-years imprisonment for terrorist activity and in detention in Tunisia as at Jun. 2009.
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 20 Jul.
-2009. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Considered a fugitive from justice by the Italian authorities and sentenced in absentia to 6 years detention on 20 Nov. 2008. Sentenced in Tunisia to 4 years imprisonment for terrorist activity and in detention in Tunisia as at Jun. 2009 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H382" s="5" t="inlineStr">
@@ -15821,7 +15687,7 @@
       </c>
       <c r="G383" s="5" t="inlineStr">
         <is>
-          <t>Considered a fugitive from justice by the Italian authorities and sentenced in absentia to 6 years imprisonment on 20 Nov. 2008. Member of Libyan Islamic Fighting Group (QDe.011). Mother’s name is Wanisa Abdessalam. Review pursuant to Security Council resolution 1822 (2008) was concluded on 20 Jul. 2009. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Considered a fugitive from justice by the Italian authorities and sentenced in absentia to 6 years imprisonment on 20 Nov. 2008. Member of Libyan Islamic Fighting Group (QDe.011). Mother’s name is Wanisa Abdessalam INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H383" s="5" t="inlineStr">
@@ -15863,8 +15729,7 @@
       </c>
       <c r="G384" s="5" t="inlineStr">
         <is>
-          <t>Mother’s name: Masouma Abd al-Rahman. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Review pursuant to Security Council resolution 1822 (2008) was concluded on 20 May 2010.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother’s name: Masouma Abd al-Rahman. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H384" s="5" t="inlineStr">
@@ -15906,10 +15771,7 @@
       </c>
       <c r="G385" s="5" t="inlineStr">
         <is>
-          <t>Father’s name is Mohamed Ayman Ghabra. Mother’s name is Dalal. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 5 Oct.
-2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019.
-Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father’s name is Mohamed Ayman Ghabra. Mother’s name is Dalal INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H385" s="5" t="inlineStr">
@@ -15951,7 +15813,7 @@
       </c>
       <c r="G386" s="5" t="inlineStr">
         <is>
-          <t>Member of Libyan Islamic Fighting Group (QDe.011). Review pursuant to Security Council resolution 1822 (2008) was concluded on 24 Nov. 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Libyan Islamic Fighting Group (QDe.011) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H386" s="5" t="inlineStr">
@@ -15993,10 +15855,7 @@
       </c>
       <c r="G387" s="5" t="inlineStr">
         <is>
-          <t>Mother's name is Kalthoum Abdul Salam al-Shaftari. Senior member of
-Libyan Islamic Fighting Group (QDe.011) and member of Al-Qaida (QDe.004). Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 24 Nov.
-2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother's name is Kalthoum Abdul Salam al-Shaftari. Senior member of Libyan Islamic Fighting Group (QDe.011) and member of Al-Qaida (QDe.004) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H387" s="5" t="inlineStr">
@@ -16038,10 +15897,7 @@
       </c>
       <c r="G388" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased in June 2020. Head of The Organization of Al-Qaida in the Islamic Maghreb (QDe.014).
-Sentenced in absentia to life imprisonment in Algeria on 21 March 2007. Father's name is
-Rabah Droukdel. Mother's name is Z'hour Zdigha. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 4 May 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased in June 2020. Head of The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Sentenced in absentia to life imprisonment in Algeria on 21 March 2007. Father's name is Rabah Droukdel. Mother's name is Z'hour Zdigha INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H388" s="5" t="inlineStr">
@@ -16083,8 +15939,7 @@
       </c>
       <c r="G389" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 14 Sep. 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H389" s="5" t="inlineStr">
@@ -16126,9 +15981,7 @@
       </c>
       <c r="G390" s="5" t="inlineStr">
         <is>
-          <t>Previously listed between 16 Jan. 2008 and 3 Jan. 2014 (amended on 1 Jul.
-2008, 23 Jul. 2008, 25 Jan. 2010). Review pursuant to Security Council resolution 1822
-(2008) was concluded on 14 Sep. 2009. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Previously listed between 16 Jan. 2008 and 3 Jan. 2014 (amended on 1 Jul. 2008, 23 Jul. 2008, 25 Jan. 2010) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H390" s="5" t="inlineStr">
@@ -16170,7 +16023,7 @@
       </c>
       <c r="G391" s="5" t="inlineStr">
         <is>
-          <t>Sentenced to prison by Kuwait on 24 August 2018. Review pursuant to Security Council resolution 1822 (2008) was concluded on 14 Sep. 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Sentenced to prison by Kuwait on 24 August 2018 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H391" s="5" t="inlineStr">
@@ -16212,11 +16065,7 @@
       </c>
       <c r="G392" s="5" t="inlineStr">
         <is>
-          <t>Distinguishing marks include scars on both legs. Member of the Rajah
-Solaiman Movement (QDe.128), and associated with the Abu Sayyaf Group (QDe.001) and the
-Jemaah Islamiyah (QDe.092). In detention in the Philippines as of May 2011. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 13 May
-2010.  Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Distinguishing marks include scars on both legs. Member of the Rajah Solaiman Movement (QDe.128), and associated with the Abu Sayyaf Group (QDe.001) and the Jemaah Islamiyah (QDe.092). In detention in the Philippines as of May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H392" s="5" t="inlineStr">
@@ -16258,9 +16107,7 @@
       </c>
       <c r="G393" s="5" t="inlineStr">
         <is>
-          <t>Member of the Rajah Solaiman Movement (QDe.128). Father's name is
-Amorsolo Jarabata Pareja. Mother's name is Leonila Cambaya Rosalejos. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 13 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Rajah Solaiman Movement (QDe.128). Father's name is Amorsolo Jarabata Pareja. Mother's name is Leonila Cambaya Rosalejos INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H393" s="5" t="inlineStr">
@@ -16302,10 +16149,7 @@
       </c>
       <c r="G394" s="5" t="inlineStr">
         <is>
-          <t>Member of the Rajah Solaiman Movement (QDe.128). Father's name is
-Feliciano Delos Reyes Sr. Mother's name is Aurea Semborio. In detention in the
-Philippines as of May 2011. Review pursuant to Security Council resolution 1822 (2008)
-was concluded on 13 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Rajah Solaiman Movement (QDe.128). Father's name is Feliciano Delos Reyes Sr. Mother's name is Aurea Semborio. In detention in the Philippines as of May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H394" s="5" t="inlineStr">
@@ -16347,11 +16191,7 @@
       </c>
       <c r="G395" s="5" t="inlineStr">
         <is>
-          <t>Founder and leader of the Rajah Solaiman Movement (QDe.128) and linked to
-the Abu Sayyaf Group (QDe.001). In detention in the Philippines as of May 2011. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 13 May
-2010. Photos included in
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Founder and leader of the Rajah Solaiman Movement (QDe.128) and linked to the Abu Sayyaf Group (QDe.001). In detention in the Philippines as of May 2011. Photos included in INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H395" s="5" t="inlineStr">
@@ -16393,10 +16233,7 @@
       </c>
       <c r="G396" s="5" t="inlineStr">
         <is>
-          <t>Member of the Rajah Solaiman Movement (QDe.128), Abu Sayyaf Group
-(QDe.001) and Jemaah Islamiyah (QDe.092). Father's name is Honorio Devera. Mother's name
-is Fausta Abogne. In detention in the Philippines as of May 2011. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 13 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Rajah Solaiman Movement (QDe.128), Abu Sayyaf Group (QDe.001) and Jemaah Islamiyah (QDe.092). Father's name is Honorio Devera. Mother's name is Fausta Abogne. In detention in the Philippines as of May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H396" s="5" t="inlineStr">
@@ -16438,10 +16275,7 @@
       </c>
       <c r="G397" s="5" t="inlineStr">
         <is>
-          <t>Member of the Rajah Solaiman Movement (QDe.128) and linked to the Abu
-Sayyaf Group (QDe.001). Father's name is Fernando Rafael Dellosa. Mother's name is
-Editha Parado Cain. In detention in the Philippines as of Jan. 2010. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 13 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Rajah Solaiman Movement (QDe.128) and linked to the Abu Sayyaf Group (QDe.001). Father's name is Fernando Rafael Dellosa. Mother's name is Editha Parado Cain. In detention in the Philippines as of Jan. 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H397" s="5" t="inlineStr">
@@ -16483,10 +16317,7 @@
       </c>
       <c r="G398" s="5" t="inlineStr">
         <is>
-          <t>Spiritual leader of the Rajah Solaiman Movement (QDe.128). Associated
-with Khadafi Abubakar Janjalani (deceased). In detention in the Philippines as of May
-2011. Review pursuant to Security Council resolution 1822 (2008) was concluded on 13 May
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Spiritual leader of the Rajah Solaiman Movement (QDe.128). Associated with Khadafi Abubakar Janjalani (deceased). In detention in the Philippines as of May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H398" s="5" t="inlineStr">
@@ -16528,9 +16359,7 @@
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
-          <t>Member of the Rajah Solaiman Movement (QDe.128). Arrested by the
-Philippines authorities on 14 Mar. 2011. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 13 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Rajah Solaiman Movement (QDe.128). Arrested by the Philippines authorities on 14 Mar. 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
@@ -16572,7 +16401,7 @@
       </c>
       <c r="G400" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased as of February 2022. Belonged to the leadership of the Organization of Al-Qaida in the Islamic Maghreb (listed under permanent reference number QDe.014). Located in Northern Mali as of Jun. 2008. Mother’s name is Zohra Fares. Father’s name is Mohamed. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased as of February 2022. Belonged to the leadership of the Organization of Al-Qaida in the Islamic Maghreb (listed under permanent reference number QDe.014). Located in Northern Mali as of Jun. 2008. Mother’s name is Zohra Fares. Father’s name is Mohamed INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H400" s="5" t="inlineStr">
@@ -16614,13 +16443,7 @@
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014).
-                Located in Northern Mali as of Jun. 2008. Mother’s name is Benarouba Bachira.
-                Father’s name is Mabrouk. He usurped the identity of Abid Hammadou, who allegedly
-                died in Chad in 2004. Reportedly deceased as of 24 February 2013. Review pursuant to
-                Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review
-                pursuant to Security Council resolution 2368 (2017) was concluded on 15 November
-                2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Located in Northern Mali as of Jun. 2008. Mother’s name is Benarouba Bachira. Father’s name is Mabrouk. He usurped the identity of Abid Hammadou, who allegedly died in Chad in 2004. Reportedly deceased as of 24 February 2013 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
@@ -16662,7 +16485,7 @@
       </c>
       <c r="G402" s="5" t="inlineStr">
         <is>
-          <t>Belongs to the leadership and is in charge of information committee of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Mother’s name is Yamina Soltane. Father’s name is Abdelaziz. Associated with Abdelmalek Droukdel (QDi.232, reported deceased in June 2020). Arrested in Algeria on 16 Dec. 2012. Incarcerated at the El-Harrach prison in Algiers, as of August 2015. Incarcerated in the Blida penitentiary, Algeria as of November 2023. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to the leadership and is in charge of information committee of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Mother’s name is Yamina Soltane. Father’s name is Abdelaziz. Associated with Abdelmalek Droukdel (QDi.232, reported deceased in June 2020). Arrested in Algeria on 16 Dec. 2012. Incarcerated at the El-Harrach prison in Algiers, as of August 2015. Incarcerated in the Blida penitentiary, Algeria as of November 2023. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H402" s="5" t="inlineStr">
@@ -16704,9 +16527,7 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>Belongs to the leadership and is the finance chief of the Organization of
-Al-Qaida in the Islamic Maghreb (QDe.014). Mother’s name is Zakia Chebira. Father’s name
-is Lakhdar. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to the leadership and is the finance chief of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Mother’s name is Zakia Chebira. Father’s name is Lakhdar INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
@@ -16748,7 +16569,7 @@
       </c>
       <c r="G404" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Islamic Jihad Union (IJU), also known as the Islamic Jihad Group (QDe.119). Deported from Germany to Türkiye in February 2019. Ongoing judicial process as of November 2023. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with the Islamic Jihad Union (IJU), also known as the Islamic Jihad Group (QDe.119). Deported from Germany to Türkiye in February 2019. Ongoing judicial process as of November 2023 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H404" s="5" t="inlineStr">
@@ -16790,7 +16611,7 @@
       </c>
       <c r="G405" s="5" t="inlineStr">
         <is>
-          <t>Released from custody in Germany in Apr. 2012. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Released from custody in Germany in Apr. 2012 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H405" s="5" t="inlineStr">
@@ -16832,7 +16653,7 @@
       </c>
       <c r="G406" s="5" t="inlineStr">
         <is>
-          <t>Muhammad Saeed is the leader of Lashkar-e-Tayyiba (QDe.118).In custody of the Government of Pakistan serving a 78 year imprisonment sentence since 12 February 2020 as a result of conviction in seven terror financing cases. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Muhammad Saeed is the leader of Lashkar-e-Tayyiba (QDe.118).In custody of the Government of Pakistan serving a 78 year imprisonment sentence since 12 February 2020 as a result of conviction in seven terror financing cases INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H406" s="5" t="inlineStr">
@@ -16874,8 +16695,7 @@
       </c>
       <c r="G407" s="5" t="inlineStr">
         <is>
-          <t>Chief of operations of Lashkar-e-Tayyiba (listed under permanent
-reference number QDe.118). Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Chief of operations of Lashkar-e-Tayyiba (listed under permanent reference number QDe.118) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H407" s="5" t="inlineStr">
@@ -16917,8 +16737,7 @@
       </c>
       <c r="G408" s="5" t="inlineStr">
         <is>
-          <t>Chief of finance of Lashkar-e-Tayyiba (QDe.118). His father’s name is
-Noor Muhammad. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Chief of finance of Lashkar-e-Tayyiba (QDe.118). His father’s name is Noor Muhammad INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H408" s="5" t="inlineStr">
@@ -16960,7 +16779,7 @@
       </c>
       <c r="G409" s="5" t="inlineStr">
         <is>
-          <t>Financier of Lashkar-e-Tayyiba (listed under permanent reference number QDe.118). Has served as the leader of Lashkar-e-Tayyiba in Saudi Arabia. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Financier of Lashkar-e-Tayyiba (listed under permanent reference number QDe.118). Has served as the leader of Lashkar-e-Tayyiba in Saudi Arabia INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H409" s="5" t="inlineStr">
@@ -17002,7 +16821,7 @@
       </c>
       <c r="G410" s="5" t="inlineStr">
         <is>
-          <t>Overall leader and commander of the Eastern Turkistan Islamic Movement (QDe.088). Involved in fundraising and recruitment for this organization. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Overall leader and commander of the Eastern Turkistan Islamic Movement (QDe.088). Involved in fundraising and recruitment for this organization. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H410" s="5" t="inlineStr">
@@ -17044,8 +16863,7 @@
       </c>
       <c r="G411" s="5" t="inlineStr">
         <is>
-          <t>Associated with Lashkar-e-Tayyiba (QDe.118) and Al-Qaida (QDe.004). In
-detention as at June 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Lashkar-e-Tayyiba (QDe.118) and Al-Qaida (QDe.004). In detention as at June 2009 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H411" s="5" t="inlineStr">
@@ -17087,9 +16905,7 @@
       </c>
       <c r="G412" s="5" t="inlineStr">
         <is>
-          <t>Associated with Lashkar-e-Tayyiba (QDe.118). In detention as at June
-2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019.
-Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Lashkar-e-Tayyiba (QDe.118). In detention as at June 2009 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H412" s="5" t="inlineStr">
@@ -17131,9 +16947,7 @@
       </c>
       <c r="G413" s="5" t="inlineStr">
         <is>
-          <t>Associated with Al-Qaida (QDe.004). Head of Ganj madrasa, a.k.a. Madrasa
-Jamia Taleemul Quran wal Hadith, a.k.a. Madrasa Taleemul Quran wal Sunnah, located at
-the Ganj Gate, Phandu Road, Peshawar, Pakistan. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Al-Qaida (QDe.004). Head of Ganj madrasa, a.k.a. Madrasa Jamia Taleemul Quran wal Hadith, a.k.a. Madrasa Taleemul Quran wal Sunnah, located at the Ganj Gate, Phandu Road, Peshawar, Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H413" s="5" t="inlineStr">
@@ -17171,8 +16985,7 @@
       <c r="F414" s="5" t="inlineStr"/>
       <c r="G414" s="5" t="inlineStr">
         <is>
-          <t>Other possible date of birth: 1979. He is a cousin of Ghazy Fezza Hishan Al Mazidih (QDi.277). Financial facilitator of the Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115) as of 2015.  Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Other possible date of birth: 1979. He is a cousin of Ghazy Fezza Hishan Al Mazidih (QDi.277). Financial facilitator of the Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115) as of 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H414" s="5" t="inlineStr">
@@ -17210,7 +17023,7 @@
       <c r="F415" s="5" t="inlineStr"/>
       <c r="G415" s="5" t="inlineStr">
         <is>
-          <t>He is a cousin of Akram Turki Hishan Al Mazidih (QDi.276). Terrorist attack organizer for the Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115) as of 2015.  Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>He is a cousin of Akram Turki Hishan Al Mazidih (QDi.276). Terrorist attack organizer for the Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115) as of 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H415" s="5" t="inlineStr">
@@ -17252,7 +17065,7 @@
       </c>
       <c r="G416" s="5" t="inlineStr">
         <is>
-          <t>Mother’s name: Heba Khamis Dari. Father’s name: Harith bin Salman Al-Dari bin Mahmud al-Shammari Provided operational guidance financial support and other services to or in support of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). He is the head of the political department of the Association of Muslim Scholars in Iraq. Involved in oil smuggling. Wanted by the Iraqi security forces. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother’s name: Heba Khamis Dari. Father’s name: Harith bin Salman Al-Dari bin Mahmud al-Shammari Provided operational guidance financial support and other services to or in support of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). He is the head of the political department of the Association of Muslim Scholars in Iraq. Involved in oil smuggling. Wanted by the Iraqi security forces. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H416" s="5" t="inlineStr">
@@ -17294,7 +17107,7 @@
       </c>
       <c r="G417" s="5" t="inlineStr">
         <is>
-          <t>Reportedly a member of Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM, QDe.159) as of November 2023. Convicted in absentia by Algerian tribunal on 28 Mar. 1996. Algerian international arrest warrant number 03/09 of 6 Jun. 2009 issued by the Tribunal of Sidi Mhamed, Algiers, Algeria. Algerian extradition request number 2307/09 of 3 Sep. 2009, presented to Malian authorities. Father’s name is Ali Belkalem. Mother’s name is Fatma Saadoudi. Member of The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.   INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly a member of Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM, QDe.159) as of November 2023. Convicted in absentia by Algerian tribunal on 28 Mar. 1996. Algerian international arrest warrant number 03/09 of 6 Jun. 2009 issued by the Tribunal of Sidi Mhamed, Algiers, Algeria. Algerian extradition request number 2307/09 of 3 Sep. 2009, presented to Malian authorities. Father’s name is Ali Belkalem. Mother’s name is Fatma Saadoudi. Member of The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H417" s="5" t="inlineStr">
@@ -17336,7 +17149,7 @@
       </c>
       <c r="G418" s="5" t="inlineStr">
         <is>
-          <t>Reportedly a member of Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM, QDe.159) as of November 2023. Convicted in absentia by Algerian tribunal on 28 Mar. 1996. Algerian international arrest warrant number 04/09 of 6 Jun. 2009 issued by the Tribunal of Sidi Mhamed, Algiers, Algeria. Algerian extradition request number 2307/09 of 3 Sep. 2009, presented to Malian authorities. Father’s name was Benazouz Nail. Mother’s name is Belkheiri Oum El Kheir. Member of The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly a member of Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM, QDe.159) as of November 2023. Convicted in absentia by Algerian tribunal on 28 Mar. 1996. Algerian international arrest warrant number 04/09 of 6 Jun. 2009 issued by the Tribunal of Sidi Mhamed, Algiers, Algeria. Algerian extradition request number 2307/09 of 3 Sep. 2009, presented to Malian authorities. Father’s name was Benazouz Nail. Mother’s name is Belkheiri Oum El Kheir. Member of The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H418" s="5" t="inlineStr">
@@ -17378,7 +17191,7 @@
       </c>
       <c r="G419" s="5" t="inlineStr">
         <is>
-          <t>Mother’s name: Fatima Muthanna Yahya. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Leader of Al-Qaida in the Arabian Peninsula (QDe.129) since Jun. 2015, pledged loyalty to Aiman al-Zawahiri (QDi.006). As of February 2020, reportedly killed in a counterterrorism operation in Yemen. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Mother’s name: Fatima Muthanna Yahya. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Leader of Al-Qaida in the Arabian Peninsula (QDe.129) since Jun. 2015, pledged loyalty to Aiman al-Zawahiri (QDi.006). As of February 2020, reportedly killed in a counterterrorism operation in Yemen INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H419" s="5" t="inlineStr">
@@ -17420,7 +17233,7 @@
       </c>
       <c r="G420" s="5" t="inlineStr">
         <is>
-          <t>Confirmed to have died on 30 Sep. 2011 in Yemen. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Confirmed to have died on 30 Sep. 2011 in Yemen INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H420" s="5" t="inlineStr">
@@ -17462,7 +17275,7 @@
       </c>
       <c r="G421" s="5" t="inlineStr">
         <is>
-          <t>In approximately 2005, ran a "basic training" camp for Al-Qaida (QDe.004) in Pakistan.  Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>In approximately 2005, ran a "basic training" camp for Al-Qaida (QDe.004) in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H421" s="5" t="inlineStr">
@@ -17504,11 +17317,7 @@
       </c>
       <c r="G422" s="5" t="inlineStr">
         <is>
-          <t>Physical description: 180 cm tall, dark hair, 7-9 cm. long scar on the
-face, part of the tongue is missing, has a speech defect. Resides in the Russian
-Federation as at Nov. 2010. International arrest warrant issued in the year 2000.
-INTERPOL Special Notice contains biometric information. Reportedly deceased as of April
-2014. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Physical description: 180 cm tall, dark hair, 7-9 cm. long scar on the face, part of the tongue is missing, has a speech defect. Resides in the Russian Federation as at Nov. 2010. International arrest warrant issued in the year 2000. INTERPOL Special Notice contains biometric information. Reportedly deceased as of April 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H422" s="5" t="inlineStr">
@@ -17550,7 +17359,7 @@
       </c>
       <c r="G423" s="5" t="inlineStr">
         <is>
-          <t>Operative and principal bomb maker of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Believed to be hiding in Yemen as at Mar. 2011. Wanted by Saudi Arabia. Reportedly deceased. Also associated with Nasir 'abd-al-Karim 'Abdullah Al-Wahishi (deceased), Qasim Yahya Mahdi al-Rimi (QDi.282), and Anwar Nasser Abdulla Al-Aulaqi (QDi.283) (deceased). Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Operative and principal bomb maker of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Believed to be hiding in Yemen as at Mar. 2011. Wanted by Saudi Arabia. Reportedly deceased. Also associated with Nasir 'abd-al-Karim 'Abdullah Al-Wahishi (deceased), Qasim Yahya Mahdi al-Rimi (QDi.282), and Anwar Nasser Abdulla Al-Aulaqi (QDi.283) (deceased) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H423" s="5" t="inlineStr">
@@ -17592,11 +17401,7 @@
       </c>
       <c r="G424" s="5" t="inlineStr">
         <is>
-          <t>Operational commander of Al-Qaida in the Arabian Peninsula (AQAP)
-(QDe.129). Has been involved in raising funds and stockpiling arms for AQAP operations
-and activities in Yemen. Known associate of Qasim Yahya Mahdi al-Rimi (QDi.282) and Fahd
-Mohammed Ahmed al-Quso (deceased). Father’s name is Ahmed Othman Al Omirah.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Operational commander of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Has been involved in raising funds and stockpiling arms for AQAP operations and activities in Yemen. Known associate of Qasim Yahya Mahdi al-Rimi (QDi.282) and Fahd Mohammed Ahmed al-Quso (deceased). Father’s name is Ahmed Othman Al Omirah INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H424" s="5" t="inlineStr">
@@ -17638,8 +17443,7 @@
       </c>
       <c r="G425" s="5" t="inlineStr">
         <is>
-          <t>Senior Jemaah Islamiyah (QDe.092.) leader. Father's name is Abu Bakar
-Ba'asyir (QDi.217). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior Jemaah Islamiyah (QDe.092.) leader. Father's name is Abu Bakar Ba'asyir (QDi.217) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H425" s="5" t="inlineStr">
@@ -17681,11 +17485,7 @@
       </c>
       <c r="G426" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Jemaah Islamiyah (QDe.092) involved in planning and funding
-                multiple terrorist attacks in the Philippines and Indonesia. Provided training to
-                Abu Sayyaf Group (QDe.001). Convicted for his role in the 2002 Bali bombings and
-                sentenced to 20 years in prison in Jun. 2012. Remains in custody in Indonesia as at
-                May 2015. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Photos included in INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Jemaah Islamiyah (QDe.092) involved in planning and funding multiple terrorist attacks in the Philippines and Indonesia. Provided training to Abu Sayyaf Group (QDe.001). Convicted for his role in the 2002 Bali bombings and sentenced to 20 years in prison in Jun. 2012. Remains in custody in Indonesia as at May 2015. Photos included in INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H426" s="5" t="inlineStr">
@@ -17727,11 +17527,7 @@
       </c>
       <c r="G427" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Jemaah Islamiyah (QDe.092) directly involved in obtaining
-                funding for terrorist attacks. Sentenced in Indonesia to five years in prison on 29
-                Jun. 2010. Father’s name is Mohamad Iqbal Abdurrahman (QDi.086). Review pursuant to
-                Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.
-             INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Jemaah Islamiyah (QDe.092) directly involved in obtaining funding for terrorist attacks. Sentenced in Indonesia to five years in prison on 29 Jun. 2010. Father’s name is Mohamad Iqbal Abdurrahman (QDi.086) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H427" s="5" t="inlineStr">
@@ -17773,7 +17569,7 @@
       </c>
       <c r="G428" s="5" t="inlineStr">
         <is>
-          <t>Physical description: 5 feet 2 inches; 157.4 cm. Name of father: Ali Muhammad. Mati ur-Rehman is the chief operational commander of Lashkar i Jhangvi (LJ) (QDe.096). Associated with Harakat-ul Jihad Islami (QDe.130). Reportedly deceased. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Physical description: 5 feet 2 inches; 157.4 cm. Name of father: Ali Muhammad. Mati ur-Rehman is the chief operational commander of Lashkar i Jhangvi (LJ) (QDe.096). Associated with Harakat-ul Jihad Islami (QDe.130). Reportedly deceased INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H428" s="5" t="inlineStr">
@@ -17815,7 +17611,7 @@
       </c>
       <c r="G429" s="5" t="inlineStr">
         <is>
-          <t>Senior Al-Qaida (QDe.004) leader, also associated with The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Wanted by Mauritanian authorities. He is in Mauritania since his extradition from Pakistan in 2014. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior Al-Qaida (QDe.004) leader, also associated with The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Wanted by Mauritanian authorities. He is in Mauritania since his extradition from Pakistan in 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H429" s="5" t="inlineStr">
@@ -17857,7 +17653,7 @@
       </c>
       <c r="G430" s="5" t="inlineStr">
         <is>
-          <t>Description: Height: 1.65 m. Weight: 85 kg. Black hair and eyes. White skin. Leader of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). Was based in Iraq and Syria. Declared himself “caliph” in Mosul in 2014. Responsible for managing and directing AQI large scale operations. Wife's name: Saja Hamid al-Dulaimi. Wife’s name: Asma Fawzi Mohammed al-Kubaissi. Wanted by the Iraqi security forces. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Killed in October 2019 during a counterterrorism operation.  Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Description: Height: 1.65 m. Weight: 85 kg. Black hair and eyes. White skin. Leader of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). Was based in Iraq and Syria. Declared himself “caliph” in Mosul in 2014. Responsible for managing and directing AQI large scale operations. Wife's name: Saja Hamid al-Dulaimi. Wife’s name: Asma Fawzi Mohammed al-Kubaissi. Wanted by the Iraqi security forces. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Killed in October 2019 during a counterterrorism operation INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H430" s="5" t="inlineStr">
@@ -17899,9 +17695,7 @@
       </c>
       <c r="G431" s="5" t="inlineStr">
         <is>
-          <t>Associated with Islamic Movement of Uzbekistan (QDe.010). Brother of Yassin
-                Chouka (QDi.301) Arrest warrant issued by the investigating judge of the German
-                Federal Court of Justice on 5 Oct. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Islamic Movement of Uzbekistan (QDe.010). Brother of Yassin Chouka (QDi.301) Arrest warrant issued by the investigating judge of the German Federal Court of Justice on 5 Oct. 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H431" s="5" t="inlineStr">
@@ -17943,9 +17737,7 @@
       </c>
       <c r="G432" s="5" t="inlineStr">
         <is>
-          <t>Associated with Islamic Movement of Uzbekistan (QDe.010). Brother of Monir
-                Chouka (QDi.300). Arrest warrant issued by the investigating judge of the German
-                Federal Court of Justice on 5 Oct. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Islamic Movement of Uzbekistan (QDe.010). Brother of Monir Chouka (QDi.300). Arrest warrant issued by the investigating judge of the German Federal Court of Justice on 5 Oct. 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H432" s="5" t="inlineStr">
@@ -17987,9 +17779,7 @@
       </c>
       <c r="G433" s="5" t="inlineStr">
         <is>
-          <t>Was a financial facilitator for the Islamic Movement of Uzbekistan
-(QDe.010) and Al-Qaida (QDe.004). Was associated with Tohir Abdulkhalilovich Yuldashev.
-As of late 2010, in custody of Pakistan authorities. Father’s name is Fazal Ahmad. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Was a financial facilitator for the Islamic Movement of Uzbekistan (QDe.010) and Al-Qaida (QDe.004). Was associated with Tohir Abdulkhalilovich Yuldashev. As of late 2010, in custody of Pakistan authorities. Father’s name is Fazal Ahmad INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H433" s="5" t="inlineStr">
@@ -18031,10 +17821,7 @@
       </c>
       <c r="G434" s="5" t="inlineStr">
         <is>
-          <t>Acting emir of Jemmah Anshorut Tauhid (JAT) (QDe.133). Associated with Abu
-                Bakar Ba’asyir (QDi.217), Abdul Rahim Ba’aysir (QDi.293) and Jemaah Islamiyah
-                (QDe.092). Review pursuant to Security Council resolution 2368 (2017) was concluded
-                on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Acting emir of Jemmah Anshorut Tauhid (JAT) (QDe.133). Associated with Abu Bakar Ba’asyir (QDi.217), Abdul Rahim Ba’aysir (QDi.293) and Jemaah Islamiyah (QDe.092) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H434" s="5" t="inlineStr">
@@ -18076,10 +17863,7 @@
       </c>
       <c r="G435" s="5" t="inlineStr">
         <is>
-          <t>Father's name is Abu Bakar Ba'asyir (QDi.217). Brother of Abdul Rahim
-Ba’aysir (QDi.293). Belongs to the leadership of and is involved in recruitment and
-fundraising for Jemmah Anshorut Tauhid (JAT) (QDe.133) Associated with Jemaah Islamiyah
-(QDe.092). Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father's name is Abu Bakar Ba'asyir (QDi.217). Brother of Abdul Rahim Ba’aysir (QDi.293). Belongs to the leadership of and is involved in recruitment and fundraising for Jemmah Anshorut Tauhid (JAT) (QDe.133) Associated with Jemaah Islamiyah (QDe.092) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H435" s="5" t="inlineStr">
@@ -18121,11 +17905,7 @@
       </c>
       <c r="G436" s="5" t="inlineStr">
         <is>
-          <t>Senior leader and co-founder of Lashkar-e-Tayyiba (QDe.118) (LeT) who has
-held various senior leader positions in LeT and its front organization, Jamaat-ud-Dawa
-(JUD) (listed as an alias of LeT). As of 2010, in charge of LeT/JUD finance department,
-director of its education department and president of its medical wing. Other title:
-Professor.  Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior leader and co-founder of Lashkar-e-Tayyiba (QDe.118) (LeT) who has held various senior leader positions in LeT and its front organization, Jamaat-ud-Dawa (JUD) (listed as an alias of LeT). As of 2010, in charge of LeT/JUD finance department, director of its education department and president of its medical wing. Other title: Professor INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H436" s="5" t="inlineStr">
@@ -18167,9 +17947,7 @@
       </c>
       <c r="G437" s="5" t="inlineStr">
         <is>
-          <t>Has provided facilitation and financial services to Al-Qaida (QDe.004).
-Associated with Harakatul Jihad Islami (QDe.130), Jaish-I-Mohammed (QDe.019), and
-Al-Akhtar Trust International (QDe.121).  Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Has provided facilitation and financial services to Al-Qaida (QDe.004). Associated with Harakatul Jihad Islami (QDe.130), Jaish-I-Mohammed (QDe.019), and Al-Akhtar Trust International (QDe.121) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H437" s="5" t="inlineStr">
@@ -18211,15 +17989,7 @@
       </c>
       <c r="G438" s="5" t="inlineStr">
         <is>
-          <t>Member of leadership council as of early 2010 and head of finance for the
-                Islamic Movement of Uzbekistan (QDe.010). Coordinated financial and logistical
-                support for the Islamic Movement of Uzbekistan in Afghanistan and Pakistan between
-                2009-2012. Transferred and delivered funds to Fazal Rahim (QDi.303). Reportedly
-                deceased in an airstrike in Chordar, Kunduz Province of Afghanistan in Dec. 2015.
-                Review pursuant to Security Council resolution 2253 (2015) was concluded on 7 Jun.
-                2018. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21
-                Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded
-                on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of leadership council as of early 2010 and head of finance for the Islamic Movement of Uzbekistan (QDe.010). Coordinated financial and logistical support for the Islamic Movement of Uzbekistan in Afghanistan and Pakistan between 2009-2012. Transferred and delivered funds to Fazal Rahim (QDi.303). Reportedly deceased in an airstrike in Chordar, Kunduz Province of Afghanistan in Dec. 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H438" s="5" t="inlineStr">
@@ -18261,9 +18031,7 @@
       </c>
       <c r="G439" s="5" t="inlineStr">
         <is>
-          <t>Father’s name is Slimane. Mother’s name is Akrouf Khadidja. Coordinator
-of groups associated with The Organisation of Al-Qaida in the Islamic Maghreb (QDe.014)
-in northern Mali. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019.Reportedly deceased in February 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father’s name is Slimane. Mother’s name is Akrouf Khadidja. Coordinator of groups associated with The Organisation of Al-Qaida in the Islamic Maghreb (QDe.014) in northern Mali.Reportedly deceased in February 2019 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H439" s="5" t="inlineStr">
@@ -18305,11 +18073,7 @@
       </c>
       <c r="G440" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased as of December 2014. Leader of the Mouvement pour l’Unification et le Jihad en Afrique de
-l’Ouest (MUJAO) (QDe.134). Member of The Organization of Al-Qaida in the Islamic Maghreb
-(QDe.014). Arrested in April 2005 in Mauritania, escaped from Nouakchott jail on 26 Apr.
-2006. Re-arrested in Sep. 2008 in Mali and released on 15 Apr. 2009. Associated with
-Mokhtar Belmokhtar (QDi.136). Father’s name is Leewemere. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased as of December 2014. Leader of the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Member of The Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Arrested in April 2005 in Mauritania, escaped from Nouakchott jail on 26 Apr. 2006. Re-arrested in Sep. 2008 in Mali and released on 15 Apr. 2009. Associated with Mokhtar Belmokhtar (QDi.136). Father’s name is Leewemere INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H440" s="5" t="inlineStr">
@@ -18351,11 +18115,7 @@
       </c>
       <c r="G441" s="5" t="inlineStr">
         <is>
-          <t>Leader of the Mouvement pour l’Unification et le Jihad en Afrique de
-l’Ouest (MUJAO) (QDe.134). Has provided logistical support to the Sahelian group Al
-Moulathamine, linked with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014).
-International arrest warrant issued by Mauritania. Mother’s name is Tijal Bint Mohamed
-Dadda. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019.Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Has provided logistical support to the Sahelian group Al Moulathamine, linked with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). International arrest warrant issued by Mauritania. Mother’s name is Tijal Bint Mohamed Dadda INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H441" s="5" t="inlineStr">
@@ -18397,12 +18157,7 @@
       </c>
       <c r="G442" s="5" t="inlineStr">
         <is>
-          <t>Founder and leader of Ansar Eddine (QDe.135). Member of the Tuareg Ifogas
-                tribe. Linked to the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and
-                Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134).
-                Name of father is Ag Bobacer Arhali, name of mother is Rhiachatou Wallet Sidi.
-                Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb.
-                2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Founder and leader of Ansar Eddine (QDe.135). Member of the Tuareg Ifogas tribe. Linked to the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Name of father is Ag Bobacer Arhali, name of mother is Rhiachatou Wallet Sidi INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H442" s="5" t="inlineStr">
@@ -18444,19 +18199,7 @@
       </c>
       <c r="G443" s="5" t="inlineStr">
         <is>
-          <t>rained in Afghanistan in the late 1980s with Al-Qaida (QDe.004) to make bombs.
-                Former top military commander of the Egyptian Islamic Jihad (QDe.003). Since 2011,
-                established Muhammad Jamal Network (MJN) (QDe.136) and terrorist training camps in
-                Egypt and Libya. Conducted MJN’s terrorist activities with support from Al-Qaida in
-                the Arabian Peninsula (AQAP) (QDe.129). Reported to be involved in the attack on the
-                United States Mission in Benghazi, Libya, on 11 Sep. 2012. Headed Nasr City
-                terrorist cell in Egypt in 2012. Linked to Aiman al-Zawahiri (QDi.006) and the
-                leadership of AQAP and the Organization of Al-Qaida in the Islamic Maghreb (AQIM)
-                (QDe.014). Arrested and imprisoned multiple times by Egyptian authorities since ca.
-                2000. Released in 2011 but re-arrested by Egyptian authorities in Nov. 2012.
-                Imprisoned in Egypt pending trial as of Sep. 2013. Wife’s name is Samah ‘Ali
-                Al-Dahabani (Yemeni national). Review pursuant to Security Council resolution 2253
-                (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>rained in Afghanistan in the late 1980s with Al-Qaida (QDe.004) to make bombs. Former top military commander of the Egyptian Islamic Jihad (QDe.003). Since 2011, established Muhammad Jamal Network (MJN) (QDe.136) and terrorist training camps in Egypt and Libya. Conducted MJN’s terrorist activities with support from Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Reported to be involved in the attack on the United States Mission in Benghazi, Libya, on 11 Sep. 2012. Headed Nasr City terrorist cell in Egypt in 2012. Linked to Aiman al-Zawahiri (QDi.006) and the leadership of AQAP and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Arrested and imprisoned multiple times by Egyptian authorities since ca. 2000. Released in 2011 but re-arrested by Egyptian authorities in Nov. 2012. Imprisoned in Egypt pending trial as of Sep. 2013. Wife’s name is Samah ‘Ali Al-Dahabani (Yemeni national) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H443" s="5" t="inlineStr">
@@ -18498,8 +18241,7 @@
       </c>
       <c r="G444" s="5" t="inlineStr">
         <is>
-          <t>Member of the Mouvement pour l’Unification et le Jihad en Afrique de
-l’Ouest (MUJAO) (QDe.134). Reportedly deceased as of 14 February 2018 . Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 February 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Reportedly deceased as of 14 February 2018 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H444" s="5" t="inlineStr">
@@ -18541,8 +18283,7 @@
       </c>
       <c r="G445" s="5" t="inlineStr">
         <is>
-          <t>Leader and trainer of an Al-Qaida electronics and explosives workshop
-producing improvised explosive device components. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader and trainer of an Al-Qaida electronics and explosives workshop producing improvised explosive device components INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H445" s="5" t="inlineStr">
@@ -18584,7 +18325,7 @@
       </c>
       <c r="G446" s="5" t="inlineStr">
         <is>
-          <t>Member of the Kanuri tribe. Physical description: eye colour: black; hair colour: black. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Leader of Jama'atu Ahlis Sunna Lidda'Awati Wal-Jihad (Boko Haram) (QDe.138). Under Shekau’s leadership, Boko Haram has been responsible for a series of major terrorist attacks. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019 Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Kanuri tribe. Physical description: eye colour: black; hair colour: black. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Leader of Jama'atu Ahlis Sunna Lidda'Awati Wal-Jihad (Boko Haram) (QDe.138). Under Shekau’s leadership, Boko Haram has been responsible for a series of major terrorist attacks INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H446" s="5" t="inlineStr">
@@ -18626,7 +18367,7 @@
       </c>
       <c r="G447" s="5" t="inlineStr">
         <is>
-          <t>Reportedly killed in an air strike in Syria on 25 May 2015. A veteran member of the ‘Chechen Network’ (not listed) and other terrorist groups. He was convicted of his role and membership in the ‘Chechen Network’ in France in 2006. Joined Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant in October 2013. Father’s name: Mohamed. Mother’s name: Saliha Boukhari. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly killed in an air strike in Syria on 25 May 2015. A veteran member of the ‘Chechen Network’ (not listed) and other terrorist groups. He was convicted of his role and membership in the ‘Chechen Network’ in France in 2006. Joined Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant in October 2013. Father’s name: Mohamed. Mother’s name: Saliha Boukhari. Photograph and fingerprints available for inclusion in INTERPOL-UNSC Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H447" s="5" t="inlineStr">
@@ -18668,7 +18409,7 @@
       </c>
       <c r="G448" s="5" t="inlineStr">
         <is>
-          <t>A long time facilitator and financier for Al-Qaida (QDe.004), appointed as a regional leader of Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant Reportedly killed in a counterterrorism operation in Northwest Syria in October 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A long time facilitator and financier for Al-Qaida (QDe.004), appointed as a regional leader of Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant Reportedly killed in a counterterrorism operation in Northwest Syria in October 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H448" s="5" t="inlineStr">
@@ -18710,7 +18451,7 @@
       </c>
       <c r="G449" s="5" t="inlineStr">
         <is>
-          <t>Was the official spokesman of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), and emir of ISIL in Syria, closely associated with Abu Mohammed al-Jawlani (formerly listed) and Abu Bakr al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299). Reportedly killed in August 2016 in air strike near al-Bab, Syria. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Was the official spokesman of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), and emir of ISIL in Syria, closely associated with Abu Mohammed al-Jawlani (formerly listed) and Abu Bakr al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299). Reportedly killed in August 2016 in air strike near al-Bab, Syria.. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H449" s="5" t="inlineStr">
@@ -18748,12 +18489,7 @@
       </c>
       <c r="G450" s="5" t="inlineStr">
         <is>
-          <t>A Kuwait-based financier, recruiter and facilitator for Islamic State in Iraq
-                and the Levant, listed as Al-Qaida in Iraq (QDe.115), and Jabhat al-Nusrah, formerly listed
-                as Al-Nusrah Front for the People of the Levant. Associated with Ibrahim
-                Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299) and Abu Mohammed al-Jawlani
-                (formerly listed). Review pursuant to Security Council resolution 2368 (2017) was concluded
-                on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A Kuwait-based financier, recruiter and facilitator for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), and Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant. Associated with Ibrahim Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299) and Abu Mohammed al-Jawlani (formerly listed) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H450" s="5" t="inlineStr">
@@ -18795,9 +18531,7 @@
       </c>
       <c r="G451" s="5" t="inlineStr">
         <is>
-          <t>A member and regional commander of Jabhat al-Nusrah, formerly listed as Al-Nusrah
-Front for the People of the Levant and a facilitator of foreign recruits for
-that group. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A member and regional commander of Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant and a facilitator of foreign recruits for that group INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H451" s="5" t="inlineStr">
@@ -18839,7 +18573,7 @@
       </c>
       <c r="G452" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Al-Qaida (QDe.004). Reportedly killed in January 2020 in Yemen. Wanted by the Saudi Arabian Government for terrorism. Father's name is Abdullah Saleh al Zahrani. Physical description: eye colour: dark; hair colour: dark; complexion: olive. Speaks Arabic. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Al-Qaida (QDe.004). Reportedly killed in January 2020 in Yemen. Wanted by the Saudi Arabian Government for terrorism. Father's name is Abdullah Saleh al Zahrani. Physical description: eye colour: dark; hair colour: dark; complexion: olive. Speaks Arabic. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H452" s="5" t="inlineStr">
@@ -18881,11 +18615,7 @@
       </c>
       <c r="G453" s="5" t="inlineStr">
         <is>
-          <t>Has ties to numerous senior Al-Qaida (QDe.004) leaders. Wanted by the
-Saudi Arabian Government for terrorism. Father's name is Abdullah Razeeq al Mouled al
-Sbhua. Physical description: eye colour: dark; hair colour: dark; complexion: dark.
-Speaks Arabic. Photo available for inclusion in the INTERPOL-UN Security Council Special
-Notice.  Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Has ties to numerous senior Al-Qaida (QDe.004) leaders. Wanted by the Saudi Arabian Government for terrorism. Father's name is Abdullah Razeeq al Mouled al Sbhua. Physical description: eye colour: dark; hair colour: dark; complexion: dark. Speaks Arabic. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H453" s="5" t="inlineStr">
@@ -18927,7 +18657,7 @@
       </c>
       <c r="G454" s="5" t="inlineStr">
         <is>
-          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Physical description: eye colour: brown; hair colour: brown; height: 185 cm. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019 Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Physical description: eye colour: brown; hair colour: brown; height: 185 cm INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H454" s="5" t="inlineStr">
@@ -18969,10 +18699,7 @@
       </c>
       <c r="G455" s="5" t="inlineStr">
         <is>
-          <t>Explosives expert and operative for the Abdallah Azzam Brigades (AAB)
-(QDe.144). Wanted by the Saudi Arabian Government for terrorism. Physical description:
-eye colour: dark; hair colour: dark; complexion: olive. Speaks Arabic. Photo available
-for inclusion in the INTERPOL-UN Security Council Special Notice.  Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Explosives expert and operative for the Abdallah Azzam Brigades (AAB) (QDe.144). Wanted by the Saudi Arabian Government for terrorism. Physical description: eye colour: dark; hair colour: dark; complexion: olive. Speaks Arabic. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H455" s="5" t="inlineStr">
@@ -19014,9 +18741,7 @@
       </c>
       <c r="G456" s="5" t="inlineStr">
         <is>
-          <t>Founder of the Tunisian Combatant Group (QDe.090) and leader of Ansar
-al-Shari'a in Tunisia (AAS-T) (QDe.143). Arrest warrant issued by Tunisian Court of First
-Instance on 23 Aug. 2013. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Founder of the Tunisian Combatant Group (QDe.090) and leader of Ansar al-Shari'a in Tunisia (AAS-T) (QDe.143). Arrest warrant issued by Tunisian Court of First Instance on 23 Aug. 2013 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H456" s="5" t="inlineStr">
@@ -19058,8 +18783,7 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>Financier and facilitator for Al-Qaida (QDe.004) and Al-Qaida in Iraq
-(QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Financier and facilitator for Al-Qaida (QDe.004) and Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
@@ -19101,9 +18825,7 @@
       </c>
       <c r="G458" s="5" t="inlineStr">
         <is>
-          <t>A sentence of imprisonment for 15 years was issued against him by Kuwait in absentia on 30 July 2015. Provides support to Al-Qaida (QDe.004) and Islamic State in Iraq and the
-Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115), in Syria and Iraq.  Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A sentence of imprisonment for 15 years was issued against him by Kuwait in absentia on 30 July 2015. Provides support to Al-Qaida (QDe.004) and Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115), in Syria and Iraq INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H458" s="5" t="inlineStr">
@@ -19145,8 +18867,7 @@
       </c>
       <c r="G459" s="5" t="inlineStr">
         <is>
-          <t>Sharia amir of Al-Nusrah Front for the People of the Levant (formerly listed) as
-of early 2014. Reportedly died in the Syrian Arab Republic on 2 April 2024, Mother’s name: Subhah Muhammad Sayf. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019 Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Sharia amir of Al-Nusrah Front for the People of the Levant (formerly listed) as of early 2014. Reportedly died in the Syrian Arab Republic on 2 April 2024, Mother’s name: Subhah Muhammad Sayf INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H459" s="5" t="inlineStr">
@@ -19188,8 +18909,7 @@
       </c>
       <c r="G460" s="5" t="inlineStr">
         <is>
-          <t>Fundraiser for Al-Nusrah Front for the People of the Levant (formerly listed). In November 2023, he was released from prison in Kuwait as part of the Special Amiri Decree Pardon No. 225/2023. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Fundraiser for Al-Nusrah Front for the People of the Levant (formerly listed). In November 2023, he was released from prison in Kuwait as part of the Special Amiri Decree Pardon No. 225/2023 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H460" s="5" t="inlineStr">
@@ -19231,7 +18951,7 @@
       </c>
       <c r="G461" s="5" t="inlineStr">
         <is>
-          <t>Senior Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115), official. Reportedly killed in Syria in 2016. Previously served as a representative of AQI to Al-Qaida (QDe.004) senior leadership in Pakistan. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115), official. Reportedly killed in Syria in 2016. Previously served as a representative of AQI to Al-Qaida (QDe.004) senior leadership in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H461" s="5" t="inlineStr">
@@ -19273,12 +18993,7 @@
       </c>
       <c r="G462" s="5" t="inlineStr">
         <is>
-          <t>French terrorist fighter who travelled to Syria and joined Islamic State in
-                Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). Active in
-                radicalizing and propagating Al-Qaida’s (QDe.004) ideology through the Internet.
-                Incites violent activities against France. French arrest warrant issued on 12 Jun.
-                2015 by a magistrate of the anti-terrorism division of the Prosecutor’s Office in
-                Paris for her participation in a terrorist criminal association. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>French terrorist fighter who travelled to Syria and joined Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). Active in radicalizing and propagating Al-Qaida’s (QDe.004) ideology through the Internet. Incites violent activities against France. French arrest warrant issued on 12 Jun. 2015 by a magistrate of the anti-terrorism division of the Prosecutor’s Office in Paris for her participation in a terrorist criminal association INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H462" s="5" t="inlineStr">
@@ -19316,7 +19031,7 @@
       </c>
       <c r="G463" s="5" t="inlineStr">
         <is>
-          <t>French terrorist fighter associated with Al-Nusrah Front for the People of the Levant (formerly listed) and the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Facilitated foreign terrorist fighters travel from France to Syria. Activist in violent propaganda through the Internet. A warrant for his arrest was issued in 2014 by French authorities and executed in Jan. 2017 upon his expulsion from Turkey where he was arrested in Jun. 2016. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>French terrorist fighter associated with Al-Nusrah Front for the People of the Levant (formerly listed) and the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Facilitated foreign terrorist fighters travel from France to Syria. Activist in violent propaganda through the Internet. A warrant for his arrest was issued in 2014 by French authorities and executed in Jan. 2017 upon his expulsion from Turkey where he was arrested in Jun. 2016 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H463" s="5" t="inlineStr">
@@ -19358,9 +19073,7 @@
       </c>
       <c r="G464" s="5" t="inlineStr">
         <is>
-          <t>A leader of an armed group linked to Al-Nusrah Front for the People of
-the Levant (formerly listed) and a key facilitator for a Syrian foreign terrorist fighter
-network. Active in terrorist propaganda through the Internet. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A leader of an armed group linked to Al-Nusrah Front for the People of the Levant (formerly listed) and a key facilitator for a Syrian foreign terrorist fighter network. Active in terrorist propaganda through the Internet INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H464" s="5" t="inlineStr">
@@ -19402,11 +19115,7 @@
       </c>
       <c r="G465" s="5" t="inlineStr">
         <is>
-          <t>A member of Al-Qaida (QDe.004) as of 2012 and a fighter in the Syrian Arab
-                Republic since early 2014. Provided financial, material, and technological support
-                for Al-Qaida, Al-Nusrah Front for the People of the Levant (formerly listed) and Al-Qaida in
-                Iraq (AQI) (QDe.115).Review pursuant to Security Council resolution 2368 (2017) was
-                concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A member of Al-Qaida (QDe.004) as of 2012 and a fighter in the Syrian Arab Republic since early 2014. Provided financial, material, and technological support for Al-Qaida, Al-Nusrah Front for the People of the Levant (formerly listed) and Al-Qaida in Iraq (AQI) (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H465" s="5" t="inlineStr">
@@ -19448,9 +19157,7 @@
       </c>
       <c r="G466" s="5" t="inlineStr">
         <is>
-          <t>Facilitator who provides financial support for and financial services to
-and in support of Al-Qaida (QDe.004).
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Facilitator who provides financial support for and financial services to and in support of Al-Qaida (QDe.004) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H466" s="5" t="inlineStr">
@@ -19492,11 +19199,7 @@
       </c>
       <c r="G467" s="5" t="inlineStr">
         <is>
-          <t>As of mid-2014, Syria-based senior military commander and shura council
-member of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI)
-(QDe.115). Led approximately 1,000 foreign fighters for ISIL and committed a number of
-attacks in northern Syria.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As of mid-2014, Syria-based senior military commander and shura council member of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). Led approximately 1,000 foreign fighters for ISIL and committed a number of attacks in northern Syria INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H467" s="5" t="inlineStr">
@@ -19538,9 +19241,7 @@
       </c>
       <c r="G468" s="5" t="inlineStr">
         <is>
-          <t>Member of Jemaah Islamiyah (QDe.092) and leader of Hilal Ahmar Society
-Indonesia (HASI) (QDe.147).
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Jemaah Islamiyah (QDe.092) and leader of Hilal Ahmar Society Indonesia (HASI) (QDe.147) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H468" s="5" t="inlineStr">
@@ -19582,9 +19283,7 @@
       </c>
       <c r="G469" s="5" t="inlineStr">
         <is>
-          <t>A senior leader of Jemaah Islamiyah (QDe.092) who has held leadership
-positions in Hilal Ahmar Society Indonesia (HASI) (QDe.147).
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A senior leader of Jemaah Islamiyah (QDe.092) who has held leadership positions in Hilal Ahmar Society Indonesia (HASI) (QDe.147) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H469" s="5" t="inlineStr">
@@ -19626,10 +19325,7 @@
       </c>
       <c r="G470" s="5" t="inlineStr">
         <is>
-          <t>Head of the foreign affairs division and key outreach player of Jemaah
-Islamiyah (QDe.092). Associated with Hilal Ahmar Society Indonesia (HASI)
-(QDe.147).
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Head of the foreign affairs division and key outreach player of Jemaah Islamiyah (QDe.092). Associated with Hilal Ahmar Society Indonesia (HASI) (QDe.147) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H470" s="5" t="inlineStr">
@@ -19671,7 +19367,7 @@
       </c>
       <c r="G471" s="5" t="inlineStr">
         <is>
-          <t>Physical description: eye colour: brown; height: 171cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Previous occupation:  trading agent. A member of Ansar al-Shari’a in Tunisia (QDe.143), active in recruitment of foreign terrorist fighters and arms smuggling. Detained and sentenced to 30 months imprisonment for planning terrorist acts in 2005 in Tunisia. Planned and perpetrated the attack against the Consulate of the United States in Benghazi, Libya on 11 Sep. 2012. Arrest warrant issued by the Tunisian National Guard (as at Mar. 2015). Father’s name is  Taher Ouni Harzi, mother’s name is Borkana Bedairia. Reportedly killed in an airstrike in Mosul, Iraq, in Jun. 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Physical description: eye colour: brown; height: 171cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Previous occupation: trading agent. A member of Ansar al-Shari’a in Tunisia (QDe.143), active in recruitment of foreign terrorist fighters and arms smuggling. Detained and sentenced to 30 months imprisonment for planning terrorist acts in 2005 in Tunisia. Planned and perpetrated the attack against the Consulate of the United States in Benghazi, Libya on 11 Sep. 2012. Arrest warrant issued by the Tunisian National Guard (as at Mar. 2015). Father’s name is Taher Ouni Harzi, mother’s name is Borkana Bedairia. Reportedly killed in an airstrike in Mosul, Iraq, in Jun. 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H471" s="5" t="inlineStr">
@@ -19713,7 +19409,7 @@
       </c>
       <c r="G472" s="5" t="inlineStr">
         <is>
-          <t>Physical description: eye colour: brown; height: 172cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Previous occupation:  worker. A dangerous and active member of Al Qaida in Iraq (QDe.115) in 2004, also active in facilitating and hosting members of Ansar al-Shari’a in Tunisia (QDe.143) in Syria. Sentenced, in absentia, on 30 October 2007, to 24 years imprisonment for terrorist activities by the Appeals Court of Tunis. Father’s name is Taher Ouni Harzi, mother’s name is Borkana Bedairia. Reportedly killed in Syria in Jun. 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Physical description: eye colour: brown; height: 172cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Previous occupation: worker. A dangerous and active member of Al Qaida in Iraq (QDe.115) in 2004, also active in facilitating and hosting members of Ansar al-Shari’a in Tunisia (QDe.143) in Syria. Sentenced, in absentia, on 30 October 2007, to 24 years imprisonment for terrorist activities by the Appeals Court of Tunis. Father’s name is Taher Ouni Harzi, mother’s name is Borkana Bedairia. Reportedly killed in Syria in Jun. 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H472" s="5" t="inlineStr">
@@ -19755,8 +19451,7 @@
       </c>
       <c r="G473" s="5" t="inlineStr">
         <is>
-          <t>Leader of Ansar al Charia Derna (QDe.145).
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Ansar al Charia Derna (QDe.145) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H473" s="5" t="inlineStr">
@@ -19798,8 +19493,7 @@
       </c>
       <c r="G474" s="5" t="inlineStr">
         <is>
-          <t>Recruiter for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic, and a key figure in the the Al-Khanssaa brigade, a female ISIL brigade established in Al-Raqqa to enforce ISIL’s interpretation of Sharia law. Sex: female. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Recruiter for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic, and a key figure in the the Al-Khanssaa brigade, a female ISIL brigade established in Al-Raqqa to enforce ISIL’s interpretation of Sharia law. Sex: female. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H474" s="5" t="inlineStr">
@@ -19837,8 +19531,7 @@
       </c>
       <c r="G475" s="5" t="inlineStr">
         <is>
-          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Wanted by the authorities of the United Kingdom. Physical description: hair colour: brown/black.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Wanted by the authorities of the United Kingdom. Physical description: hair colour: brown/black INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H475" s="5" t="inlineStr">
@@ -19880,9 +19573,7 @@
       </c>
       <c r="G476" s="5" t="inlineStr">
         <is>
-          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Wanted by the authorities of the United Kingdom. Physical description: hair colour: brown/black. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Wanted by the authorities of the United Kingdom. Physical description: hair colour: brown/black. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H476" s="5" t="inlineStr">
@@ -19924,8 +19615,7 @@
       </c>
       <c r="G477" s="5" t="inlineStr">
         <is>
-          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Physical description: eye colour: brown; hair colour: brown/black. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Physical description: eye colour: brown; hair colour: brown/black. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H477" s="5" t="inlineStr">
@@ -19967,8 +19657,7 @@
       </c>
       <c r="G478" s="5" t="inlineStr">
         <is>
-          <t>Recruiter for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Sex: female. Husband’s name is: Junaid Hussain. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Recruiter for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Sex: female. Husband’s name is: Junaid Hussain. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H478" s="5" t="inlineStr">
@@ -20006,7 +19695,7 @@
       <c r="F479" s="5" t="inlineStr"/>
       <c r="G479" s="5" t="inlineStr">
         <is>
-          <t>Shura council member of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115) and in charge of ISIL’s media arm. ISIL’s provincial leader for Homs, Syrian Arab Republic as of mid-2014. Dubbed as the ISIL’s “kidnapper-in-chief”. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Shura council member of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115) and in charge of ISIL’s media arm. ISIL’s provincial leader for Homs, Syrian Arab Republic as of mid-2014. Dubbed as the ISIL’s “kidnapper-in-chief” INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H479" s="5" t="inlineStr">
@@ -20048,8 +19737,7 @@
       </c>
       <c r="G480" s="5" t="inlineStr">
         <is>
-          <t>As at Aug. 2015, leader of Jamaat Abu Banat terrorist group, which forms part of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), and operates on the outskirts of Syrian Arab Republic cities Aleppo and Idlib, extorting funds from and carrying out kidnappings and public executions of local Syrians. Physical description: eye colour brown, hair colour: dark, build: strong, straight nose, height: 180-185 cm, speaks Russian, English, Arabic. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As at Aug. 2015, leader of Jamaat Abu Banat terrorist group, which forms part of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), and operates on the outskirts of Syrian Arab Republic cities Aleppo and Idlib, extorting funds from and carrying out kidnappings and public executions of local Syrians. Physical description: eye colour brown, hair colour: dark, build: strong, straight nose, height: 180-185 cm, speaks Russian, English, Arabic. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H480" s="5" t="inlineStr">
@@ -20091,8 +19779,7 @@
       </c>
       <c r="G481" s="5" t="inlineStr">
         <is>
-          <t>As at Aug. 2015, emir of Russian-speaking militants of the Islamic State of Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Controls the Syrian Arab Republic cities of Al Dana and Idlib as an ISIL chief. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As at Aug. 2015, emir of Russian-speaking militants of the Islamic State of Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Controls the Syrian Arab Republic cities of Al Dana and Idlib as an ISIL chief. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H481" s="5" t="inlineStr">
@@ -20134,9 +19821,7 @@
       </c>
       <c r="G482" s="5" t="inlineStr">
         <is>
-          <t>As at Aug. 2015, one of the leaders of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), commanding directly 130 militants. Physical description: eye colour: brown, hair colour: black, build: solid; distinguishing marks: oval face, beard, missing a right hand and left leg, speaks Russian, Chechen and possibly German and Arabic. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As at Aug. 2015, one of the leaders of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), commanding directly 130 militants. Physical description: eye colour: brown, hair colour: black, build: solid; distinguishing marks: oval face, beard, missing a right hand and left leg, speaks Russian, Chechen and possibly German and Arabic. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H482" s="5" t="inlineStr">
@@ -20178,11 +19863,7 @@
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>As at Aug. 2015, leads Jamaat Tarkhan, a terrorist group that forms part of the
-                Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Wanted
-                by the authorities of the Russian Federation for terrorist crimes committed in its
-                territory, including through an international arrest warrant. Photo available for
-                inclusion in the INTERPOL-UN Security Council Special Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As at Aug. 2015, leads Jamaat Tarkhan, a terrorist group that forms part of the Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory, including through an international arrest warrant. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H483" s="5" t="inlineStr">
@@ -20224,8 +19905,7 @@
       </c>
       <c r="G484" s="5" t="inlineStr">
         <is>
-          <t>As at Aug. 2015, one of the leaders of the Army of Emigrants and Supporters (QDe.148). Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As at Aug. 2015, one of the leaders of the Army of Emigrants and Supporters (QDe.148). Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H484" s="5" t="inlineStr">
@@ -20267,8 +19947,7 @@
       </c>
       <c r="G485" s="5" t="inlineStr">
         <is>
-          <t>As at Aug. 2015, leader of Jamaat Abu Hanifa, a terrorist group that was part of the Al-Nusrah Front for the People of the Levant (formerly listed). Physical description: eye colour: brown, hair colour: black, build: slim, height 175-180 cm. Distinguishing marks: long face, speech defect. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As at Aug. 2015, leader of Jamaat Abu Hanifa, a terrorist group that was part of the Al-Nusrah Front for the People of the Levant (formerly listed). Physical description: eye colour: brown, hair colour: black, build: slim, height 175-180 cm. Distinguishing marks: long face, speech defect. Wanted by the authorities of the Russian Federation for terrorist crimes committed in its territory. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H485" s="5" t="inlineStr">
@@ -20310,7 +19989,7 @@
       </c>
       <c r="G486" s="5" t="inlineStr">
         <is>
-          <t>Financial and foreign fighter facilitator for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129) since at least Jun. 2014. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Financial and foreign fighter facilitator for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129) since at least Jun. 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H486" s="5" t="inlineStr">
@@ -20352,7 +20031,7 @@
       </c>
       <c r="G487" s="5" t="inlineStr">
         <is>
-          <t>Border emir of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) as of Apr. 2015, and ISIL’s leader for operations outside of the Syrian Arab Republic and Iraq as of mid-2014. Facilitated the travel from Turkey to the Syrian Arab Republic of prospective ISIL fighters from Australia, Europe, and the Middle East. Managed ISIL’s guesthouse in Azaz, Syrian Arabic Republic as of 2014. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Border emir of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) as of Apr. 2015, and ISIL’s leader for operations outside of the Syrian Arab Republic and Iraq as of mid-2014. Facilitated the travel from Turkey to the Syrian Arab Republic of prospective ISIL fighters from Australia, Europe, and the Middle East. Managed ISIL’s guesthouse in Azaz, Syrian Arabic Republic as of 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H487" s="5" t="inlineStr">
@@ -20394,8 +20073,7 @@
       </c>
       <c r="G488" s="5" t="inlineStr">
         <is>
-          <t>Key operative in Al-Qaida (QDe.004). Under the direction of Aiman al-Zawahiri (QDi.006), recruited 200 militants in the eastern part of Libya.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Key operative in Al-Qaida (QDe.004). Under the direction of Aiman al-Zawahiri (QDi.006), recruited 200 militants in the eastern part of Libya INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H488" s="5" t="inlineStr">
@@ -20433,8 +20111,7 @@
       </c>
       <c r="G489" s="5" t="inlineStr">
         <is>
-          <t>Syria-based military expert, member and recruiter of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Wanted by the Government of Tajikistan.
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Syria-based military expert, member and recruiter of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Wanted by the Government of Tajikistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H489" s="5" t="inlineStr">
@@ -20476,7 +20153,7 @@
       </c>
       <c r="G490" s="5" t="inlineStr">
         <is>
-          <t>Believed to be fighting with Al-Nusrah Front for the People of the Levant (formerly listed) in Syrian Arab Republic and reported to be a leader in the group as of Apr. 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 February 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be fighting with Al-Nusrah Front for the People of the Levant (formerly listed) in Syrian Arab Republic and reported to be a leader in the group as of Apr. 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H490" s="5" t="inlineStr">
@@ -20518,7 +20195,7 @@
       </c>
       <c r="G491" s="5" t="inlineStr">
         <is>
-          <t>French-Tunisian foreign terrorist fighter for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>French-Tunisian foreign terrorist fighter for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H491" s="5" t="inlineStr">
@@ -20556,9 +20233,7 @@
       </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Convicted in
-                absentia to five years in prison in France in 2012. Wanted by French authorities as
-                of 2015. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Convicted in absentia to five years in prison in France in 2012. Wanted by French authorities as of 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H492" s="5" t="inlineStr">
@@ -20600,7 +20275,7 @@
       </c>
       <c r="G493" s="5" t="inlineStr">
         <is>
-          <t>Syria-based Al-Qaida (QDe.004) facilitator. Involved in the development of improvised explosive devices for use in Afghanistan and Syrian Arab Republic since at least 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Syria-based Al-Qaida (QDe.004) facilitator. Involved in the development of improvised explosive devices for use in Afghanistan and Syrian Arab Republic since at least 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H493" s="5" t="inlineStr">
@@ -20642,11 +20317,7 @@
       </c>
       <c r="G494" s="5" t="inlineStr">
         <is>
-          <t>French foreign terrorist fighter for Islamic State in Iraq and the Levant,
-                listed as Al-Qaida in Iraq (QDe.115). French arrest warrant issued on 20 Jan. 2015
-                by a magistrate of the anti-terrorism division of the Prosecutor’s Office in Paris
-                for murder in connection with a terrorist entity and participation in a terrorist
-                criminal association. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>French foreign terrorist fighter for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). French arrest warrant issued on 20 Jan. 2015 by a magistrate of the anti-terrorism division of the Prosecutor’s Office in Paris for murder in connection with a terrorist entity and participation in a terrorist criminal association INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H494" s="5" t="inlineStr">
@@ -20688,7 +20359,7 @@
       </c>
       <c r="G495" s="5" t="inlineStr">
         <is>
-          <t>Qatar-based facilitator who provides financial services to, or in support of, Al-Qaida (QDe.004). Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Qatar-based facilitator who provides financial services to, or in support of, Al-Qaida (QDe.004) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H495" s="5" t="inlineStr">
@@ -20730,7 +20401,7 @@
       </c>
       <c r="G496" s="5" t="inlineStr">
         <is>
-          <t>Qatar-based facilitator who provides financial services to, or in support of, Al-Nusrah Front for the People of the Levant (formerly listed). Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Qatar-based facilitator who provides financial services to, or in support of, Al-Nusrah Front for the People of the Levant (formerly listed) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H496" s="5" t="inlineStr">
@@ -20772,9 +20443,7 @@
       </c>
       <c r="G497" s="5" t="inlineStr">
         <is>
-          <t>Facilitator for travel of foreign terrorist fighters to join Islamic State in
-                Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), in Syrian Arab
-                Republic. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Facilitator for travel of foreign terrorist fighters to join Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), in Syrian Arab Republic INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H497" s="5" t="inlineStr">
@@ -20816,7 +20485,7 @@
       </c>
       <c r="G498" s="5" t="inlineStr">
         <is>
-          <t>A leader of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). As of Jun, 2015, al-Shawakh was the ISIL governor of Aleppo. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A leader of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). As of Jun, 2015, al-Shawakh was the ISIL governor of Aleppo INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H498" s="5" t="inlineStr">
@@ -20858,7 +20527,7 @@
       </c>
       <c r="G499" s="5" t="inlineStr">
         <is>
-          <t>Facilitator for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Facilitator for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H499" s="5" t="inlineStr">
@@ -20900,7 +20569,7 @@
       </c>
       <c r="G500" s="5" t="inlineStr">
         <is>
-          <t>Foreign terrorist fighter facilitator experienced in establishing and securing travel routes. Deeply involved in providing material support to the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) in North Africa. Assisted foreign terrorist fighters’ travel throughout North Africa and to Syrian Arab Republic to join Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Profession: farm worker. Mother's name: Mbarka Helali. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Foreign terrorist fighter facilitator experienced in establishing and securing travel routes. Deeply involved in providing material support to the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) in North Africa. Assisted foreign terrorist fighters’ travel throughout North Africa and to Syrian Arab Republic to join Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Profession: farm worker. Mother's name: Mbarka Helali INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H500" s="5" t="inlineStr">
@@ -20942,9 +20611,7 @@
       </c>
       <c r="G501" s="5" t="inlineStr">
         <is>
-          <t>Member of Al-Qaida (QDe.004). Involved in recruiting suicide bombers to go to
-                Syrian Arab Republic and planning terrorist activities against targets in Europe.
-                Arrested in Cairo, Egypt in 2013. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Al-Qaida (QDe.004). Involved in recruiting suicide bombers to go to Syrian Arab Republic and planning terrorist activities against targets in Europe. Arrested in Cairo, Egypt in 2013 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H501" s="5" t="inlineStr">
@@ -20982,7 +20649,7 @@
       </c>
       <c r="G502" s="5" t="inlineStr">
         <is>
-          <t>Syria-based French violent extremist and member of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Subject to a European Arrest Warrant. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Syria-based French violent extremist and member of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Subject to a European Arrest Warrant INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H502" s="5" t="inlineStr">
@@ -21024,9 +20691,7 @@
       </c>
       <c r="G503" s="5" t="inlineStr">
         <is>
-          <t>A leader of the Organization of Al-Qaida in the Islamic Maghreb (AQIM)
-                (QDe.014). Photo available for inclusion in the INTERPOL-UN Security Council Special
-                Notice. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A leader of the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H503" s="5" t="inlineStr">
@@ -21068,7 +20733,7 @@
       </c>
       <c r="G504" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased. Was the lead oil and gas division official of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), for Al Barakah Governorate, Syrian Arab Republic, as of May 2015. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased. Was the lead oil and gas division official of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), for Al Barakah Governorate, Syrian Arab Republic, as of May 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H504" s="5" t="inlineStr">
@@ -21110,7 +20775,7 @@
       </c>
       <c r="G505" s="5" t="inlineStr">
         <is>
-          <t>Link between Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), leader Abu Bakr al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299), and armed groups in Gaza. Was using money to build an ISIL presence in Gaza. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Link between Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), leader Abu Bakr al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali al-Badri al-Samarrai (QDi.299), and armed groups in Gaza. Was using money to build an ISIL presence in Gaza INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H505" s="5" t="inlineStr">
@@ -21152,7 +20817,7 @@
       </c>
       <c r="G506" s="5" t="inlineStr">
         <is>
-          <t>Has served as the acting emir of Jemmah Anshorut Tauhid (JAT) (QDe.133) since 2014 and has supported Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Profession: Lecturer/Private Teacher. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Has served as the acting emir of Jemmah Anshorut Tauhid (JAT) (QDe.133) since 2014 and has supported Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Profession: Lecturer/Private Teacher INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H506" s="5" t="inlineStr">
@@ -21194,7 +20859,7 @@
       </c>
       <c r="G507" s="5" t="inlineStr">
         <is>
-          <t>Wanted by the authorities of the Russian Federation for terrorist crimes. Commands a suicide battalion of Riyadus-Salikhin Reconnaissance and Sabotage Battalion of Chechen Martyrs (RSRSBCM) (QDe.100). Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Wanted by the authorities of the Russian Federation for terrorist crimes. Commands a suicide battalion of Riyadus-Salikhin Reconnaissance and Sabotage Battalion of Chechen Martyrs (RSRSBCM) (QDe.100) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H507" s="5" t="inlineStr">
@@ -21236,11 +20901,7 @@
       </c>
       <c r="G508" s="5" t="inlineStr">
         <is>
-          <t>May use a fake passport of a Syrian or Iraqi citizen. Member of the Al-Nusrah
-                Front for the People of the Levant (ANF) (formerly listed), “Bulgar Group”, leads a group of
-                100 fighters. Photo available for inclusion in the INTERPOL-UN Security Council
-                Special Notice. Review pursuant to Security Council resolution 2368 (2017) was
-                concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>May use a fake passport of a Syrian or Iraqi citizen. Member of the Al-Nusrah Front for the People of the Levant (ANF) (formerly listed), “Bulgar Group”, leads a group of 100 fighters. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H508" s="5" t="inlineStr">
@@ -21282,7 +20943,7 @@
       </c>
       <c r="G509" s="5" t="inlineStr">
         <is>
-          <t>Led a group of over 160 terrorist fighters, which operates in the Republics of Dagestan, Chechnya and Ingushetia, Russian Federation. Killed on 3 December 2016 in Makhachkala, the Republic of Dagestan, Russian Federation. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Led a group of over 160 terrorist fighters, which operates in the Republics of Dagestan, Chechnya and Ingushetia, Russian Federation. Killed on 3 December 2016 in Makhachkala, the Republic of Dagestan, Russian Federation. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H509" s="5" t="inlineStr">
@@ -21324,7 +20985,7 @@
       </c>
       <c r="G510" s="5" t="inlineStr">
         <is>
-          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) for southern Syrian Arab Republic since July 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) for southern Syrian Arab Republic since July 2016 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H510" s="5" t="inlineStr">
@@ -21366,7 +21027,7 @@
       </c>
       <c r="G511" s="5" t="inlineStr">
         <is>
-          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) for coastal area of Syrian Arab Republic since March 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) for coastal area of Syrian Arab Republic since March 2016 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H511" s="5" t="inlineStr">
@@ -21408,7 +21069,7 @@
       </c>
       <c r="G512" s="5" t="inlineStr">
         <is>
-          <t>A leader of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129) in Marib Governorate, Yemen since 2015. Provided AQAP with weapons, funding and recruits. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A leader of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129) in Marib Governorate, Yemen since 2015. Provided AQAP with weapons, funding and recruits INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H512" s="5" t="inlineStr">
@@ -21450,7 +21111,7 @@
       </c>
       <c r="G513" s="5" t="inlineStr">
         <is>
-          <t>German foreign terrorist fighter for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Physical description: eye colour: brown; hair colour: black; height: 178cm; weight: 80kg. European arrest warrant issued by the investigating judge of the German Federal Supreme Court on 13 Aug. 2014. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>German foreign terrorist fighter for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Physical description: eye colour: brown; hair colour: black; height: 178cm; weight: 80kg. European arrest warrant issued by the investigating judge of the German Federal Supreme Court on 13 Aug. 2014 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H513" s="5" t="inlineStr">
@@ -21492,7 +21153,7 @@
       </c>
       <c r="G514" s="5" t="inlineStr">
         <is>
-          <t>Syrian-based Indonesian national who has served in a variety of roles supporting the Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Syrian-based Indonesian national who has served in a variety of roles supporting the Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H514" s="5" t="inlineStr">
@@ -21534,7 +21195,7 @@
       </c>
       <c r="G515" s="5" t="inlineStr">
         <is>
-          <t>Joined the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) in September 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Joined the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) in September 2016 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H515" s="5" t="inlineStr">
@@ -21576,7 +21237,7 @@
       </c>
       <c r="G516" s="5" t="inlineStr">
         <is>
-          <t>Associated with Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Jabhat al-Nusrah, formerly listed as Al-Nusrah Front for the People of the Levant INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H516" s="5" t="inlineStr">
@@ -21618,7 +21279,7 @@
       </c>
       <c r="G517" s="5" t="inlineStr">
         <is>
-          <t>De facto leader for all Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), supporters in Indonesia, despite his incarceration in Indonesia since December 2010. Sentenced to death by the Indonesian Supreme Court. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>De facto leader for all Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115), supporters in Indonesia, despite his incarceration in Indonesia since December 2010. Sentenced to death by the Indonesian Supreme Court INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H517" s="5" t="inlineStr">
@@ -21660,7 +21321,7 @@
       </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
-          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Sentenced to life imprisonment on 29 April 2022 in the United States of America, Federal Bureau of Prisons inmate number 11685-509. Physical description: eye colour: dark brown; hair colour: black; complexion: dark. Distinguishing marks: beard. Ethnic background: Ghanaian Cypriot. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Sentenced to life imprisonment on 29 April 2022 in the United States of America, Federal Bureau of Prisons inmate number 11685-509. Physical description: eye colour: dark brown; hair colour: black; complexion: dark. Distinguishing marks: beard. Ethnic background: Ghanaian Cypriot INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr">
@@ -21702,7 +21363,7 @@
       </c>
       <c r="G519" s="5" t="inlineStr">
         <is>
-          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Sentenced to life imprisonment on 19 August 2022 in the United States of America, Federal Bureau of Prisons inmate number 11698-509. Physical description: eye colour: dark brown; hair colour: black; complexion: dark. Distinguishing marks: beard. Mother’s name: Maha Elgizouli. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Foreign terrorist fighter with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in the Syrian Arab Republic. Sentenced to life imprisonment on 19 August 2022 in the United States of America, Federal Bureau of Prisons inmate number 11698-509. Physical description: eye colour: dark brown; hair colour: black; complexion: dark. Distinguishing marks: beard. Mother’s name: Maha Elgizouli INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H519" s="5" t="inlineStr">
@@ -21744,7 +21405,7 @@
       </c>
       <c r="G520" s="5" t="inlineStr">
         <is>
-          <t>English language propagandist for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115). Wanted in Trinidad and Tobago for possession of ammunition and firearms and receiving stolen goods. Physical description: eye colour: brown; hair colour: dark; complexion: light brown; build: medium; height: 174cm; weight: 64kg; speaks English, Arabic. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>English language propagandist for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115). Wanted in Trinidad and Tobago for possession of ammunition and firearms and receiving stolen goods. Physical description: eye colour: brown; hair colour: dark; complexion: light brown; build: medium; height: 174cm; weight: 64kg; speaks English, Arabic INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H520" s="5" t="inlineStr">
@@ -21786,7 +21447,7 @@
       </c>
       <c r="G521" s="5" t="inlineStr">
         <is>
-          <t>: Finance “emir” for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Mother’s name: Khadijah Mustafa Salih , Held in detention by the Iraqi intelligence service since 2019 and has been sentenced to death, Physical description: hair colour: black; eye colour: honey; height: 170 cm. Speaks Arabic. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>: Finance “emir” for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Mother’s name: Khadijah Mustafa Salih, Held in detention by the Iraqi intelligence service since 2019 and has been sentenced to death, Physical description: hair colour: black; eye colour: honey; height: 170 cm. Speaks Arabic INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H521" s="5" t="inlineStr">
@@ -21828,7 +21489,7 @@
       </c>
       <c r="G522" s="5" t="inlineStr">
         <is>
-          <t>Financial facilitator for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Director of Al-Kawthar Money Exchange (QDe.157). Physical description: sex: male, hair colour: black; height: 175 cm. Speaks Arabic. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Financial facilitator for Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Director of Al-Kawthar Money Exchange (QDe.157). Physical description: sex: male, hair colour: black; height: 175 cm. Speaks Arabic INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H522" s="5" t="inlineStr">
@@ -21870,7 +21531,7 @@
       </c>
       <c r="G523" s="5" t="inlineStr">
         <is>
-          <t>Facilitator for the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Gender: female. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Facilitator for the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Gender: female INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H523" s="5" t="inlineStr">
@@ -21912,7 +21573,7 @@
       </c>
       <c r="G524" s="5" t="inlineStr">
         <is>
-          <t>Facilitator for the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Gender: male. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Facilitator for the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Gender: male INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H524" s="5" t="inlineStr">
@@ -21950,7 +21611,7 @@
       <c r="F525" s="5" t="inlineStr"/>
       <c r="G525" s="5" t="inlineStr">
         <is>
-          <t>Reportedly Deceased. Former spokesperson of the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Emir of the Al-Mourabitoun (QDe.141) group in Mali. Pledged allegiance to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) in May 2015. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly Deceased. Former spokesperson of the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Emir of the Al-Mourabitoun (QDe.141) group in Mali. Pledged allegiance to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) in May 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H525" s="5" t="inlineStr">
@@ -21992,7 +21653,7 @@
       </c>
       <c r="G526" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts via online video. Physical description: hair colour: black; build: slight. Speaks Indonesian, Arabic and Mindanao dialect. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts via online video. Physical description: hair colour: black; build: slight. Speaks Indonesian, Arabic and Mindanao dialect INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H526" s="5" t="inlineStr">
@@ -22034,7 +21695,7 @@
       </c>
       <c r="G527" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts via online video. Reportedly deceased. Physical description: eye colour: brown; hair colour: brown; complexion: dark. Speaks Malay, English, limited Arabic. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts via online video. Reportedly deceased. Physical description: eye colour: brown; hair colour: brown; complexion: dark. Speaks Malay, English, limited Arabic INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H527" s="5" t="inlineStr">
@@ -22076,9 +21737,7 @@
       </c>
       <c r="G528" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts via online video. Physical description: height: 156cm; weight: 60 kg (as at Sep. 2016); eye colour: black; hair colour: black; build: medium; high cheekbones. Speaks Tagalog, English, Arabic.  
-Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts via online video. Physical description: height: 156cm; weight: 60 kg (as at Sep. 2016); eye colour: black; hair colour: black; build: medium; high cheekbones. Speaks Tagalog, English, Arabic INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H528" s="5" t="inlineStr">
@@ -22120,9 +21779,7 @@
       </c>
       <c r="G529" s="5" t="inlineStr">
         <is>
-          <t>Pledged allegiance to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) in July 2014 and subsequently released on licence in October 2018 which expires in July 2021. 
-Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Pledged allegiance to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) in July 2014 and subsequently released on licence in October 2018 which expires in July 2021 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H529" s="5" t="inlineStr">
@@ -22164,11 +21821,7 @@
       </c>
       <c r="G530" s="5" t="inlineStr">
         <is>
-          <t>Former ISIL governor of al-Jazira Province, military leader in the Syrian Arab
-                Republic as well as member and chair of the ISIL Delegated Committee, which
-                exercises administrative control of ISIL's affairs. In custody of Iraq since 2019.
-                Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.
-             INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Former ISIL governor of al-Jazira Province, military leader in the Syrian Arab Republic as well as member and chair of the ISIL Delegated Committee, which exercises administrative control of ISIL's affairs. In custody of Iraq since 2019. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H530" s="5" t="inlineStr">
@@ -22202,7 +21855,7 @@
       <c r="F531" s="5" t="inlineStr"/>
       <c r="G531" s="5" t="inlineStr">
         <is>
-          <t>Son of Usama bin Laden (deceased). Announced by Aiman Muhammed Rabi al-Zawahiri (QDi.006) as an official member of Al-Qaida (QDe.004). Has called for followers of Al-Qaida to commit terror attacks. Was seen as the most probable successor of al-Zawahiri. Reportedly killed in a counterterrorism operation as of September 2019 in the Afghanistan/Pakistan region.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Son of Usama bin Laden (deceased). Announced by Aiman Muhammed Rabi al-Zawahiri (QDi.006) as an official member of Al-Qaida (QDe.004). Has called for followers of Al-Qaida to commit terror attacks. Was seen as the most probable successor of al-Zawahiri. Reportedly killed in a counterterrorism operation as of September 2019 in the Afghanistan/Pakistan region INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H531" s="5" t="inlineStr">
@@ -22244,8 +21897,7 @@
       </c>
       <c r="G532" s="5" t="inlineStr">
         <is>
-          <t>Founder of Jaish-i-Mohammed (QDe.019). Former leader of Harakat ul-Mujahidin / HUM (QDe.008).
-              INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Founder of Jaish-i-Mohammed (QDe.019). Former leader of Harakat ul-Mujahidin / HUM (QDe.008) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H532" s="5" t="inlineStr">
@@ -22287,7 +21939,7 @@
       </c>
       <c r="G533" s="5" t="inlineStr">
         <is>
-          <t>Member of Al Qaida in the Islamic Maghreb (AQIM) (QDe.014), Ansar Eddine (QDe.135), and Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM) (QDe.159). Physical description: height: 185 cm; weight: 80 kg  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Al Qaida in the Islamic Maghreb (AQIM) (QDe.014), Ansar Eddine (QDe.135), and Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM) (QDe.159). Physical description: height: 185 cm; weight: 80 kg INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H533" s="5" t="inlineStr">
@@ -22329,7 +21981,7 @@
       </c>
       <c r="G534" s="5" t="inlineStr">
         <is>
-          <t>Founding member of Ansar Eddine (QDe.135), operational leader of Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM) (QDe.159).  Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Founding member of Ansar Eddine (QDe.135), operational leader of Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM) (QDe.159) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H534" s="5" t="inlineStr">
@@ -22367,7 +22019,7 @@
       <c r="F535" s="5" t="inlineStr"/>
       <c r="G535" s="5" t="inlineStr">
         <is>
-          <t>Founder of the Katiba Macina of Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM) (QDe.159), executive of the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Eye colour: brown. Hair colour: dark.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Founder of the Katiba Macina of Jama'a Nusrat ul-Islam wa al-Muslimin (JNIM) (QDe.159), executive of the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Eye colour: brown. Hair colour: dark INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H535" s="5" t="inlineStr">
@@ -22409,15 +22061,7 @@
       </c>
       <c r="G536" s="5" t="inlineStr">
         <is>
-          <t>Leader of Islamic State in Iraq and the
-                                                  Levant, listed as Al-Qaida in Iraq (QDe.115).
-                                                  Mother’s name: Samira Shareef (سميرة شريف) or
-                                                  Sahra Sharif Abd al-Qader (سهرة شريف عبد القادر).
-                                                  Height 170 cm, right leg amputated. Photo
-                                                  available for inclusion in the INTERPOL-UN
-                                                  Security Council Special Notice. Arrest warrant
-                                                  issued by Iraq 2018. Reportedly deceased as of 3
-                                                  February 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Mother’s name: Samira Shareef (سميرة شريف) or Sahra Sharif Abd al-Qader (سهرة شريف عبد القادر). Height 170 cm, right leg amputated. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Arrest warrant issued by Iraq 2018. Reportedly deceased as of 3 February 2022 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H536" s="5" t="inlineStr">
@@ -22459,7 +22103,7 @@
       </c>
       <c r="G537" s="5" t="inlineStr">
         <is>
-          <t>Leader of Tehrik-e Taliban Pakistan (TTP) (QDe.132) following the death of former TTP leader Maulana Fazlullah (QDi.352). Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Tehrik-e Taliban Pakistan (TTP) (QDe.132) following the death of former TTP leader Maulana Fazlullah (QDi.352) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H537" s="5" t="inlineStr">
@@ -22501,7 +22145,7 @@
       </c>
       <c r="G538" s="5" t="inlineStr">
         <is>
-          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) in West Kalamoun, Syrian Arab Republic. Mother’s name is Amina Tohmeh.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Al-Nusrah Front for the People of the Levant (formerly listed) in West Kalamoun, Syrian Arab Republic. Mother’s name is Amina Tohmeh INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H538" s="5" t="inlineStr">
@@ -22543,7 +22187,7 @@
       </c>
       <c r="G539" s="5" t="inlineStr">
         <is>
-          <t>Turkey-based facilitator who provides financial services to, or in support of, Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Turkey-based facilitator who provides financial services to, or in support of, Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H539" s="5" t="inlineStr">
@@ -22585,7 +22229,7 @@
       </c>
       <c r="G540" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts. Physical description: height 176 cm, weight 73 kg, medium built, colour of eyes- brown, colour of hair- black/bald, complexion- brown.  Speaks English.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts. Physical description: height 176 cm, weight 73 kg, medium built, colour of eyes- brown, colour of hair- black/bald, complexion- brown. Speaks English INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H540" s="5" t="inlineStr">
@@ -22627,7 +22271,7 @@
       </c>
       <c r="G541" s="5" t="inlineStr">
         <is>
-          <t>Leader of the Islamic State of Iraq and the Levant - Khorasan (ISIL - K) (QDe.161). Information Technology Expert. Father’s name: Abdul Jabbar. Grandfather’s name: Abdul Ghaffar. Photo is available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of the Islamic State of Iraq and the Levant - Khorasan (ISIL - K) (QDe.161). Information Technology Expert. Father’s name: Abdul Jabbar. Grandfather’s name: Abdul Ghaffar. Photo is available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H541" s="5" t="inlineStr">
@@ -22669,8 +22313,7 @@
       </c>
       <c r="G542" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts via online video. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Recruited for ISIL and instructed individuals to perpetrate terrorist acts via online video INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H542" s="5" t="inlineStr">
@@ -22712,7 +22355,7 @@
       </c>
       <c r="G543" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of the Islamic State in Iraq and the Levant - Khorasan (ISIL - K) (QDe.161).</t>
+          <t>Senior leader of the Islamic State in Iraq and the Levant - Khorasan (ISIL - K) (QDe.161)</t>
         </is>
       </c>
       <c r="H543" s="5" t="inlineStr">
@@ -22746,7 +22389,7 @@
       <c r="F544" s="5" t="inlineStr"/>
       <c r="G544" s="5" t="inlineStr">
         <is>
-          <t>Spokesperson of the Islamic State in Iraq and the Levant - Khorasan (ISIL - K) (QDe.161). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Spokesperson of the Islamic State in Iraq and the Levant - Khorasan (ISIL - K) (QDe.161) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H544" s="5" t="inlineStr">
@@ -22788,7 +22431,7 @@
       </c>
       <c r="G545" s="5" t="inlineStr">
         <is>
-          <t>Abubakar Swalleh provides financial, material, or technological support for, or financial or other services to, or in support of, ISIL (listed as Al-Qaida in Iraq (QDe.115). He acted, since 2018, as an ISIL facilitator who provides financial and logistic support including recruitment for ISIL in East and Southern Africa. Phone number: +963936016952. Gender: Male  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Abubakar Swalleh provides financial, material, or technological support for, or financial or other services to, or in support of, ISIL (listed as Al-Qaida in Iraq (QDe.115). He acted, since 2018, as an ISIL facilitator who provides financial and logistic support including recruitment for ISIL in East and Southern Africa. Phone number: +963936016952. Gender: Male INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H545" s="5" t="inlineStr">
@@ -22830,7 +22473,7 @@
       </c>
       <c r="G546" s="5" t="inlineStr">
         <is>
-          <t>Assumed multiples roles within ISIL (Da’esh) listed as Al-Qaida in Iraq (QDe.115), including overseeing ISIL’s finances, material affairs and sources of revenue. He was also a member of the so-called Delegated Committee, which is the decision-making body of ISIL (Da’esh). He also participated in several terrorist operations against security forces while ISIL was controlling territory and was involved in the smuggling of oil derivates. Mother’s name: A’ishah Hasan. Gender: Male, Physical description: eye colour: black; hair colour: black; Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:</t>
+          <t>Assumed multiples roles within ISIL (Da’esh) listed as Al-Qaida in Iraq (QDe.115), including overseeing ISIL’s finances, material affairs and sources of revenue. He was also a member of the so-called Delegated Committee, which is the decision-making body of ISIL (Da’esh). He also participated in several terrorist operations against security forces while ISIL was controlling territory and was involved in the smuggling of oil derivates. Mother’s name: A’ishah Hasan. Gender: Male, Physical description: eye colour: black; hair colour: black; Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:</t>
         </is>
       </c>
       <c r="H546" s="5" t="inlineStr">
@@ -22872,7 +22515,7 @@
       </c>
       <c r="G547" s="5" t="inlineStr">
         <is>
-          <t>Served as a senior leader in ISIL (Da’esh) listed as Al-Qaida in Iraq (QDe.115) as its financial management officer. Mother’s name: Khadija Hattab Ismail. Gender: Male.  INTERPOL-UN Security Council Special Notice web link:</t>
+          <t>Served as a senior leader in ISIL (Da’esh) listed as Al-Qaida in Iraq (QDe.115) as its financial management officer. Mother’s name: Khadija Hattab Ismail. Gender: Male INTERPOL-UN Security Council Special Notice:</t>
         </is>
       </c>
       <c r="H547" s="5" t="inlineStr">
@@ -22914,7 +22557,7 @@
       </c>
       <c r="G548" s="5" t="inlineStr">
         <is>
-          <t>Works as a mediator in financing channels for ISIL in Central Africa, has been charged with financing a bombing that occurred in the Ugandan capital, Kampala, in 2021, attempted to coerce her three children in Uganda to send them to ISIL camps in the Democratic Republic of the Congo. Gender: Female.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2026-23487</t>
+          <t>Works as a mediator in financing channels for ISIL in Central Africa, has been charged with financing a bombing that occurred in the Ugandan capital, Kampala, in 2021, attempted to coerce her three children in Uganda to send them to ISIL camps in the Democratic Republic of the Congo. Gender: Female INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2026-23487</t>
         </is>
       </c>
       <c r="H548" s="5" t="inlineStr">
@@ -22956,7 +22599,7 @@
       </c>
       <c r="G549" s="5" t="inlineStr">
         <is>
-          <t>Retired from the Sudanese Army. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Retired from the Sudanese Army. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H549" s="5" t="inlineStr">
@@ -22998,7 +22641,7 @@
       </c>
       <c r="G550" s="5" t="inlineStr">
         <is>
-          <t>Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H550" s="5" t="inlineStr">
@@ -23040,7 +22683,7 @@
       </c>
       <c r="G551" s="5" t="inlineStr">
         <is>
-          <t>Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H551" s="5" t="inlineStr">
@@ -23196,7 +22839,7 @@
       </c>
       <c r="G555" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. INTERPOL-UN Security Council Special Notice web link:</t>
+          <t>Gender: Male. INTERPOL-UN Security Council Special Notice:</t>
         </is>
       </c>
       <c r="H555" s="5" t="inlineStr">
@@ -23322,7 +22965,7 @@
       </c>
       <c r="G558" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H558" s="5" t="inlineStr">
@@ -23360,7 +23003,7 @@
       </c>
       <c r="G559" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H559" s="5" t="inlineStr">
@@ -23399,7 +23042,7 @@
       <c r="G560" s="5" t="inlineStr">
         <is>
           <t>Gender: Female. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+ INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H560" s="5" t="inlineStr">
@@ -23437,7 +23080,7 @@
       </c>
       <c r="G561" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender: Male  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H561" s="5" t="inlineStr">
@@ -23479,7 +23122,7 @@
       </c>
       <c r="G562" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H562" s="5" t="inlineStr">
@@ -23521,7 +23164,7 @@
       </c>
       <c r="G563" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H563" s="5" t="inlineStr">
@@ -23563,7 +23206,7 @@
       </c>
       <c r="G564" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr">
@@ -23605,7 +23248,7 @@
       </c>
       <c r="G565" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H565" s="5" t="inlineStr">
@@ -23685,7 +23328,7 @@
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H567" s="5" t="inlineStr">
@@ -23723,7 +23366,7 @@
       <c r="F568" s="5" t="inlineStr"/>
       <c r="G568" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H568" s="5" t="inlineStr">
@@ -23765,7 +23408,7 @@
       </c>
       <c r="G569" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H569" s="5" t="inlineStr">
@@ -23808,7 +23451,7 @@
       <c r="G570" s="5" t="inlineStr">
         <is>
           <t>Married to a Somali woman. Lived in Egypt in 2005 and moved to Somalia in
-2009. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+2009. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H570" s="5" t="inlineStr">
@@ -23846,7 +23489,7 @@
       <c r="F571" s="5" t="inlineStr"/>
       <c r="G571" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H571" s="5" t="inlineStr">
@@ -23884,7 +23527,7 @@
       <c r="F572" s="5" t="inlineStr"/>
       <c r="G572" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H572" s="5" t="inlineStr">
@@ -23922,7 +23565,7 @@
       <c r="F573" s="5" t="inlineStr"/>
       <c r="G573" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H573" s="5" t="inlineStr">
@@ -23960,7 +23603,7 @@
       <c r="F574" s="5" t="inlineStr"/>
       <c r="G574" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H574" s="5" t="inlineStr">
@@ -24002,7 +23645,7 @@
       </c>
       <c r="G575" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H575" s="5" t="inlineStr">
@@ -24044,7 +23687,7 @@
       </c>
       <c r="G576" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H576" s="5" t="inlineStr">
@@ -24082,7 +23725,7 @@
       <c r="F577" s="5" t="inlineStr"/>
       <c r="G577" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraph 8(a) of resolution 1844 (2008) as “Engaging in or providing support for acts that threaten the peace, security or stability of Somalia, including acts that threaten the Djibouti Agreement of 18 August 2008 or the political process, or threaten the TFIs or AMISOM by force.” Adan is also associated with Al-Qaida affiliates, Al-Qaida in the Arabian Peninsula (AQAP – QDe.129) and Al-Qaida in the Islamic Maghreb (AQIM – Qde.014). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Listed pursuant to paragraph 8(a) of resolution 1844 (2008) as “Engaging in or providing support for acts that threaten the peace, security or stability of Somalia, including acts that threaten the Djibouti Agreement of 18 August 2008 or the political process, or threaten the TFIs or AMISOM by force.” Adan is also associated with Al-Qaida affiliates, Al-Qaida in the Arabian Peninsula (AQAP – QDe.129) and Al-Qaida in the Islamic Maghreb (AQIM – Qde.014). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H577" s="5" t="inlineStr">
@@ -24120,7 +23763,7 @@
       <c r="F578" s="5" t="inlineStr"/>
       <c r="G578" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraph 8(a) of resolution 1844 (2008) as “Engaging in or providing support for acts that threaten the peace, security or stability of Somalia, including acts that threaten the Djibouti Agreement of 18 August 2008 or the political process, or threaten the TFIs or AMISOM by force.” Ayman helped with preparations for the 5 January 2020 attack on Camp Simba in Lamu County, Kenya.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Listed pursuant to paragraph 8(a) of resolution 1844 (2008) as “Engaging in or providing support for acts that threaten the peace, security or stability of Somalia, including acts that threaten the Djibouti Agreement of 18 August 2008 or the political process, or threaten the TFIs or AMISOM by force.” Ayman helped with preparations for the 5 January 2020 attack on Camp Simba in Lamu County, Kenya.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H578" s="5" t="inlineStr">
@@ -24158,7 +23801,7 @@
       <c r="F579" s="5" t="inlineStr"/>
       <c r="G579" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraph 8(a) of resolution 1844 (2008) as “Engaging in or providing support for acts that threaten the peace, security or stability of Somalia, including acts that threaten the Djibouti Agreement of 18 August 2008 or the political process, or threaten the TFIs or AMISOM by force.” Karate played a key role in the Amniyat, the wing of al-Shabaab responsible for the recent attack on Garissa University College in Kenya that resulted in nearly 150 deaths. The Amniyat is al-Shabaab’s intelligence wing, which plays a key role in the execution of suicide attacks and assassinations in Somalia, Kenya, and other countries in the region, and provides logistics and support for al-Shabaab’s terrorist activities.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Listed pursuant to paragraph 8(a) of resolution 1844 (2008) as “Engaging in or providing support for acts that threaten the peace, security or stability of Somalia, including acts that threaten the Djibouti Agreement of 18 August 2008 or the political process, or threaten the TFIs or AMISOM by force.” Karate played a key role in the Amniyat, the wing of al-Shabaab responsible for the recent attack on Garissa University College in Kenya that resulted in nearly 150 deaths. The Amniyat is al-Shabaab’s intelligence wing, which plays a key role in the execution of suicide attacks and assassinations in Somalia, Kenya, and other countries in the region, and provides logistics and support for al-Shabaab’s terrorist activities.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H579" s="5" t="inlineStr">
@@ -24200,7 +23843,7 @@
       </c>
       <c r="G580" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraph 43(a) of resolution 2093 (2013) as “Engaging in or providing support for acts that threaten the peace, security or stability of Somalia, including acts that threaten the peace and reconciliation process in Somalia, or threaten the Federal Government of Somalia or AMISOM by force.” As a spokesperson for Al-Shabaab, Rage is involved in promulgating and supporting the group’s terrorist activities.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Listed pursuant to paragraph 43(a) of resolution 2093 (2013) as “Engaging in or providing support for acts that threaten the peace, security or stability of Somalia, including acts that threaten the peace and reconciliation process in Somalia, or threaten the Federal Government of Somalia or AMISOM by force.” As a spokesperson for Al-Shabaab, Rage is involved in promulgating and supporting the group’s terrorist activities.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H580" s="5" t="inlineStr">
@@ -24408,7 +24051,7 @@
       </c>
       <c r="G585" s="5" t="inlineStr">
         <is>
-          <t>Appointed as Chief of Defence Forces on 2 May 2018. Commanded SPLA Sector One, which operates primarily within Unity State, since January 2013. In his position as the SPLA Sector One commander, he has expanded or extended the conflict in South Sudan through breaches of the Cessation of Hostilities Agreement. The SPLA is a South Sudanese military entity that has engaged in actions that have extended the conflict in South Sudan, including breaches of the January 2014 Cessation of Hostilities Agreement and the May 9, 2014 Agreement to Resolve the Crisis in South Sudan, which was a re-commitment to the CoHA and has obstructed the activities of IGAD’s Monitoring and Verification Mechanism.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Appointed as Chief of Defence Forces on 2 May 2018. Commanded SPLA Sector One, which operates primarily within Unity State, since January 2013. In his position as the SPLA Sector One commander, he has expanded or extended the conflict in South Sudan through breaches of the Cessation of Hostilities Agreement. The SPLA is a South Sudanese military entity that has engaged in actions that have extended the conflict in South Sudan, including breaches of the January 2014 Cessation of Hostilities Agreement and the May 9, 2014 Agreement to Resolve the Crisis in South Sudan, which was a re-commitment to the CoHA and has obstructed the activities of IGAD’s Monitoring and Verification Mechanism.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H585" s="5" t="inlineStr">
@@ -24449,7 +24092,7 @@
           <t>Is the SPLM-IO Chief of General Staff and was previously the commander of
 opposition forces in Jonglei State. His forces conducted an early February 2015 attack
 in Jonglei State, and as of March 2015, he had tried to destroy the peace in Jonglei
-State through attacks on the civilian population. Photograph available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+State through attacks on the civilian population. Photograph available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H586" s="5" t="inlineStr">
@@ -24496,7 +24139,7 @@
 against civilians. In February 2014, forces under his command attacked United Nations
 camps, hospitals, churches, and schools, engaging in widespread rape, torture, and the
 destruction of property, in an attempt to flush out civilians, soldiers, and policemen
-allied with the government. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+allied with the government. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H587" s="5" t="inlineStr">
@@ -24537,7 +24180,7 @@
           <t>Has led and directed military actions against opposition forces and
 conducted confrontational troop movements in violation of the CoHA. During May 2015,
 forces under his command killed children, women and old men, burned property, and stole
-livestock as they advanced through Unity State towards Thorjath oil field. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+livestock as they advanced through Unity State towards Thorjath oil field. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H588" s="5" t="inlineStr">
@@ -24581,7 +24224,7 @@
         <is>
           <t>His Presidential Guard led the slaughter of Nuer civilians in and around
 Juba, many who were buried in mass graves. One such grave was purported to contain
-200-300 civilians. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+200-300 civilians. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H589" s="5" t="inlineStr">
@@ -24622,7 +24265,7 @@
           <t>Appointed the SPLA-IO’s Deputy Chief of Staff for Operations on December
 21, 2014. Forces under his command targeted civilians, including women, in April 2014
 during an assault on Bentiu, including targeted killings on the basis of
-ethnicity. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+ethnicity. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H590" s="5" t="inlineStr">
@@ -24744,7 +24387,7 @@
       </c>
       <c r="G593" s="5" t="inlineStr">
         <is>
-          <t>A close associate of Mullah Mohammed Omar (TAi.004). Member of Taliban Supreme Council as at Dec. 2009. Belongs to Baabar tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A close associate of Mullah Mohammed Omar (TAi.004). Member of Taliban Supreme Council as at Dec. 2009. Belongs to Baabar tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H593" s="5" t="inlineStr">
@@ -24786,7 +24429,7 @@
       </c>
       <c r="G594" s="5" t="inlineStr">
         <is>
-          <t>Active in terrorist operations in Eastern Afghanistan. Collects money from drug traffickers. Member of the Taliban Supreme Council as at 2009. Family is originally from Neka District, Paktia Province, Afghanistan. Responsible for attack on Afghan parliamentarians in November 2007 in Baghlan; owns land in central Baghlan Province. Belongs to Zadran tribe. Height 185 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47114</t>
+          <t>Active in terrorist operations in Eastern Afghanistan. Collects money from drug traffickers. Member of the Taliban Supreme Council as at 2009. Family is originally from Neka District, Paktia Province, Afghanistan. Responsible for attack on Afghan parliamentarians in November 2007 in Baghlan; owns land in central Baghlan Province. Belongs to Zadran tribe. Height 185 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47114</t>
         </is>
       </c>
       <c r="H594" s="5" t="inlineStr">
@@ -24824,7 +24467,7 @@
       </c>
       <c r="G595" s="5" t="inlineStr">
         <is>
-          <t>Father's name is Ghulam Nabi, also known as Mullah Musafir. Left eye missing. Brother-in-law of Ahmad Jan Akhundzada Shukoor Akhundzada (TAi.109). Believed to be in Afghanistan/Pakistan border area. Belongs to Hotak tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Reportedly deceased as of April 2013. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father's name is Ghulam Nabi, also known as Mullah Musafir. Left eye missing. Brother-in-law of Ahmad Jan Akhundzada Shukoor Akhundzada (TAi.109). Believed to be in Afghanistan/Pakistan border area. Belongs to Hotak tribe. Reportedly deceased as of April 2013 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H595" s="5" t="inlineStr">
@@ -24866,8 +24509,7 @@
       </c>
       <c r="G596" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Andar tribe. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to Andar tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H596" s="5" t="inlineStr">
@@ -24909,11 +24551,7 @@
       </c>
       <c r="G597" s="5" t="inlineStr">
         <is>
-          <t>Graduate of the Haqqaniya madrasa in Akora Khattak, Pakistan. Believed to
-have had close relations with Taliban Leader Mullah Mohammed Omar (TAi.004). Believed to
-be in Afghanistan/Pakistan border area. Member of Taliban Supreme Council as at June
-2010. Belongs to Barakzai tribe. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 27 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  Reportedly deceased as of January 2016. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Graduate of the Haqqaniya madrasa in Akora Khattak, Pakistan. Believed to have had close relations with Taliban Leader Mullah Mohammed Omar (TAi.004). Believed to be in Afghanistan/Pakistan border area. Member of Taliban Supreme Council as at June 2010. Belongs to Barakzai tribe. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Reportedly deceased as of January 2016 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H597" s="5" t="inlineStr">
@@ -24955,7 +24593,7 @@
       </c>
       <c r="G598" s="5" t="inlineStr">
         <is>
-          <t>Taliban Shadow Governor for Logar Province as of late 2012. Belongs to Sahak tribe (Ghilzai). Height 170 cm . Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25913</t>
+          <t>Taliban Shadow Governor for Logar Province as of late 2012. Belongs to Sahak tribe (Ghilzai). Height 170 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25913</t>
         </is>
       </c>
       <c r="H598" s="5" t="inlineStr">
@@ -24997,9 +24635,7 @@
       </c>
       <c r="G599" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Involved in drug
-trafficking. Belongs to Ghilzai tribe. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Involved in drug trafficking. Belongs to Ghilzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H599" s="5" t="inlineStr">
@@ -25037,9 +24673,7 @@
       </c>
       <c r="G600" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Military Council as well as Taliban Supreme
-Council as at June 2010. Belongs to Popalzai tribe. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Military Council as well as Taliban Supreme Council as at June 2010. Belongs to Popalzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H600" s="5" t="inlineStr">
@@ -25081,15 +24715,7 @@
       </c>
       <c r="G601" s="5" t="inlineStr">
         <is>
-          <t>Involved in drug trafficking as of 2011, primarily through Gerd-e-Jangal,
-Afghanistan. Active in the provinces of Khost, Paktia and Paktika, Afghanistan as of May
-2007. Taliban "Governor" of Kandahar as of May 2007. Deputy to Mullah Abdul Ghani
-Baradar (TAi.024) in the Taliban Supreme Council as of 2009. Taliban official
-responsible for four southern provinces of Afghanistan. Following the arrest of Mullah
-Baradar in February 2010 he was temporarily-in-charge of the Taliban Supreme Council.
-Believed to be in Afghanistan/Pakistan border area. Belongs to Ishaqzai tribe. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jul.
-2010. Reportedly killed in May 2016. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Involved in drug trafficking as of 2011, primarily through Gerd-e-Jangal, Afghanistan. Active in the provinces of Khost, Paktia and Paktika, Afghanistan as of May 2007. Taliban "Governor" of Kandahar as of May 2007. Deputy to Mullah Abdul Ghani Baradar (TAi.024) in the Taliban Supreme Council as of 2009. Taliban official responsible for four southern provinces of Afghanistan. Following the arrest of Mullah Baradar in February 2010 he was temporarily-in-charge of the Taliban Supreme Council. Believed to be in Afghanistan/Pakistan border area. Belongs to Ishaqzai tribe. Reportedly killed in May 2016 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H601" s="5" t="inlineStr">
@@ -25131,9 +24757,7 @@
       </c>
       <c r="G602" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Military Commission as at mid-2013. Believed to be
-in Afghanistan/Pakistan border area. Belongs to Barich tribe. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 1 Jun. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Taliban Military Commission as at mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Barich tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H602" s="5" t="inlineStr">
@@ -25175,9 +24799,7 @@
       </c>
       <c r="G603" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Ghilzai
-tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 29
-Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Ghilzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H603" s="5" t="inlineStr">
@@ -25215,9 +24837,7 @@
       </c>
       <c r="G604" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council as at 2009. Believed to be in
-Afghanistan/Pakistan border area. Belongs to Nurzai tribe. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Council as at 2009. Believed to be in Afghanistan/Pakistan border area. Belongs to Nurzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H604" s="5" t="inlineStr">
@@ -25259,8 +24879,7 @@
       </c>
       <c r="G605" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Popalzai tribe. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 29 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Deceased as of November 2015. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to Popalzai tribe. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Deceased as of November 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H605" s="5" t="inlineStr">
@@ -25302,10 +24921,7 @@
       </c>
       <c r="G606" s="5" t="inlineStr">
         <is>
-          <t>Leads a commission to register enemies of the Taliban as of mid-2013.
-Believed to be in Afghanistan/Pakistan border area. Belongs to Nurzai tribe. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul.
-2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leads a commission to register enemies of the Taliban as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Nurzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H606" s="5" t="inlineStr">
@@ -25343,9 +24959,7 @@
       </c>
       <c r="G607" s="5" t="inlineStr">
         <is>
-          <t>Works on recruitment for the Taliban movement as of mid-2013. Believed to
-be in Afghanistan/Pakistan border area. Belongs to Popalzai tribe. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Works on recruitment for the Taliban movement as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Popalzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H607" s="5" t="inlineStr">
@@ -25387,9 +25001,7 @@
       </c>
       <c r="G608" s="5" t="inlineStr">
         <is>
-          <t>One foot lost in landmine explosion. Believed to be in
-Afghanistan/Pakistan border area. Belongs to Nurzai tribe. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>One foot lost in landmine explosion. Believed to be in Afghanistan/Pakistan border area. Belongs to Nurzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H608" s="5" t="inlineStr">
@@ -25431,12 +25043,7 @@
       </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
-          <t>He was one of the deputies of Mullah Mohammed Omar (TAi.004) and a member
-of the Taliban's Supreme Council, in charge of military operations. Arrested in 2007 and
-was in custody in Pakistan. Confirmed deceased in March 2010 and buried in Karachi,
-Pakistan. Linked by marriage to Saleh Mohammad Kakar Akhtar Muhammad (TAi.149). Belonged
-to Alokozai tribe. Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>He was one of the deputies of Mullah Mohammed Omar (TAi.004) and a member of the Taliban's Supreme Council, in charge of military operations. Arrested in 2007 and was in custody in Pakistan. Confirmed deceased in March 2010 and buried in Karachi, Pakistan. Linked by marriage to Saleh Mohammad Kakar Akhtar Muhammad (TAi.149). Belonged to Alokozai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H609" s="5" t="inlineStr">
@@ -25478,7 +25085,7 @@
       </c>
       <c r="G610" s="5" t="inlineStr">
         <is>
-          <t>Missing left leg since 1996. Serious injury on his right foot. Height 168 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-316058</t>
+          <t>Missing left leg since 1996. Serious injury on his right foot. Height 168 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-316058</t>
         </is>
       </c>
       <c r="H610" s="5" t="inlineStr">
@@ -25520,7 +25127,7 @@
       </c>
       <c r="G611" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Popalzai tribe. Height 173 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 1 Jun. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to Popalzai tribe. Height 173 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H611" s="5" t="inlineStr">
@@ -25562,9 +25169,7 @@
       </c>
       <c r="G612" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Quetta Shura as at 2009. Taliban member responsible
-for Uruzgan Province, Afghanistan, as at 2011. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 1 Jun. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Taliban Quetta Shura as at 2009. Taliban member responsible for Uruzgan Province, Afghanistan, as at 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H612" s="5" t="inlineStr">
@@ -25606,7 +25211,7 @@
       </c>
       <c r="G613" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Supreme Council as of June 2007. Belongs to Sulaimankhel tribe. Height 170 cm.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Taliban Supreme Council as of June 2007. Belongs to Sulaimankhel tribe. Height 170 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H613" s="5" t="inlineStr">
@@ -25648,7 +25253,7 @@
       </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Jawzjan Province in Northern Afghanistan until 2008. Involved in drug trafficking. Height 178 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 1 Jun. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25909</t>
+          <t>Taliban member responsible for Jawzjan Province in Northern Afghanistan until 2008. Involved in drug trafficking. Height 178 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25909</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">
@@ -25686,10 +25291,7 @@
       </c>
       <c r="G615" s="5" t="inlineStr">
         <is>
-          <t>In July 2003 he was in custody in Kabul, Afghanistan. Released from
-custody in 2007. Believed to be in Afghanistan/Pakistan border area. Member of the
-Taliban leadership council as of mid-2013. Belongs to Andar tribe. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>In July 2003 he was in custody in Kabul, Afghanistan. Released from custody in 2007. Believed to be in Afghanistan/Pakistan border area. Member of the Taliban leadership council as of mid-2013. Belongs to Andar tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H615" s="5" t="inlineStr">
@@ -25731,10 +25333,7 @@
       </c>
       <c r="G616" s="5" t="inlineStr">
         <is>
-          <t>Directs Taliban "front" in Gelan District, Ghazni Province, Afghanistan
-as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Andar
-tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27
-Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Directs Taliban "front" in Gelan District, Ghazni Province, Afghanistan as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Andar tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H616" s="5" t="inlineStr">
@@ -25772,9 +25371,7 @@
       </c>
       <c r="G617" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Kakar
-tribe. He is a member of the Taliban Supreme Council. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Kakar tribe. He is a member of the Taliban Supreme Council INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H617" s="5" t="inlineStr">
@@ -25816,8 +25413,7 @@
       </c>
       <c r="G618" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H618" s="5" t="inlineStr">
@@ -25859,12 +25455,7 @@
       </c>
       <c r="G619" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Member of the Taliban
-Supreme Council as of May 2007. Member of the Financial Commission of the Taliban
-Council. Responsible for logistics for the Taliban and also active as a businessman in
-his personal capacity as at mid-2013. Belongs to Alizai tribe. Brother of Atiqullah Wali
-Mohammad (TAi.070). Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Member of the Taliban Supreme Council as of May 2007. Member of the Financial Commission of the Taliban Council. Responsible for logistics for the Taliban and also active as a businessman in his personal capacity as at mid-2013. Belongs to Alizai tribe. Brother of Atiqullah Wali Mohammad (TAi.070) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H619" s="5" t="inlineStr">
@@ -25902,8 +25493,7 @@
       </c>
       <c r="G620" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H620" s="5" t="inlineStr">
@@ -25945,7 +25535,7 @@
       </c>
       <c r="G621" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Nangarhar Province as at 2008. Until 7 Sep. 2007 he was also listed under number TAi.048. Height 175 cm.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 1 Jun. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47507</t>
+          <t>Taliban member responsible for Nangarhar Province as at 2008. Until 7 Sep. 2007 he was also listed under number TAi.048. Height 175 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47507</t>
         </is>
       </c>
       <c r="H621" s="5" t="inlineStr">
@@ -25983,9 +25573,7 @@
       </c>
       <c r="G622" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Wazir
-tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23
-Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Wazir tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H622" s="5" t="inlineStr">
@@ -26027,12 +25615,7 @@
       </c>
       <c r="G623" s="5" t="inlineStr">
         <is>
-          <t>Father of Sirajuddin Jallaloudine Haqqani (TAi.144), Nasiruddin Haqqani
-(TAi.146) and Badruddin Haqqani (deceased). Brother of Mohammad Ibrahim Omari (TAi.042)
-and Khalil Ahmed Haqqani (TAi.150). He is an active Taliban leader. Believed to be in
-Afghanistan/Pakistan border area. Head of the Taliban Miram Shah Shura as at 2008.
-Belongs to Zadran tribe. Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 27 Jul. 2010. Reportedly deceased as of September 2018. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Father of Sirajuddin Jallaloudine Haqqani (TAi.144), Nasiruddin Haqqani (TAi.146) and Badruddin Haqqani (deceased). Brother of Mohammad Ibrahim Omari (TAi.042) and Khalil Ahmed Haqqani (TAi.150). He is an active Taliban leader. Believed to be in Afghanistan/Pakistan border area. Head of the Taliban Miram Shah Shura as at 2008. Belongs to Zadran tribe. Reportedly deceased as of September 2018 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H623" s="5" t="inlineStr">
@@ -26074,9 +25657,7 @@
       </c>
       <c r="G624" s="5" t="inlineStr">
         <is>
-          <t>Brother of Jalaluddin Haqqani (TAi.040) Believed to be in
-Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Brother of Jalaluddin Haqqani (TAi.040) Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H624" s="5" t="inlineStr">
@@ -26118,7 +25699,7 @@
       </c>
       <c r="G625" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council responsible for Takhar and Badakhshan provinces. Height 172 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47175</t>
+          <t>Member of Taliban Supreme Council responsible for Takhar and Badakhshan provinces. Height 172 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47175</t>
         </is>
       </c>
       <c r="H625" s="5" t="inlineStr">
@@ -26160,7 +25741,7 @@
       </c>
       <c r="G626" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Supreme Council. Believed to be in Afghanistan/Pakistan border area. Height 174 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25939</t>
+          <t>Member of the Taliban Supreme Council. Believed to be in Afghanistan/Pakistan border area. Height 174 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25939</t>
         </is>
       </c>
       <c r="H626" s="5" t="inlineStr">
@@ -26202,7 +25783,7 @@
       </c>
       <c r="G627" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council and member of Taliban Cultural Commission as at 2010. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jul. 2010.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Council and member of Taliban Cultural Commission as at 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H627" s="5" t="inlineStr">
@@ -26244,9 +25825,7 @@
       </c>
       <c r="G628" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Hotak
-tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 29
-Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Hotak tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H628" s="5" t="inlineStr">
@@ -26288,11 +25867,7 @@
       </c>
       <c r="G629" s="5" t="inlineStr">
         <is>
-          <t>Family is originally from Zabul, but settled later in Helmand. Member of
-the Taliban Supreme Council and spokesperson for Mullah Mohammed Omar (TAi.004) as of
-2007. Believed to be in Afghanistan/Pakistan border area. Belongs to Kharoti tribe.
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul.
-2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Family is originally from Zabul, but settled later in Helmand. Member of the Taliban Supreme Council and spokesperson for Mullah Mohammed Omar (TAi.004) as of 2007. Believed to be in Afghanistan/Pakistan border area. Belongs to Kharoti tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H629" s="5" t="inlineStr">
@@ -26330,11 +25905,7 @@
       </c>
       <c r="G630" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Cultural Commission. Directs a Taliban "front" and
-coordinates all military activities of Taliban forces in Maiwand District, Kandahar
-Province, Afghanistan as of mid-2013. Believed to be in Afghanistan/Pakistan border
-area. Belongs to Kharoti (Taraki) tribe. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Cultural Commission. Directs a Taliban "front" and coordinates all military activities of Taliban forces in Maiwand District, Kandahar Province, Afghanistan as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Kharoti (Taraki) tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H630" s="5" t="inlineStr">
@@ -26372,11 +25943,7 @@
       </c>
       <c r="G631" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council as at June 2008. Deputy of Mullah
-Mohammed Omar (TAi.004) as at Mar. 2010. Member of the Supervision Commission of the
-Taliban as of mid-2013. Involved in drug trafficking. Believed to be in
-Afghanistan/Pakistan border area. Belongs to Achekzai tribe. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Council as at June 2008. Deputy of Mullah Mohammed Omar (TAi.004) as at Mar. 2010. Member of the Supervision Commission of the Taliban as of mid-2013. Involved in drug trafficking. Believed to be in Afghanistan/Pakistan border area. Belongs to Achekzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H631" s="5" t="inlineStr">
@@ -26418,10 +25985,7 @@
       </c>
       <c r="G632" s="5" t="inlineStr">
         <is>
-          <t>Directs a Taliban "front"(mahaz) and serves as member of the military
-commission of the Taliban as of mid-2013. Believed to be in Afghanistan/Pakistan border
-area. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23
-Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Directs a Taliban "front"(mahaz) and serves as member of the military commission of the Taliban as of mid-2013. Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H632" s="5" t="inlineStr">
@@ -26463,7 +26027,7 @@
       </c>
       <c r="G633" s="5" t="inlineStr">
         <is>
-          <t>Deputy to Mullah Mohammed Omar (TAi.004). Height 165 cm . Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25960</t>
+          <t>Deputy to Mullah Mohammed Omar (TAi.004). Height 165 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25960</t>
         </is>
       </c>
       <c r="H633" s="5" t="inlineStr">
@@ -26505,7 +26069,7 @@
       </c>
       <c r="G634" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Nurzai tribe. Height 185 cm.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25957</t>
+          <t>Belongs to Nurzai tribe. Height 185 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25957</t>
         </is>
       </c>
       <c r="H634" s="5" t="inlineStr">
@@ -26547,8 +26111,7 @@
       </c>
       <c r="G635" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased in 2005. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased in 2005 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H635" s="5" t="inlineStr">
@@ -26590,9 +26153,7 @@
       </c>
       <c r="G636" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Peshawar Shura as of 2008. Believed to be in
-Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 1 Jun. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Taliban Peshawar Shura as of 2008. Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H636" s="5" t="inlineStr">
@@ -26630,11 +26191,7 @@
       </c>
       <c r="G637" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council in charge of the Medical Committee as
-of Jan. 2011. Directly supervises three medical centers caring for wounded Taliban
-fighters as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to
-Barakzai tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Council in charge of the Medical Committee as of Jan. 2011. Directly supervises three medical centers caring for wounded Taliban fighters as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Barakzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H637" s="5" t="inlineStr">
@@ -26672,7 +26229,7 @@
       </c>
       <c r="G638" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. Picture available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Picture available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H638" s="5" t="inlineStr">
@@ -26714,10 +26271,7 @@
       </c>
       <c r="G639" s="5" t="inlineStr">
         <is>
-          <t>Lost one leg in 1980s. Interim leader of Taliban Supreme Council from
-February to April 2010. In charge of recruitment activities as of mid-2013. Believed to
-be in Afghanistan/Pakistan border area. Belongs to Isakzai tribe. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Lost one leg in 1980s. Interim leader of Taliban Supreme Council from February to April 2010. In charge of recruitment activities as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Isakzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H639" s="5" t="inlineStr">
@@ -26759,9 +26313,7 @@
       </c>
       <c r="G640" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Nuristan Province, Afghanistan, as of May
-2007. Belongs to Nuristani tribe. Reportedly deceased in early 2012. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Taliban member responsible for Nuristan Province, Afghanistan, as of May 2007. Belongs to Nuristani tribe. Reportedly deceased in early 2012 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H640" s="5" t="inlineStr">
@@ -26803,12 +26355,7 @@
       </c>
       <c r="G641" s="5" t="inlineStr">
         <is>
-          <t>Originally from Uruzgan, settled and lived later in Kandahar. Was a
-member of Taliban Supreme Council Political Commission in 2010. No specific role in the
-Taliban movement, active as a businessman in his personal capacity as of mid-2013.
-Believed to be in Afghanistan/Pakistan border area. Belongs to Alizai tribe. Brother of
-Abdul Jalil Haqqani Wali Mohammad (TAi.034). Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Originally from Uruzgan, settled and lived later in Kandahar. Was a member of Taliban Supreme Council Political Commission in 2010. No specific role in the Taliban movement, active as a businessman in his personal capacity as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Alizai tribe. Brother of Abdul Jalil Haqqani Wali Mohammad (TAi.034) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H641" s="5" t="inlineStr">
@@ -26850,7 +26397,7 @@
       </c>
       <c r="G642" s="5" t="inlineStr">
         <is>
-          <t>Cousin of Moulavi Noor Jalal. Grandfather’s name is Salam. Taliban member responsible for Laghman Province as of late 2010. Review pursuant to Security Council resolution 1822 (2008) was concluded on 1 Jun. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47312</t>
+          <t>Cousin of Moulavi Noor Jalal. Grandfather’s name is Salam. Taliban member responsible for Laghman Province as of late 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47312</t>
         </is>
       </c>
       <c r="H642" s="5" t="inlineStr">
@@ -26892,11 +26439,7 @@
       </c>
       <c r="G643" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Faryab, Jawzjan, Sari Pul and Balkh
-Provinces, Afghanistan as at June 2010. Involved in drug trafficking. Member of Taliban
-Supreme Council and Taliban Military Council as at December 2009. Believed to be in
-Afghanistan/Pakistan border area. Belongs to Sadat ethnic group. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Taliban member responsible for Faryab, Jawzjan, Sari Pul and Balkh Provinces, Afghanistan as at June 2010. Involved in drug trafficking. Member of Taliban Supreme Council and Taliban Military Council as at December 2009. Believed to be in Afghanistan/Pakistan border area. Belongs to Sadat ethnic group INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H643" s="5" t="inlineStr">
@@ -26938,10 +26481,7 @@
       </c>
       <c r="G644" s="5" t="inlineStr">
         <is>
-          <t>Ethnic Pashtun from Baghlan Province. Believed to be in
-Afghanistan/Pakistan border area. Speaks fluent English, Urdu and Arabic. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 29 Jul.
-2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Ethnic Pashtun from Baghlan Province. Believed to be in Afghanistan/Pakistan border area. Speaks fluent English, Urdu and Arabic INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H644" s="5" t="inlineStr">
@@ -26979,10 +26519,7 @@
       </c>
       <c r="G645" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council responsible for Takhar and Badakhshan
-provinces as at Dec. 2009. Confirmed killed on 17 February in Peshawar, Pakistan and
-buried in Takhar Province, Afghanistan. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Council responsible for Takhar and Badakhshan provinces as at Dec. 2009. Confirmed killed on 17 February in Peshawar, Pakistan and buried in Takhar Province, Afghanistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H645" s="5" t="inlineStr">
@@ -27024,9 +26561,7 @@
       </c>
       <c r="G646" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased in December 2006 and buried in Panjwai District,
-Kandahar Province, Afghanistan. Belonged to Ghilzai tribe. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased in December 2006 and buried in Panjwai District, Kandahar Province, Afghanistan. Belonged to Ghilzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H646" s="5" t="inlineStr">
@@ -27064,10 +26599,7 @@
       </c>
       <c r="G647" s="5" t="inlineStr">
         <is>
-          <t>Deputy Commander of Ezatullah Haqqani Khan Sayyid (TAi.064) as at Mar.
-2010. Member of Taliban Peshawar Military Council as at June 2010. Belongs to Pashai
-ethnic group. Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Deputy Commander of Ezatullah Haqqani Khan Sayyid (TAi.064) as at Mar. 2010. Member of Taliban Peshawar Military Council as at June 2010. Belongs to Pashai ethnic group INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H647" s="5" t="inlineStr">
@@ -27109,11 +26641,7 @@
       </c>
       <c r="G648" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Supreme Council as of May 2007. Believed to be in
-Afghanistan/Pakistan border area. Member of the Taliban Peshawar Shura. Responsible for
-Afghan Taliban activity in Federally Administrated Tribal Areas, Pakistan as at 2008. A
-leading expert in IED and suicide attacks as of 2012. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 1 Jun. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Taliban Supreme Council as of May 2007. Believed to be in Afghanistan/Pakistan border area. Member of the Taliban Peshawar Shura. Responsible for Afghan Taliban activity in Federally Administrated Tribal Areas, Pakistan as at 2008. A leading expert in IED and suicide attacks as of 2012 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H648" s="5" t="inlineStr">
@@ -27155,7 +26683,7 @@
       </c>
       <c r="G649" s="5" t="inlineStr">
         <is>
-          <t>Height 168 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25979</t>
+          <t>Height 168 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25979</t>
         </is>
       </c>
       <c r="H649" s="5" t="inlineStr">
@@ -27197,9 +26725,7 @@
       </c>
       <c r="G650" s="5" t="inlineStr">
         <is>
-          <t>As of mid-2007, he provided support to the Taliban in the form of weapons
-and money. Believed to be in the Gulf region. Belongs to Taraki tribe. Review pursuant
-to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As of mid-2007, he provided support to the Taliban in the form of weapons and money. Believed to be in the Gulf region. Belongs to Taraki tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H650" s="5" t="inlineStr">
@@ -27237,9 +26763,7 @@
       </c>
       <c r="G651" s="5" t="inlineStr">
         <is>
-          <t>Deputy Head (Intelligence) of the Quetta Military Council as of 2009.
-Believed to be in Afghanistan/Pakistan border area. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Deputy Head (Intelligence) of the Quetta Military Council as of 2009. Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H651" s="5" t="inlineStr">
@@ -27281,9 +26805,7 @@
       </c>
       <c r="G652" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Military Council as at 2009. Believed to be in
-Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Military Council as at 2009. Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H652" s="5" t="inlineStr">
@@ -27325,9 +26847,7 @@
       </c>
       <c r="G653" s="5" t="inlineStr">
         <is>
-          <t>Advisor to the Taliban Supreme Council as of mid-2013. Believed to be in
-Afghanistan/Pakistan border area. Belongs to Barakzai tribe. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Advisor to the Taliban Supreme Council as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Barakzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H653" s="5" t="inlineStr">
@@ -27369,8 +26889,7 @@
       </c>
       <c r="G654" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Hottak tribe. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 1 Jun. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to Hottak tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H654" s="5" t="inlineStr">
@@ -27412,7 +26931,7 @@
       </c>
       <c r="G655" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Tokhi tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to Tokhi tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H655" s="5" t="inlineStr">
@@ -27454,10 +26973,7 @@
       </c>
       <c r="G656" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council and advisor to Mullah Mohammed Omar
-(TAi.004) as at June 2010. Leads a Taliban "front" (mahaz) as of mid-2013. Believed to
-be in Afghanistan/Pakistan border area. Belongs to Sadat ethnic group. Review pursuant
-to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Council and advisor to Mullah Mohammed Omar (TAi.004) as at June 2010. Leads a Taliban "front" (mahaz) as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Sadat ethnic group INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H656" s="5" t="inlineStr">
@@ -27499,9 +27015,7 @@
       </c>
       <c r="G657" s="5" t="inlineStr">
         <is>
-          <t>Associated with Mullah Jalil Haqqani (TAi.034). Believed to be in
-Afghanistan/Pakistan border area. Belongs to Popalzai tribe. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Mullah Jalil Haqqani (TAi.034). Believed to be in Afghanistan/Pakistan border area. Belongs to Popalzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H657" s="5" t="inlineStr">
@@ -27543,7 +27057,7 @@
       </c>
       <c r="G658" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Popalzai tribe. Height 176 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25973</t>
+          <t>Belongs to Popalzai tribe. Height 176 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25973</t>
         </is>
       </c>
       <c r="H658" s="5" t="inlineStr">
@@ -27585,10 +27099,7 @@
       </c>
       <c r="G659" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Supreme Council as of 2009. Believed to be in
-Afghanistan/Pakistan border area. Belongs to Alokozai tribe. Member of Taliban
-leadership in Helmand Province, Afghanistan. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 1 Jun. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Taliban Supreme Council as of 2009. Believed to be in Afghanistan/Pakistan border area. Belongs to Alokozai tribe. Member of Taliban leadership in Helmand Province, Afghanistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H659" s="5" t="inlineStr">
@@ -27626,9 +27137,7 @@
       </c>
       <c r="G660" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Gerd-e-Jangal Shura and Head of the Taliban
-Prisoners and Refugees Committee. Belongs to Ishaqzai tribe. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Taliban Gerd-e-Jangal Shura and Head of the Taliban Prisoners and Refugees Committee. Belongs to Ishaqzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H660" s="5" t="inlineStr">
@@ -27670,7 +27179,7 @@
       </c>
       <c r="G661" s="5" t="inlineStr">
         <is>
-          <t>Has a prosthetic right leg. Member of Taliban Supreme Council as of mid-2013, acted as deputy of Mullah Mohammed Omar (TAi.004) in Mar. 2010. Believed to be in Afghanistan/Pakistan border area. Belongs to Achekzai tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. Deceased as of 9 February 2016. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Has a prosthetic right leg. Member of Taliban Supreme Council as of mid-2013, acted as deputy of Mullah Mohammed Omar (TAi.004) in Mar. 2010. Believed to be in Afghanistan/Pakistan border area. Belongs to Achekzai tribe. Deceased as of 9 February 2016 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H661" s="5" t="inlineStr">
@@ -27712,11 +27221,7 @@
       </c>
       <c r="G662" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Herat, Farah and Nimroz provinces as at
-mid-2013. Member of the Taliban Supreme Council and Quetta Shura. Believed to be in
-Afghanistan/Pakistan border area. Belongs to Achekzai tribe. Involved in transporting
-suicide bombers to Afghanistan. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Taliban member responsible for Herat, Farah and Nimroz provinces as at mid-2013. Member of the Taliban Supreme Council and Quetta Shura. Believed to be in Afghanistan/Pakistan border area. Belongs to Achekzai tribe. Involved in transporting suicide bombers to Afghanistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H662" s="5" t="inlineStr">
@@ -27754,8 +27259,7 @@
       </c>
       <c r="G663" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H663" s="5" t="inlineStr">
@@ -27793,10 +27297,7 @@
       </c>
       <c r="G664" s="5" t="inlineStr">
         <is>
-          <t>Supervises two military training centers of the Taliban as of mid-2013.
-Believed to be in Afghanistan/Pakistan border area. Belongs to Hotak tribe. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 29 Jul.
-2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Supervises two military training centers of the Taliban as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Hotak tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H664" s="5" t="inlineStr">
@@ -27838,10 +27339,7 @@
       </c>
       <c r="G665" s="5" t="inlineStr">
         <is>
-          <t>Alternative title: Sar Muallim. Reconciled after the fall of the Taliban
-regime, and assumed duties under the new Government on district level in Kunduz
-Province. Confirmed assassinated by Taliban on 9 November 2008. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Alternative title: Sar Muallim. Reconciled after the fall of the Taliban regime, and assumed duties under the new Government on district level in Kunduz Province. Confirmed assassinated by Taliban on 9 November 2008 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H665" s="5" t="inlineStr">
@@ -27883,9 +27381,7 @@
       </c>
       <c r="G666" s="5" t="inlineStr">
         <is>
-          <t>Taliban commander for Ghazni Province as at 2008. Belongs to Andar tribe.
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul.
-2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Taliban commander for Ghazni Province as at 2008. Belongs to Andar tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H666" s="5" t="inlineStr">
@@ -27927,13 +27423,7 @@
       </c>
       <c r="G667" s="5" t="inlineStr">
         <is>
-          <t>Involved in drug trafficking. Taliban member responsible for military
-affairs in Takhar province, Afghanistan, as of May 2007. Facilitated fund raising in the
-Gulf on behalf of the Taliban since 2003. Also facilitated meetings between Taliban
-officials and wealthy supporters and arranged for more than a dozen individuals to
-travel to Kabul, Afghanistan, for suicide attacks. Believed to be in the Gulf region.
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul.
-2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Involved in drug trafficking. Taliban member responsible for military affairs in Takhar province, Afghanistan, as of May 2007. Facilitated fund raising in the Gulf on behalf of the Taliban since 2003. Also facilitated meetings between Taliban officials and wealthy supporters and arranged for more than a dozen individuals to travel to Kabul, Afghanistan, for suicide attacks. Believed to be in the Gulf region INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H667" s="5" t="inlineStr">
@@ -27975,8 +27465,7 @@
       </c>
       <c r="G668" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan/Iran border area. Review pursuant
-to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan/Iran border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H668" s="5" t="inlineStr">
@@ -28018,9 +27507,7 @@
       </c>
       <c r="G669" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Quetta Shura. Believed to be in
-Afghanistan/Pakistan border area. Belongs to Nurzai tribe. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of the Taliban Quetta Shura. Believed to be in Afghanistan/Pakistan border area. Belongs to Nurzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H669" s="5" t="inlineStr">
@@ -28058,10 +27545,7 @@
       </c>
       <c r="G670" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Nangarhar Province as at 2011. Believed to
-be in Afghanistan/Pakistan border area. Belongs to Zadran tribe. Close associate of
-Sirajuddin Jallaloudine Haqqani (TAi.144). Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 1 Jun. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Taliban member responsible for Nangarhar Province as at 2011. Believed to be in Afghanistan/Pakistan border area. Belongs to Zadran tribe. Close associate of Sirajuddin Jallaloudine Haqqani (TAi.144) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H670" s="5" t="inlineStr">
@@ -28103,7 +27587,7 @@
       </c>
       <c r="G671" s="5" t="inlineStr">
         <is>
-          <t>Originally from Ghazni Province, but later lived in Uruzgan. Taliban Shadow Governor for Uruzgan Province as of late 2012. Serves as a member of the Military Commission as of July 2016. Belongs to Hotak tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Originally from Ghazni Province, but later lived in Uruzgan. Taliban Shadow Governor for Uruzgan Province as of late 2012. Serves as a member of the Military Commission as of July 2016. Belongs to Hotak tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H671" s="5" t="inlineStr">
@@ -28145,9 +27629,7 @@
       </c>
       <c r="G672" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council as at 2011. Belongs to Nurzai tribe.
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul.
-2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Supreme Council as at 2011. Belongs to Nurzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H672" s="5" t="inlineStr">
@@ -28185,9 +27667,7 @@
       </c>
       <c r="G673" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased in North Afghanistan in 1999. Belonged to Wardak
-tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27
-Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased in North Afghanistan in 1999. Belonged to Wardak tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H673" s="5" t="inlineStr">
@@ -28229,10 +27709,7 @@
       </c>
       <c r="G674" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Uruzgan Province, Afghanistan, as at early
-2007. Brother-in-law of Mullah Mohammed Omar (TAi.004). Believed to be in
-Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Taliban member responsible for Uruzgan Province, Afghanistan, as at early 2007. Brother-in-law of Mullah Mohammed Omar (TAi.004). Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H674" s="5" t="inlineStr">
@@ -28274,7 +27751,7 @@
       </c>
       <c r="G675" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council and Head of Taliban Religious Committee. Belongs to Ahmadzai tribe. Height 175 cm or 180 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 23 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-26129</t>
+          <t>Member of Taliban Supreme Council and Head of Taliban Religious Committee. Belongs to Ahmadzai tribe. Height 175 cm or 180 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-26129</t>
         </is>
       </c>
       <c r="H675" s="5" t="inlineStr">
@@ -28316,8 +27793,7 @@
       </c>
       <c r="G676" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased in 2001. Belonged to Kakar tribe. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010.</t>
+          <t>Reportedly deceased in 2001. Belonged to Kakar tribe</t>
         </is>
       </c>
       <c r="H676" s="5" t="inlineStr">
@@ -28355,7 +27831,7 @@
       </c>
       <c r="G677" s="5" t="inlineStr">
         <is>
-          <t>Deputy Head of Taliban Embassy in Riyadh, Saudi Arabia until 25 Sept. 1998. Believed to be in Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Picture available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Deputy Head of Taliban Embassy in Riyadh, Saudi Arabia until 25 Sept. 1998. Believed to be in Afghanistan/Pakistan border area. Picture available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H677" s="5" t="inlineStr">
@@ -28393,8 +27869,7 @@
       </c>
       <c r="G678" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H678" s="5" t="inlineStr">
@@ -28436,7 +27911,7 @@
       </c>
       <c r="G679" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Ghilzai tribe. Height: 175 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-26140</t>
+          <t>Belongs to Ghilzai tribe. Height: 175 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-26140</t>
         </is>
       </c>
       <c r="H679" s="5" t="inlineStr">
@@ -28474,7 +27949,7 @@
       </c>
       <c r="G680" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Alizai tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. Picture available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Alizai tribe. Picture available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H680" s="5" t="inlineStr">
@@ -28516,7 +27991,7 @@
       </c>
       <c r="G681" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Hotak tribe. Height 169 cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-306385</t>
+          <t>Belongs to Hotak tribe. Height 169 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-306385</t>
         </is>
       </c>
       <c r="H681" s="5" t="inlineStr">
@@ -28554,8 +28029,7 @@
       </c>
       <c r="G682" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H682" s="5" t="inlineStr">
@@ -28597,8 +28071,7 @@
       </c>
       <c r="G683" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Mangal tribe. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to Mangal tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H683" s="5" t="inlineStr">
@@ -28640,7 +28113,7 @@
       </c>
       <c r="G684" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. Picture available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Picture available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H684" s="5" t="inlineStr">
@@ -28682,10 +28155,7 @@
       </c>
       <c r="G685" s="5" t="inlineStr">
         <is>
-          <t>Financial advisor to Taliban Peshawar Military Council and Head of
-Taliban Peshawar Financial Commission. Believed to be in Afghanistan/Pakistan border
-area. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21
-Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Financial advisor to Taliban Peshawar Military Council and Head of Taliban Peshawar Financial Commission. Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H685" s="5" t="inlineStr">
@@ -28727,8 +28197,7 @@
       </c>
       <c r="G686" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H686" s="5" t="inlineStr">
@@ -28770,9 +28239,7 @@
       </c>
       <c r="G687" s="5" t="inlineStr">
         <is>
-          <t>Involved in drug trafficking. Belongs to Tajik ethnic group. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 29 Jul.
-2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Involved in drug trafficking. Belongs to Tajik ethnic group INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H687" s="5" t="inlineStr">
@@ -28814,9 +28281,7 @@
       </c>
       <c r="G688" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Peshawar Military Council as at 2010. Believed to be in
-Afghanistan/Pakistan border area. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Taliban Peshawar Military Council as at 2010. Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H688" s="5" t="inlineStr">
@@ -28854,8 +28319,7 @@
       </c>
       <c r="G689" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H689" s="5" t="inlineStr">
@@ -28897,8 +28361,7 @@
       </c>
       <c r="G690" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Popalzai tribe. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to Popalzai tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H690" s="5" t="inlineStr">
@@ -28936,8 +28399,7 @@
       </c>
       <c r="G691" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Reportedly deceased INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H691" s="5" t="inlineStr">
@@ -28979,10 +28441,7 @@
       </c>
       <c r="G692" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Ghazni Province, Afghanistan, as of May
-2007. Head of an intelligence network. Believed to be in Afghanistan/Pakistan border
-area. Belongs to Suleimankheil tribe. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 21 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Taliban member responsible for Ghazni Province, Afghanistan, as of May 2007. Head of an intelligence network. Believed to be in Afghanistan/Pakistan border area. Belongs to Suleimankheil tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H692" s="5" t="inlineStr">
@@ -29020,8 +28479,7 @@
       </c>
       <c r="G693" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H693" s="5" t="inlineStr">
@@ -29059,9 +28517,7 @@
       </c>
       <c r="G694" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Safi
-tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 29
-Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Safi tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H694" s="5" t="inlineStr">
@@ -29099,8 +28555,7 @@
       </c>
       <c r="G695" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H695" s="5" t="inlineStr">
@@ -29142,9 +28597,7 @@
       </c>
       <c r="G696" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Baloch
-ethnic group. Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Baloch ethnic group INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H696" s="5" t="inlineStr">
@@ -29186,8 +28639,7 @@
       </c>
       <c r="G697" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 29 Jul. 2010. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H697" s="5" t="inlineStr">
@@ -29225,9 +28677,7 @@
       </c>
       <c r="G698" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Baloch
-ethnic group. Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 21 Jul. 2010. Additional title: Hafiz. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Belongs to Baloch ethnic group. Additional title: Hafiz INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H698" s="5" t="inlineStr">
@@ -29269,7 +28719,7 @@
       </c>
       <c r="G699" s="5" t="inlineStr">
         <is>
-          <t>Heading the Haqqani Network (TAe.012) as of late 2012. Son of Jalaluddin Haqqani (TAi.040). Belongs to Sultan Khel section, Zadran tribe of Garda Saray of Paktia province, Afghanistan. Height 187 cm or 180cm. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-44300</t>
+          <t>Heading the Haqqani Network (TAe.012) as of late 2012. Son of Jalaluddin Haqqani (TAi.040). Belongs to Sultan Khel section, Zadran tribe of Garda Saray of Paktia province, Afghanistan. Height 187 cm or 180cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-44300</t>
         </is>
       </c>
       <c r="H699" s="5" t="inlineStr">
@@ -29311,10 +28761,7 @@
       </c>
       <c r="G700" s="5" t="inlineStr">
         <is>
-          <t>Has travelled to Kuwait, Saudi Arabia, the Libyan Arab Jamahiriya and the
-United Arab Emirates to raise funds for the Taliban. Treasurer to Abdul Ghani Baradar
-Abdul Ahmad Turk (TAi.024). Believed to be in Afghanistan/Pakistan border
-area. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Has travelled to Kuwait, Saudi Arabia, the Libyan Arab Jamahiriya and the United Arab Emirates to raise funds for the Taliban. Treasurer to Abdul Ghani Baradar Abdul Ahmad Turk (TAi.024). Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H700" s="5" t="inlineStr">
@@ -29356,10 +28803,7 @@
       </c>
       <c r="G701" s="5" t="inlineStr">
         <is>
-          <t>A leader of the Haqqani Network (TAe.012), which operates out of North
-Waziristan in the Federally Administered Tribal Areas of Pakistan. Son of Jalaluddin
-Haqqani (TAi.040). Has travelled to Saudi Arabia and the United Arab Emirates to raise
-funds for the Taliban. Reportedly deceased as of 2013. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A leader of the Haqqani Network (TAe.012), which operates out of North Waziristan in the Federally Administered Tribal Areas of Pakistan. Son of Jalaluddin Haqqani (TAi.040). Has travelled to Saudi Arabia and the United Arab Emirates to raise funds for the Taliban. Reportedly deceased as of 2013 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H701" s="5" t="inlineStr">
@@ -29401,7 +28845,7 @@
       </c>
       <c r="G702" s="5" t="inlineStr">
         <is>
-          <t>Head of Taliban Financial Commission as at mid-2013. Associated with Mullah Mohammed Omar (TAi.004). Served as Omar's principal finance officer and one of his closest advisors. Belongs to Ishaqzai tribe. Height: 156 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Head of Taliban Financial Commission as at mid-2013. Associated with Mullah Mohammed Omar (TAi.004). Served as Omar's principal finance officer and one of his closest advisors. Belongs to Ishaqzai tribe. Height: 156 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H702" s="5" t="inlineStr">
@@ -29443,8 +28887,7 @@
       </c>
       <c r="G703" s="5" t="inlineStr">
         <is>
-          <t>Has managed a drug trafficking network in Helmand Province, Afghanistan.
-Has regularly traveled to Pakistan. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Has managed a drug trafficking network in Helmand Province, Afghanistan. Has regularly traveled to Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H703" s="5" t="inlineStr">
@@ -29486,12 +28929,7 @@
       </c>
       <c r="G704" s="5" t="inlineStr">
         <is>
-          <t>Has run an organized smuggling network in Kandahar and Helmand provinces,
-Afghanistan. Previously operated heroin processing laboratories in Band-e Temur,
-Kandahar Province, Afghanistan. Has owned a car dealership in Mirwais Mena, Dand
-District in Kandahar Province, Afghanistan. Released from custody in Afghanistan in
-February 2014. Linked by marriage to Mullah Ubaidullah Akhund Yar Mohammad Akhund
-(TAi.022). Belongs to Kakar tribe. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Has run an organized smuggling network in Kandahar and Helmand provinces, Afghanistan. Previously operated heroin processing laboratories in Band-e Temur, Kandahar Province, Afghanistan. Has owned a car dealership in Mirwais Mena, Dand District in Kandahar Province, Afghanistan. Released from custody in Afghanistan in February 2014. Linked by marriage to Mullah Ubaidullah Akhund Yar Mohammad Akhund (TAi.022). Belongs to Kakar tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H704" s="5" t="inlineStr">
@@ -29533,7 +28971,7 @@
       </c>
       <c r="G705" s="5" t="inlineStr">
         <is>
-          <t>Has previously traveled to, and raised funds in, Dubai, United Arab Emirates. Brother of Jalaluddin Haqqani (TAi.040) and uncle of Sirajuddin Jallaloudine Haqqani (TAi.144). Reportedly deceased as of 11 December 2024.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Has previously traveled to, and raised funds in, Dubai, United Arab Emirates. Brother of Jalaluddin Haqqani (TAi.040) and uncle of Sirajuddin Jallaloudine Haqqani (TAi.144). Reportedly deceased as of 11 December 2024 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H705" s="5" t="inlineStr">
@@ -29575,13 +29013,7 @@
       </c>
       <c r="G706" s="5" t="inlineStr">
         <is>
-          <t>Prominent Taliban financier. As of mid-2009, supplied weapons,
-ammunition, explosives and medical equipment to Taliban fighters; and raised funds for
-the Taliban, and provided training to them, in the Afghanistan/Pakistan border region.
-Has previously organized and funded Taliban operations in Kandahar Province,
-Afghanistan. As of 2010, travelled to and owned businesses in Dubai, United Arab
-Emirates, and Japan. Belongs to Noorzai tribe, Miralzai sub-tribe. Brother of Malik
-Noorzai (TAi.154). Father’s name is Akhtar Mohammed (a.k.a.: Haji Mira Khan). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Prominent Taliban financier. As of mid-2009, supplied weapons, ammunition, explosives and medical equipment to Taliban fighters; and raised funds for the Taliban, and provided training to them, in the Afghanistan/Pakistan border region. Has previously organized and funded Taliban operations in Kandahar Province, Afghanistan. As of 2010, travelled to and owned businesses in Dubai, United Arab Emirates, and Japan. Belongs to Noorzai tribe, Miralzai sub-tribe. Brother of Malik Noorzai (TAi.154). Father’s name is Akhtar Mohammed (a.k.a.: Haji Mira Khan) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H706" s="5" t="inlineStr">
@@ -29623,7 +29055,7 @@
       </c>
       <c r="G707" s="5" t="inlineStr">
         <is>
-          <t>Taliban financier. Owns businesses in Japan and frequently travels to Dubai, United Arab Emirates, and Japan. As of 2009, facilitated Taliban activities, including through recruitment and the provision of logistical support. Belongs to Noorzai tribe. Brother of Faizullah Khan Noorzai (TAi.153). Father’s name is Haji Akhtar Muhammad. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Taliban financier. Owns businesses in Japan and frequently travels to Dubai, United Arab Emirates, and Japan. As of 2009, facilitated Taliban activities, including through recruitment and the provision of logistical support. Belongs to Noorzai tribe. Brother of Faizullah Khan Noorzai (TAi.153). Father’s name is Haji Akhtar Muhammad INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H707" s="5" t="inlineStr">
@@ -29661,10 +29093,7 @@
       <c r="F708" s="5" t="inlineStr"/>
       <c r="G708" s="5" t="inlineStr">
         <is>
-          <t>Key commander in the Haqqani Network (TAe.012) under Sirajuddin
-Jallaloudine Haqqani (TAi.144). Taliban Shadow Governor for Orgun District, Paktika
-Province as of early 2010. Operated a training camp for non-Afghan fighters in Paktika
-Province. Has been involved in the transport of weapons to Afghanistan. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Key commander in the Haqqani Network (TAe.012) under Sirajuddin Jallaloudine Haqqani (TAi.144). Taliban Shadow Governor for Orgun District, Paktika Province as of early 2010. Operated a training camp for non-Afghan fighters in Paktika Province. Has been involved in the transport of weapons to Afghanistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H708" s="5" t="inlineStr">
@@ -29706,7 +29135,7 @@
       </c>
       <c r="G709" s="5" t="inlineStr">
         <is>
-          <t>Senior Taliban official with military and financial responsibilities as at 2011. Leader of the Taliban’s Military Council as of 2010. In 2008 and 2009, served as a Taliban finance officer and distributed money to Taliban commanders in Afghanistan/Pakistan border area. Height: 180 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-308182</t>
+          <t>Senior Taliban official with military and financial responsibilities as at 2011. Leader of the Taliban’s Military Council as of 2010. In 2008 and 2009, served as a Taliban finance officer and distributed money to Taliban commanders in Afghanistan/Pakistan border area. Height: 180 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-308182</t>
         </is>
       </c>
       <c r="H709" s="5" t="inlineStr">
@@ -29748,11 +29177,7 @@
       </c>
       <c r="G710" s="5" t="inlineStr">
         <is>
-          <t>Represents and provides financial and logistical support to the Haqqani
-Network (TAe.012), which is based in Afghanistan/Pakistan border area. Member of the
-Taliban Financial Council. Has travelled abroad to raise funds on behalf of Sirajuddin
-Jallaloudine Haqqani (TAi.144), Jalaluddin Haqqani (TAi.040), the Haqqani network and
-the Taliban. Believed to be in Afghanistan/Pakistan border area. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Represents and provides financial and logistical support to the Haqqani Network (TAe.012), which is based in Afghanistan/Pakistan border area. Member of the Taliban Financial Council. Has travelled abroad to raise funds on behalf of Sirajuddin Jallaloudine Haqqani (TAi.144), Jalaluddin Haqqani (TAi.040), the Haqqani network and the Taliban. Believed to be in Afghanistan/Pakistan border area INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H710" s="5" t="inlineStr">
@@ -29790,13 +29215,7 @@
       <c r="F711" s="5" t="inlineStr"/>
       <c r="G711" s="5" t="inlineStr">
         <is>
-          <t>Senior Taliban member as at 2011 with financial duties, including raising funds
-                on behalf of the leadership. Has provided logistical support for Taliban operations
-                and channeled proceeds from drug trafficking to arms purchases. Has acted as
-                secretary to Taliban leader Mullah Mohammed Omar (TAi.004) and as his messenger at
-                senior-level meetings of the Taliban. Also associated with Gul Agha Ishakzai
-                (TAi.147). Member of Mullah Mohammed Omar’s (TAi.004) inner circle during the
-                Taliban regime. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior Taliban member as at 2011 with financial duties, including raising funds on behalf of the leadership. Has provided logistical support for Taliban operations and channeled proceeds from drug trafficking to arms purchases. Has acted as secretary to Taliban leader Mullah Mohammed Omar (TAi.004) and as his messenger at senior-level meetings of the Taliban. Also associated with Gul Agha Ishakzai (TAi.147). Member of Mullah Mohammed Omar’s (TAi.004) inner circle during the Taliban regime INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H711" s="5" t="inlineStr">
@@ -29834,12 +29253,7 @@
       <c r="F712" s="5" t="inlineStr"/>
       <c r="G712" s="5" t="inlineStr">
         <is>
-          <t>Key commander of the Haqqani Network (TAe.012), which is based in
-Afghanistan/Pakistan border area. Acts as deputy, spokesperson and advisor for Haqqani
-Network senior leader Sirajuddin Jallaloudine Haqqani (TAi.144). Liaises with the
-Taliban Supreme Council. Has travelled abroad. Liaises with and provides Taliban
-commanders in Ghazni Province, Afghanistan, with money, weapons, communications
-equipment and supplies. Reportedly deceased as of 2013. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Key commander of the Haqqani Network (TAe.012), which is based in Afghanistan/Pakistan border area. Acts as deputy, spokesperson and advisor for Haqqani Network senior leader Sirajuddin Jallaloudine Haqqani (TAi.144). Liaises with the Taliban Supreme Council. Has travelled abroad. Liaises with and provides Taliban commanders in Ghazni Province, Afghanistan, with money, weapons, communications equipment and supplies. Reportedly deceased as of 2013 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H712" s="5" t="inlineStr">
@@ -29881,7 +29295,7 @@
       </c>
       <c r="G713" s="5" t="inlineStr">
         <is>
-          <t>Senior Taliban member responsible for the manufacturing of improvised explosive devices (IED). Involved in recruiting and deploying suicide bombers to conduct attacks in Afghanistan. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior Taliban member responsible for the manufacturing of improvised explosive devices (IED). Involved in recruiting and deploying suicide bombers to conduct attacks in Afghanistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H713" s="5" t="inlineStr">
@@ -29923,7 +29337,7 @@
       </c>
       <c r="G714" s="5" t="inlineStr">
         <is>
-          <t>Communications assistant to Badruddin Haqqani (deceased). Also coordinates movement of Haqqani insurgents, foreign fighters and weapons in the Afghanistan/Pakistan border area. Belongs to Zadran tribe. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Communications assistant to Badruddin Haqqani (deceased). Also coordinates movement of Haqqani insurgents, foreign fighters and weapons in the Afghanistan/Pakistan border area. Belongs to Zadran tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H714" s="5" t="inlineStr">
@@ -29961,9 +29375,7 @@
       <c r="F715" s="5" t="inlineStr"/>
       <c r="G715" s="5" t="inlineStr">
         <is>
-          <t>Co-owner of Haji Khairullah Haji Sattar Money Exchange (TAe.010) and
-associated also with Khairullah Barakzai (TAi.163). Belongs to Barakzai tribe. Father’s
-name is Hajji ‘Abd-al-Manaf. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Co-owner of Haji Khairullah Haji Sattar Money Exchange (TAe.010) and associated also with Khairullah Barakzai (TAi.163). Belongs to Barakzai tribe. Father’s name is Hajji ‘Abd-al-Manaf INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H715" s="5" t="inlineStr">
@@ -30001,10 +29413,7 @@
       <c r="F716" s="5" t="inlineStr"/>
       <c r="G716" s="5" t="inlineStr">
         <is>
-          <t>Co-owner of Haji Khairullah Haji Sattar Money Exchange (TAe.010) and
-associated also with Abdul Satar Abdul Manan (TAi.162). Belongs to Barakzai tribe.
-Father’s name is Haji Khudai Nazar. Alternative father’s name is Nazar
-Mohammad. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Co-owner of Haji Khairullah Haji Sattar Money Exchange (TAe.010) and associated also with Abdul Satar Abdul Manan (TAi.162). Belongs to Barakzai tribe. Father’s name is Haji Khudai Nazar. Alternative father’s name is Nazar Mohammad INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H716" s="5" t="inlineStr">
@@ -30046,7 +29455,7 @@
       </c>
       <c r="G717" s="5" t="inlineStr">
         <is>
-          <t>Chief of suicide operations for the Haqqani Network (TAe.012) under Sirajuddin Jallaloudine Haqqani (TAi.144) and in charge of all operations in Kabul, Takhar, Kunduz and Baghlan provinces. Oversees training of suicide attackers and provides instructions on how to construct improvised explosives devices (IEDs). Reportedly deceased as of 22 September 2018. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Chief of suicide operations for the Haqqani Network (TAe.012) under Sirajuddin Jallaloudine Haqqani (TAi.144) and in charge of all operations in Kabul, Takhar, Kunduz and Baghlan provinces. Oversees training of suicide attackers and provides instructions on how to construct improvised explosives devices (IEDs). Reportedly deceased as of 22 September 2018 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H717" s="5" t="inlineStr">
@@ -30088,7 +29497,7 @@
       </c>
       <c r="G718" s="5" t="inlineStr">
         <is>
-          <t>Owner of Rahat Ltd. (TAe.013). Involved in the supply of weapons for Taliban, including improvised explosive devices (IED). Arrested in 2012 and in custody in Afghanistan as of January 2013. Associated with Rahat Ltd. (TAe.013). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Owner of Rahat Ltd. (TAe.013). Involved in the supply of weapons for Taliban, including improvised explosive devices (IED). Arrested in 2012 and in custody in Afghanistan as of January 2013. Associated with Rahat Ltd. (TAe.013) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H718" s="5" t="inlineStr">
@@ -30126,9 +29535,7 @@
       <c r="F719" s="5" t="inlineStr"/>
       <c r="G719" s="5" t="inlineStr">
         <is>
-          <t>Owns and operates the Roshan Money Exchange (TAe.011). Provided financial
-services to Ghul Agha Ishakzai (TAi.147) and other Taliban in Helmand Province.
-Alternative title is Maulavi. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Owns and operates the Roshan Money Exchange (TAe.011). Provided financial services to Ghul Agha Ishakzai (TAi.147) and other Taliban in Helmand Province. Alternative title is Maulavi INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H719" s="5" t="inlineStr">
@@ -30170,12 +29577,7 @@
       </c>
       <c r="G720" s="5" t="inlineStr">
         <is>
-          <t>Improvised explosive device manufacturer and facilitator for the Taliban.
-Taliban member responsible for Badghis Province, Afghanistan, as at mid – 2010. Former
-Taliban member responsible for Sar-e Pul and Samangan Provinces, Afghanistan. As Taliban
-military commander in Kandahar Province, Afghanistan, he was involved in organizing
-suicide attacks in neighboring provinces. Associated with Abdul Samad Achekzai
-(TAi.160). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Improvised explosive device manufacturer and facilitator for the Taliban. Taliban member responsible for Badghis Province, Afghanistan, as at mid – 2010. Former Taliban member responsible for Sar-e Pul and Samangan Provinces, Afghanistan. As Taliban military commander in Kandahar Province, Afghanistan, he was involved in organizing suicide attacks in neighboring provinces. Associated with Abdul Samad Achekzai (TAi.160) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H720" s="5" t="inlineStr">
@@ -30217,16 +29619,7 @@
       </c>
       <c r="G721" s="5" t="inlineStr">
         <is>
-          <t>Believed to be in Afghanistan/Pakistan border area. Taliban Shadow Deputy
-Governor and operational commander in Zabul Province, Afghanistan, responsible for the
-laying of improvised explosive devices and the organisation of suicide attacks. Physical
-description: height: 180 cm; weight: approximately 90 kg; build: athletic build; eye
-colour: brown; hair colour: red; complexion: medium brown. Distinguishing physical
-marks: large round face, full beard, and walks with a limp due to plastic prosthesis in
-place of his left lower leg. Ethnic background: Pashtun; Belongs to Tokhi tribe,
-Barkozai sub-tribe (alternative tribe spelling: Torchi). Barkozai (alternative tribe
-spelling: Bakorzai, باکورزی) sub-tribe, Kishta Barkorzai (lower Barkorzai) clan. Marital
-Status: married. Father’s name: Agha Mohammad. Brother’s name: Humdullah. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Believed to be in Afghanistan/Pakistan border area. Taliban Shadow Deputy Governor and operational commander in Zabul Province, Afghanistan, responsible for the laying of improvised explosive devices and the organisation of suicide attacks. Physical description: height: 180 cm; weight: approximately 90 kg; build: athletic build; eye colour: brown; hair colour: red; complexion: medium brown. Distinguishing physical marks: large round face, full beard, and walks with a limp due to plastic prosthesis in place of his left lower leg. Ethnic background: Pashtun; Belongs to Tokhi tribe, Barkozai sub-tribe (alternative tribe spelling: Torchi). Barkozai (alternative tribe spelling: Bakorzai, باکورزی) sub-tribe, Kishta Barkorzai (lower Barkorzai) clan. Marital Status: married. Father’s name: Agha Mohammad. Brother’s name: Humdullah INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H721" s="5" t="inlineStr">
@@ -30268,9 +29661,7 @@
       </c>
       <c r="G722" s="5" t="inlineStr">
         <is>
-          <t>Senior Haqqani Network (HQN) (TAe.012) member. Closely involved in the
-group’s military, financial, and propaganda activities. Injured leg. Father’s name is
-Hajji Meyawar Khan (deceased). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior Haqqani Network (HQN) (TAe.012) member. Closely involved in the group’s military, financial, and propaganda activities. Injured leg. Father’s name is Hajji Meyawar Khan (deceased) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H722" s="5" t="inlineStr">
@@ -30308,7 +29699,7 @@
       <c r="F723" s="5" t="inlineStr"/>
       <c r="G723" s="5" t="inlineStr">
         <is>
-          <t>Senior member of the Haqqani Network (HQN) (TE.H.12.12.) as of 2013. Provided critical facilitation support to drivers and vehicles transporting HQN ammunition. Also involved in the group’s recruiting efforts as of 2011.  Father’s name is Bakhta Jan.   INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of the Haqqani Network (HQN) (TE.H.12.12.) as of 2013. Provided critical facilitation support to drivers and vehicles transporting HQN ammunition. Also involved in the group’s recruiting efforts as of 2011. Father’s name is Bakhta Jan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H723" s="5" t="inlineStr">
@@ -30346,7 +29737,7 @@
       <c r="F724" s="5" t="inlineStr"/>
       <c r="G724" s="5" t="inlineStr">
         <is>
-          <t>Haqqani Network (HQN) (TAe.012) leader in command of over 100 militants active in Khost Province, Afghanistan as of 2013. Involved in the preparation of attacks against Afghan and international forces in Afghanistan. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Haqqani Network (HQN) (TAe.012) leader in command of over 100 militants active in Khost Province, Afghanistan as of 2013. Involved in the preparation of attacks against Afghan and international forces in Afghanistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H724" s="5" t="inlineStr">
@@ -30388,7 +29779,7 @@
       </c>
       <c r="G725" s="5" t="inlineStr">
         <is>
-          <t>Physical description: eye colour brown, hair colour: black, weight: 77-81 kg, height: 178 cm short-to-medium black beard, short black hair. Belongs to Shinwari tribe, Sepahi sub-tribe.  A Taliban commander since at least Feb. 2010. Collects taxes and bribes on behalf of the Taliban as of April 2015. Liaises with and provides Taliban operatives in Nangarhar Province, Afghanistan, with information, guidance, housing and weapons and has emplaced improvised explosive devices (IED) and conducted attacks against International Security Assistance Force (ISAF) and Afghan forces. Involved in drug trafficking and operates heroin laboratory in Abdulkhel village, Achin district, Nangarhar province, Afghanistan. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Physical description: eye colour brown, hair colour: black, weight: 77-81 kg, height: 178 cm short-to-medium black beard, short black hair. Belongs to Shinwari tribe, Sepahi sub-tribe. A Taliban commander since at least Feb. 2010. Collects taxes and bribes on behalf of the Taliban as of April 2015. Liaises with and provides Taliban operatives in Nangarhar Province, Afghanistan, with information, guidance, housing and weapons and has emplaced improvised explosive devices (IED) and conducted attacks against International Security Assistance Force (ISAF) and Afghan forces. Involved in drug trafficking and operates heroin laboratory in Abdulkhel village, Achin district, Nangarhar province, Afghanistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H725" s="5" t="inlineStr">
@@ -30430,8 +29821,7 @@
       </c>
       <c r="G726" s="5" t="inlineStr">
         <is>
-          <t>Owner of Haji Basir and Zarjmil Company Hawala (TAe.014), which provides
-financial services to Taliban in the region. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Owner of Haji Basir and Zarjmil Company Hawala (TAe.014), which provides financial services to Taliban in the region INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H726" s="5" t="inlineStr">
@@ -30469,7 +29859,7 @@
       <c r="F727" s="5" t="inlineStr"/>
       <c r="G727" s="5" t="inlineStr">
         <is>
-          <t>Key commander for Taliban military council involved in fundraising from Gulf-based donors. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Reportedly deceased as of November 2018. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Key commander for Taliban military council involved in fundraising from Gulf-based donors. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. Reportedly deceased as of November 2018 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H727" s="5" t="inlineStr">
@@ -30511,7 +29901,7 @@
       </c>
       <c r="G728" s="5" t="inlineStr">
         <is>
-          <t>Gender [Male]. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender [Male]. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H728" s="5" t="inlineStr">
@@ -30553,7 +29943,7 @@
       </c>
       <c r="G729" s="5" t="inlineStr">
         <is>
-          <t>Gender [Male]. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Gender [Male]. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H729" s="5" t="inlineStr">
@@ -30634,7 +30024,7 @@
       </c>
       <c r="G731" s="5" t="inlineStr">
         <is>
-          <t>Sultan Saleh Aida Aida Zabin has engaged in acts that threaten the peace, security and stability of Yemen, including violations of applicable international humanitarian law and human rights abuses in Yemen. Zabin has played a prominent role in a policy of intimidation and use of systematic arrest, detention, torture, sexual violence and rape against politically active women. Zabin as director for CID is directly responsible for, or by virtue of his authority responsible for, and complicit in the use of multiple places of detention including house arrest, police stations, formal prisons and detention centres and undisclosed detention centres. In these sites, women, including at least one minor, were forcibly disappeared, repeatedly interrogated, raped, tortured, denied timely medical treatment and subjected to forced labour. Zabin himself directly inflicted torture in some cases. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Sultan Saleh Aida Aida Zabin has engaged in acts that threaten the peace, security and stability of Yemen, including violations of applicable international humanitarian law and human rights abuses in Yemen. Zabin has played a prominent role in a policy of intimidation and use of systematic arrest, detention, torture, sexual violence and rape against politically active women. Zabin as director for CID is directly responsible for, or by virtue of his authority responsible for, and complicit in the use of multiple places of detention including house arrest, police stations, formal prisons and detention centres and undisclosed detention centres. In these sites, women, including at least one minor, were forcibly disappeared, repeatedly interrogated, raped, tortured, denied timely medical treatment and subjected to forced labour. Zabin himself directly inflicted torture in some cases. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H731" s="5" t="inlineStr">
@@ -30676,7 +30066,7 @@
       </c>
       <c r="G732" s="5" t="inlineStr">
         <is>
-          <t>As Houthi ‘Assistant Minister of Defence for Logistics’, assisted the Houthis in acquiring smuggled arms and weapons. As ‘Judicial Custodian’ directly involved in the widespread and unlawful appropriation of assets and entities owned by private individuals under arrest by the Houthis or forced to take refuge outside of Yemen. Physical Description: Eye Colour: Brown; Hair: Grey; Complexion: Medium; Build: Slim; Height (ft/in): Unknown; Weight (lbs): Unknown; and Clan: Member of the Hashid tribal confederacy. Photograph available for inclusion in INTERPOL-UNSC Special Notice web link: INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>As Houthi ‘Assistant Minister of Defence for Logistics’, assisted the Houthis in acquiring smuggled arms and weapons. As ‘Judicial Custodian’ directly involved in the widespread and unlawful appropriation of assets and entities owned by private individuals under arrest by the Houthis or forced to take refuge outside of Yemen. Physical Description: Eye Colour: Brown; Hair: Grey; Complexion: Medium; Build: Slim; Height (ft/in): Unknown; Weight (lbs): Unknown; and Clan: Member of the Hashid tribal confederacy. Photograph available for inclusion in INTERPOL-UNSC Special Notice web link: INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H732" s="5" t="inlineStr">
@@ -30718,7 +30108,7 @@
       </c>
       <c r="G733" s="5" t="inlineStr">
         <is>
-          <t>Houthi Military Chief of General Staff, plays the leading role in orchestrating the Houthis’ military efforts that are directly threatening the peace, security and stability of Yemen, including in Marib, as well as cross-border attacks against Saudi Arabia. Photograph available for inclusion in INTERPOL-UN Security Council Special Notice web link:  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Houthi Military Chief of General Staff, plays the leading role in orchestrating the Houthis’ military efforts that are directly threatening the peace, security and stability of Yemen, including in Marib, as well as cross-border attacks against Saudi Arabia. Photograph available for inclusion in INTERPOL-UN Security Council Special Notice web link:  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H733" s="5" t="inlineStr">
@@ -30756,7 +30146,7 @@
       </c>
       <c r="G734" s="5" t="inlineStr">
         <is>
-          <t>A prominent leader of Houthi forces and commander of forces in Hudaydah, Hajjah, Al Mahwit, and Raymah, Yemen – threatening the peace, security, and stability of Yemen. As of 2021, Al-Madani was assigned to the offensive targeting Marib. Photograph available for inclusion in INTERPOL-UN Security Council Special Notice web link:  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A prominent leader of Houthi forces and commander of forces in Hudaydah, Hajjah, Al Mahwit, and Raymah, Yemen – threatening the peace, security, and stability of Yemen. As of 2021, Al-Madani was assigned to the offensive targeting Marib. Photograph available for inclusion in INTERPOL-UN Security Council Special Notice web link:  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H734" s="5" t="inlineStr">
@@ -30798,7 +30188,7 @@
       </c>
       <c r="G735" s="5" t="inlineStr">
         <is>
-          <t>Houthi Naval Forces Chief of Staff, who has masterminded lethal attacks against international shipping in the Red Sea, plays a leading role in Houthi naval efforts that directly threaten the peace, security, and stability of Yemen. Physical Description: Eye Color: Brown; Hair: Brown. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Houthi Naval Forces Chief of Staff, who has masterminded lethal attacks against international shipping in the Red Sea, plays a leading role in Houthi naval efforts that directly threaten the peace, security, and stability of Yemen. Physical Description: Eye Color: Brown; Hair: Brown. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H735" s="5" t="inlineStr">
@@ -30840,7 +30230,7 @@
       </c>
       <c r="G736" s="5" t="inlineStr">
         <is>
-          <t>Former Deputy Head of the Houthi National Security Bureau (NSB), oversaw detainees of the NSB who were subjected to torture and other mistreatment while detained, planned and directed illegal arrests and detention of humanitarian workers and the unlawful diversion of humanitarian assistance in violation of international humanitarian law. Physical Description: Eye Color: Brown; Hair: Brown. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Former Deputy Head of the Houthi National Security Bureau (NSB), oversaw detainees of the NSB who were subjected to torture and other mistreatment while detained, planned and directed illegal arrests and detention of humanitarian workers and the unlawful diversion of humanitarian assistance in violation of international humanitarian law. Physical Description: Eye Color: Brown; Hair: Brown. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H736" s="5" t="inlineStr">
@@ -30882,7 +30272,7 @@
       </c>
       <c r="G737" s="5" t="inlineStr">
         <is>
-          <t>Ahmad al-Hamzi, the commander of the Houthi Air Force and Air Defense Forces, as well as its UAV program, plays a leading role in Houthi military efforts that directly threaten the peace, security, and stability of Yemen. Physical Description: Eye Color: Brown; Hair: Brown. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Ahmad al-Hamzi, the commander of the Houthi Air Force and Air Defense Forces, as well as its UAV program, plays a leading role in Houthi military efforts that directly threaten the peace, security, and stability of Yemen. Physical Description: Eye Color: Brown; Hair: Brown. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H737" s="5" t="inlineStr">
@@ -30920,7 +30310,7 @@
       <c r="F738" s="5" t="inlineStr"/>
       <c r="G738" s="5" t="inlineStr">
         <is>
-          <t>ADF founder and leader, Jamil Mukulu (CDi.015), was arrested in Dar es Salaam, Tanzania in April 2015. He was subsequently extradited to Kampala, Uganda in July 2015. As of June 2016, Mukulu is reportedly being held in a police detention cell awaiting his trial. Seka Baluku (CDi.036) succeeded Jamil Mukulu (CDi.015) as the overall leader of the ADF. As highlighted in several reports from the Group of Experts on the DRC (S/2015/19, S/2015/797, S/2016/1102, S/2017/672, S/2018/531, S/2019/469, S/2019/974, S/2020/482), the ADF, including under Seka Baluku’s leadership, continued to commit the repeated targeting, killing and maiming, rape and other sexual violence, abduction of civilians, including children, as well as attacks on villages and health facilities, in particular in Mamove, Beni territory, on 12 and 24 February 2019, and Mantumbi, Beni territory, on 5 December 2019 and 30 January 2020, as well as the continuous recruitment and use of children during attacks and for forced labour in Beni territory in the DRC since at least 2015. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>ADF founder and leader, Jamil Mukulu (CDi.015), was arrested in Dar es Salaam, Tanzania in April 2015. He was subsequently extradited to Kampala, Uganda in July 2015. As of June 2016, Mukulu is reportedly being held in a police detention cell awaiting his trial. Seka Baluku (CDi.036) succeeded Jamil Mukulu (CDi.015) as the overall leader of the ADF. As highlighted in several reports from the Group of Experts on the DRC (S/2015/19, S/2015/797, S/2016/1102, S/2017/672, S/2018/531, S/2019/469, S/2019/974, S/2020/482), the ADF, including under Seka Baluku’s leadership, continued to commit the repeated targeting, killing and maiming, rape and other sexual violence, abduction of civilians, including children, as well as attacks on villages and health facilities, in particular in Mamove, Beni territory, on 12 and 24 February 2019, and Mantumbi, Beni territory, on 5 December 2019 and 30 January 2020, as well as the continuous recruitment and use of children during attacks and for forced labour in Beni territory in the DRC since at least 2015. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H738" s="5" t="inlineStr">
@@ -30954,7 +30344,7 @@
       <c r="F739" s="5" t="inlineStr"/>
       <c r="G739" s="5" t="inlineStr">
         <is>
-          <t>Privately-owned airline, operates out of Butembo. Since December 2008, BAL no longer holds an aircraft operating license in the DRC. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Privately-owned airline, operates out of Butembo. Since December 2008, BAL no longer holds an aircraft operating license in the DRC. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H739" s="5" t="inlineStr">
@@ -30993,7 +30383,7 @@
       <c r="G740" s="5" t="inlineStr">
         <is>
           <t>As of December 2008, GLBC no longer had any operational aircraft,
-although several aircraft continued flying in 2008 despite UN sanctions. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+although several aircraft continued flying in 2008 despite UN sanctions. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H740" s="5" t="inlineStr">
@@ -31028,7 +30418,7 @@
       <c r="G741" s="5" t="inlineStr">
         <is>
           <t>No longer exists as a gold trading house in Butembo, North
-Kivu. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+Kivu. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H741" s="5" t="inlineStr">
@@ -31067,7 +30457,7 @@
       <c r="G742" s="5" t="inlineStr">
         <is>
           <t>Email: Fdlr@fmx.de; fldrrse@yahoo.fr; fdlr@gmx.net; fdlrsrt@gmail.com;
-humura2020@gmail.com. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+humura2020@gmail.com. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H742" s="5" t="inlineStr">
@@ -31105,7 +30495,7 @@
       <c r="F743" s="5" t="inlineStr"/>
       <c r="G743" s="5" t="inlineStr">
         <is>
-          <t>e-mail: mouvementdu23mars1@gmail.com INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>e-mail: mouvementdu23mars1@gmail.com INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H743" s="5" t="inlineStr">
@@ -31142,7 +30532,7 @@
           <t>Gold export company (Directors: Mr. Rajendra Kumar Vaya and Mr. Hirendra
 M. Vaya). In 2010, assets belonging to Machanga, held in the account of Emirates Gold,
 were frozen by Bank of Nova Scotia Mocatta (UK). The owners of Machanga have remained
-involved in purchasing gold from eastern DRC. Machanga Ltd last filed an annual return in 2004 and was listed as “status inactive” according to the authorities of the Republic of Uganda. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+involved in purchasing gold from eastern DRC. Machanga Ltd last filed an annual return in 2004 and was listed as “status inactive” according to the authorities of the Republic of Uganda. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H744" s="5" t="inlineStr">
@@ -31185,7 +30575,7 @@
 June 2011 TPD offices are open and involved in cases related to returns of IDPs,
 community reconciliation initiatives, land conflict settlements, etc. The TPD President
 is Eugene Serufuli and Vice-President is Saverina Karomba. Important members include
-North Kivu provincial deputies Robert Seninga and Bertin Kirivita. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+North Kivu provincial deputies Robert Seninga and Bertin Kirivita. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H745" s="5" t="inlineStr">
@@ -31224,7 +30614,7 @@
 authorities notified the Committee that following an exemption on its financial
 holdings, Emirates Gold repaid UCI’s debt to Crane Bank in Kampala, leading to final
 closure of its accounts. The directors of UCI have remained involved in purchasing gold
-from eastern DRC. Uganda Commercial Impex (UCI) Ltd last filed a return in 2013 and was listed as “Inactive – status inactive” by the authorities of the Republic of Uganda.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+from eastern DRC. Uganda Commercial Impex (UCI) Ltd last filed a return in 2013 and was listed as “Inactive – status inactive” by the authorities of the Republic of Uganda.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H746" s="5" t="inlineStr">
@@ -31258,7 +30648,7 @@
       <c r="F747" s="5" t="inlineStr"/>
       <c r="G747" s="5" t="inlineStr">
         <is>
-          <t>Established in 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Established in 2023.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H747" s="5" t="inlineStr">
@@ -31292,7 +30682,7 @@
       <c r="F748" s="5" t="inlineStr"/>
       <c r="G748" s="5" t="inlineStr">
         <is>
-          <t>Congolese armed group. Formed 2008 to early 2010. TWIRWANEHO has been involved in atrocities in the South-Kivu province of the DRC, including the killing of civilians, recruiting children, and activities that threaten the peace and security of the people of the DRC.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Congolese armed group. Formed 2008 to early 2010. TWIRWANEHO has been involved in atrocities in the South-Kivu province of the DRC, including the killing of civilians, recruiting children, and activities that threaten the peace and security of the people of the DRC.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H748" s="5" t="inlineStr">
@@ -31330,7 +30720,7 @@
       <c r="F749" s="5" t="inlineStr"/>
       <c r="G749" s="5" t="inlineStr">
         <is>
-          <t>Emerged in northern Uganda in the 1980s. Has engaged in the abduction, killing and mutilation of thousands of civilians in Central Africa, including hundreds in the Central African Republic. The leader is Joseph Kony (CFi.009). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Emerged in northern Uganda in the 1980s. Has engaged in the abduction, killing and mutilation of thousands of civilians in Central Africa, including hundreds in the Central African Republic. The leader is Joseph Kony (CFi.009). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H749" s="5" t="inlineStr">
@@ -31368,7 +30758,7 @@
       <c r="F750" s="5" t="inlineStr"/>
       <c r="G750" s="5" t="inlineStr">
         <is>
-          <t>Luckson Elan (HTi.007) is the leader of the Gran Grif gang.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Luckson Elan (HTi.007) is the leader of the Gran Grif gang.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H750" s="5" t="inlineStr">
@@ -31406,7 +30796,7 @@
       <c r="F751" s="5" t="inlineStr"/>
       <c r="G751" s="5" t="inlineStr">
         <is>
-          <t>Jimmy Chérizier (HTi.001) is the leader of the Viv Ansanm gang coalition. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Jimmy Chérizier (HTi.001) is the leader of the Viv Ansanm gang coalition. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H751" s="5" t="inlineStr">
@@ -37340,7 +36730,7 @@
       <c r="G915" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 17 of resolution 1973, as modified on 16
-September pursuant to paragraph 15 of resolution 2009. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+September pursuant to paragraph 15 of resolution 2009. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H915" s="5" t="inlineStr">
@@ -37375,7 +36765,7 @@
       <c r="G916" s="5" t="inlineStr">
         <is>
           <t>Listed pursuant to paragraph 17 of resolution 1973, as modified on 16
-September pursuant to paragraph 15 of resolution 2009. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+September pursuant to paragraph 15 of resolution 2009. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H916" s="5" t="inlineStr">
@@ -37448,9 +36838,7 @@
       <c r="F918" s="5" t="inlineStr"/>
       <c r="G918" s="5" t="inlineStr">
         <is>
-          <t>Associated with Jemaah Islamiyah (JI) (QDe.092). Current leader is
-Radulan Sahiron (QDi.208). Review pursuant to Security Council resolution 1822 (2008)
-was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with Jemaah Islamiyah (JI) (QDe.092). Current leader is Radulan Sahiron (QDi.208) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H918" s="5" t="inlineStr">
@@ -37484,15 +36872,7 @@
       <c r="F919" s="5" t="inlineStr"/>
       <c r="G919" s="5" t="inlineStr">
         <is>
-          <t>Reported to have operated in Somalia and Ethiopia and to have merged with
-Harakat Al-Shabaab Al-Mujaahidiin (Al-Shabaab), which was accepted as an affiliate of
-Al-Qaida (QDe.004) by Aiman Muhammed Rabi al-Zawahiri (QDi.006) in Feb. 2012, and is
-also subject to the sanctions measures set out in Security Council resolution 1844
-(2008) concerning Somalia and Eritrea (see https://www.un.org/sc/suborg/en/sanctions/751).
-Leadership included Hassan Dahir Aweys
-(QDi.042). AIAI has received funds through the Al-Haramain Islamic Foundation (Somalia)
-(QDe.072). Review pursuant to Security Council resolution 1822 (2008) was concluded on
-21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reported to have operated in Somalia and Ethiopia and to have merged with Harakat Al-Shabaab Al-Mujaahidiin (Al-Shabaab), which was accepted as an affiliate of Al-Qaida (QDe.004) by Aiman Muhammed Rabi al-Zawahiri (QDi.006) in Feb. 2012, and is also subject to the sanctions measures set out in Security Council resolution 1844 (2008) concerning Somalia and Eritrea (see https://www.un.org/sc/suborg/en/sanctions/751). Leadership included Hassan Dahir Aweys (QDi.042). AIAI has received funds through the Al-Haramain Islamic Foundation (Somalia) (QDe.072) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H919" s="5" t="inlineStr">
@@ -37530,9 +36910,7 @@
       <c r="F920" s="5" t="inlineStr"/>
       <c r="G920" s="5" t="inlineStr">
         <is>
-          <t>Co-founded by Aiman Muhammed Rabi al-Zawahiri (QDi.006), who was also its
-military leader. Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Co-founded by Aiman Muhammed Rabi al-Zawahiri (QDi.006), who was also its military leader INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H920" s="5" t="inlineStr">
@@ -37570,8 +36948,7 @@
       <c r="F921" s="5" t="inlineStr"/>
       <c r="G921" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H921" s="5" t="inlineStr">
@@ -37609,7 +36986,7 @@
       <c r="F922" s="5" t="inlineStr"/>
       <c r="G922" s="5" t="inlineStr">
         <is>
-          <t>Reportedly defunct. Headquarters were in Pakistan. Operations in Afghanistan: Herat Jalalabad, Kabul, Kandahar, Mazar Sherif. Also operations in Kosovo, Chechnya. Involved in the financing of Al-Qaida and the Taliban. Until 21 Oct. 2008, this entity appeared also as "Aid Organization of the Ulema, Pakistan" (QDe.073), listed on 24 Apr. 2002 and amended on 25 Jul. 2006. The two entries Al Rashid Trust (QDe.005) and Aid Organization of the Ulema, Pakistan (QDe.073) were consolidated into this entity on 21 Oct. 2008. Founded by Mufti Rashid Ahmad Ledahyanoy (deceased). Associated with Jaish-i-Mohammed (QDe.019). Banned in Pakistan since Oct. 2001. No indication of any activity under the name of Al-Rashid Trust has emerged as of November 2023. Review pursuant to Security Council resolution 1822 (2008) was concluded on 6 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reportedly defunct. Headquarters were in Pakistan. Operations in Afghanistan: Herat Jalalabad, Kabul, Kandahar, Mazar Sherif. Also operations in Kosovo, Chechnya. Involved in the financing of Al-Qaida and the Taliban. Until 21 Oct. 2008, this entity appeared also as "Aid Organization of the Ulema, Pakistan" (QDe.073), listed on 24 Apr. 2002 and amended on 25 Jul. 2006. The two entries Al Rashid Trust (QDe.005) and Aid Organization of the Ulema, Pakistan (QDe.073) were consolidated into this entity on 21 Oct. 2008. Founded by Mufti Rashid Ahmad Ledahyanoy (deceased). Associated with Jaish-i-Mohammed (QDe.019). Banned in Pakistan since Oct. 2001. No indication of any activity under the name of Al-Rashid Trust has emerged as of November 2023 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H922" s="5" t="inlineStr">
@@ -37647,8 +37024,7 @@
       <c r="F923" s="5" t="inlineStr"/>
       <c r="G923" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H923" s="5" t="inlineStr">
@@ -37682,9 +37058,7 @@
       <c r="F924" s="5" t="inlineStr"/>
       <c r="G924" s="5" t="inlineStr">
         <is>
-          <t>Active in northern Iraq. Associated with Al-Qaida in Iraq (QDe.115).
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun.
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Active in northern Iraq. Associated with Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H924" s="5" t="inlineStr">
@@ -37722,10 +37096,7 @@
       <c r="F925" s="5" t="inlineStr"/>
       <c r="G925" s="5" t="inlineStr">
         <is>
-          <t>Associated with Jaish-i-Mohammed (QDe.019), Lashkar i Jhangvi (LJ)
-(QDe.096) and Lashkar-e-Tayyiba (QDe.118). Active in Pakistan and Afghanistan. Banned in
-Pakistan. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21
-Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with Jaish-i-Mohammed (QDe.019), Lashkar i Jhangvi (LJ) (QDe.096) and Lashkar-e-Tayyiba (QDe.118). Active in Pakistan and Afghanistan. Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H925" s="5" t="inlineStr">
@@ -37759,8 +37130,7 @@
       <c r="F926" s="5" t="inlineStr"/>
       <c r="G926" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded on 9
-Jul. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H926" s="5" t="inlineStr">
@@ -37798,10 +37168,7 @@
       <c r="F927" s="5" t="inlineStr"/>
       <c r="G927" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Eastern Turkistan Islamic Movement (QDe.088), Islamic
-Jihad Group (QDe.119) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan
-border area, northern Afghanistan and Central Asia. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Eastern Turkistan Islamic Movement (QDe.088), Islamic Jihad Group (QDe.119) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan border area, northern Afghanistan and Central Asia INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H927" s="5" t="inlineStr">
@@ -37839,9 +37206,7 @@
       <c r="F928" s="5" t="inlineStr"/>
       <c r="G928" s="5" t="inlineStr">
         <is>
-          <t>Members in Afghanistan merged with Al-Qaida (QDe.004) in Nov. 2007.
-Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun.
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Members in Afghanistan merged with Al-Qaida (QDe.004) in Nov. 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H928" s="5" t="inlineStr">
@@ -37879,8 +37244,7 @@
       <c r="F929" s="5" t="inlineStr"/>
       <c r="G929" s="5" t="inlineStr">
         <is>
-          <t>Absorbed into Al-Qaida (QDe.004). Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Absorbed into Al-Qaida (QDe.004) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H929" s="5" t="inlineStr">
@@ -37918,9 +37282,7 @@
       <c r="F930" s="5" t="inlineStr"/>
       <c r="G930" s="5" t="inlineStr">
         <is>
-          <t>Headed by Abdelmalek Droukdel (QDi.232). Zone of operation includes
-Algeria and parts of Mali, Mauritania, Niger, Tunisia and Morocco. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Headed by Abdelmalek Droukdel (QDi.232). Zone of operation includes Algeria and parts of Mali, Mauritania, Niger, Tunisia and Morocco INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H930" s="5" t="inlineStr">
@@ -37958,9 +37320,7 @@
       <c r="F931" s="5" t="inlineStr"/>
       <c r="G931" s="5" t="inlineStr">
         <is>
-          <t>Headquarters was in Kandahar, Afghanistan as at 2001. Wafa was a
-component of Al-Qaida (QDe.004) in 2001. Review pursuant to Security Council resolution
-1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Headquarters was in Kandahar, Afghanistan as at 2001. Wafa was a component of Al-Qaida (QDe.004) in 2001 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H931" s="5" t="inlineStr">
@@ -37998,10 +37358,7 @@
       <c r="F932" s="5" t="inlineStr"/>
       <c r="G932" s="5" t="inlineStr">
         <is>
-          <t>Based in Peshawar and Muzaffarabad, Pakistan Associated with Harakat
-ul-Mujahidin / HUM (QDe.008), Lashkar-e-Tayyiba (QDe.118), Al-Akhtar Trust International
-(QDe.121), and Harakat-ul Jihad Islami (QDe.130). Banned in Pakistan. Review pursuant to
-Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Based in Peshawar and Muzaffarabad, Pakistan Associated with Harakat ul-Mujahidin / HUM (QDe.008), Lashkar-e-Tayyiba (QDe.118), Al-Akhtar Trust International (QDe.121), and Harakat-ul Jihad Islami (QDe.130). Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H932" s="5" t="inlineStr">
@@ -38039,9 +37396,7 @@
       <c r="F933" s="5" t="inlineStr"/>
       <c r="G933" s="5" t="inlineStr">
         <is>
-          <t>Founded by Usama Mohammad Awad bin Laden (deceased) in 2001. Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun.
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Founded by Usama Mohammad Awad bin Laden (deceased) in 2001 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H933" s="5" t="inlineStr">
@@ -38075,8 +37430,7 @@
       <c r="F934" s="5" t="inlineStr"/>
       <c r="G934" s="5" t="inlineStr">
         <is>
-          <t>Banned in Pakistan. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H934" s="5" t="inlineStr">
@@ -38110,7 +37464,7 @@
       <c r="F935" s="5" t="inlineStr"/>
       <c r="G935" s="5" t="inlineStr">
         <is>
-          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055), Majeed Abdul Chaudhry (QDi.054) and Mohammed Tufail (QDi.056). Banned in Pakistan. Review pursuant to Security Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055), Majeed Abdul Chaudhry (QDi.054) and Mohammed Tufail (QDi.056). Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H935" s="5" t="inlineStr">
@@ -38148,7 +37502,7 @@
       <c r="F936" s="5" t="inlineStr"/>
       <c r="G936" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Revival of Islamic Heritage Society (QDe.070). Abu Bakr al-Jaziri (QDi.058) served as finance chief of ASC. Review pursuant to Security Council resolution 1822 (2008) was concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Revival of Islamic Heritage Society (QDe.070). Abu Bakr al-Jaziri (QDi.058) served as finance chief of ASC INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H936" s="5" t="inlineStr">
@@ -38186,10 +37540,7 @@
       <c r="F937" s="5" t="inlineStr"/>
       <c r="G937" s="5" t="inlineStr">
         <is>
-          <t>NOTE: Only the Pakistan and Afghanistan offices of this entity are
-designated. Associated with Abu Bakr al-Jaziri (QDi.058) and Afghan Support Committee
-(ASC) (QDe.069). Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>NOTE: Only the Pakistan and Afghanistan offices of this entity are designated. Associated with Abu Bakr al-Jaziri (QDi.058) and Afghan Support Committee (ASC) (QDe.069) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H937" s="5" t="inlineStr">
@@ -38227,8 +37578,7 @@
       <c r="F938" s="5" t="inlineStr"/>
       <c r="G938" s="5" t="inlineStr">
         <is>
-          <t>Active in China, South Asia and Central Asia. Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 20 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Active in China, South Asia and Central Asia INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H938" s="5" t="inlineStr">
@@ -38266,9 +37616,7 @@
       <c r="F939" s="5" t="inlineStr"/>
       <c r="G939" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb
-(QDe.014). Review pursuant to Security Council resolution 1822 (2008) was concluded on
-20 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H939" s="5" t="inlineStr">
@@ -38306,10 +37654,7 @@
       <c r="F940" s="5" t="inlineStr"/>
       <c r="G940" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014).
-                Review pursuant to Security Council resolution 1822 (2008) was concluded on 6 May
-                2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24
-                November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H940" s="5" t="inlineStr">
@@ -38343,10 +37688,7 @@
       <c r="F941" s="5" t="inlineStr"/>
       <c r="G941" s="5" t="inlineStr">
         <is>
-          <t>Other Foreign Locations: Afghanistan, Bangladesh, Eritrea, Ethiopia,
-India, Iraq, West Bank and Gaza, Somalia and Syria. Federal Employer Identification
-Number (United States of America): 36-3804626. Review pursuant to Security Council
-resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Other Foreign Locations: Afghanistan, Bangladesh, Eritrea, Ethiopia, India, Iraq, West Bank and Gaza, Somalia and Syria. Federal Employer Identification Number (United States of America): 36-3804626 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H941" s="5" t="inlineStr">
@@ -38384,9 +37726,7 @@
       <c r="F942" s="5" t="inlineStr"/>
       <c r="G942" s="5" t="inlineStr">
         <is>
-          <t>Operates in Southeast Asia, including Indonesia, Malaysia and the
-Philippines. Associated with the Abu Sayyaf Group (QDe.001). Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 25 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Operates in Southeast Asia, including Indonesia, Malaysia and the Philippines. Associated with the Abu Sayyaf Group (QDe.001) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H942" s="5" t="inlineStr">
@@ -38424,7 +37764,7 @@
       <c r="F943" s="5" t="inlineStr"/>
       <c r="G943" s="5" t="inlineStr">
         <is>
-          <t>Reportedly defunct. No longer operates in Bosnia and Herzegovina. Employer Identification Number (United States of America): 36-3823186.  Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reportedly defunct. No longer operates in Bosnia and Herzegovina. Employer Identification Number (United States of America): 36-3823186 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H943" s="5" t="inlineStr">
@@ -38458,7 +37798,7 @@
       <c r="F944" s="5" t="inlineStr"/>
       <c r="G944" s="5" t="inlineStr">
         <is>
-          <t>Based primarily in Pakistan’s Punjab region and in the city of Karachi. Active in Pakistan although banned as at 2010. Review pursuant to Security Council resolution 2161 (2014) was concluded on 23 Dec. 2016. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Based primarily in Pakistan’s Punjab region and in the city of Karachi. Active in Pakistan although banned as at 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H944" s="5" t="inlineStr">
@@ -38496,11 +37836,7 @@
       <c r="F945" s="5" t="inlineStr"/>
       <c r="G945" s="5" t="inlineStr">
         <is>
-          <t>The founder is Najmuddin Faraj Ahmad (QDi.226). Associated with Al-Qaida in
-                Iraq (QDe.115). Located and primarily active in northern Iraq but maintains a
-                presence in western and central Iraq. Review pursuant to Security Council resolution
-                1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council
-                resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>The founder is Najmuddin Faraj Ahmad (QDi.226). Associated with Al-Qaida in Iraq (QDe.115). Located and primarily active in northern Iraq but maintains a presence in western and central Iraq INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H945" s="5" t="inlineStr">
@@ -38538,11 +37874,7 @@
       <c r="F946" s="5" t="inlineStr"/>
       <c r="G946" s="5" t="inlineStr">
         <is>
-          <t>Linked to the Riyadus-Salikhin Reconnaissance and Sabotage Battalion of Chechen
-                Martyrs (RSRSBCM) (QDe.100) and the Special Purpose Islamic Regiment (SPIR)
-                (QDe.101). Review pursuant to Security Council resolution 1822 (2008) was concluded
-                on 17 May 2010. Review pursuant to Security Council resolution 2368 (2017) was
-                concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Linked to the Riyadus-Salikhin Reconnaissance and Sabotage Battalion of Chechen Martyrs (RSRSBCM) (QDe.100) and the Special Purpose Islamic Regiment (SPIR) (QDe.101) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H946" s="5" t="inlineStr">
@@ -38580,10 +37912,7 @@
       <c r="F947" s="5" t="inlineStr"/>
       <c r="G947" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Islamic International Brigade (IIB) (QDe.099), the
-Special Purpose Islamic Regiment (SPIR) (QDe.101) and Emarat Kavkaz (QDe.131). Review
-pursuant to Security Council resolution 1822 (2008) was concluded on 17 May
-2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Islamic International Brigade (IIB) (QDe.099), the Special Purpose Islamic Regiment (SPIR) (QDe.101) and Emarat Kavkaz (QDe.131) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H947" s="5" t="inlineStr">
@@ -38621,10 +37950,7 @@
       <c r="F948" s="5" t="inlineStr"/>
       <c r="G948" s="5" t="inlineStr">
         <is>
-          <t>Linked to the Islamic International Brigade (IIB) (QDe.099) and the
-Riyadus-Salikhin Reconnaissance and Sabotage Battalion of Chechen Martyrs (RSRSBCM)
-(QDe.100). Review pursuant to Security Council resolution 1822 (2008) was concluded on
-17 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Linked to the Islamic International Brigade (IIB) (QDe.099) and the Riyadus-Salikhin Reconnaissance and Sabotage Battalion of Chechen Martyrs (RSRSBCM) (QDe.100) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H948" s="5" t="inlineStr">
@@ -38658,8 +37984,7 @@
       <c r="F949" s="5" t="inlineStr"/>
       <c r="G949" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 19 Oct. 2009. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H949" s="5" t="inlineStr">
@@ -38693,8 +38018,7 @@
       <c r="F950" s="5" t="inlineStr"/>
       <c r="G950" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H950" s="5" t="inlineStr">
@@ -38728,8 +38052,7 @@
       <c r="F951" s="5" t="inlineStr"/>
       <c r="G951" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H951" s="5" t="inlineStr">
@@ -38767,7 +38090,7 @@
       <c r="F952" s="5" t="inlineStr"/>
       <c r="G952" s="5" t="inlineStr">
         <is>
-          <t>Reportedly defunct. Registered in Bosnia and Herzegovina as a citizens’ association under the name of “Citizens’ Association for Support and Prevention of lies – Furqan” on 26 Sep. 1997. Al Furqan ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision number 03-054-286/97 dated 8 Nov. 2002). Al Furqan was no longer in existence as of Dec. 2008. Review pursuant to Security Council resolution 1822 (2008) was concluded on 15 Jun. 2010. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reportedly defunct. Registered in Bosnia and Herzegovina as a citizens’ association under the name of “Citizens’ Association for Support and Prevention of lies – Furqan” on 26 Sep. 1997. Al Furqan ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision number 03-054-286/97 dated 8 Nov. 2002). Al Furqan was no longer in existence as of Dec. 2008 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H952" s="5" t="inlineStr">
@@ -38805,13 +38128,7 @@
       <c r="F953" s="5" t="inlineStr"/>
       <c r="G953" s="5" t="inlineStr">
         <is>
-          <t>Reportedly defunct. In 2002-2004, Taibah International – Bosnia offices used premises of the
-Culture Home in Hadzici, Sarajevo, Bosnia and Herzegovina. The organization was
-officially registered in Bosnia and Herzegovina as a branch of Taibah International Aid
-Association under registry number 7. Taibah International – Bosnia offices ceased its
-work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation
-(decision on cessation of operation number 03-05-2-70/03). Review pursuant to Security
-Council resolution 1822 (2008) was concluded on 21 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reportedly defunct. In 2002-2004, Taibah International – Bosnia offices used premises of the Culture Home in Hadzici, Sarajevo, Bosnia and Herzegovina. The organization was officially registered in Bosnia and Herzegovina as a branch of Taibah International Aid Association under registry number 7. Taibah International – Bosnia offices ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision on cessation of operation number 03-05-2-70/03) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H953" s="5" t="inlineStr">
@@ -38849,7 +38166,7 @@
       <c r="F954" s="5" t="inlineStr"/>
       <c r="G954" s="5" t="inlineStr">
         <is>
-          <t>Reportedly defunct. Used to be officially registered in Bosnia and Herzegovina under registry number 24. Al-Haramain &amp; Al Masjed Al-Aqsa Charity Foundation ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision on cessation of operation number 03-05-2-203/04). It was no longer in existence as of Dec. 2008. Its premises and humanitarian activities were transferred under Government supervision to a new entity called Sretna Buducnost. Review pursuant to Security Council resolution 1822 (2008) was concluded on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reportedly defunct. Used to be officially registered in Bosnia and Herzegovina under registry number 24. Al-Haramain &amp; Al Masjed Al-Aqsa Charity Foundation ceased its work by decision of the Ministry of Justice of the Bosnia and Herzegovina Federation (decision on cessation of operation number 03-05-2-203/04). It was no longer in existence as of Dec. 2008. Its premises and humanitarian activities were transferred under Government supervision to a new entity called Sretna Buducnost INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H954" s="5" t="inlineStr">
@@ -38883,8 +38200,7 @@
       <c r="F955" s="5" t="inlineStr"/>
       <c r="G955" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H955" s="5" t="inlineStr">
@@ -38918,8 +38234,7 @@
       <c r="F956" s="5" t="inlineStr"/>
       <c r="G956" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H956" s="5" t="inlineStr">
@@ -38953,8 +38268,7 @@
       <c r="F957" s="5" t="inlineStr"/>
       <c r="G957" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H957" s="5" t="inlineStr">
@@ -38988,8 +38302,7 @@
       <c r="F958" s="5" t="inlineStr"/>
       <c r="G958" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H958" s="5" t="inlineStr">
@@ -39027,8 +38340,7 @@
       <c r="F959" s="5" t="inlineStr"/>
       <c r="G959" s="5" t="inlineStr">
         <is>
-          <t>Reportedly defunct.Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 28 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Reportedly defunct INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H959" s="5" t="inlineStr">
@@ -39066,10 +38378,7 @@
       <c r="F960" s="5" t="inlineStr"/>
       <c r="G960" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 25 May 2010. 
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020.
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H960" s="5" t="inlineStr">
@@ -39103,8 +38412,7 @@
       <c r="F961" s="5" t="inlineStr"/>
       <c r="G961" s="5" t="inlineStr">
         <is>
-          <t>Review pursuant to Security Council resolution 1822 (2008) was concluded
-on 22 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H961" s="5" t="inlineStr">
@@ -39142,9 +38450,7 @@
       <c r="F962" s="5" t="inlineStr"/>
       <c r="G962" s="5" t="inlineStr">
         <is>
-          <t>Associated with Hafiz Muhammad Saeed (QDi.263) who is the leader of
-Lashkar-e-Tayyiba. Review pursuant to Security Council resolution 1822 (2008) was
-concluded on 8 Jun. 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with Hafiz Muhammad Saeed (QDi.263) who is the leader of Lashkar-e-Tayyiba INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H962" s="5" t="inlineStr">
@@ -39182,11 +38488,7 @@
       <c r="F963" s="5" t="inlineStr"/>
       <c r="G963" s="5" t="inlineStr">
         <is>
-          <t>Founded and led by Najmiddin Kamolitdinovich Jalolov (deceased) and Suhayl
-                Fatilloevich Buranov (deceased). Associated with the Islamic Movement of Uzbekistan
-                (QDe.010) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan border
-                area, Central Asia, South Asia region and some European States. Review pursuant to
-                Security Council resolution 1822 (2008) was concluded on 20 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Founded and led by Najmiddin Kamolitdinovich Jalolov (deceased) and Suhayl Fatilloevich Buranov (deceased). Associated with the Islamic Movement of Uzbekistan (QDe.010) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan border area, Central Asia, South Asia region and some European States INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H963" s="5" t="inlineStr">
@@ -39224,12 +38526,7 @@
       <c r="F964" s="5" t="inlineStr"/>
       <c r="G964" s="5" t="inlineStr">
         <is>
-          <t>Regional offices in Pakistan: Bahawalpur, Bawalnagar, Gilgit, Islamabad,
-Mirpur Khas, Tando-Jan-Muhammad. Akhtarabad Medical Camp is in Spin Boldak, Afghanistan.
-Registered by members of Jaish-i-Mohammed (QDe.019). Associated with Harakat
-ul-Mujahidin/ HUM (QDe.008), Lashkar I Jhanghvi (LJ) (QDe.096) and Lashkar-e-Tayyiba
-(QDe.118). Banned in Pakistan. Review pursuant to Security Council resolution 1822
-(2008) was concluded on 14 Sep. 2009. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Regional offices in Pakistan: Bahawalpur, Bawalnagar, Gilgit, Islamabad, Mirpur Khas, Tando-Jan-Muhammad. Akhtarabad Medical Camp is in Spin Boldak, Afghanistan. Registered by members of Jaish-i-Mohammed (QDe.019). Associated with Harakat ul-Mujahidin/ HUM (QDe.008), Lashkar I Jhanghvi (LJ) (QDe.096) and Lashkar-e-Tayyiba (QDe.118). Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H964" s="5" t="inlineStr">
@@ -39267,12 +38564,7 @@
       <c r="F965" s="5" t="inlineStr"/>
       <c r="G965" s="5" t="inlineStr">
         <is>
-          <t>Founded and headed by Hilarion Del Rosario Santos III (QDi.244).
-Associated with the Abu Sayyaf Group (QDe.001), Jemaah Islamiyah (QDe.092) and Khadafi
-Abubakar Janjalani (deceased). Review pursuant to Security Council resolution 1822 (2008)
-was concluded on 13 May 2010. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. 
-Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Founded and headed by Hilarion Del Rosario Santos III (QDi.244). Associated with the Abu Sayyaf Group (QDe.001), Jemaah Islamiyah (QDe.092) and Khadafi Abubakar Janjalani (deceased) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H965" s="5" t="inlineStr">
@@ -39310,13 +38602,7 @@
       <c r="F966" s="5" t="inlineStr"/>
       <c r="G966" s="5" t="inlineStr">
         <is>
-          <t>AQAP is a regional affiliate of Al-Qaida (QDe.004) and an armed group operating
-                primarily in Arabian Peninsula. Location: Yemen. Alternative location: Saudi Arabia
-                (2004 – 2006). Formed in Jan. 2009 when Al-Qaida in Yemen combined with Saudi
-                Arabian Al-Qaida operatives. Leader of AQAP is Qasim Mohamed Mahdi Al-Rimi
-                (QDi.282). Ansar al-Shari’a was formed in early 2011 by AQAP and has taken
-                responsibility for multiple attacks in Yemen against both government and civilian
-                targets. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>AQAP is a regional affiliate of Al-Qaida (QDe.004) and an armed group operating primarily in Arabian Peninsula. Location: Yemen. Alternative location: Saudi Arabia (2004 – 2006). Formed in Jan. 2009 when Al-Qaida in Yemen combined with Saudi Arabian Al-Qaida operatives. Leader of AQAP is Qasim Mohamed Mahdi Al-Rimi (QDi.282). Ansar al-Shari’a was formed in early 2011 by AQAP and has taken responsibility for multiple attacks in Yemen against both government and civilian targets INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H966" s="5" t="inlineStr">
@@ -39354,10 +38640,7 @@
       <c r="F967" s="5" t="inlineStr"/>
       <c r="G967" s="5" t="inlineStr">
         <is>
-          <t>Was established in Afghanistan in 1980. In 1993, Harakat-ul Jihad Islami merged
-                with Harakat ul-Mujahidin (QDe.008) to form Harakat ul-Ansar. In 1997, Harakat-ul
-                Jihad Islami split from Harakat ul-Ansar and resumed using its former name.
-                Operations are in India, Pakistan and Afghanistan. Banned in Pakistan. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Was established in Afghanistan in 1980. In 1993, Harakat-ul Jihad Islami merged with Harakat ul-Mujahidin (QDe.008) to form Harakat ul-Ansar. In 1997, Harakat-ul Jihad Islami split from Harakat ul-Ansar and resumed using its former name. Operations are in India, Pakistan and Afghanistan. Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H967" s="5" t="inlineStr">
@@ -39391,8 +38674,7 @@
       <c r="F968" s="5" t="inlineStr"/>
       <c r="G968" s="5" t="inlineStr">
         <is>
-          <t>Mainly active in the Russian Federation, Afghanistan and Pakistan. Led by Doku
-Khamatovich Umarov (QDi.290). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Mainly active in the Russian Federation, Afghanistan and Pakistan. Led by Doku Khamatovich Umarov (QDi.290) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H968" s="5" t="inlineStr">
@@ -39430,8 +38712,7 @@
       <c r="F969" s="5" t="inlineStr"/>
       <c r="G969" s="5" t="inlineStr">
         <is>
-          <t>Tehrik-e Taliban is based in the tribal areas along the Afghanistan/Pakistan
-border. Formed in 2007, its leader is Maulana Fazlullah (QDi.352). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Tehrik-e Taliban is based in the tribal areas along the Afghanistan/Pakistan border. Formed in 2007, its leader is Maulana Fazlullah (QDi.352) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H969" s="5" t="inlineStr">
@@ -39469,13 +38750,7 @@
       <c r="F970" s="5" t="inlineStr"/>
       <c r="G970" s="5" t="inlineStr">
         <is>
-          <t>A group affiliated with the Islamic State in Iraq and the Levant (ISIL), listed
-                as Al-Qaida in Iraq (QDe.115), that has perpetrated attacks in Indonesia. Founded
-                and led by Abu Bakar Ba'asyir (QDi.217). Established on 27 Jul. 2008 in Solo,
-                Indonesia. Had been associated with Jemmah Islamiya (JI) (QDe.092). Review pursuant
-                to Security Council resolution 2253 (2015) was concluded on 7 June 2018. Website:
-                http://ansharuttauhid.com/
-                Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>A group affiliated with the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), that has perpetrated attacks in Indonesia. Founded and led by Abu Bakar Ba'asyir (QDi.217). Established on 27 Jul. 2008 in Solo, Indonesia. Had been associated with Jemmah Islamiya (JI) (QDe.092). Website: http://ansharuttauhid.com/ INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H970" s="5" t="inlineStr">
@@ -39509,7 +38784,7 @@
       <c r="F971" s="5" t="inlineStr"/>
       <c r="G971" s="5" t="inlineStr">
         <is>
-          <t>Associated with The Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with The Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H971" s="5" t="inlineStr">
@@ -39547,10 +38822,7 @@
       <c r="F972" s="5" t="inlineStr"/>
       <c r="G972" s="5" t="inlineStr">
         <is>
-          <t>Was founded in December 2011 by Iyad ag Ghali (QDi.316). Linked to the
-Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mouvement pour
-l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Associated with
-Abdelmalek Droukdel (QDi.232). Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Was founded in December 2011 by Iyad ag Ghali (QDi.316). Linked to the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Associated with Abdelmalek Droukdel (QDi.232) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H972" s="5" t="inlineStr">
@@ -39588,7 +38860,7 @@
       <c r="F973" s="5" t="inlineStr"/>
       <c r="G973" s="5" t="inlineStr">
         <is>
-          <t>Terrorist and paramilitary group established by Muhammad Jamal al Kashif (QDi.318) in 2011 and linked to Al-Qaida (QDe.004), Aiman al-Zawahiri (QDi.006), and the leadership of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129) and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Funded and supported by AQAP. Multiple terrorist training camps in Egypt and Libya. Reportedly acquiring weapons, conducting training and establishing terrorist groups in the Sinai, Egypt. Training suicide bombers, foreign fighters and planning terrorist attacks in Egypt, Libya and elsewhere as of Sep. 2013. MJN members were reported to be involved in the attack on the United States Mission in Benghazi, Libya, on 11 Sep. 2012. Review pursuant to Security Council resolution 2253 (2015) was concluded on 21 Feb. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Terrorist and paramilitary group established by Muhammad Jamal al Kashif (QDi.318) in 2011 and linked to Al-Qaida (QDe.004), Aiman al-Zawahiri (QDi.006), and the leadership of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129) and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Funded and supported by AQAP. Multiple terrorist training camps in Egypt and Libya. Reportedly acquiring weapons, conducting training and establishing terrorist groups in the Sinai, Egypt. Training suicide bombers, foreign fighters and planning terrorist attacks in Egypt, Libya and elsewhere as of Sep. 2013. MJN members were reported to be involved in the attack on the United States Mission in Benghazi, Libya, on 11 Sep. 2012 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H973" s="5" t="inlineStr">
@@ -39626,7 +38898,7 @@
       <c r="F974" s="5" t="inlineStr"/>
       <c r="G974" s="5" t="inlineStr">
         <is>
-          <t>Affiliate of Al-Qaida (QDe.004), and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Associated with Jama'atu Ansarul Muslimina Fi Biladis-Sudan (Ansaru). The leader is Abubakar Shekau. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Affiliate of Al-Qaida (QDe.004), and the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Associated with Jama'atu Ansarul Muslimina Fi Biladis-Sudan (Ansaru). The leader is Abubakar Shekau INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H974" s="5" t="inlineStr">
@@ -39664,9 +38936,7 @@
       <c r="F975" s="5" t="inlineStr"/>
       <c r="G975" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb
-(QDe.014) and led by Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara
-region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and led by Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H975" s="5" t="inlineStr">
@@ -39704,12 +38974,7 @@
       <c r="F976" s="5" t="inlineStr"/>
       <c r="G976" s="5" t="inlineStr">
         <is>
-          <t>Founded in 2012 as a splinter group of the Organization of Al-Qaida in
-the Islamic Maghreb (QDe.014). On 20 Aug. 2013, Al Moulathamoun merged with the
-Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134) and
-established Al Mourabitoun (QDe.141). Associated with the Organization of Al-Qaida in
-the Islamic Maghreb (QDe.014) and led by Mokhtar Belmokhtar (QDi.136). Active in the
-Sahel/Sahara region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Founded in 2012 as a splinter group of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). On 20 Aug. 2013, Al Moulathamoun merged with the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134) and established Al Mourabitoun (QDe.141). Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and led by Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H976" s="5" t="inlineStr">
@@ -39747,10 +39012,7 @@
       <c r="F977" s="5" t="inlineStr"/>
       <c r="G977" s="5" t="inlineStr">
         <is>
-          <t>Founded on 20 Aug. 2013 as result of a merger between Al Moulathamoun
-(QDe.140) and the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO)
-(QDe.134). Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014)
-and led by Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Founded on 20 Aug. 2013 as result of a merger between Al Moulathamoun (QDe.140) and the Mouvement pour l’Unification et le Jihad en Afrique de l’Ouest (MUJAO) (QDe.134). Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and led by Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H977" s="5" t="inlineStr">
@@ -39788,10 +39050,7 @@
       <c r="F978" s="5" t="inlineStr"/>
       <c r="G978" s="5" t="inlineStr">
         <is>
-          <t>Terrorist and paramilitary group established in 2012 and operating in
-Nigeria. Associated with the Organization of Al-Qaida in the Islamic Maghreb (AQIM)
-(QDe.014), Jama'atu Ahlis Sunna Lidda'Awati Wal-Jihad (Boko Haram) (QDe.138) and
-Abubakar Mohammed Shekau (QDi322). Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Terrorist and paramilitary group established in 2012 and operating in Nigeria. Associated with the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014), Jama'atu Ahlis Sunna Lidda'Awati Wal-Jihad (Boko Haram) (QDe.138) and Abubakar Mohammed Shekau (QDi322) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H978" s="5" t="inlineStr">
@@ -39829,8 +39088,7 @@
       <c r="F979" s="5" t="inlineStr"/>
       <c r="G979" s="5" t="inlineStr">
         <is>
-          <t>A Tunisian armed group with links to the Organization of Al-Qaida in the
-Islamic Maghreb (QDe.014). The leader is Seifallah ben Hassine (QDi.333). Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>A Tunisian armed group with links to the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). The leader is Seifallah ben Hassine (QDi.333) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H979" s="5" t="inlineStr">
@@ -39868,8 +39126,7 @@
       <c r="F980" s="5" t="inlineStr"/>
       <c r="G980" s="5" t="inlineStr">
         <is>
-          <t>An armed group that has carried out joint attacks with Al-Nusrah Front
-for the People of the Levant (formerly listed).  Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>An armed group that has carried out joint attacks with Al-Nusrah Front for the People of the Levant (formerly listed) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H980" s="5" t="inlineStr">
@@ -39907,10 +39164,7 @@
       <c r="F981" s="5" t="inlineStr"/>
       <c r="G981" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb
-(QDe.014), Ansar al-Shari’a in Tunisia (AAS-T) (QDe.143) and Ansar al Charia Benghazi
-(QDe.146). Runs training camps for foreign terrorist fighters travelling to Syria and
-Iraq. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014), Ansar al-Shari’a in Tunisia (AAS-T) (QDe.143) and Ansar al Charia Benghazi (QDe.146). Runs training camps for foreign terrorist fighters travelling to Syria and Iraq INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H981" s="5" t="inlineStr">
@@ -39948,13 +39202,7 @@
       <c r="F982" s="5" t="inlineStr"/>
       <c r="G982" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb
-(QDe.014), Al Mourabitoun (QDe.141), Ansar al-Shari’a in Tunisia (AAS-T) (QDe.143), and
-Ansar al Charia Derna (QDe.145). The leader is Mohamed al-Zahawi (not listed). Runs
-training camps for foreign terrorist fighters travelling to Syria, Iraq and
-Mali. Review pursuant to Security Council resolution 2368 (2017) was concluded on 4 Dec. 2019. 
-Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Organization of Al-Qaida in the Islamic Maghreb (QDe.014), Al Mourabitoun (QDe.141), Ansar al-Shari’a in Tunisia (AAS-T) (QDe.143), and Ansar al Charia Derna (QDe.145). The leader is Mohamed al-Zahawi (not listed). Runs training camps for foreign terrorist fighters travelling to Syria, Iraq and Mali INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H982" s="5" t="inlineStr">
@@ -39992,11 +39240,7 @@
       <c r="F983" s="5" t="inlineStr"/>
       <c r="G983" s="5" t="inlineStr">
         <is>
-          <t>Ostensibly humanitarian wing of Jemaah Islamiyah (QDe.092). Operates in
-                Lampung, Jakarta, Semarang, Yogyakarta, Solo, Surabaya and Makassar, Indonesia. Has
-                been recruiting, funding and facilitating travel of foreign terrorist fighters to
-                Syria. Not affiliated with the humanitarian group International Federation of the
-                Red Cross and Red Crescent Societies (IFRC). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Ostensibly humanitarian wing of Jemaah Islamiyah (QDe.092). Operates in Lampung, Jakarta, Semarang, Yogyakarta, Solo, Surabaya and Makassar, Indonesia. Has been recruiting, funding and facilitating travel of foreign terrorist fighters to Syria. Not affiliated with the humanitarian group International Federation of the Red Cross and Red Crescent Societies (IFRC) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H983" s="5" t="inlineStr">
@@ -40034,10 +39278,7 @@
       <c r="F984" s="5" t="inlineStr"/>
       <c r="G984" s="5" t="inlineStr">
         <is>
-          <t>Established by foreign terrorist fighters in 2013. Location: Syrian Arab
-                Republic. Affiliated with Islamic State in Iraq and the Levant, listed as Al-Qaida
-                in Iraq (QDe.115) and AI-Nusrah Front for the People of the Levant
-                (formerly listed). Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Established by foreign terrorist fighters in 2013. Location: Syrian Arab Republic. Affiliated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115) and AI-Nusrah Front for the People of the Levant (formerly listed) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H984" s="5" t="inlineStr">
@@ -40075,7 +39316,7 @@
       <c r="F985" s="5" t="inlineStr"/>
       <c r="G985" s="5" t="inlineStr">
         <is>
-          <t>Moroccan-led terrorist organization formed in Aug. 2013 and operating in Syrian Arab Republic. Principally composed of foreign terrorist fighters and associated with AI-Nusrah Front for the People of the Levant (formerly listed).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Moroccan-led terrorist organization formed in Aug. 2013 and operating in Syrian Arab Republic. Principally composed of foreign terrorist fighters and associated with AI-Nusrah Front for the People of the Levant (formerly listed) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H985" s="5" t="inlineStr">
@@ -40113,8 +39354,7 @@
       <c r="F986" s="5" t="inlineStr"/>
       <c r="G986" s="5" t="inlineStr">
         <is>
-          <t>Terrorist group linked to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), Jemaah Islamiyah (JI) (QDe.092), and Jemmah Anshorut Tauhid (JAT) (QDe.133). Operates in Java and Sulawesi, Indonesia and also active in Indonesia’s eastern provinces. Its former leader was Abu Wardah, a.k.a. Santoso (deceased). 
-Review pursuant to Security Council resolution 2368 (2017) was concluded on 15 November 2021. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Terrorist group linked to Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), Jemaah Islamiyah (JI) (QDe.092), and Jemmah Anshorut Tauhid (JAT) (QDe.133). Operates in Java and Sulawesi, Indonesia and also active in Indonesia’s eastern provinces. Its former leader was Abu Wardah, a.k.a. Santoso (deceased) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H986" s="5" t="inlineStr">
@@ -40152,9 +39392,7 @@
       <c r="F987" s="5" t="inlineStr"/>
       <c r="G987" s="5" t="inlineStr">
         <is>
-          <t>Emerged on 13 Sep. 2014. Most known for its abduction and subsequent beheading
-                of French national Herve Gourdel. Claimed responsibility for attacking police and
-                gendarmes in Algeria and continued planning future attacks. Review pursuant to Security Council resolution 2368 (2017) was concluded on 24 November 2020. INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Emerged on 13 Sep. 2014. Most known for its abduction and subsequent beheading of French national Herve Gourdel. Claimed responsibility for attacking police and gendarmes in Algeria and continued planning future attacks INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H987" s="5" t="inlineStr">
@@ -40192,7 +39430,7 @@
       <c r="F988" s="5" t="inlineStr"/>
       <c r="G988" s="5" t="inlineStr">
         <is>
-          <t>Splinter group of the Tehrik-e Taliban Pakistan (QDe.132). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Formed in Aug. 2014 in Mohmand Agency, Pakistan. Operates from Nangarhar Province, Afghanistan and Pakistan-Afghanistan border region. Banned in Pakistan on 21 Nov. 2016. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Splinter group of the Tehrik-e Taliban Pakistan (QDe.132). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). Formed in Aug. 2014 in Mohmand Agency, Pakistan. Operates from Nangarhar Province, Afghanistan and Pakistan-Afghanistan border region. Banned in Pakistan on 21 Nov. 2016 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H988" s="5" t="inlineStr">
@@ -40230,7 +39468,7 @@
       <c r="F989" s="5" t="inlineStr"/>
       <c r="G989" s="5" t="inlineStr">
         <is>
-          <t>Money exchange business in Albu Kamal (Al-Bukamal), Syrian Arab Republic, facilitating the movement of funds on behalf of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Used exclusively for ISIL-related transactions. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Money exchange business in Albu Kamal (Al-Bukamal), Syrian Arab Republic, facilitating the movement of funds on behalf of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Used exclusively for ISIL-related transactions INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H989" s="5" t="inlineStr">
@@ -40268,7 +39506,7 @@
       <c r="F990" s="5" t="inlineStr"/>
       <c r="G990" s="5" t="inlineStr">
         <is>
-          <t>Money exchange business facilitating the movement of funds on behalf of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), as of Apr. 2016. Conducted over one hundred financial transfers into ISIL-controlled territory. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Money exchange business facilitating the movement of funds on behalf of Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), as of Apr. 2016. Conducted over one hundred financial transfers into ISIL-controlled territory INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H990" s="5" t="inlineStr">
@@ -40306,7 +39544,7 @@
       <c r="F991" s="5" t="inlineStr"/>
       <c r="G991" s="5" t="inlineStr">
         <is>
-          <t>Joined the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in May 2015. Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Joined the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), in May 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H991" s="5" t="inlineStr">
@@ -40344,7 +39582,7 @@
       <c r="F992" s="5" t="inlineStr"/>
       <c r="G992" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Al Nusrah Front for the People of the Levant (formerly listed). Review pursuant to Security Council resolution 2610 (2021) was concluded on 8 November 2022.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Al Nusrah Front for the People of the Levant (formerly listed) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H992" s="5" t="inlineStr">
@@ -40382,9 +39620,7 @@
       <c r="F993" s="5" t="inlineStr"/>
       <c r="G993" s="5" t="inlineStr">
         <is>
-          <t>Money exchange business and owned by Umar Mahmud Irhayyim al-Kubaysi (QDi.412) as of mid-2016. Facilitated financial transactions on behalf of companies associated with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Established in 2000 under License number 202, issued on 17 May 2000, and since withdrawn. 
-Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Money exchange business and owned by Umar Mahmud Irhayyim al-Kubaysi (QDi.412) as of mid-2016. Facilitated financial transactions on behalf of companies associated with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Established in 2000 under License number 202, issued on 17 May 2000, and since withdrawn INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H993" s="5" t="inlineStr">
@@ -40422,7 +39658,7 @@
       <c r="F994" s="5" t="inlineStr"/>
       <c r="G994" s="5" t="inlineStr">
         <is>
-          <t>Associated with Al-Nusrah Front for the People of the Levant (formerly listed). Committed terrorist attacks in the Syrian Arab Republic. Since 2016 redeployed to Northern Afghanistan to project attacks against Central Asia countries. Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with Al-Nusrah Front for the People of the Levant (formerly listed). Committed terrorist attacks in the Syrian Arab Republic. Since 2016 redeployed to Northern Afghanistan to project attacks against Central Asia countries INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H994" s="5" t="inlineStr">
@@ -40456,9 +39692,7 @@
       <c r="F995" s="5" t="inlineStr"/>
       <c r="G995" s="5" t="inlineStr">
         <is>
-          <t>Associated with Al-Qaida (QDe.004), the Organization of Al-Qaida in the Islamic Maghreb (QDe.014), Ansar Eddine (QDe.135) and Al-Mourabitoun (QDe.141). Operations in Mali and Burkina Faso. 
-Review pursuant to Security Council resolution 2610 (2021) was concluded on 30 October 2023. 
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with Al-Qaida (QDe.004), the Organization of Al-Qaida in the Islamic Maghreb (QDe.014), Ansar Eddine (QDe.135) and Al-Mourabitoun (QDe.141). Operations in Mali and Burkina Faso INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H995" s="5" t="inlineStr">
@@ -40496,7 +39730,7 @@
       <c r="F996" s="5" t="inlineStr"/>
       <c r="G996" s="5" t="inlineStr">
         <is>
-          <t>Splinter group of Tehrik-e Taliban Pakistan (TTP) (QDe.132). The group was formed in Darra Adam Khel, Federally Administered Tribal Area (FATA), Pakistan, in 2007.       INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Splinter group of Tehrik-e Taliban Pakistan (TTP) (QDe.132). The group was formed in Darra Adam Khel, Federally Administered Tribal Area (FATA), Pakistan, in 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H996" s="5" t="inlineStr">
@@ -40534,12 +39768,7 @@
       <c r="F997" s="5" t="inlineStr"/>
       <c r="G997" s="5" t="inlineStr">
         <is>
-          <t>Islamic State of Iraq and the Levant - Khorasan (ISIL - K) was formed on
-                January 10, 2015 by a former Tehrik-e Taliban Pakistan (TTP) (QDe.132) commander and
-                was established by former Taliban faction commanders who swore an oath of allegiance
-                to the Islamic State of Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)).
-                ISIL – K has claimed responsibility for numerous attacks in both Afghanistan and
-                Pakistan.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Islamic State of Iraq and the Levant - Khorasan (ISIL - K) was formed on January 10, 2015 by a former Tehrik-e Taliban Pakistan (TTP) (QDe.132) commander and was established by former Taliban faction commanders who swore an oath of allegiance to the Islamic State of Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). ISIL – K has claimed responsibility for numerous attacks in both Afghanistan and Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H997" s="5" t="inlineStr">
@@ -40577,7 +39806,7 @@
       <c r="F998" s="5" t="inlineStr"/>
       <c r="G998" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Islamic State in Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). Formed in March 2015 by Abubakar Shekau (QDi.322). Splinter group of Jama'atu Ahlis Sunna Lidda'Awati Wal-Jihad (Boko Haram) (QDe.138). Committed terrorist attacks in Nigeria.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Islamic State in Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). Formed in March 2015 by Abubakar Shekau (QDi.322). Splinter group of Jama'atu Ahlis Sunna Lidda'Awati Wal-Jihad (Boko Haram) (QDe.138). Committed terrorist attacks in Nigeria INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H998" s="5" t="inlineStr">
@@ -40615,7 +39844,7 @@
       <c r="F999" s="5" t="inlineStr"/>
       <c r="G999" s="5" t="inlineStr">
         <is>
-          <t>Formed in May 2015 by Adnan Abu Walid al-Sahraoui (QDi.415). Associated with the Islamic State in Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). Splinter group of Al-Mourabitoun (QDe.141). Committed terrorist attacks in Mali, Niger and Burkina Faso.  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Formed in May 2015 by Adnan Abu Walid al-Sahraoui (QDi.415). Associated with the Islamic State in Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). Splinter group of Al-Mourabitoun (QDe.141). Committed terrorist attacks in Mali, Niger and Burkina Faso INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H999" s="5" t="inlineStr">
@@ -40653,7 +39882,7 @@
       <c r="F1000" s="5" t="inlineStr"/>
       <c r="G1000" s="5" t="inlineStr">
         <is>
-          <t>Established in 2015 as an umbrella group of Indonesian extremist groups that pledged allegiance to then-ISIL leader Abu Bakr al-Baghdadi.  Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Established in 2015 as an umbrella group of Indonesian extremist groups that pledged allegiance to then-ISIL leader Abu Bakr al-Baghdadi. Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1000" s="5" t="inlineStr">
@@ -40691,7 +39920,7 @@
       <c r="F1001" s="5" t="inlineStr"/>
       <c r="G1001" s="5" t="inlineStr">
         <is>
-          <t>Formed in November 2014 upon announcement by Abu Bakr Al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali Al-Badri Al-Samarrai (QDi.299). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Formed in November 2014 upon announcement by Abu Bakr Al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali Al-Badri Al-Samarrai (QDi.299). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1001" s="5" t="inlineStr">
@@ -40729,7 +39958,7 @@
       <c r="F1002" s="5" t="inlineStr"/>
       <c r="G1002" s="5" t="inlineStr">
         <is>
-          <t>Formed in November 2014 upon acceptance of oaths of allegiance by Abu Bakr Al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali Al-Badri Al-Samarrai (QDi.299). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Formed in November 2014 upon acceptance of oaths of allegiance by Abu Bakr Al-Baghdadi, listed as Ibrahim Awwad Ibrahim Ali Al-Badri Al-Samarrai (QDi.299). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1002" s="5" t="inlineStr">
@@ -40767,8 +39996,7 @@
       <c r="F1003" s="5" t="inlineStr"/>
       <c r="G1003" s="5" t="inlineStr">
         <is>
-          <t>Formed in November 2014.Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115).    
- INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Formed in November 2014.Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1003" s="5" t="inlineStr">
@@ -40806,7 +40034,7 @@
       <c r="F1004" s="5" t="inlineStr"/>
       <c r="G1004" s="5" t="inlineStr">
         <is>
-          <t>Khatiba al-Tawhid wal-Jihad (formerly known as Jannat Oshiklari) is a terrorist organization operating under the umbrella of the international terrorist organization Al-Nusrah Front for the People of the Levant (formerly listed). The group mainly operates in the provinces of Hama, Idlib and Ladhiqiyah, in the Syrian Arab Republic, and also conduct operations in Turkey, Kyrgyzstan, Uzbekistan, Russian Federation, Tajikistan, Kazakhstan, Egypt, Afghanistan, Ukraine.  The number of fighters of KTJ is about 500. KTJ also cooperates with such terrorist organizations as Khatiba Imam al-Bukhari (QDe.158) and the Islamic Jihad Group (QDe.119).  INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Khatiba al-Tawhid wal-Jihad (formerly known as Jannat Oshiklari) is a terrorist organization operating under the umbrella of the international terrorist organization Al-Nusrah Front for the People of the Levant (formerly listed). The group mainly operates in the provinces of Hama, Idlib and Ladhiqiyah, in the Syrian Arab Republic, and also conduct operations in Turkey, Kyrgyzstan, Uzbekistan, Russian Federation, Tajikistan, Kazakhstan, Egypt, Afghanistan, Ukraine. The number of fighters of KTJ is about 500. KTJ also cooperates with such terrorist organizations as Khatiba Imam al-Bukhari (QDe.158) and the Islamic Jihad Group (QDe.119) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1004" s="5" t="inlineStr">
@@ -40844,7 +40072,7 @@
       <c r="F1005" s="5" t="inlineStr"/>
       <c r="G1005" s="5" t="inlineStr">
         <is>
-          <t>Formed in June 2016 upon announcement by now-deceased Isnilon Hapilon (QDi.204). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Formed in June 2016 upon announcement by now-deceased Isnilon Hapilon (QDi.204). Associated with Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1005" s="5" t="inlineStr">
@@ -40882,7 +40110,7 @@
       <c r="F1006" s="5" t="inlineStr"/>
       <c r="G1006" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1006" s="5" t="inlineStr">
@@ -40920,7 +40148,7 @@
       <c r="F1007" s="5" t="inlineStr"/>
       <c r="G1007" s="5" t="inlineStr">
         <is>
-          <t>Afghan Money Service Provider License Number: 044. Haji Khairullah Haji Sattar Money Exchange was used by Taliban leadership to transfer money to Taliban commanders to fund fighters and operations in Afghanistan as of 2011. Active in Kunar Province. Associated with Abdul Sattar Abdul Manan (TAi.162) and Khairullah Barakzai Khudai Nazar (TAi.163). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Afghan Money Service Provider License Number: 044. Haji Khairullah Haji Sattar Money Exchange was used by Taliban leadership to transfer money to Taliban commanders to fund fighters and operations in Afghanistan as of 2011. Active in Kunar Province. Associated with Abdul Sattar Abdul Manan (TAi.162) and Khairullah Barakzai Khudai Nazar (TAi.163) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1007" s="5" t="inlineStr">
@@ -40958,9 +40186,7 @@
       <c r="F1008" s="5" t="inlineStr"/>
       <c r="G1008" s="5" t="inlineStr">
         <is>
-          <t>Roshan Money Exchange stores and transfers funds to support Taliban
-military operations and narcotics trade in Afghanistan. Owned by Ahmed Shah Noorzai
-Obaidullah (TAi.166). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Roshan Money Exchange stores and transfers funds to support Taliban military operations and narcotics trade in Afghanistan. Owned by Ahmed Shah Noorzai Obaidullah (TAi.166) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1008" s="5" t="inlineStr">
@@ -40994,16 +40220,7 @@
       <c r="F1009" s="5" t="inlineStr"/>
       <c r="G1009" s="5" t="inlineStr">
         <is>
-          <t>Network of Taliban fighters centered around the border between Khost
-Province, Afghanistan and North Waziristan, Pakistan. Founded by Jalaluddin Haqqani
-(TAi.040) and currently headed by his son Sirajuddin Jallaloudine Haqqani (TAi.144).
-Other listed members include Nasiruddin Haqqani (TAi.146), Sangeen Zadran Sher Mohammad
-(TAi.152), Abdul Aziz Abbasin (TAi.155), Fazl Rabi (TAi.157), Ahmed Jan Wazir (TAi.159),
-Bakht Gul (TAi.161), Abdul Rauf Zakir (TAi.164). Responsible for suicide attacks and
-targeted assassination as well as kidnappings in Kabul and other provinces of
-Afghanistan. Linked to Al-Qaida (QDe.004), Islamic Movement of Uzbekistan (QDe.010),
-Tehrik-e Taliban Pakistan (QDe.132), Lashkar I Jhangvi (QDe.096), and Jaish-IMohammed
-(QDe.019). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Network of Taliban fighters centered around the border between Khost Province, Afghanistan and North Waziristan, Pakistan. Founded by Jalaluddin Haqqani (TAi.040) and currently headed by his son Sirajuddin Jallaloudine Haqqani (TAi.144). Other listed members include Nasiruddin Haqqani (TAi.146), Sangeen Zadran Sher Mohammad (TAi.152), Abdul Aziz Abbasin (TAi.155), Fazl Rabi (TAi.157), Ahmed Jan Wazir (TAi.159), Bakht Gul (TAi.161), Abdul Rauf Zakir (TAi.164). Responsible for suicide attacks and targeted assassination as well as kidnappings in Kabul and other provinces of Afghanistan. Linked to Al-Qaida (QDe.004), Islamic Movement of Uzbekistan (QDe.010), Tehrik-e Taliban Pakistan (QDe.132), Lashkar I Jhangvi (QDe.096), and Jaish-IMohammed (QDe.019) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1009" s="5" t="inlineStr">
@@ -41041,10 +40258,7 @@
       <c r="F1010" s="5" t="inlineStr"/>
       <c r="G1010" s="5" t="inlineStr">
         <is>
-          <t>Rahat Ltd. was used by Taliban leadership to transfer funds originating
-from external donors and narcotics trafficking to finance Taliban activity as of 2011
-and 2012. Owned by Mohammed Qasim Mir Wali Khudai Rahim (TAi.165). Also associated
-Mohammad Naim Barich Khudaidad (TAi.013). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Rahat Ltd. was used by Taliban leadership to transfer funds originating from external donors and narcotics trafficking to finance Taliban activity as of 2011 and 2012. Owned by Mohammed Qasim Mir Wali Khudai Rahim (TAi.165). Also associated Mohammad Naim Barich Khudaidad (TAi.013) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1010" s="5" t="inlineStr">
@@ -41082,8 +40296,7 @@
       <c r="F1011" s="5" t="inlineStr"/>
       <c r="G1011" s="5" t="inlineStr">
         <is>
-          <t>Money service provider used by senior Taliban leaders to transfer funds
-to Taliban commanders in the region. Owned by Abdul Basir Noorzai (TAi.173). INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Money service provider used by senior Taliban leaders to transfer funds to Taliban commanders in the region. Owned by Abdul Basir Noorzai (TAi.173) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1011" s="5" t="inlineStr">
@@ -41121,7 +40334,7 @@
       <c r="F1012" s="5" t="inlineStr"/>
       <c r="G1012" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraph 5 of resolution 2624 (2022) as subject to the measures imposed by paragraph 14 of resolution 2216 (2015) (targeted arms embargo). The Houthis have engaged in acts that threaten the peace, security, and stability of Yemen. The Houthis have engaged in attacks striking civilians and civilian infrastructure in Yemen, implemented a policy of sexual violence and repression against politically active and professional women, engaged in the recruitment and use of children, incited violence against groups including on the basis of religion and nationality, and indiscriminately used landmines and improvised explosive devices on the West Coast of Yemen. The Houthis have also obstructed the delivery of humanitarian assistance to Yemen, or access to, or distribution of, humanitarian assistance in Yemen. The Houthis have conducted attacks on commercial shipping in the Red Sea using waterborne improvised explosive devices and sea mines. The Houthis have also perpetrated repeated cross-border terrorist attacks striking civilians and civilian infrastructure in the Kingdom of Saudi Arabia and the United Arab Emirates and threatened to intentionally target civilian sites.    INTERPOL-UN Security Council Special Notice web link:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Listed pursuant to paragraph 5 of resolution 2624 (2022) as subject to the measures imposed by paragraph 14 of resolution 2216 (2015) (targeted arms embargo). The Houthis have engaged in acts that threaten the peace, security, and stability of Yemen. The Houthis have engaged in attacks striking civilians and civilian infrastructure in Yemen, implemented a policy of sexual violence and repression against politically active and professional women, engaged in the recruitment and use of children, incited violence against groups including on the basis of religion and nationality, and indiscriminately used landmines and improvised explosive devices on the West Coast of Yemen. The Houthis have also obstructed the delivery of humanitarian assistance to Yemen, or access to, or distribution of, humanitarian assistance in Yemen. The Houthis have conducted attacks on commercial shipping in the Red Sea using waterborne improvised explosive devices and sea mines. The Houthis have also perpetrated repeated cross-border terrorist attacks striking civilians and civilian infrastructure in the Kingdom of Saudi Arabia and the United Arab Emirates and threatened to intentionally target civilian sites.    INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H1012" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04T01:44:32+00:00</t>
+          <t>2026-08-05T01:45:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05T01:45:42+00:00</t>
+          <t>2026-08-06T01:46:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06T01:46:02+00:00</t>
+          <t>2026-08-07T02:10:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07T02:10:29+00:00</t>
+          <t>2026-08-08T00:57:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08T00:57:38+00:00</t>
+          <t>2026-08-09T01:01:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09T01:01:36+00:00</t>
+          <t>2026-08-10T01:03:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10T01:03:50+00:00</t>
+          <t>2026-08-11T01:02:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11T01:02:20+00:00</t>
+          <t>2026-08-12T01:09:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12T01:09:29+00:00</t>
+          <t>2026-08-13T01:11:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13T01:11:31+00:00</t>
+          <t>2026-08-14T01:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>Sayf-Al Adl ; Muhamad Ibrahim Makkawi ; Ibrahim al-Madani ; Saif Al-'Adil ; Seif al Adel</t>
+          <t>Sayf-Al Adl ; Muhamad Ibrahim Makkawi ; Ibrahim al-Madani ; Saif Al-'Adil ; Seif al Adel ; SALEM AL-SHARIF ; HAZEM AL-MADANI ; ABER SABIL ; MUHANNAD SALEM ; ABU KHALED AL-SAN’ANI</t>
         </is>
       </c>
       <c r="F301" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Responsible for Usama bin Laden’s (deceased) security. Hair: Dark. Eyes: Dark. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Responsible for Usama bin Laden’s (deceased) security. Hair: Dark. Eyes: Dark. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-312380</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="G404" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Islamic Jihad Union (IJU), also known as the Islamic Jihad Group (QDe.119). Deported from Germany to Türkiye in February 2019. Ongoing judicial process as of November 2023 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with the Islamic Jihad Union (IJU), also known as the Islamic Jihad Group (QDe.119). Deported from Germany to Türkiye in February 2019. Ongoing judicial process as of November 2023. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-44887</t>
         </is>
       </c>
       <c r="H404" s="5" t="inlineStr">
@@ -18894,12 +18894,12 @@
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>SHAFI SULTAN MOHAMMED AL-AJMI</t>
+          <t>SHAFI SULTAN MOHAMMED SULTAN AL-AJMI</t>
         </is>
       </c>
       <c r="E460" s="5" t="inlineStr">
         <is>
-          <t>Shafi al-Ajmi ; Sheikh Shafi al-Ajmi ; Shaykh Abu-Sultan</t>
+          <t>Shafi al-Ajmi ; Sheikh Shafi al-Ajmi ; Shaykh Abu-Sultan ; SHAFI S. M. S. ALAJMI</t>
         </is>
       </c>
       <c r="F460" s="5" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G460" s="5" t="inlineStr">
         <is>
-          <t>Fundraiser for Al-Nusrah Front for the People of the Levant (formerly listed). In November 2023, he was released from prison in Kuwait as part of the Special Amiri Decree Pardon No. 225/2023 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Fundraiser for Al-Nusrah Front for the People of the Levant (formerly listed). In November 2023, he was released from prison in Kuwait as part of the Special Amiri Decree Pardon No. 225/2023. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2014-58611</t>
         </is>
       </c>
       <c r="H460" s="5" t="inlineStr">
@@ -37464,7 +37464,7 @@
       <c r="F935" s="5" t="inlineStr"/>
       <c r="G935" s="5" t="inlineStr">
         <is>
-          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055), Majeed Abdul Chaudhry (QDi.054) and Mohammed Tufail (QDi.056). Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055). Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2008-18090</t>
         </is>
       </c>
       <c r="H935" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14T01:10:11+00:00</t>
+          <t>2026-08-15T00:43:46+00:00</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>Security coordinator for Usama bin Laden (deceased). Repatriated to Afghanistan in February 2006. He was in Afghanistan as of August 2021 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Security coordinator for Usama bin Laden (deceased). Repatriated to Afghanistan in February 2006. He was in Afghanistan as of August 2021. Arrested in Pakistan 2024 and deported to Afghanistan in 2025. Father’s name: Abdul Rahman. Photo and fingerprints available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-21201</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="B545" s="5" t="inlineStr">
         <is>
-          <t>6909290</t>
+          <t>6909632</t>
         </is>
       </c>
       <c r="C545" s="5" t="inlineStr">
@@ -22421,7 +22421,7 @@
       </c>
       <c r="E545" s="5" t="inlineStr">
         <is>
-          <t>ABUBAKER SWALEH ; TOM KIYURIGE</t>
+          <t>ABUBAKER SWALEH ; TOM KIYURIGE ; ISAAC MUPETA</t>
         </is>
       </c>
       <c r="F545" s="5" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="G545" s="5" t="inlineStr">
         <is>
-          <t>Abubakar Swalleh provides financial, material, or technological support for, or financial or other services to, or in support of, ISIL (listed as Al-Qaida in Iraq (QDe.115). He acted, since 2018, as an ISIL facilitator who provides financial and logistic support including recruitment for ISIL in East and Southern Africa. Phone number: +963936016952. Gender: Male INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Abubakar Swalleh provides financial, material, or technological support for, or financial or other services to, or in support of, ISIL (listed as Al-Qaida in Iraq (QDe.115). He acted, since 2018, as an ISIL facilitator who provides financial and logistic support including recruitment for ISIL in East and Southern Africa. Phone number: +963936016952. Gender: Male. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2025-47413</t>
         </is>
       </c>
       <c r="H545" s="5" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="B548" s="5" t="inlineStr">
         <is>
-          <t>6909621</t>
+          <t>6909633</t>
         </is>
       </c>
       <c r="C548" s="5" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G548" s="5" t="inlineStr">
         <is>
-          <t>Works as a mediator in financing channels for ISIL in Central Africa, has been charged with financing a bombing that occurred in the Ugandan capital, Kampala, in 2021, attempted to coerce her three children in Uganda to send them to ISIL camps in the Democratic Republic of the Congo. Gender: Female INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2026-23487</t>
+          <t>Works as a mediator in financing channels for ISIL in Central Africa, has been charged with financing a bombing that occurred in the Ugandan capital, Kampala, in 2021, attempted to coerce her three children in Uganda to send them to ISIL camps in the Democratic Republic of the Congo. Gender: Female. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2026-23487</t>
         </is>
       </c>
       <c r="H548" s="5" t="inlineStr">
@@ -39762,13 +39762,13 @@
       </c>
       <c r="E997" s="5" t="inlineStr">
         <is>
-          <t>ISIL KHORASAN ; ISLAMIC STATE’S KHORASAN PROVINCE ; ISIS WILAYAT KHORASAN ; ISIL’S SOUTH ASIA BRANCH ; SOUTH ASIAN CHAPTER OF ISIL ; The Islamic State of Iraq and ash-Sham—Khorasan Province ; The Islamic State of Iraq and Syria—Khorasan ; Islamic State of Iraq and Levant in Khorasan Province ; Islamic State Khurasan ; ISIS-K ; ISISK ; IS-Khorasan</t>
+          <t>ISIL KHORASAN ; ISLAMIC STATE’S KHORASAN PROVINCE ; ISIS WILAYAT KHORASAN ; ISIL’S SOUTH ASIA BRANCH ; SOUTH ASIAN CHAPTER OF ISIL ; The Islamic State of Iraq and ash-Sham—Khorasan Province ; The Islamic State of Iraq and Syria—Khorasan ; Islamic State of Iraq and Levant in Khorasan Province ; Islamic State Khurasan ; ISIS-K ; ISISK ; IS-Khorasan ; ISLAMIC STATE KHORASAN PROVINCE (ISKP)</t>
         </is>
       </c>
       <c r="F997" s="5" t="inlineStr"/>
       <c r="G997" s="5" t="inlineStr">
         <is>
-          <t>Islamic State of Iraq and the Levant - Khorasan (ISIL - K) was formed on January 10, 2015 by a former Tehrik-e Taliban Pakistan (TTP) (QDe.132) commander and was established by former Taliban faction commanders who swore an oath of allegiance to the Islamic State of Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). ISIL – K has claimed responsibility for numerous attacks in both Afghanistan and Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Islamic State of Iraq and the Levant - Khorasan (ISIL - K) was formed on January 10, 2015 by a former Tehrik-e Taliban Pakistan (TTP) (QDe.132) commander and was established by former Taliban faction commanders who swore an oath of allegiance to the Islamic State of Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). ISIL – K has claimed responsibility for numerous attacks in both Afghanistan and Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2019-54448</t>
         </is>
       </c>
       <c r="H997" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15T00:43:46+00:00</t>
+          <t>2026-08-16T00:44:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-16T00:44:43+00:00</t>
+          <t>2026-08-17T00:42:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T00:42:51+00:00</t>
+          <t>2026-08-17T06:42:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:42:58+00:00</t>
+          <t>2026-08-17T06:55:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:55:25+00:00</t>
+          <t>2026-08-17T07:42:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T07:42:46+00:00</t>
+          <t>2026-08-17T08:00:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:00:09+00:00</t>
+          <t>2026-08-17T08:13:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:13:39+00:00</t>
+          <t>2026-08-17T08:28:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:28:55+00:00</t>
+          <t>2026-08-17T09:21:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:21:27+00:00</t>
+          <t>2026-08-17T09:26:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:26:53+00:00</t>
+          <t>2026-08-17T10:45:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T10:45:33+00:00</t>
+          <t>2026-08-17T12:52:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:52:00+00:00</t>
+          <t>2026-08-17T23:14:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T23:14:27+00:00</t>
+          <t>2026-08-18T05:52:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T05:52:55+00:00</t>
+          <t>2026-08-18T23:14:41+00:00</t>
         </is>
       </c>
     </row>
@@ -13761,17 +13761,17 @@
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>Hambali ; Nurjaman ; Isomuddin, Nurjaman Riduan ; Hambali Bin Ending ; Encep Nurjaman (birth name) ; Hambali Ending Hambali ; Isamuddin Riduan ; Isamudin Ridwan</t>
+          <t>Hambali ; Nurjaman ; Isomuddin, Nurjaman Riduan ; Hambali Bin Ending ; ENCEP NURJAMAN ; Hambali Ending Hambali ; Isamuddin Riduan ; Isamudin Ridwan</t>
         </is>
       </c>
       <c r="F337" s="5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Indonesia ; Malaysia</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of Jemaah Islamiyah (QDe.092). Brother of Gun Gun Rusman Gunawan (QDi.218). In custody of the United States of America, as of July 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior leader of Jemaah Islamiyah (QDe.092). Brother of Gun Gun Rusman Gunawan (QDi.218). In custody of the United States of America, as of July 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2002-40158</t>
         </is>
       </c>
       <c r="H337" s="5" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G341" s="5" t="inlineStr">
         <is>
-          <t>In detention in the Philippines as at May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A member of the Abu Sayyaf Group (QDe.001). In detention in the Philippines as at May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-22291</t>
         </is>
       </c>
       <c r="H341" s="5" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="G376" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of Abu Sayyaf Group (ASG) (QDe.001). Leader of local affiliates of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115), in the southern Philippines as of May 2017. Reportedly deceased in 2017. Physical description: eye colour: brown; hair colour: brown; height: 5 feet 6 inches – 168 cm; weight: 120 pounds – 54 kg; build: slim; complexion: light-skinned; has facial birthmarks. Wanted by the Philippines authorities for terrorist offences and by authorities of the United States of America for involvement in terrorist acts. Photos included in INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior leader of Abu Sayyaf Group (ASG) (QDe.001). Leader of local affiliates of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115), in the southern Philippines as of May 2017. Killed in Marawi City, Philippines on 15 October 2017. Physical description: eye colour: brown; hair colour: brown; height: 5 feet 6 inches – 168 cm; weight: 120 pounds – 54 kg; build: slim; complexion: light-skinned; has facial birthmarks. Wanted by the Philippines authorities for terrorist offences and by authorities of the United States of America for involvement in terrorist acts. Photos included in INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2016-35239</t>
         </is>
       </c>
       <c r="H376" s="5" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="G400" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased as of February 2022. Belonged to the leadership of the Organization of Al-Qaida in the Islamic Maghreb (listed under permanent reference number QDe.014). Located in Northern Mali as of Jun. 2008. Mother’s name is Zohra Fares. Father’s name is Mohamed INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Located in Northern Mali as of Jun. 2008. Reportedly killed on 25 February 2022 in Timbuktu, Mali. Belonged to the leadership of the Organization of Al-Qaida in the Islamic Maghreb (listed under permanent reference number QDe.014). Mother’s name is Zohra Fares. Father’s name is Mohamed. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2003-33116</t>
         </is>
       </c>
       <c r="H400" s="5" t="inlineStr">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>Abd El Illah ; Abdellillah dit Abdellah Ahmed dit Said</t>
+          <t>Abd El Illah ; Abdellillah dit Abdellah Ahmed dit Said ; ABD EL ILAH ; ABOU ABDELLAH AHMED ; SAID DIT MERRIKH</t>
         </is>
       </c>
       <c r="F403" s="5" t="inlineStr">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>Belongs to the leadership and is the finance chief of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Mother’s name is Zakia Chebira. Father’s name is Lakhdar INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Belongs to the leadership and is the finance chief of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Mother’s name is Zakia Chebira. Father’s name is Lakhdar. Reportedly died in Algeria in 2020. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2008-27768</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="G423" s="5" t="inlineStr">
         <is>
-          <t>Operative and principal bomb maker of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Believed to be hiding in Yemen as at Mar. 2011. Wanted by Saudi Arabia. Reportedly deceased. Also associated with Nasir 'abd-al-Karim 'Abdullah Al-Wahishi (deceased), Qasim Yahya Mahdi al-Rimi (QDi.282), and Anwar Nasser Abdulla Al-Aulaqi (QDi.283) (deceased) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Operative and principal bomb maker of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Reportedly deceased in 2017. Also associated with Nasir 'abd-al-Karim 'Abdullah Al-Wahishi (deceased), Qasim Yahya Mahdi al-Rimi (QDi.282), and Anwar Nasser Abdulla Al-Aulaqi (QDi.283) (deceased). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-3367</t>
         </is>
       </c>
       <c r="H423" s="5" t="inlineStr">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="G426" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Jemaah Islamiyah (QDe.092) involved in planning and funding multiple terrorist attacks in the Philippines and Indonesia. Provided training to Abu Sayyaf Group (QDe.001). Convicted for his role in the 2002 Bali bombings and sentenced to 20 years in prison in Jun. 2012. Remains in custody in Indonesia as at May 2015. Photos included in INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Jemaah Islamiyah (QDe.092) involved in planning and funding multiple terrorist attacks in the Philippines and Indonesia. Provided training to Abu Sayyaf Group (QDe.001). Convicted for his role in the 2002 Bali bombings and sentenced to 20 years in prison in Jun. 2012. Released on parole in 2022 and as at late 2025, he operated a business in Surabaya, Indonesia. Photos included in  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-3367</t>
         </is>
       </c>
       <c r="H426" s="5" t="inlineStr">
@@ -17527,7 +17527,7 @@
       </c>
       <c r="G427" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Jemaah Islamiyah (QDe.092) directly involved in obtaining funding for terrorist attacks. Sentenced in Indonesia to five years in prison on 29 Jun. 2010. Father’s name is Mohamad Iqbal Abdurrahman (QDi.086) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Senior member of Jemaah Islamiyah (QDe.092) directly involved in obtaining funding for terrorist attacks. Sentenced in Indonesia to five years in prison on 29 Jun. 2010. Father’s name is Mohamad Iqbal Abdurrahman (QDi.086). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-290638</t>
         </is>
       </c>
       <c r="H427" s="5" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="E431" s="5" t="inlineStr">
         <is>
-          <t>Abu Adam</t>
+          <t>Abu Adam ; ABU HAMZA</t>
         </is>
       </c>
       <c r="F431" s="5" t="inlineStr">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="G431" s="5" t="inlineStr">
         <is>
-          <t>Associated with Islamic Movement of Uzbekistan (QDe.010). Brother of Yassin Chouka (QDi.301) Arrest warrant issued by the investigating judge of the German Federal Court of Justice on 5 Oct. 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Associated with Islamic Movement of Uzbekistan (QDe.010). Associated with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), between October 2015 and August 2016. Brother of Yassin Chouka (QDi.301). Arrest warrant issued by the investigating judge of the German Federal Court of Justice on 5 Oct. 2010. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-290688</t>
         </is>
       </c>
       <c r="H431" s="5" t="inlineStr">
@@ -17821,7 +17821,7 @@
       </c>
       <c r="G434" s="5" t="inlineStr">
         <is>
-          <t>Acting emir of Jemmah Anshorut Tauhid (JAT) (QDe.133). Associated with Abu Bakar Ba’asyir (QDi.217), Abdul Rahim Ba’aysir (QDi.293) and Jemaah Islamiyah (QDe.092) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Acting emir of Jemmah Anshorut Tauhid (JAT) (QDe.133). Associated with Abu Bakar Ba’asyir (QDi.217), Abdul Rahim Ba’aysir (QDi.293) and Jemaah Islamiyah (QDe.092). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-312423</t>
         </is>
       </c>
       <c r="H434" s="5" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="G491" s="5" t="inlineStr">
         <is>
-          <t>French-Tunisian foreign terrorist fighter for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>French-Tunisian foreign terrorist fighter for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Reportedly killed in Raqqa, Syria on 26 November 2016. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2015-64575</t>
         </is>
       </c>
       <c r="H491" s="5" t="inlineStr">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Convicted in absentia to five years in prison in France in 2012. Wanted by French authorities as of 2015 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Convicted in absentia to five years in prison in France in 2012. Wanted by French authorities as of 2015. Sentenced to life imprisonment by a French court on 3 October 2024.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2015-64577</t>
         </is>
       </c>
       <c r="H492" s="5" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="G503" s="5" t="inlineStr">
         <is>
-          <t>A leader of the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A leader of the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Father’s name is Omar Mebrak. Mother’s name is Zohra Mebrak. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2016-13643</t>
         </is>
       </c>
       <c r="H503" s="5" t="inlineStr">
@@ -37320,7 +37320,7 @@
       <c r="F931" s="5" t="inlineStr"/>
       <c r="G931" s="5" t="inlineStr">
         <is>
-          <t>Headquarters was in Kandahar, Afghanistan as at 2001. Wafa was a component of Al-Qaida (QDe.004) in 2001 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Headquarters was in Kandahar, Afghanistan as at 2001. Wafa was a component of Al-Qaida (QDe.004) in 2001. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2008-18095</t>
         </is>
       </c>
       <c r="H931" s="5" t="inlineStr">
@@ -37464,7 +37464,7 @@
       <c r="F935" s="5" t="inlineStr"/>
       <c r="G935" s="5" t="inlineStr">
         <is>
-          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055). Banned in Pakistan INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2008-18090</t>
+          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055). Banned in Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2008-18090</t>
         </is>
       </c>
       <c r="H935" s="5" t="inlineStr">
@@ -37502,7 +37502,7 @@
       <c r="F936" s="5" t="inlineStr"/>
       <c r="G936" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Revival of Islamic Heritage Society (QDe.070). Abu Bakr al-Jaziri (QDi.058) served as finance chief of ASC INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with the Revival of Islamic Heritage Society (QDe.070). Abu Bakr al-Jaziri (QDi.058) served as finance chief of ASC. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2023-75320</t>
         </is>
       </c>
       <c r="H936" s="5" t="inlineStr">
@@ -37798,7 +37798,7 @@
       <c r="F944" s="5" t="inlineStr"/>
       <c r="G944" s="5" t="inlineStr">
         <is>
-          <t>Based primarily in Pakistan’s Punjab region and in the city of Karachi. Active in Pakistan although banned as at 2010 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Banned in Pakistan as at 2010. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-17114</t>
         </is>
       </c>
       <c r="H944" s="5" t="inlineStr">
@@ -37984,7 +37984,7 @@
       <c r="F949" s="5" t="inlineStr"/>
       <c r="G949" s="5" t="inlineStr">
         <is>
-          <t>INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>As at late 2025, it was not active and had no structures in Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-46151</t>
         </is>
       </c>
       <c r="H949" s="5" t="inlineStr">
@@ -38488,7 +38488,7 @@
       <c r="F963" s="5" t="inlineStr"/>
       <c r="G963" s="5" t="inlineStr">
         <is>
-          <t>Founded and led by Najmiddin Kamolitdinovich Jalolov (deceased) and Suhayl Fatilloevich Buranov (deceased). Associated with the Islamic Movement of Uzbekistan (QDe.010) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan border area, Central Asia, South Asia region and some European States INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Founded and led by Najmiddin Kamolitdinovich Jalolov (reportedly deceased) and Suhayl Fatilloevich Buranov (reportedly deceased). Its activities are funded and coordinated by Al-Qaida. Associated with the Islamic Movement of Uzbekistan (QDe.010) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan border area, Central Asia, South Asia region and some European States. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-16764</t>
         </is>
       </c>
       <c r="H963" s="5" t="inlineStr">
@@ -38602,7 +38602,7 @@
       <c r="F966" s="5" t="inlineStr"/>
       <c r="G966" s="5" t="inlineStr">
         <is>
-          <t>AQAP is a regional affiliate of Al-Qaida (QDe.004) and an armed group operating primarily in Arabian Peninsula. Location: Yemen. Alternative location: Saudi Arabia (2004 – 2006). Formed in Jan. 2009 when Al-Qaida in Yemen combined with Saudi Arabian Al-Qaida operatives. Leader of AQAP is Qasim Mohamed Mahdi Al-Rimi (QDi.282). Ansar al-Shari’a was formed in early 2011 by AQAP and has taken responsibility for multiple attacks in Yemen against both government and civilian targets INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>AQAP is a regional affiliate of Al-Qaida (QDe.004) and an armed group operating primarily in Arabian Peninsula. Location: Yemen. Alternative location: Saudi Arabia (2004 – 2006). Formed in Jan. 2009 when Al-Qaida in Yemen combined with Saudi Arabian Al-Qaida operatives. Leader of AQAP is Sa'ad bin Atef al-Awlaki. Ansar al-Shari’a was formed in early 2011 by AQAP and has taken responsibility for multiple attacks in Yemen against both government and civilian targets. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-17222</t>
         </is>
       </c>
       <c r="H966" s="5" t="inlineStr">
@@ -38784,7 +38784,7 @@
       <c r="F971" s="5" t="inlineStr"/>
       <c r="G971" s="5" t="inlineStr">
         <is>
-          <t>Associated with The Organization of Al-Qaida in the Islamic Maghreb (QDe.014) and Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Associated with The Organization of Al-Qaida in the Islamic Maghreb, (QDe.014), Al Mourabitoun (QDe.141), and Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-17116</t>
         </is>
       </c>
       <c r="H971" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T23:14:41+00:00</t>
+          <t>2026-08-19T23:15:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:15:18+00:00</t>
+          <t>2026-08-20T23:17:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20T23:17:44+00:00</t>
+          <t>2026-08-21T23:15:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:09+00:00</t>
+          <t>2026-08-22T23:12:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22T23:12:52+00:00</t>
+          <t>2026-08-23T23:12:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23T23:12:32+00:00</t>
+          <t>2026-08-24T23:15:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24T23:15:53+00:00</t>
+          <t>2026-08-25T23:17:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25T23:17:45+00:00</t>
+          <t>2026-08-27T04:09:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27T04:09:37+00:00</t>
+          <t>2026-08-28T06:26:27+00:00</t>
         </is>
       </c>
     </row>
@@ -25253,7 +25253,7 @@
       </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Jawzjan Province in Northern Afghanistan until 2008. Involved in drug trafficking. Height 178 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25909</t>
+          <t>Taliban member responsible for Jawzjan Province in Northern Afghanistan until 2008. Involved in drug trafficking. Height 178 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25909</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28T06:26:27+00:00</t>
+          <t>2026-08-29T03:58:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29T03:58:45+00:00</t>
+          <t>2026-08-30T00:56:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30T00:56:05+00:00</t>
+          <t>2026-08-31T01:00:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31T01:00:49+00:00</t>
+          <t>2026-09-01T01:31:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01T01:31:28+00:00</t>
+          <t>2026-09-02T00:41:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:41:23+00:00</t>
+          <t>2026-09-03T00:53:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03T00:53:02+00:00</t>
+          <t>2026-09-04T00:33:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04T00:33:11+00:00</t>
+          <t>2026-09-05T00:29:26+00:00</t>
         </is>
       </c>
     </row>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="B545" s="5" t="inlineStr">
         <is>
-          <t>6909632</t>
+          <t>6909642</t>
         </is>
       </c>
       <c r="C545" s="5" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="G545" s="5" t="inlineStr">
         <is>
-          <t>Abubakar Swalleh provides financial, material, or technological support for, or financial or other services to, or in support of, ISIL (listed as Al-Qaida in Iraq (QDe.115). He acted, since 2018, as an ISIL facilitator who provides financial and logistic support including recruitment for ISIL in East and Southern Africa. Phone number: +963936016952. Gender: Male. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2025-47413</t>
+          <t>Abubakar Swalleh provides financial, material, or technological support for, or financial or other services to, or in support of, ISIL (listed as Al-Qaida in Iraq (QDe.115)). He acted, since 2018, as an ISIL facilitator who provides financial and logistic support including recruitment for ISIL in East and Southern Africa. Phone number: +963936016952. Gender: Male. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2025-47413</t>
         </is>
       </c>
       <c r="H545" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05T00:29:26+00:00</t>
+          <t>2026-09-06T00:24:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06T00:24:05+00:00</t>
+          <t>2026-09-07T00:31:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T00:31:03+00:00</t>
+          <t>2026-09-07T07:49:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T07:49:15+00:00</t>
+          <t>2026-09-07T09:42:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:42:47+00:00</t>
+          <t>2026-09-07T11:02:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:02:33+00:00</t>
+          <t>2026-09-08T00:49:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:49:46+00:00</t>
+          <t>2026-09-09T00:53:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T00:53:29+00:00</t>
+          <t>2026-09-09T01:45:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T01:45:09+00:00</t>
+          <t>2026-09-09T02:38:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T02:38:16+00:00</t>
+          <t>2026-09-10T00:43:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10T00:43:53+00:00</t>
+          <t>2026-09-11T00:41:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11T00:41:56+00:00</t>
+          <t>2026-09-12T00:49:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12T00:49:52+00:00</t>
+          <t>2026-09-13T00:30:44+00:00</t>
         </is>
       </c>
     </row>
